--- a/assets/excel/Staff_Doctor_Details(Responses).xlsx
+++ b/assets/excel/Staff_Doctor_Details(Responses).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5250" uniqueCount="2267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5273" uniqueCount="2274">
   <si>
     <t>Name</t>
   </si>
@@ -7067,6 +7067,27 @@
   </si>
   <si>
     <t>Radio Diagnosis | USG | CT | MRI</t>
+  </si>
+  <si>
+    <t>936b5976-bb60-4111-932d-82cc98286c53 - shri devi.jpeg</t>
+  </si>
+  <si>
+    <t>Tamil English</t>
+  </si>
+  <si>
+    <t>shridevi181998@gmail.com</t>
+  </si>
+  <si>
+    <t>Kattur , trichy</t>
+  </si>
+  <si>
+    <t>MBBS,MD ( radiology)</t>
+  </si>
+  <si>
+    <t>Radio-diagnosis|</t>
+  </si>
+  <si>
+    <t>Shridevi</t>
   </si>
 </sst>
 </file>
@@ -7137,7 +7158,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -7160,12 +7181,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="22" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -7219,6 +7268,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7488,7 +7543,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AN231"/>
+  <dimension ref="A1:AT232"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -30780,7 +30835,7 @@
       <c r="AM220" s="6"/>
       <c r="AN220" s="6"/>
     </row>
-    <row r="221" spans="1:40" ht="165.75" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:40" ht="153" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <v>45994.485266203701</v>
       </c>
@@ -31208,7 +31263,7 @@
       <c r="AM224" s="5"/>
       <c r="AN224" s="5"/>
     </row>
-    <row r="225" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <v>45996.555462962962</v>
       </c>
@@ -31312,7 +31367,7 @@
       <c r="AM225" s="13"/>
       <c r="AN225" s="13"/>
     </row>
-    <row r="226" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>45999.364525462966</v>
       </c>
@@ -31416,7 +31471,7 @@
       <c r="AM226" s="6"/>
       <c r="AN226" s="6"/>
     </row>
-    <row r="227" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <v>46002.523680555554</v>
       </c>
@@ -31520,7 +31575,7 @@
       <c r="AM227" s="13"/>
       <c r="AN227" s="13"/>
     </row>
-    <row r="228" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>46010.499398148146</v>
       </c>
@@ -31624,7 +31679,7 @@
       <c r="AM228" s="6"/>
       <c r="AN228" s="6"/>
     </row>
-    <row r="229" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <v>46015.435925925929</v>
       </c>
@@ -31732,7 +31787,7 @@
       <c r="AM229" s="13"/>
       <c r="AN229" s="13"/>
     </row>
-    <row r="230" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>46017.628229166665</v>
       </c>
@@ -31836,7 +31891,7 @@
       <c r="AM230" s="6"/>
       <c r="AN230" s="6"/>
     </row>
-    <row r="231" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:46" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A231" s="8">
         <v>46028.591863425929</v>
       </c>
@@ -31939,6 +31994,118 @@
       <c r="AL231" s="13"/>
       <c r="AM231" s="13"/>
       <c r="AN231" s="13"/>
+    </row>
+    <row r="232" spans="1:46" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="1">
+        <v>46032.41710648148</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>2273</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D232" s="3">
+        <v>28</v>
+      </c>
+      <c r="E232" s="4">
+        <v>46099</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H232" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I232" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J232" s="5" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K232" s="2" t="s">
+        <v>2268</v>
+      </c>
+      <c r="L232" s="3">
+        <v>8098893437</v>
+      </c>
+      <c r="M232" s="2" t="s">
+        <v>2269</v>
+      </c>
+      <c r="N232" s="2" t="s">
+        <v>2270</v>
+      </c>
+      <c r="O232" s="2" t="s">
+        <v>2203</v>
+      </c>
+      <c r="P232" s="3">
+        <v>620019</v>
+      </c>
+      <c r="Q232" s="2" t="s">
+        <v>2203</v>
+      </c>
+      <c r="R232" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="S232" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T232" s="3">
+        <v>8098893437</v>
+      </c>
+      <c r="U232" s="2" t="s">
+        <v>2271</v>
+      </c>
+      <c r="V232" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W232" s="4">
+        <v>45733</v>
+      </c>
+      <c r="X232" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y232" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z232" s="2" t="s">
+        <v>1969</v>
+      </c>
+      <c r="AA232" s="2" t="s">
+        <v>2272</v>
+      </c>
+      <c r="AB232" s="6"/>
+      <c r="AC232" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD232" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE232" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF232" s="7">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AG232" s="7">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="AH232" s="6"/>
+      <c r="AI232" s="6"/>
+      <c r="AJ232" s="6"/>
+      <c r="AK232" s="6"/>
+      <c r="AL232" s="6"/>
+      <c r="AM232" s="6"/>
+      <c r="AN232" s="6"/>
+      <c r="AO232" s="20"/>
+      <c r="AP232" s="19"/>
+      <c r="AQ232" s="19"/>
+      <c r="AR232" s="19"/>
+      <c r="AS232" s="19"/>
+      <c r="AT232" s="19"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -32243,8 +32410,9 @@
     <hyperlink ref="AB229" r:id="rId299" display="http://www.tctmd.com/"/>
     <hyperlink ref="J230" r:id="rId300"/>
     <hyperlink ref="J231" r:id="rId301"/>
+    <hyperlink ref="J232" r:id="rId302" display="https://drive.google.com/open?id=1DdV0m0St0MUfekgVF6f_7SnKmkRAsjJZ"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId302"/>
+  <pageSetup orientation="portrait" r:id="rId303"/>
 </worksheet>
 </file>
--- a/assets/excel/Staff_Doctor_Details(Responses).xlsx
+++ b/assets/excel/Staff_Doctor_Details(Responses).xlsx
@@ -29971,7 +29971,7 @@
       <c r="AM212" s="6"/>
       <c r="AN212" s="6"/>
     </row>
-    <row r="213" spans="1:40" ht="127.5" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:40" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <v>45991.931631944448</v>
       </c>
@@ -32072,7 +32072,7 @@
         <v>11</v>
       </c>
       <c r="Z232" s="2" t="s">
-        <v>1969</v>
+        <v>2183</v>
       </c>
       <c r="AA232" s="2" t="s">
         <v>2272</v>

--- a/assets/excel/Staff_Doctor_Details(Responses).xlsx
+++ b/assets/excel/Staff_Doctor_Details(Responses).xlsx
@@ -7545,7 +7545,7 @@
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" customWidth="1"/>
     <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="54" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>

--- a/assets/excel/Staff_Doctor_Details(Responses).xlsx
+++ b/assets/excel/Staff_Doctor_Details(Responses).xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\NewSRMTrichy\assets\excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24240" windowHeight="12315"/>
   </bookViews>
@@ -7091,7 +7096,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -7541,7 +7546,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AT232"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
@@ -7578,7 +7583,7 @@
     <col min="40" max="40" width="58" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:40" ht="15.75" customHeight="1">
       <c r="A1" s="15">
         <v>45956.692314814813</v>
       </c>
@@ -7700,7 +7705,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="2" spans="1:40" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" ht="409.5">
       <c r="A2" s="1">
         <v>45957.692314814813</v>
       </c>
@@ -7806,7 +7811,7 @@
       <c r="AM2" s="6"/>
       <c r="AN2" s="6"/>
     </row>
-    <row r="3" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" ht="15.75" customHeight="1">
       <c r="A3" s="8">
         <v>45957.836099537039</v>
       </c>
@@ -7912,7 +7917,7 @@
       <c r="AM3" s="13"/>
       <c r="AN3" s="13"/>
     </row>
-    <row r="4" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" ht="15.75" customHeight="1">
       <c r="A4" s="1">
         <v>45957.892523148148</v>
       </c>
@@ -8022,7 +8027,7 @@
       </c>
       <c r="AN4" s="6"/>
     </row>
-    <row r="5" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" ht="15.75" customHeight="1">
       <c r="A5" s="8">
         <v>45959.447812500002</v>
       </c>
@@ -8126,7 +8131,7 @@
       <c r="AM5" s="13"/>
       <c r="AN5" s="13"/>
     </row>
-    <row r="6" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" ht="15.75" customHeight="1">
       <c r="A6" s="1">
         <v>45959.619328703702</v>
       </c>
@@ -8232,7 +8237,7 @@
       <c r="AM6" s="6"/>
       <c r="AN6" s="6"/>
     </row>
-    <row r="7" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" ht="15.75" customHeight="1">
       <c r="A7" s="8">
         <v>45959.628240740742</v>
       </c>
@@ -8342,7 +8347,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" ht="15.75" customHeight="1">
       <c r="A8" s="1">
         <v>45962.704074074078</v>
       </c>
@@ -8448,7 +8453,7 @@
       <c r="AM8" s="6"/>
       <c r="AN8" s="6"/>
     </row>
-    <row r="9" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" ht="15.75" customHeight="1">
       <c r="A9" s="8">
         <v>45962.830706018518</v>
       </c>
@@ -8558,7 +8563,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" ht="15.75" customHeight="1">
       <c r="A10" s="1">
         <v>45962.861979166664</v>
       </c>
@@ -8664,7 +8669,7 @@
       <c r="AM10" s="6"/>
       <c r="AN10" s="6"/>
     </row>
-    <row r="11" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" ht="15.75" customHeight="1">
       <c r="A11" s="8">
         <v>45963.404826388891</v>
       </c>
@@ -8768,7 +8773,7 @@
       <c r="AM11" s="13"/>
       <c r="AN11" s="13"/>
     </row>
-    <row r="12" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" ht="15.75" customHeight="1">
       <c r="A12" s="1">
         <v>45963.419293981482</v>
       </c>
@@ -8874,7 +8879,7 @@
       <c r="AM12" s="6"/>
       <c r="AN12" s="6"/>
     </row>
-    <row r="13" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" ht="15.75" customHeight="1">
       <c r="A13" s="8">
         <v>45964.385462962964</v>
       </c>
@@ -8978,7 +8983,7 @@
       <c r="AM13" s="13"/>
       <c r="AN13" s="13"/>
     </row>
-    <row r="14" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" ht="15.75" customHeight="1">
       <c r="A14" s="1">
         <v>45964.427928240744</v>
       </c>
@@ -9082,7 +9087,7 @@
       <c r="AM14" s="6"/>
       <c r="AN14" s="6"/>
     </row>
-    <row r="15" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" ht="15.75" customHeight="1">
       <c r="A15" s="8">
         <v>45964.533125000002</v>
       </c>
@@ -9188,7 +9193,7 @@
       <c r="AM15" s="13"/>
       <c r="AN15" s="13"/>
     </row>
-    <row r="16" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" ht="15.75" customHeight="1">
       <c r="A16" s="1">
         <v>45964.573194444441</v>
       </c>
@@ -9292,7 +9297,7 @@
       <c r="AM16" s="6"/>
       <c r="AN16" s="6"/>
     </row>
-    <row r="17" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" ht="15.75" customHeight="1">
       <c r="A17" s="8">
         <v>45964.575567129628</v>
       </c>
@@ -9396,7 +9401,7 @@
       <c r="AM17" s="13"/>
       <c r="AN17" s="13"/>
     </row>
-    <row r="18" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" ht="15.75" customHeight="1">
       <c r="A18" s="1">
         <v>45964.577222222222</v>
       </c>
@@ -9502,7 +9507,7 @@
       <c r="AM18" s="6"/>
       <c r="AN18" s="6"/>
     </row>
-    <row r="19" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" ht="15.75" customHeight="1">
       <c r="A19" s="8">
         <v>45964.584108796298</v>
       </c>
@@ -9606,7 +9611,7 @@
       <c r="AM19" s="13"/>
       <c r="AN19" s="13"/>
     </row>
-    <row r="20" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" ht="15.75" customHeight="1">
       <c r="A20" s="1">
         <v>45964.591550925928</v>
       </c>
@@ -9710,7 +9715,7 @@
       <c r="AM20" s="6"/>
       <c r="AN20" s="6"/>
     </row>
-    <row r="21" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:40" ht="15.75" customHeight="1">
       <c r="A21" s="8">
         <v>45964.592106481483</v>
       </c>
@@ -9814,7 +9819,7 @@
       <c r="AM21" s="13"/>
       <c r="AN21" s="13"/>
     </row>
-    <row r="22" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:40" ht="15.75" customHeight="1">
       <c r="A22" s="1">
         <v>45964.598437499997</v>
       </c>
@@ -9920,7 +9925,7 @@
       <c r="AM22" s="6"/>
       <c r="AN22" s="6"/>
     </row>
-    <row r="23" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" ht="15.75" customHeight="1">
       <c r="A23" s="8">
         <v>45964.603194444448</v>
       </c>
@@ -10026,7 +10031,7 @@
       <c r="AM23" s="13"/>
       <c r="AN23" s="13"/>
     </row>
-    <row r="24" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:40" ht="15.75" customHeight="1">
       <c r="A24" s="1">
         <v>45964.606122685182</v>
       </c>
@@ -10132,7 +10137,7 @@
       <c r="AM24" s="6"/>
       <c r="AN24" s="6"/>
     </row>
-    <row r="25" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:40" ht="15.75" customHeight="1">
       <c r="A25" s="8">
         <v>45964.608634259261</v>
       </c>
@@ -10236,7 +10241,7 @@
       <c r="AM25" s="13"/>
       <c r="AN25" s="13"/>
     </row>
-    <row r="26" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:40" ht="15.75" customHeight="1">
       <c r="A26" s="1">
         <v>45964.610312500001</v>
       </c>
@@ -10342,7 +10347,7 @@
       <c r="AM26" s="6"/>
       <c r="AN26" s="6"/>
     </row>
-    <row r="27" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:40" ht="15.75" customHeight="1">
       <c r="A27" s="8">
         <v>45964.613171296296</v>
       </c>
@@ -10450,7 +10455,7 @@
       <c r="AM27" s="13"/>
       <c r="AN27" s="13"/>
     </row>
-    <row r="28" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:40" ht="15.75" customHeight="1">
       <c r="A28" s="1">
         <v>45964.617430555554</v>
       </c>
@@ -10554,7 +10559,7 @@
       <c r="AM28" s="6"/>
       <c r="AN28" s="6"/>
     </row>
-    <row r="29" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:40" ht="15.75" customHeight="1">
       <c r="A29" s="8">
         <v>45964.618437500001</v>
       </c>
@@ -10658,7 +10663,7 @@
       <c r="AM29" s="13"/>
       <c r="AN29" s="13"/>
     </row>
-    <row r="30" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:40" ht="15.75" customHeight="1">
       <c r="A30" s="1">
         <v>45964.621215277781</v>
       </c>
@@ -10768,7 +10773,7 @@
       <c r="AM30" s="6"/>
       <c r="AN30" s="6"/>
     </row>
-    <row r="31" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:40" ht="15.75" customHeight="1">
       <c r="A31" s="8">
         <v>45964.63071759259</v>
       </c>
@@ -10872,7 +10877,7 @@
       <c r="AM31" s="13"/>
       <c r="AN31" s="13"/>
     </row>
-    <row r="32" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:40" ht="15.75" customHeight="1">
       <c r="A32" s="1">
         <v>45964.632025462961</v>
       </c>
@@ -10976,7 +10981,7 @@
       <c r="AM32" s="6"/>
       <c r="AN32" s="6"/>
     </row>
-    <row r="33" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:40" ht="15.75" customHeight="1">
       <c r="A33" s="8">
         <v>45964.660057870373</v>
       </c>
@@ -11080,7 +11085,7 @@
       <c r="AM33" s="13"/>
       <c r="AN33" s="13"/>
     </row>
-    <row r="34" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:40" ht="15.75" customHeight="1">
       <c r="A34" s="1">
         <v>45964.683622685188</v>
       </c>
@@ -11184,7 +11189,7 @@
       <c r="AM34" s="6"/>
       <c r="AN34" s="6"/>
     </row>
-    <row r="35" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:40" ht="15.75" customHeight="1">
       <c r="A35" s="8">
         <v>45964.694976851853</v>
       </c>
@@ -11298,7 +11303,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="36" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:40" ht="15.75" customHeight="1">
       <c r="A36" s="1">
         <v>45964.718078703707</v>
       </c>
@@ -11402,7 +11407,7 @@
       <c r="AM36" s="6"/>
       <c r="AN36" s="6"/>
     </row>
-    <row r="37" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:40" ht="15.75" customHeight="1">
       <c r="A37" s="8">
         <v>45964.720648148148</v>
       </c>
@@ -11510,7 +11515,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="38" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:40" ht="15.75" customHeight="1">
       <c r="A38" s="1">
         <v>45964.749942129631</v>
       </c>
@@ -11614,7 +11619,7 @@
       <c r="AM38" s="6"/>
       <c r="AN38" s="6"/>
     </row>
-    <row r="39" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:40" ht="15.75" customHeight="1">
       <c r="A39" s="8">
         <v>45964.753599537034</v>
       </c>
@@ -11720,7 +11725,7 @@
       <c r="AM39" s="13"/>
       <c r="AN39" s="13"/>
     </row>
-    <row r="40" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:40" ht="15.75" customHeight="1">
       <c r="A40" s="1">
         <v>45964.756678240738</v>
       </c>
@@ -11824,7 +11829,7 @@
       <c r="AM40" s="6"/>
       <c r="AN40" s="6"/>
     </row>
-    <row r="41" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:40" ht="15.75" customHeight="1">
       <c r="A41" s="8">
         <v>45964.769467592596</v>
       </c>
@@ -11928,7 +11933,7 @@
       <c r="AM41" s="13"/>
       <c r="AN41" s="13"/>
     </row>
-    <row r="42" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:40" ht="15.75" customHeight="1">
       <c r="A42" s="1">
         <v>45964.770439814813</v>
       </c>
@@ -12034,7 +12039,7 @@
       <c r="AM42" s="6"/>
       <c r="AN42" s="6"/>
     </row>
-    <row r="43" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:40" ht="15.75" customHeight="1">
       <c r="A43" s="8">
         <v>45964.962500000001</v>
       </c>
@@ -12138,7 +12143,7 @@
       <c r="AM43" s="13"/>
       <c r="AN43" s="13"/>
     </row>
-    <row r="44" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:40" ht="15.75" customHeight="1">
       <c r="A44" s="1">
         <v>45965.415185185186</v>
       </c>
@@ -12244,7 +12249,7 @@
       <c r="AM44" s="6"/>
       <c r="AN44" s="6"/>
     </row>
-    <row r="45" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:40" ht="15.75" customHeight="1">
       <c r="A45" s="8">
         <v>45965.417916666665</v>
       </c>
@@ -12352,7 +12357,7 @@
       <c r="AM45" s="13"/>
       <c r="AN45" s="13"/>
     </row>
-    <row r="46" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:40" ht="15.75" customHeight="1">
       <c r="A46" s="1">
         <v>45965.447060185186</v>
       </c>
@@ -12458,7 +12463,7 @@
       <c r="AM46" s="6"/>
       <c r="AN46" s="6"/>
     </row>
-    <row r="47" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:40" ht="15.75" customHeight="1">
       <c r="A47" s="8">
         <v>45965.450416666667</v>
       </c>
@@ -12566,7 +12571,7 @@
       <c r="AM47" s="13"/>
       <c r="AN47" s="13"/>
     </row>
-    <row r="48" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:40" ht="15.75" customHeight="1">
       <c r="A48" s="1">
         <v>45965.512662037036</v>
       </c>
@@ -12670,7 +12675,7 @@
       <c r="AM48" s="6"/>
       <c r="AN48" s="6"/>
     </row>
-    <row r="49" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:40" ht="15.75" customHeight="1">
       <c r="A49" s="8">
         <v>45965.874374999999</v>
       </c>
@@ -12776,7 +12781,7 @@
       <c r="AM49" s="13"/>
       <c r="AN49" s="13"/>
     </row>
-    <row r="50" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:40" ht="15.75" customHeight="1">
       <c r="A50" s="1">
         <v>45966.385312500002</v>
       </c>
@@ -12880,7 +12885,7 @@
       <c r="AM50" s="6"/>
       <c r="AN50" s="6"/>
     </row>
-    <row r="51" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:40" ht="15.75" customHeight="1">
       <c r="A51" s="8">
         <v>45966.389178240737</v>
       </c>
@@ -12984,7 +12989,7 @@
       <c r="AM51" s="13"/>
       <c r="AN51" s="13"/>
     </row>
-    <row r="52" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:40" ht="15.75" customHeight="1">
       <c r="A52" s="1">
         <v>45966.392407407409</v>
       </c>
@@ -13088,7 +13093,7 @@
       <c r="AM52" s="6"/>
       <c r="AN52" s="6"/>
     </row>
-    <row r="53" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:40" ht="15.75" customHeight="1">
       <c r="A53" s="8">
         <v>45966.418391203704</v>
       </c>
@@ -13192,7 +13197,7 @@
       <c r="AM53" s="13"/>
       <c r="AN53" s="13"/>
     </row>
-    <row r="54" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:40" ht="15.75" customHeight="1">
       <c r="A54" s="1">
         <v>45966.540497685186</v>
       </c>
@@ -13296,7 +13301,7 @@
       <c r="AM54" s="6"/>
       <c r="AN54" s="6"/>
     </row>
-    <row r="55" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:40" ht="15.75" customHeight="1">
       <c r="A55" s="8">
         <v>45966.62300925926</v>
       </c>
@@ -13406,7 +13411,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="56" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:40" ht="15.75" customHeight="1">
       <c r="A56" s="1">
         <v>45966.626886574071</v>
       </c>
@@ -13510,7 +13515,7 @@
       <c r="AM56" s="6"/>
       <c r="AN56" s="6"/>
     </row>
-    <row r="57" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:40" ht="15.75" customHeight="1">
       <c r="A57" s="8">
         <v>45966.640393518515</v>
       </c>
@@ -13618,7 +13623,7 @@
       <c r="AM57" s="13"/>
       <c r="AN57" s="13"/>
     </row>
-    <row r="58" spans="1:40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:40" ht="24" customHeight="1">
       <c r="A58" s="1">
         <v>45967.46361111111</v>
       </c>
@@ -13728,7 +13733,7 @@
       </c>
       <c r="AN58" s="6"/>
     </row>
-    <row r="59" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:40" ht="15.75" customHeight="1">
       <c r="A59" s="8">
         <v>45967.559479166666</v>
       </c>
@@ -13834,7 +13839,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="60" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:40" ht="15.75" customHeight="1">
       <c r="A60" s="1">
         <v>45967.610891203702</v>
       </c>
@@ -13940,7 +13945,7 @@
       <c r="AM60" s="6"/>
       <c r="AN60" s="6"/>
     </row>
-    <row r="61" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:40" ht="15.75" customHeight="1">
       <c r="A61" s="8">
         <v>45967.617152777777</v>
       </c>
@@ -14044,7 +14049,7 @@
       <c r="AM61" s="13"/>
       <c r="AN61" s="13"/>
     </row>
-    <row r="62" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:40" ht="15.75" customHeight="1">
       <c r="A62" s="1">
         <v>45967.620428240742</v>
       </c>
@@ -14148,7 +14153,7 @@
       <c r="AM62" s="6"/>
       <c r="AN62" s="6"/>
     </row>
-    <row r="63" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:40" ht="15.75" customHeight="1">
       <c r="A63" s="8">
         <v>45967.624560185184</v>
       </c>
@@ -14254,7 +14259,7 @@
       <c r="AM63" s="13"/>
       <c r="AN63" s="13"/>
     </row>
-    <row r="64" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:40" ht="15.75" customHeight="1">
       <c r="A64" s="1">
         <v>45967.633842592593</v>
       </c>
@@ -14360,7 +14365,7 @@
       <c r="AM64" s="6"/>
       <c r="AN64" s="6"/>
     </row>
-    <row r="65" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:40" ht="15.75" customHeight="1">
       <c r="A65" s="8">
         <v>45967.635555555556</v>
       </c>
@@ -14466,7 +14471,7 @@
       <c r="AM65" s="13"/>
       <c r="AN65" s="13"/>
     </row>
-    <row r="66" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:40" ht="15.75" customHeight="1">
       <c r="A66" s="1">
         <v>45967.642025462963</v>
       </c>
@@ -14572,7 +14577,7 @@
       <c r="AM66" s="6"/>
       <c r="AN66" s="6"/>
     </row>
-    <row r="67" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:40" ht="15.75" customHeight="1">
       <c r="A67" s="8">
         <v>45967.643321759257</v>
       </c>
@@ -14676,7 +14681,7 @@
       <c r="AM67" s="13"/>
       <c r="AN67" s="13"/>
     </row>
-    <row r="68" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:40" ht="15.75" customHeight="1">
       <c r="A68" s="1">
         <v>45967.645590277774</v>
       </c>
@@ -14780,7 +14785,7 @@
       <c r="AM68" s="6"/>
       <c r="AN68" s="6"/>
     </row>
-    <row r="69" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:40" ht="15.75" customHeight="1">
       <c r="A69" s="8">
         <v>45967.695185185185</v>
       </c>
@@ -14884,7 +14889,7 @@
       <c r="AM69" s="13"/>
       <c r="AN69" s="13"/>
     </row>
-    <row r="70" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:40" ht="15.75" customHeight="1">
       <c r="A70" s="1">
         <v>45968.390150462961</v>
       </c>
@@ -14988,7 +14993,7 @@
       <c r="AM70" s="6"/>
       <c r="AN70" s="6"/>
     </row>
-    <row r="71" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:40" ht="15.75" customHeight="1">
       <c r="A71" s="8">
         <v>45968.459675925929</v>
       </c>
@@ -15094,7 +15099,7 @@
       <c r="AM71" s="13"/>
       <c r="AN71" s="13"/>
     </row>
-    <row r="72" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:40" ht="15.75" customHeight="1">
       <c r="A72" s="1">
         <v>45968.466990740744</v>
       </c>
@@ -15198,7 +15203,7 @@
       <c r="AM72" s="6"/>
       <c r="AN72" s="6"/>
     </row>
-    <row r="73" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:40" ht="15.75" customHeight="1">
       <c r="A73" s="8">
         <v>45968.480254629627</v>
       </c>
@@ -15304,7 +15309,7 @@
       <c r="AM73" s="13"/>
       <c r="AN73" s="13"/>
     </row>
-    <row r="74" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:40" ht="15.75" customHeight="1">
       <c r="A74" s="1">
         <v>45968.601412037038</v>
       </c>
@@ -15410,7 +15415,7 @@
       <c r="AM74" s="6"/>
       <c r="AN74" s="6"/>
     </row>
-    <row r="75" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:40" ht="15.75" customHeight="1">
       <c r="A75" s="8">
         <v>45968.787569444445</v>
       </c>
@@ -15514,7 +15519,7 @@
       <c r="AM75" s="13"/>
       <c r="AN75" s="13"/>
     </row>
-    <row r="76" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:40" ht="15.75" customHeight="1">
       <c r="A76" s="1">
         <v>45969.473912037036</v>
       </c>
@@ -15620,7 +15625,7 @@
       <c r="AM76" s="6"/>
       <c r="AN76" s="6"/>
     </row>
-    <row r="77" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:40" ht="15.75" customHeight="1">
       <c r="A77" s="8">
         <v>45971.35670138889</v>
       </c>
@@ -15724,7 +15729,7 @@
       <c r="AM77" s="13"/>
       <c r="AN77" s="13"/>
     </row>
-    <row r="78" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:40" ht="15.75" customHeight="1">
       <c r="A78" s="1">
         <v>45972.659039351849</v>
       </c>
@@ -15828,7 +15833,7 @@
       <c r="AM78" s="6"/>
       <c r="AN78" s="6"/>
     </row>
-    <row r="79" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:40" ht="15.75" customHeight="1">
       <c r="A79" s="8">
         <v>45973.38857638889</v>
       </c>
@@ -15932,7 +15937,7 @@
       <c r="AM79" s="13"/>
       <c r="AN79" s="13"/>
     </row>
-    <row r="80" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:40" ht="15.75" customHeight="1">
       <c r="A80" s="1">
         <v>45973.42355324074</v>
       </c>
@@ -16038,7 +16043,7 @@
       <c r="AM80" s="6"/>
       <c r="AN80" s="6"/>
     </row>
-    <row r="81" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:40" ht="15.75" customHeight="1">
       <c r="A81" s="8">
         <v>45973.453125</v>
       </c>
@@ -16144,7 +16149,7 @@
       <c r="AM81" s="13"/>
       <c r="AN81" s="13"/>
     </row>
-    <row r="82" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:40" ht="15.75" customHeight="1">
       <c r="A82" s="1">
         <v>45973.487337962964</v>
       </c>
@@ -16250,7 +16255,7 @@
       <c r="AM82" s="6"/>
       <c r="AN82" s="6"/>
     </row>
-    <row r="83" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:40" ht="15.75" customHeight="1">
       <c r="A83" s="8">
         <v>45973.493680555555</v>
       </c>
@@ -16354,7 +16359,7 @@
       <c r="AM83" s="13"/>
       <c r="AN83" s="13"/>
     </row>
-    <row r="84" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:40" ht="15.75" customHeight="1">
       <c r="A84" s="1">
         <v>45973.499756944446</v>
       </c>
@@ -16456,7 +16461,7 @@
       <c r="AM84" s="6"/>
       <c r="AN84" s="6"/>
     </row>
-    <row r="85" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:40" ht="15.75" customHeight="1">
       <c r="A85" s="8">
         <v>45973.53</v>
       </c>
@@ -16560,7 +16565,7 @@
       <c r="AM85" s="13"/>
       <c r="AN85" s="13"/>
     </row>
-    <row r="86" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:40" ht="15.75" customHeight="1">
       <c r="A86" s="1">
         <v>45973.579444444447</v>
       </c>
@@ -16664,7 +16669,7 @@
       <c r="AM86" s="6"/>
       <c r="AN86" s="6"/>
     </row>
-    <row r="87" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:40" ht="15.75" customHeight="1">
       <c r="A87" s="8">
         <v>45973.586597222224</v>
       </c>
@@ -16770,7 +16775,7 @@
       <c r="AM87" s="13"/>
       <c r="AN87" s="13"/>
     </row>
-    <row r="88" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:40" ht="15.75" customHeight="1">
       <c r="A88" s="1">
         <v>45973.606805555559</v>
       </c>
@@ -16874,7 +16879,7 @@
       <c r="AM88" s="6"/>
       <c r="AN88" s="6"/>
     </row>
-    <row r="89" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:40" ht="15.75" customHeight="1">
       <c r="A89" s="8">
         <v>45973.627118055556</v>
       </c>
@@ -16978,7 +16983,7 @@
       <c r="AM89" s="13"/>
       <c r="AN89" s="13"/>
     </row>
-    <row r="90" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:40" ht="15.75" customHeight="1">
       <c r="A90" s="1">
         <v>45973.630613425928</v>
       </c>
@@ -17082,7 +17087,7 @@
       <c r="AM90" s="6"/>
       <c r="AN90" s="6"/>
     </row>
-    <row r="91" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:40" ht="15.75" customHeight="1">
       <c r="A91" s="8">
         <v>45973.637025462966</v>
       </c>
@@ -17186,7 +17191,7 @@
       <c r="AM91" s="13"/>
       <c r="AN91" s="13"/>
     </row>
-    <row r="92" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:40" ht="15.75" customHeight="1">
       <c r="A92" s="1">
         <v>45973.652430555558</v>
       </c>
@@ -17292,7 +17297,7 @@
       <c r="AM92" s="6"/>
       <c r="AN92" s="6"/>
     </row>
-    <row r="93" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:40" ht="15.75" customHeight="1">
       <c r="A93" s="8">
         <v>45973.657650462963</v>
       </c>
@@ -17398,7 +17403,7 @@
       <c r="AM93" s="13"/>
       <c r="AN93" s="13"/>
     </row>
-    <row r="94" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:40" ht="15.75" customHeight="1">
       <c r="A94" s="1">
         <v>45973.66611111111</v>
       </c>
@@ -17506,7 +17511,7 @@
       </c>
       <c r="AN94" s="6"/>
     </row>
-    <row r="95" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:40" ht="15.75" customHeight="1">
       <c r="A95" s="8">
         <v>45973.691122685188</v>
       </c>
@@ -17612,7 +17617,7 @@
       </c>
       <c r="AN95" s="13"/>
     </row>
-    <row r="96" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:40" ht="15.75" customHeight="1">
       <c r="A96" s="1">
         <v>45973.703530092593</v>
       </c>
@@ -17716,7 +17721,7 @@
       <c r="AM96" s="6"/>
       <c r="AN96" s="6"/>
     </row>
-    <row r="97" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:40" ht="15.75" customHeight="1">
       <c r="A97" s="8">
         <v>45974.3046875</v>
       </c>
@@ -17820,7 +17825,7 @@
       <c r="AM97" s="13"/>
       <c r="AN97" s="13"/>
     </row>
-    <row r="98" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:40" ht="15.75" customHeight="1">
       <c r="A98" s="1">
         <v>45974.332615740743</v>
       </c>
@@ -17924,7 +17929,7 @@
       <c r="AM98" s="6"/>
       <c r="AN98" s="6"/>
     </row>
-    <row r="99" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:40" ht="15.75" customHeight="1">
       <c r="A99" s="8">
         <v>45974.383553240739</v>
       </c>
@@ -18030,7 +18035,7 @@
       <c r="AM99" s="13"/>
       <c r="AN99" s="13"/>
     </row>
-    <row r="100" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:40" ht="15.75" customHeight="1">
       <c r="A100" s="1">
         <v>45974.393182870372</v>
       </c>
@@ -18136,7 +18141,7 @@
       <c r="AM100" s="6"/>
       <c r="AN100" s="6"/>
     </row>
-    <row r="101" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:40" ht="15.75" customHeight="1">
       <c r="A101" s="8">
         <v>45974.406481481485</v>
       </c>
@@ -18240,7 +18245,7 @@
       <c r="AM101" s="13"/>
       <c r="AN101" s="13"/>
     </row>
-    <row r="102" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:40" ht="15.75" customHeight="1">
       <c r="A102" s="1">
         <v>45974.409050925926</v>
       </c>
@@ -18354,7 +18359,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="103" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:40" ht="15.75" customHeight="1">
       <c r="A103" s="8">
         <v>45974.417291666665</v>
       </c>
@@ -18458,7 +18463,7 @@
       <c r="AM103" s="13"/>
       <c r="AN103" s="13"/>
     </row>
-    <row r="104" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:40" ht="15.75" customHeight="1">
       <c r="A104" s="1">
         <v>45974.417326388888</v>
       </c>
@@ -18564,7 +18569,7 @@
       <c r="AM104" s="6"/>
       <c r="AN104" s="6"/>
     </row>
-    <row r="105" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:40" ht="15.75" customHeight="1">
       <c r="A105" s="8">
         <v>45974.423506944448</v>
       </c>
@@ -18672,7 +18677,7 @@
       </c>
       <c r="AN105" s="13"/>
     </row>
-    <row r="106" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:40" ht="15.75" customHeight="1">
       <c r="A106" s="1">
         <v>45974.42428240741</v>
       </c>
@@ -18776,7 +18781,7 @@
       <c r="AM106" s="6"/>
       <c r="AN106" s="6"/>
     </row>
-    <row r="107" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:40" ht="15.75" customHeight="1">
       <c r="A107" s="8">
         <v>45974.435567129629</v>
       </c>
@@ -18880,7 +18885,7 @@
       <c r="AM107" s="13"/>
       <c r="AN107" s="13"/>
     </row>
-    <row r="108" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:40" ht="15.75" customHeight="1">
       <c r="A108" s="1">
         <v>45974.464259259257</v>
       </c>
@@ -18986,7 +18991,7 @@
       <c r="AM108" s="6"/>
       <c r="AN108" s="6"/>
     </row>
-    <row r="109" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:40" ht="15.75" customHeight="1">
       <c r="A109" s="8">
         <v>45974.506307870368</v>
       </c>
@@ -19090,7 +19095,7 @@
       <c r="AM109" s="13"/>
       <c r="AN109" s="13"/>
     </row>
-    <row r="110" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:40" ht="15.75" customHeight="1">
       <c r="A110" s="1">
         <v>45974.516064814816</v>
       </c>
@@ -19194,7 +19199,7 @@
       <c r="AM110" s="6"/>
       <c r="AN110" s="6"/>
     </row>
-    <row r="111" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:40" ht="15.75" customHeight="1">
       <c r="A111" s="8">
         <v>45974.594675925924</v>
       </c>
@@ -19300,7 +19305,7 @@
       </c>
       <c r="AN111" s="13"/>
     </row>
-    <row r="112" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:40" ht="15.75" customHeight="1">
       <c r="A112" s="1">
         <v>45974.605011574073</v>
       </c>
@@ -19406,7 +19411,7 @@
       <c r="AM112" s="6"/>
       <c r="AN112" s="6"/>
     </row>
-    <row r="113" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:40" ht="15.75" customHeight="1">
       <c r="A113" s="8">
         <v>45974.619108796294</v>
       </c>
@@ -19510,7 +19515,7 @@
       <c r="AM113" s="13"/>
       <c r="AN113" s="13"/>
     </row>
-    <row r="114" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:40" ht="15.75" customHeight="1">
       <c r="A114" s="1">
         <v>45974.62736111111</v>
       </c>
@@ -19618,7 +19623,7 @@
       <c r="AM114" s="6"/>
       <c r="AN114" s="6"/>
     </row>
-    <row r="115" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:40" ht="15.75" customHeight="1">
       <c r="A115" s="8">
         <v>45974.62972222222</v>
       </c>
@@ -19726,7 +19731,7 @@
       <c r="AM115" s="13"/>
       <c r="AN115" s="13"/>
     </row>
-    <row r="116" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:40" ht="15.75" customHeight="1">
       <c r="A116" s="1">
         <v>45974.634756944448</v>
       </c>
@@ -19832,7 +19837,7 @@
       <c r="AM116" s="6"/>
       <c r="AN116" s="6"/>
     </row>
-    <row r="117" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:40" ht="15.75" customHeight="1">
       <c r="A117" s="8">
         <v>45974.639641203707</v>
       </c>
@@ -19938,7 +19943,7 @@
       <c r="AM117" s="13"/>
       <c r="AN117" s="13"/>
     </row>
-    <row r="118" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:40" ht="15.75" customHeight="1">
       <c r="A118" s="1">
         <v>45975.367986111109</v>
       </c>
@@ -20044,7 +20049,7 @@
       <c r="AM118" s="6"/>
       <c r="AN118" s="6"/>
     </row>
-    <row r="119" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:40" ht="15.75" customHeight="1">
       <c r="A119" s="8">
         <v>45975.375219907408</v>
       </c>
@@ -20150,7 +20155,7 @@
       <c r="AM119" s="13"/>
       <c r="AN119" s="13"/>
     </row>
-    <row r="120" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:40" ht="15.75" customHeight="1">
       <c r="A120" s="1">
         <v>45975.401122685187</v>
       </c>
@@ -20256,7 +20261,7 @@
       <c r="AM120" s="6"/>
       <c r="AN120" s="6"/>
     </row>
-    <row r="121" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:40" ht="15.75" customHeight="1">
       <c r="A121" s="8">
         <v>45975.414409722223</v>
       </c>
@@ -20360,7 +20365,7 @@
       <c r="AM121" s="13"/>
       <c r="AN121" s="13"/>
     </row>
-    <row r="122" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:40" ht="15.75" customHeight="1">
       <c r="A122" s="1">
         <v>45975.419456018521</v>
       </c>
@@ -20464,7 +20469,7 @@
       <c r="AM122" s="6"/>
       <c r="AN122" s="6"/>
     </row>
-    <row r="123" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:40" ht="15.75" customHeight="1">
       <c r="A123" s="8">
         <v>45975.426435185182</v>
       </c>
@@ -20568,7 +20573,7 @@
       <c r="AM123" s="13"/>
       <c r="AN123" s="13"/>
     </row>
-    <row r="124" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:40" ht="15.75" customHeight="1">
       <c r="A124" s="1">
         <v>45975.438136574077</v>
       </c>
@@ -20672,7 +20677,7 @@
       <c r="AM124" s="6"/>
       <c r="AN124" s="6"/>
     </row>
-    <row r="125" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:40" ht="15.75" customHeight="1">
       <c r="A125" s="8">
         <v>45975.440763888888</v>
       </c>
@@ -20776,7 +20781,7 @@
       <c r="AM125" s="13"/>
       <c r="AN125" s="13"/>
     </row>
-    <row r="126" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:40" ht="15.75" customHeight="1">
       <c r="A126" s="1">
         <v>45975.442060185182</v>
       </c>
@@ -20880,7 +20885,7 @@
       <c r="AM126" s="6"/>
       <c r="AN126" s="6"/>
     </row>
-    <row r="127" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:40" ht="15.75" customHeight="1">
       <c r="A127" s="8">
         <v>45975.49355324074</v>
       </c>
@@ -20994,7 +20999,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="128" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:40" ht="15.75" customHeight="1">
       <c r="A128" s="1">
         <v>45975.493923611109</v>
       </c>
@@ -21100,7 +21105,7 @@
       <c r="AM128" s="6"/>
       <c r="AN128" s="6"/>
     </row>
-    <row r="129" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:40" ht="15.75" customHeight="1">
       <c r="A129" s="8">
         <v>45975.54855324074</v>
       </c>
@@ -21204,7 +21209,7 @@
       <c r="AM129" s="13"/>
       <c r="AN129" s="13"/>
     </row>
-    <row r="130" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:40" ht="15.75" customHeight="1">
       <c r="A130" s="1">
         <v>45975.615324074075</v>
       </c>
@@ -21310,7 +21315,7 @@
       <c r="AM130" s="6"/>
       <c r="AN130" s="6"/>
     </row>
-    <row r="131" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:40" ht="15.75" customHeight="1">
       <c r="A131" s="8">
         <v>45975.635601851849</v>
       </c>
@@ -21422,7 +21427,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="132" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:40" ht="15.75" customHeight="1">
       <c r="A132" s="1">
         <v>45975.643194444441</v>
       </c>
@@ -21528,7 +21533,7 @@
       <c r="AM132" s="6"/>
       <c r="AN132" s="6"/>
     </row>
-    <row r="133" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:40" ht="15.75" customHeight="1">
       <c r="A133" s="8">
         <v>45975.694756944446</v>
       </c>
@@ -21632,7 +21637,7 @@
       <c r="AM133" s="13"/>
       <c r="AN133" s="13"/>
     </row>
-    <row r="134" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:40" ht="15.75" customHeight="1">
       <c r="A134" s="1">
         <v>45975.972280092596</v>
       </c>
@@ -21738,7 +21743,7 @@
       <c r="AM134" s="6"/>
       <c r="AN134" s="6"/>
     </row>
-    <row r="135" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:40" ht="15.75" customHeight="1">
       <c r="A135" s="8">
         <v>45976.37872685185</v>
       </c>
@@ -21844,7 +21849,7 @@
       <c r="AM135" s="13"/>
       <c r="AN135" s="13"/>
     </row>
-    <row r="136" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:40" ht="15.75" customHeight="1">
       <c r="A136" s="1">
         <v>45976.633912037039</v>
       </c>
@@ -21950,7 +21955,7 @@
       <c r="AM136" s="6"/>
       <c r="AN136" s="6"/>
     </row>
-    <row r="137" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:40" ht="15.75" customHeight="1">
       <c r="A137" s="8">
         <v>45978.611875000002</v>
       </c>
@@ -22056,7 +22061,7 @@
       <c r="AM137" s="13"/>
       <c r="AN137" s="13"/>
     </row>
-    <row r="138" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:40" ht="15.75" customHeight="1">
       <c r="A138" s="1">
         <v>45978.693738425929</v>
       </c>
@@ -22160,7 +22165,7 @@
       <c r="AM138" s="6"/>
       <c r="AN138" s="6"/>
     </row>
-    <row r="139" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:40" ht="15.75" customHeight="1">
       <c r="A139" s="8">
         <v>45979.365844907406</v>
       </c>
@@ -22264,7 +22269,7 @@
       <c r="AM139" s="13"/>
       <c r="AN139" s="13"/>
     </row>
-    <row r="140" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:40" ht="15.75" customHeight="1">
       <c r="A140" s="1">
         <v>45979.369976851849</v>
       </c>
@@ -22368,7 +22373,7 @@
       <c r="AM140" s="6"/>
       <c r="AN140" s="6"/>
     </row>
-    <row r="141" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:40" ht="15.75" customHeight="1">
       <c r="A141" s="8">
         <v>45979.371990740743</v>
       </c>
@@ -22474,7 +22479,7 @@
       <c r="AM141" s="13"/>
       <c r="AN141" s="13"/>
     </row>
-    <row r="142" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:40" ht="15.75" customHeight="1">
       <c r="A142" s="1">
         <v>45979.479664351849</v>
       </c>
@@ -22580,7 +22585,7 @@
       <c r="AM142" s="6"/>
       <c r="AN142" s="6"/>
     </row>
-    <row r="143" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:40" ht="15.75" customHeight="1">
       <c r="A143" s="8">
         <v>45979.498854166668</v>
       </c>
@@ -22686,7 +22691,7 @@
       <c r="AM143" s="13"/>
       <c r="AN143" s="13"/>
     </row>
-    <row r="144" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:40" ht="15.75" customHeight="1">
       <c r="A144" s="1">
         <v>45979.554236111115</v>
       </c>
@@ -22790,7 +22795,7 @@
       <c r="AM144" s="6"/>
       <c r="AN144" s="6"/>
     </row>
-    <row r="145" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:40" ht="15.75" customHeight="1">
       <c r="A145" s="8">
         <v>45980.316782407404</v>
       </c>
@@ -22894,7 +22899,7 @@
       <c r="AM145" s="13"/>
       <c r="AN145" s="13"/>
     </row>
-    <row r="146" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:40" ht="15.75" customHeight="1">
       <c r="A146" s="1">
         <v>45980.370381944442</v>
       </c>
@@ -22996,7 +23001,7 @@
       <c r="AM146" s="6"/>
       <c r="AN146" s="6"/>
     </row>
-    <row r="147" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:40" ht="15.75" customHeight="1">
       <c r="A147" s="8">
         <v>45980.380636574075</v>
       </c>
@@ -23100,7 +23105,7 @@
       <c r="AM147" s="13"/>
       <c r="AN147" s="13"/>
     </row>
-    <row r="148" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:40" ht="15.75" customHeight="1">
       <c r="A148" s="1">
         <v>45980.428622685184</v>
       </c>
@@ -23204,7 +23209,7 @@
       <c r="AM148" s="6"/>
       <c r="AN148" s="6"/>
     </row>
-    <row r="149" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:40" ht="15.75" customHeight="1">
       <c r="A149" s="8">
         <v>45980.460347222222</v>
       </c>
@@ -23308,7 +23313,7 @@
       <c r="AM149" s="13"/>
       <c r="AN149" s="13"/>
     </row>
-    <row r="150" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:40" ht="15.75" customHeight="1">
       <c r="A150" s="1">
         <v>45980.519803240742</v>
       </c>
@@ -23414,7 +23419,7 @@
       <c r="AM150" s="6"/>
       <c r="AN150" s="6"/>
     </row>
-    <row r="151" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:40" ht="15.75" customHeight="1">
       <c r="A151" s="8">
         <v>45980.595300925925</v>
       </c>
@@ -23520,7 +23525,7 @@
       <c r="AM151" s="13"/>
       <c r="AN151" s="13"/>
     </row>
-    <row r="152" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:40" ht="15.75" customHeight="1">
       <c r="A152" s="1">
         <v>45981.411817129629</v>
       </c>
@@ -23624,7 +23629,7 @@
       <c r="AM152" s="6"/>
       <c r="AN152" s="6"/>
     </row>
-    <row r="153" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:40" ht="15.75" customHeight="1">
       <c r="A153" s="8">
         <v>45981.414537037039</v>
       </c>
@@ -23730,7 +23735,7 @@
       <c r="AM153" s="13"/>
       <c r="AN153" s="13"/>
     </row>
-    <row r="154" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:40" ht="15.75" customHeight="1">
       <c r="A154" s="1">
         <v>45981.63208333333</v>
       </c>
@@ -23838,7 +23843,7 @@
       <c r="AM154" s="6"/>
       <c r="AN154" s="6"/>
     </row>
-    <row r="155" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:40" ht="15.75" customHeight="1">
       <c r="A155" s="8">
         <v>45981.752314814818</v>
       </c>
@@ -23942,7 +23947,7 @@
       <c r="AM155" s="13"/>
       <c r="AN155" s="13"/>
     </row>
-    <row r="156" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:40" ht="15.75" customHeight="1">
       <c r="A156" s="1">
         <v>45981.991898148146</v>
       </c>
@@ -24046,7 +24051,7 @@
       <c r="AM156" s="6"/>
       <c r="AN156" s="6"/>
     </row>
-    <row r="157" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:40" ht="15.75" customHeight="1">
       <c r="A157" s="8">
         <v>45982.393425925926</v>
       </c>
@@ -24150,7 +24155,7 @@
       <c r="AM157" s="13"/>
       <c r="AN157" s="13"/>
     </row>
-    <row r="158" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:40" ht="15.75" customHeight="1">
       <c r="A158" s="1">
         <v>45982.411249999997</v>
       </c>
@@ -24258,7 +24263,7 @@
       <c r="AM158" s="6"/>
       <c r="AN158" s="6"/>
     </row>
-    <row r="159" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:40" ht="15.75" customHeight="1">
       <c r="A159" s="8">
         <v>45982.422164351854</v>
       </c>
@@ -24366,7 +24371,7 @@
       </c>
       <c r="AN159" s="13"/>
     </row>
-    <row r="160" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:40" ht="15.75" customHeight="1">
       <c r="A160" s="1">
         <v>45982.430243055554</v>
       </c>
@@ -24472,7 +24477,7 @@
       <c r="AM160" s="6"/>
       <c r="AN160" s="6"/>
     </row>
-    <row r="161" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:40" ht="15.75" customHeight="1">
       <c r="A161" s="8">
         <v>45982.431990740741</v>
       </c>
@@ -24578,7 +24583,7 @@
       <c r="AM161" s="13"/>
       <c r="AN161" s="13"/>
     </row>
-    <row r="162" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:40" ht="15.75" customHeight="1">
       <c r="A162" s="1">
         <v>45982.458055555559</v>
       </c>
@@ -24684,7 +24689,7 @@
       <c r="AM162" s="6"/>
       <c r="AN162" s="6"/>
     </row>
-    <row r="163" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:40" ht="15.75" customHeight="1">
       <c r="A163" s="8">
         <v>45982.495347222219</v>
       </c>
@@ -24788,7 +24793,7 @@
       <c r="AM163" s="13"/>
       <c r="AN163" s="13"/>
     </row>
-    <row r="164" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:40" ht="15.75" customHeight="1">
       <c r="A164" s="1">
         <v>45982.528078703705</v>
       </c>
@@ -24892,7 +24897,7 @@
       <c r="AM164" s="6"/>
       <c r="AN164" s="6"/>
     </row>
-    <row r="165" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:40" ht="15.75" customHeight="1">
       <c r="A165" s="8">
         <v>45982.531574074077</v>
       </c>
@@ -24996,7 +25001,7 @@
       <c r="AM165" s="13"/>
       <c r="AN165" s="13"/>
     </row>
-    <row r="166" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:40" ht="15.75" customHeight="1">
       <c r="A166" s="1">
         <v>45982.542037037034</v>
       </c>
@@ -25100,7 +25105,7 @@
       <c r="AM166" s="6"/>
       <c r="AN166" s="6"/>
     </row>
-    <row r="167" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:40" ht="15.75" customHeight="1">
       <c r="A167" s="8">
         <v>45982.548090277778</v>
       </c>
@@ -25206,7 +25211,7 @@
       <c r="AM167" s="13"/>
       <c r="AN167" s="13"/>
     </row>
-    <row r="168" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:40" ht="15.75" customHeight="1">
       <c r="A168" s="1">
         <v>45982.551319444443</v>
       </c>
@@ -25314,7 +25319,7 @@
       <c r="AM168" s="6"/>
       <c r="AN168" s="6"/>
     </row>
-    <row r="169" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:40" ht="15.75" customHeight="1">
       <c r="A169" s="8">
         <v>45982.616423611114</v>
       </c>
@@ -25420,7 +25425,7 @@
       <c r="AM169" s="13"/>
       <c r="AN169" s="13"/>
     </row>
-    <row r="170" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:40" ht="15.75" customHeight="1">
       <c r="A170" s="1">
         <v>45982.621087962965</v>
       </c>
@@ -25524,7 +25529,7 @@
       <c r="AM170" s="6"/>
       <c r="AN170" s="6"/>
     </row>
-    <row r="171" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:40" ht="15.75" customHeight="1">
       <c r="A171" s="8">
         <v>45982.628761574073</v>
       </c>
@@ -25632,7 +25637,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="172" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:40" ht="15.75" customHeight="1">
       <c r="A172" s="1">
         <v>45982.656342592592</v>
       </c>
@@ -25738,7 +25743,7 @@
       <c r="AM172" s="6"/>
       <c r="AN172" s="6"/>
     </row>
-    <row r="173" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:40" ht="15.75" customHeight="1">
       <c r="A173" s="8">
         <v>45983.417222222219</v>
       </c>
@@ -25844,7 +25849,7 @@
       <c r="AM173" s="13"/>
       <c r="AN173" s="13"/>
     </row>
-    <row r="174" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:40" ht="15.75" customHeight="1">
       <c r="A174" s="1">
         <v>45983.460949074077</v>
       </c>
@@ -25948,7 +25953,7 @@
       <c r="AM174" s="6"/>
       <c r="AN174" s="6"/>
     </row>
-    <row r="175" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:40" ht="15.75" customHeight="1">
       <c r="A175" s="8">
         <v>45983.51185185185</v>
       </c>
@@ -26052,7 +26057,7 @@
       <c r="AM175" s="13"/>
       <c r="AN175" s="13"/>
     </row>
-    <row r="176" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:40" ht="15.75" customHeight="1">
       <c r="A176" s="1">
         <v>45983.530474537038</v>
       </c>
@@ -26164,7 +26169,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="177" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:40" ht="15.75" customHeight="1">
       <c r="A177" s="8">
         <v>45983.538344907407</v>
       </c>
@@ -26268,7 +26273,7 @@
       <c r="AM177" s="13"/>
       <c r="AN177" s="13"/>
     </row>
-    <row r="178" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:40" ht="15.75" customHeight="1">
       <c r="A178" s="1">
         <v>45983.560393518521</v>
       </c>
@@ -26372,7 +26377,7 @@
       <c r="AM178" s="6"/>
       <c r="AN178" s="6"/>
     </row>
-    <row r="179" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:40" ht="15.75" customHeight="1">
       <c r="A179" s="8">
         <v>45983.568020833336</v>
       </c>
@@ -26476,7 +26481,7 @@
       <c r="AM179" s="13"/>
       <c r="AN179" s="13"/>
     </row>
-    <row r="180" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:40" ht="15.75" customHeight="1">
       <c r="A180" s="1">
         <v>45983.578020833331</v>
       </c>
@@ -26582,7 +26587,7 @@
       <c r="AM180" s="6"/>
       <c r="AN180" s="6"/>
     </row>
-    <row r="181" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:40" ht="15.75" customHeight="1">
       <c r="A181" s="8">
         <v>45983.761250000003</v>
       </c>
@@ -26686,7 +26691,7 @@
       <c r="AM181" s="13"/>
       <c r="AN181" s="13"/>
     </row>
-    <row r="182" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:40" ht="15.75" customHeight="1">
       <c r="A182" s="1">
         <v>45984.822141203702</v>
       </c>
@@ -26790,7 +26795,7 @@
       <c r="AM182" s="6"/>
       <c r="AN182" s="6"/>
     </row>
-    <row r="183" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:40" ht="15.75" customHeight="1">
       <c r="A183" s="8">
         <v>45985.483148148145</v>
       </c>
@@ -26894,7 +26899,7 @@
       <c r="AM183" s="13"/>
       <c r="AN183" s="13"/>
     </row>
-    <row r="184" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:40" ht="15.75" customHeight="1">
       <c r="A184" s="1">
         <v>45985.525810185187</v>
       </c>
@@ -26998,7 +27003,7 @@
       <c r="AM184" s="6"/>
       <c r="AN184" s="6"/>
     </row>
-    <row r="185" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:40" ht="15.75" customHeight="1">
       <c r="A185" s="8">
         <v>45985.53052083333</v>
       </c>
@@ -27102,7 +27107,7 @@
       <c r="AM185" s="13"/>
       <c r="AN185" s="13"/>
     </row>
-    <row r="186" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:40" ht="15.75" customHeight="1">
       <c r="A186" s="1">
         <v>45985.622858796298</v>
       </c>
@@ -27208,7 +27213,7 @@
       <c r="AM186" s="6"/>
       <c r="AN186" s="6"/>
     </row>
-    <row r="187" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:40" ht="15.75" customHeight="1">
       <c r="A187" s="8">
         <v>45985.623449074075</v>
       </c>
@@ -27312,7 +27317,7 @@
       <c r="AM187" s="13"/>
       <c r="AN187" s="13"/>
     </row>
-    <row r="188" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:40" ht="15.75" customHeight="1">
       <c r="A188" s="1">
         <v>45986.487766203703</v>
       </c>
@@ -27416,7 +27421,7 @@
       <c r="AM188" s="6"/>
       <c r="AN188" s="6"/>
     </row>
-    <row r="189" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:40" ht="15.75" customHeight="1">
       <c r="A189" s="8">
         <v>45987.438449074078</v>
       </c>
@@ -27522,7 +27527,7 @@
       <c r="AM189" s="13"/>
       <c r="AN189" s="13"/>
     </row>
-    <row r="190" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:40" ht="15.75" customHeight="1">
       <c r="A190" s="1">
         <v>45987.540578703702</v>
       </c>
@@ -27628,7 +27633,7 @@
       <c r="AM190" s="6"/>
       <c r="AN190" s="6"/>
     </row>
-    <row r="191" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:40" ht="15.75" customHeight="1">
       <c r="A191" s="8">
         <v>45987.690243055556</v>
       </c>
@@ -27740,7 +27745,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="192" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:40" ht="15.75" customHeight="1">
       <c r="A192" s="1">
         <v>45987.704791666663</v>
       </c>
@@ -27846,7 +27851,7 @@
       <c r="AM192" s="6"/>
       <c r="AN192" s="6"/>
     </row>
-    <row r="193" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:40" ht="15.75" customHeight="1">
       <c r="A193" s="8">
         <v>45987.893125000002</v>
       </c>
@@ -27952,7 +27957,7 @@
       <c r="AM193" s="13"/>
       <c r="AN193" s="13"/>
     </row>
-    <row r="194" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:40" ht="15.75" customHeight="1">
       <c r="A194" s="1">
         <v>45988.458819444444</v>
       </c>
@@ -28056,7 +28061,7 @@
       <c r="AM194" s="6"/>
       <c r="AN194" s="6"/>
     </row>
-    <row r="195" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:40" ht="15.75" customHeight="1">
       <c r="A195" s="8">
         <v>45988.494988425926</v>
       </c>
@@ -28160,7 +28165,7 @@
       <c r="AM195" s="13"/>
       <c r="AN195" s="13"/>
     </row>
-    <row r="196" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:40" ht="15.75" customHeight="1">
       <c r="A196" s="1">
         <v>45988.519699074073</v>
       </c>
@@ -28264,7 +28269,7 @@
       <c r="AM196" s="6"/>
       <c r="AN196" s="6"/>
     </row>
-    <row r="197" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:40" ht="15.75" customHeight="1">
       <c r="A197" s="8">
         <v>45988.540254629632</v>
       </c>
@@ -28370,7 +28375,7 @@
       <c r="AM197" s="13"/>
       <c r="AN197" s="13"/>
     </row>
-    <row r="198" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:40" ht="15.75" customHeight="1">
       <c r="A198" s="1">
         <v>45988.613645833335</v>
       </c>
@@ -28476,7 +28481,7 @@
       <c r="AM198" s="6"/>
       <c r="AN198" s="6"/>
     </row>
-    <row r="199" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:40" ht="15.75" customHeight="1">
       <c r="A199" s="8">
         <v>45988.676562499997</v>
       </c>
@@ -28580,7 +28585,7 @@
       <c r="AM199" s="13"/>
       <c r="AN199" s="13"/>
     </row>
-    <row r="200" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:40" ht="15.75" customHeight="1">
       <c r="A200" s="1">
         <v>45989.404143518521</v>
       </c>
@@ -28686,7 +28691,7 @@
       <c r="AM200" s="6"/>
       <c r="AN200" s="6"/>
     </row>
-    <row r="201" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:40" ht="15.75" customHeight="1">
       <c r="A201" s="8">
         <v>45989.442962962959</v>
       </c>
@@ -28796,7 +28801,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="202" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:40" ht="15.75" customHeight="1">
       <c r="A202" s="1">
         <v>45989.531435185185</v>
       </c>
@@ -28904,7 +28909,7 @@
       <c r="AM202" s="6"/>
       <c r="AN202" s="6"/>
     </row>
-    <row r="203" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:40" ht="15.75" customHeight="1">
       <c r="A203" s="8">
         <v>45989.533159722225</v>
       </c>
@@ -29010,7 +29015,7 @@
       <c r="AM203" s="13"/>
       <c r="AN203" s="13"/>
     </row>
-    <row r="204" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:40" ht="15.75" customHeight="1">
       <c r="A204" s="1">
         <v>45989.555358796293</v>
       </c>
@@ -29114,7 +29119,7 @@
       <c r="AM204" s="6"/>
       <c r="AN204" s="6"/>
     </row>
-    <row r="205" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:40" ht="15.75" customHeight="1">
       <c r="A205" s="8">
         <v>45989.562418981484</v>
       </c>
@@ -29220,7 +29225,7 @@
       <c r="AM205" s="13"/>
       <c r="AN205" s="13"/>
     </row>
-    <row r="206" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:40" ht="15.75" customHeight="1">
       <c r="A206" s="1">
         <v>45989.562986111108</v>
       </c>
@@ -29326,7 +29331,7 @@
       <c r="AM206" s="6"/>
       <c r="AN206" s="6"/>
     </row>
-    <row r="207" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:40" ht="15.75" customHeight="1">
       <c r="A207" s="8">
         <v>45989.598379629628</v>
       </c>
@@ -29432,7 +29437,7 @@
       <c r="AM207" s="13"/>
       <c r="AN207" s="13"/>
     </row>
-    <row r="208" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:40" ht="15.75" customHeight="1">
       <c r="A208" s="1">
         <v>45989.642604166664</v>
       </c>
@@ -29538,7 +29543,7 @@
       </c>
       <c r="AN208" s="6"/>
     </row>
-    <row r="209" spans="1:40" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:40" ht="409.5">
       <c r="A209" s="8">
         <v>45989.642881944441</v>
       </c>
@@ -29644,7 +29649,7 @@
       <c r="AM209" s="13"/>
       <c r="AN209" s="13"/>
     </row>
-    <row r="210" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:40" ht="15.75" customHeight="1">
       <c r="A210" s="1">
         <v>45989.647222222222</v>
       </c>
@@ -29754,7 +29759,7 @@
       </c>
       <c r="AN210" s="6"/>
     </row>
-    <row r="211" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:40" ht="15.75" customHeight="1">
       <c r="A211" s="8">
         <v>45990.525219907409</v>
       </c>
@@ -29862,7 +29867,7 @@
       <c r="AM211" s="13"/>
       <c r="AN211" s="13"/>
     </row>
-    <row r="212" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:40" ht="15.75" customHeight="1">
       <c r="A212" s="1">
         <v>45991.461608796293</v>
       </c>
@@ -29968,7 +29973,7 @@
       <c r="AM212" s="6"/>
       <c r="AN212" s="6"/>
     </row>
-    <row r="213" spans="1:40" ht="114.75" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:40" ht="127.5">
       <c r="A213" s="8">
         <v>45991.931631944448</v>
       </c>
@@ -30074,7 +30079,7 @@
       <c r="AM213" s="13"/>
       <c r="AN213" s="13"/>
     </row>
-    <row r="214" spans="1:40" ht="229.5" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:40" ht="229.5">
       <c r="A214" s="1">
         <v>45992.409791666665</v>
       </c>
@@ -30184,7 +30189,7 @@
       <c r="AM214" s="6"/>
       <c r="AN214" s="6"/>
     </row>
-    <row r="215" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:40" ht="15.75" customHeight="1">
       <c r="A215" s="8">
         <v>45992.539317129631</v>
       </c>
@@ -30288,7 +30293,7 @@
       <c r="AM215" s="13"/>
       <c r="AN215" s="13"/>
     </row>
-    <row r="216" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:40" ht="15.75" customHeight="1">
       <c r="A216" s="1">
         <v>45993.426747685182</v>
       </c>
@@ -30394,7 +30399,7 @@
       <c r="AM216" s="6"/>
       <c r="AN216" s="6"/>
     </row>
-    <row r="217" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:40" ht="15.75" customHeight="1">
       <c r="A217" s="8">
         <v>45993.819548611114</v>
       </c>
@@ -30500,7 +30505,7 @@
       <c r="AM217" s="13"/>
       <c r="AN217" s="13"/>
     </row>
-    <row r="218" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:40" ht="15.75" customHeight="1">
       <c r="A218" s="1">
         <v>45994.393171296295</v>
       </c>
@@ -30614,7 +30619,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="219" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:40" ht="15.75" customHeight="1">
       <c r="A219" s="8">
         <v>45994.406215277777</v>
       </c>
@@ -30728,7 +30733,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="220" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:40" ht="15.75" customHeight="1">
       <c r="A220" s="1">
         <v>45994.417268518519</v>
       </c>
@@ -30832,7 +30837,7 @@
       <c r="AM220" s="6"/>
       <c r="AN220" s="6"/>
     </row>
-    <row r="221" spans="1:40" ht="153" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:40" ht="165.75">
       <c r="A221" s="8">
         <v>45994.485266203701</v>
       </c>
@@ -30944,7 +30949,7 @@
       </c>
       <c r="AN221" s="13"/>
     </row>
-    <row r="222" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:40" ht="15.75" customHeight="1">
       <c r="A222" s="1">
         <v>45994.618009259262</v>
       </c>
@@ -31050,7 +31055,7 @@
       <c r="AM222" s="6"/>
       <c r="AN222" s="6"/>
     </row>
-    <row r="223" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:40" ht="15.75" customHeight="1">
       <c r="A223" s="8">
         <v>45994.692442129628</v>
       </c>
@@ -31154,7 +31159,7 @@
       <c r="AM223" s="13"/>
       <c r="AN223" s="13"/>
     </row>
-    <row r="224" spans="1:40" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:40" ht="409.5">
       <c r="A224" s="1">
         <v>45995.725115740737</v>
       </c>
@@ -31260,7 +31265,7 @@
       <c r="AM224" s="5"/>
       <c r="AN224" s="5"/>
     </row>
-    <row r="225" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:46" ht="15.75" customHeight="1">
       <c r="A225" s="8">
         <v>45996.555462962962</v>
       </c>
@@ -31364,7 +31369,7 @@
       <c r="AM225" s="13"/>
       <c r="AN225" s="13"/>
     </row>
-    <row r="226" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:46" ht="15.75" customHeight="1">
       <c r="A226" s="1">
         <v>45999.364525462966</v>
       </c>
@@ -31468,7 +31473,7 @@
       <c r="AM226" s="6"/>
       <c r="AN226" s="6"/>
     </row>
-    <row r="227" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:46" ht="15.75" customHeight="1">
       <c r="A227" s="8">
         <v>46002.523680555554</v>
       </c>
@@ -31572,7 +31577,7 @@
       <c r="AM227" s="13"/>
       <c r="AN227" s="13"/>
     </row>
-    <row r="228" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:46" ht="15.75" customHeight="1">
       <c r="A228" s="1">
         <v>46010.499398148146</v>
       </c>
@@ -31676,7 +31681,7 @@
       <c r="AM228" s="6"/>
       <c r="AN228" s="6"/>
     </row>
-    <row r="229" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:46" ht="15.75" customHeight="1">
       <c r="A229" s="8">
         <v>46015.435925925929</v>
       </c>
@@ -31784,7 +31789,7 @@
       <c r="AM229" s="13"/>
       <c r="AN229" s="13"/>
     </row>
-    <row r="230" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:46" ht="15.75" customHeight="1">
       <c r="A230" s="1">
         <v>46017.628229166665</v>
       </c>
@@ -31888,7 +31893,7 @@
       <c r="AM230" s="6"/>
       <c r="AN230" s="6"/>
     </row>
-    <row r="231" spans="1:46" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:46" ht="15.75" customHeight="1" thickBot="1">
       <c r="A231" s="8">
         <v>46028.591863425929</v>
       </c>
@@ -31992,7 +31997,7 @@
       <c r="AM231" s="13"/>
       <c r="AN231" s="13"/>
     </row>
-    <row r="232" spans="1:46" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:46" ht="15.75" customHeight="1" thickBot="1">
       <c r="A232" s="1">
         <v>46032.41710648148</v>
       </c>

--- a/assets/excel/Staff_Doctor_Details(Responses).xlsx
+++ b/assets/excel/Staff_Doctor_Details(Responses).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5273" uniqueCount="2273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5250" uniqueCount="2262">
   <si>
     <t>Name</t>
   </si>
@@ -5640,27 +5640,6 @@
   </si>
   <si>
     <t>Dr.Kalyani kutti ammal Gold medal for Best Paper presentation at 2020 AKCOG</t>
-  </si>
-  <si>
-    <t>DR.DHIVYA SETHURAMAN</t>
-  </si>
-  <si>
-    <t>MD.OBG</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1yzcITi9KA09SzCwgk7bUhww3312BHl2e</t>
-  </si>
-  <si>
-    <t>dhivyasethu98@gmail.com</t>
-  </si>
-  <si>
-    <t>TSRMT0231</t>
-  </si>
-  <si>
-    <t>MBBS MD OG</t>
-  </si>
-  <si>
-    <t>It is an honor to be a part of the vibrant team that constitutes the department of OBGYN. We remain deeply committed to pursuing academic excellence and delivering compassionate and high quality maternal services to the community.</t>
   </si>
   <si>
     <t>Dr.c.balamurugan</t>
@@ -6745,17 +6724,6 @@
     <t>No-5, Kalyana Sundaram Nagar,K.K.Nagar post, Tiruchirapalli -21</t>
   </si>
   <si>
-    <t xml:space="preserve">5/1 Maris Avenue, Collectors Office Road, 
-Cantonment, Tiruchirapalli – 620 001
-</t>
-  </si>
-  <si>
-    <t>Dr.Dhivya Sethuraman.MD.OG, Professor &amp; HOD Department of OBGYN. Tiruchirapalli SRM Medical College Hospital &amp; Research Centre, Irungalur, Tiruchirapalli. Under her leadership there has been a significant increase in deliveries and laparoscopic surgeries in the department. She advocates for respectful maternity care and high quality training for both undergraduate and post graduate students. Her commitment to compassionate care, pursuit of academic excellence makes her a valued leader and mentor in OBGYN.</t>
-  </si>
-  <si>
-    <t>Best Executive Committee Member in Action Award, Tiruchirapalli OBGYN Society, CS Dawn Award for Best Paper Presentation in All India Conference OBGYN Agra</t>
-  </si>
-  <si>
     <t>balamurugan.c@mc.srmTiruchirapalli.edu.in</t>
   </si>
   <si>
@@ -6784,9 +6752,6 @@
   </si>
   <si>
     <t>manoj.sk@mc.srmTiruchirapalli.edu.in</t>
-  </si>
-  <si>
-    <t>Cantonment,Tiruchirapalli</t>
   </si>
   <si>
     <t>Chennai</t>
@@ -7096,7 +7061,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -7545,8 +7510,8 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AT232"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:AT231"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
@@ -7583,7 +7548,7 @@
     <col min="40" max="40" width="58" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="15.75" customHeight="1">
+    <row r="1" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15">
         <v>45956.692314814813</v>
       </c>
@@ -7705,7 +7670,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="2" spans="1:40" ht="409.5">
+    <row r="2" spans="1:40" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45957.692314814813</v>
       </c>
@@ -7743,7 +7708,7 @@
         <v>9894489142</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>38</v>
@@ -7776,7 +7741,7 @@
         <v>44601</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="Y2" s="2" t="s">
         <v>11</v>
@@ -7789,7 +7754,7 @@
       </c>
       <c r="AB2" s="6"/>
       <c r="AC2" s="2" t="s">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="AD2" s="6"/>
       <c r="AE2" s="2" t="s">
@@ -7811,7 +7776,7 @@
       <c r="AM2" s="6"/>
       <c r="AN2" s="6"/>
     </row>
-    <row r="3" spans="1:40" ht="15.75" customHeight="1">
+    <row r="3" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>45957.836099537039</v>
       </c>
@@ -7917,7 +7882,7 @@
       <c r="AM3" s="13"/>
       <c r="AN3" s="13"/>
     </row>
-    <row r="4" spans="1:40" ht="15.75" customHeight="1">
+    <row r="4" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45957.892523148148</v>
       </c>
@@ -7955,7 +7920,7 @@
         <v>9486643131</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>56</v>
@@ -7988,7 +7953,7 @@
         <v>40050</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="Y4" s="2" t="s">
         <v>11</v>
@@ -8001,7 +7966,7 @@
       </c>
       <c r="AB4" s="6"/>
       <c r="AC4" s="2" t="s">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="AD4" s="2" t="s">
         <v>63</v>
@@ -8027,7 +7992,7 @@
       </c>
       <c r="AN4" s="6"/>
     </row>
-    <row r="5" spans="1:40" ht="15.75" customHeight="1">
+    <row r="5" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>45959.447812500002</v>
       </c>
@@ -8131,7 +8096,7 @@
       <c r="AM5" s="13"/>
       <c r="AN5" s="13"/>
     </row>
-    <row r="6" spans="1:40" ht="15.75" customHeight="1">
+    <row r="6" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45959.619328703702</v>
       </c>
@@ -8237,7 +8202,7 @@
       <c r="AM6" s="6"/>
       <c r="AN6" s="6"/>
     </row>
-    <row r="7" spans="1:40" ht="15.75" customHeight="1">
+    <row r="7" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>45959.628240740742</v>
       </c>
@@ -8275,7 +8240,7 @@
         <v>8122557996</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="N7" s="9" t="s">
         <v>84</v>
@@ -8308,7 +8273,7 @@
         <v>45691</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="Y7" s="9" t="s">
         <v>11</v>
@@ -8320,7 +8285,7 @@
         <v>88</v>
       </c>
       <c r="AB7" s="12" t="s">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="AC7" s="9" t="s">
         <v>89</v>
@@ -8347,7 +8312,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:40" ht="15.75" customHeight="1">
+    <row r="8" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45962.704074074078</v>
       </c>
@@ -8385,7 +8350,7 @@
         <v>9840050180</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>92</v>
@@ -8453,7 +8418,7 @@
       <c r="AM8" s="6"/>
       <c r="AN8" s="6"/>
     </row>
-    <row r="9" spans="1:40" ht="15.75" customHeight="1">
+    <row r="9" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>45962.830706018518</v>
       </c>
@@ -8491,10 +8456,10 @@
         <v>9629186681</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>2027</v>
+        <v>2020</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>2028</v>
+        <v>2021</v>
       </c>
       <c r="O9" s="9" t="s">
         <v>438</v>
@@ -8563,7 +8528,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:40" ht="15.75" customHeight="1">
+    <row r="10" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45962.861979166664</v>
       </c>
@@ -8669,7 +8634,7 @@
       <c r="AM10" s="6"/>
       <c r="AN10" s="6"/>
     </row>
-    <row r="11" spans="1:40" ht="15.75" customHeight="1">
+    <row r="11" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>45963.404826388891</v>
       </c>
@@ -8773,7 +8738,7 @@
       <c r="AM11" s="13"/>
       <c r="AN11" s="13"/>
     </row>
-    <row r="12" spans="1:40" ht="15.75" customHeight="1">
+    <row r="12" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45963.419293981482</v>
       </c>
@@ -8879,7 +8844,7 @@
       <c r="AM12" s="6"/>
       <c r="AN12" s="6"/>
     </row>
-    <row r="13" spans="1:40" ht="15.75" customHeight="1">
+    <row r="13" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>45964.385462962964</v>
       </c>
@@ -8983,7 +8948,7 @@
       <c r="AM13" s="13"/>
       <c r="AN13" s="13"/>
     </row>
-    <row r="14" spans="1:40" ht="15.75" customHeight="1">
+    <row r="14" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45964.427928240744</v>
       </c>
@@ -9021,10 +8986,10 @@
         <v>9566518548</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>2029</v>
+        <v>2022</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>2030</v>
+        <v>2023</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>57</v>
@@ -9087,7 +9052,7 @@
       <c r="AM14" s="6"/>
       <c r="AN14" s="6"/>
     </row>
-    <row r="15" spans="1:40" ht="15.75" customHeight="1">
+    <row r="15" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>45964.533125000002</v>
       </c>
@@ -9128,7 +9093,7 @@
         <v>139</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>2031</v>
+        <v>2024</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>57</v>
@@ -9193,7 +9158,7 @@
       <c r="AM15" s="13"/>
       <c r="AN15" s="13"/>
     </row>
-    <row r="16" spans="1:40" ht="15.75" customHeight="1">
+    <row r="16" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>45964.573194444441</v>
       </c>
@@ -9297,7 +9262,7 @@
       <c r="AM16" s="6"/>
       <c r="AN16" s="6"/>
     </row>
-    <row r="17" spans="1:40" ht="15.75" customHeight="1">
+    <row r="17" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>45964.575567129628</v>
       </c>
@@ -9401,7 +9366,7 @@
       <c r="AM17" s="13"/>
       <c r="AN17" s="13"/>
     </row>
-    <row r="18" spans="1:40" ht="15.75" customHeight="1">
+    <row r="18" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>45964.577222222222</v>
       </c>
@@ -9439,7 +9404,7 @@
         <v>9566593108</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>2032</v>
+        <v>2025</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>166</v>
@@ -9507,7 +9472,7 @@
       <c r="AM18" s="6"/>
       <c r="AN18" s="6"/>
     </row>
-    <row r="19" spans="1:40" ht="15.75" customHeight="1">
+    <row r="19" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>45964.584108796298</v>
       </c>
@@ -9548,7 +9513,7 @@
         <v>174</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>2033</v>
+        <v>2026</v>
       </c>
       <c r="O19" s="9" t="s">
         <v>78</v>
@@ -9611,7 +9576,7 @@
       <c r="AM19" s="13"/>
       <c r="AN19" s="13"/>
     </row>
-    <row r="20" spans="1:40" ht="15.75" customHeight="1">
+    <row r="20" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>45964.591550925928</v>
       </c>
@@ -9715,7 +9680,7 @@
       <c r="AM20" s="6"/>
       <c r="AN20" s="6"/>
     </row>
-    <row r="21" spans="1:40" ht="15.75" customHeight="1">
+    <row r="21" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>45964.592106481483</v>
       </c>
@@ -9819,7 +9784,7 @@
       <c r="AM21" s="13"/>
       <c r="AN21" s="13"/>
     </row>
-    <row r="22" spans="1:40" ht="15.75" customHeight="1">
+    <row r="22" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>45964.598437499997</v>
       </c>
@@ -9925,7 +9890,7 @@
       <c r="AM22" s="6"/>
       <c r="AN22" s="6"/>
     </row>
-    <row r="23" spans="1:40" ht="15.75" customHeight="1">
+    <row r="23" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>45964.603194444448</v>
       </c>
@@ -9963,7 +9928,7 @@
         <v>8248667938</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>2034</v>
+        <v>2027</v>
       </c>
       <c r="N23" s="9" t="s">
         <v>203</v>
@@ -9996,7 +9961,7 @@
         <v>40369</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>2035</v>
+        <v>2028</v>
       </c>
       <c r="Y23" s="9" t="s">
         <v>11</v>
@@ -10031,7 +9996,7 @@
       <c r="AM23" s="13"/>
       <c r="AN23" s="13"/>
     </row>
-    <row r="24" spans="1:40" ht="15.75" customHeight="1">
+    <row r="24" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>45964.606122685182</v>
       </c>
@@ -10075,7 +10040,7 @@
         <v>207</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>2036</v>
+        <v>2029</v>
       </c>
       <c r="P24" s="3">
         <v>620005</v>
@@ -10137,7 +10102,7 @@
       <c r="AM24" s="6"/>
       <c r="AN24" s="6"/>
     </row>
-    <row r="25" spans="1:40" ht="15.75" customHeight="1">
+    <row r="25" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>45964.608634259261</v>
       </c>
@@ -10241,7 +10206,7 @@
       <c r="AM25" s="13"/>
       <c r="AN25" s="13"/>
     </row>
-    <row r="26" spans="1:40" ht="15.75" customHeight="1">
+    <row r="26" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>45964.610312500001</v>
       </c>
@@ -10282,7 +10247,7 @@
         <v>220</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>2037</v>
+        <v>2030</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>78</v>
@@ -10347,7 +10312,7 @@
       <c r="AM26" s="6"/>
       <c r="AN26" s="6"/>
     </row>
-    <row r="27" spans="1:40" ht="15.75" customHeight="1">
+    <row r="27" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>45964.613171296296</v>
       </c>
@@ -10455,7 +10420,7 @@
       <c r="AM27" s="13"/>
       <c r="AN27" s="13"/>
     </row>
-    <row r="28" spans="1:40" ht="15.75" customHeight="1">
+    <row r="28" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>45964.617430555554</v>
       </c>
@@ -10493,7 +10458,7 @@
         <v>9790585720</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>2038</v>
+        <v>2031</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>488</v>
@@ -10559,7 +10524,7 @@
       <c r="AM28" s="6"/>
       <c r="AN28" s="6"/>
     </row>
-    <row r="29" spans="1:40" ht="15.75" customHeight="1">
+    <row r="29" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>45964.618437500001</v>
       </c>
@@ -10663,7 +10628,7 @@
       <c r="AM29" s="13"/>
       <c r="AN29" s="13"/>
     </row>
-    <row r="30" spans="1:40" ht="15.75" customHeight="1">
+    <row r="30" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>45964.621215277781</v>
       </c>
@@ -10704,7 +10669,7 @@
         <v>240</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>2039</v>
+        <v>2032</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>57</v>
@@ -10749,7 +10714,7 @@
         <v>241</v>
       </c>
       <c r="AC30" s="2" t="s">
-        <v>2040</v>
+        <v>2033</v>
       </c>
       <c r="AD30" s="2" t="s">
         <v>242</v>
@@ -10773,7 +10738,7 @@
       <c r="AM30" s="6"/>
       <c r="AN30" s="6"/>
     </row>
-    <row r="31" spans="1:40" ht="15.75" customHeight="1">
+    <row r="31" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>45964.63071759259</v>
       </c>
@@ -10814,7 +10779,7 @@
         <v>245</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>2041</v>
+        <v>2034</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>57</v>
@@ -10877,7 +10842,7 @@
       <c r="AM31" s="13"/>
       <c r="AN31" s="13"/>
     </row>
-    <row r="32" spans="1:40" ht="15.75" customHeight="1">
+    <row r="32" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>45964.632025462961</v>
       </c>
@@ -10981,7 +10946,7 @@
       <c r="AM32" s="6"/>
       <c r="AN32" s="6"/>
     </row>
-    <row r="33" spans="1:40" ht="15.75" customHeight="1">
+    <row r="33" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>45964.660057870373</v>
       </c>
@@ -11022,7 +10987,7 @@
         <v>254</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>2042</v>
+        <v>2035</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>57</v>
@@ -11085,7 +11050,7 @@
       <c r="AM33" s="13"/>
       <c r="AN33" s="13"/>
     </row>
-    <row r="34" spans="1:40" ht="15.75" customHeight="1">
+    <row r="34" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>45964.683622685188</v>
       </c>
@@ -11123,7 +11088,7 @@
         <v>8248937326</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>2043</v>
+        <v>2036</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>260</v>
@@ -11189,7 +11154,7 @@
       <c r="AM34" s="6"/>
       <c r="AN34" s="6"/>
     </row>
-    <row r="35" spans="1:40" ht="15.75" customHeight="1">
+    <row r="35" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <v>45964.694976851853</v>
       </c>
@@ -11230,7 +11195,7 @@
         <v>265</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>2044</v>
+        <v>2037</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>57</v>
@@ -11303,7 +11268,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="36" spans="1:40" ht="15.75" customHeight="1">
+    <row r="36" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>45964.718078703707</v>
       </c>
@@ -11344,7 +11309,7 @@
         <v>277</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>2045</v>
+        <v>2038</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>57</v>
@@ -11407,7 +11372,7 @@
       <c r="AM36" s="6"/>
       <c r="AN36" s="6"/>
     </row>
-    <row r="37" spans="1:40" ht="15.75" customHeight="1">
+    <row r="37" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>45964.720648148148</v>
       </c>
@@ -11478,7 +11443,7 @@
         <v>40372</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>2046</v>
+        <v>2039</v>
       </c>
       <c r="Y37" s="9" t="s">
         <v>11</v>
@@ -11515,7 +11480,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="38" spans="1:40" ht="15.75" customHeight="1">
+    <row r="38" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>45964.749942129631</v>
       </c>
@@ -11556,7 +11521,7 @@
         <v>287</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>2047</v>
+        <v>2040</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>57</v>
@@ -11619,7 +11584,7 @@
       <c r="AM38" s="6"/>
       <c r="AN38" s="6"/>
     </row>
-    <row r="39" spans="1:40" ht="15.75" customHeight="1">
+    <row r="39" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
         <v>45964.753599537034</v>
       </c>
@@ -11703,7 +11668,7 @@
       </c>
       <c r="AB39" s="13"/>
       <c r="AC39" s="9" t="s">
-        <v>2048</v>
+        <v>2041</v>
       </c>
       <c r="AD39" s="13"/>
       <c r="AE39" s="9" t="s">
@@ -11725,7 +11690,7 @@
       <c r="AM39" s="13"/>
       <c r="AN39" s="13"/>
     </row>
-    <row r="40" spans="1:40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>45964.756678240738</v>
       </c>
@@ -11763,10 +11728,10 @@
         <v>9980365664</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>2049</v>
+        <v>2042</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>2050</v>
+        <v>2043</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>57</v>
@@ -11829,7 +11794,7 @@
       <c r="AM40" s="6"/>
       <c r="AN40" s="6"/>
     </row>
-    <row r="41" spans="1:40" ht="15.75" customHeight="1">
+    <row r="41" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <v>45964.769467592596</v>
       </c>
@@ -11933,7 +11898,7 @@
       <c r="AM41" s="13"/>
       <c r="AN41" s="13"/>
     </row>
-    <row r="42" spans="1:40" ht="15.75" customHeight="1">
+    <row r="42" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>45964.770439814813</v>
       </c>
@@ -11974,7 +11939,7 @@
         <v>309</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>2051</v>
+        <v>2044</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>57</v>
@@ -12039,7 +12004,7 @@
       <c r="AM42" s="6"/>
       <c r="AN42" s="6"/>
     </row>
-    <row r="43" spans="1:40" ht="15.75" customHeight="1">
+    <row r="43" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
         <v>45964.962500000001</v>
       </c>
@@ -12143,7 +12108,7 @@
       <c r="AM43" s="13"/>
       <c r="AN43" s="13"/>
     </row>
-    <row r="44" spans="1:40" ht="15.75" customHeight="1">
+    <row r="44" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>45965.415185185186</v>
       </c>
@@ -12181,7 +12146,7 @@
         <v>9566945363</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>2052</v>
+        <v>2045</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>528</v>
@@ -12249,7 +12214,7 @@
       <c r="AM44" s="6"/>
       <c r="AN44" s="6"/>
     </row>
-    <row r="45" spans="1:40" ht="15.75" customHeight="1">
+    <row r="45" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
         <v>45965.417916666665</v>
       </c>
@@ -12336,7 +12301,7 @@
         <v>532</v>
       </c>
       <c r="AD45" s="9" t="s">
-        <v>2053</v>
+        <v>2046</v>
       </c>
       <c r="AE45" s="9" t="s">
         <v>44</v>
@@ -12357,7 +12322,7 @@
       <c r="AM45" s="13"/>
       <c r="AN45" s="13"/>
     </row>
-    <row r="46" spans="1:40" ht="15.75" customHeight="1">
+    <row r="46" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45965.447060185186</v>
       </c>
@@ -12463,7 +12428,7 @@
       <c r="AM46" s="6"/>
       <c r="AN46" s="6"/>
     </row>
-    <row r="47" spans="1:40" ht="15.75" customHeight="1">
+    <row r="47" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
         <v>45965.450416666667</v>
       </c>
@@ -12501,10 +12466,10 @@
         <v>8098810385</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>2054</v>
+        <v>2047</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>2055</v>
+        <v>2048</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>57</v>
@@ -12571,7 +12536,7 @@
       <c r="AM47" s="13"/>
       <c r="AN47" s="13"/>
     </row>
-    <row r="48" spans="1:40" ht="15.75" customHeight="1">
+    <row r="48" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>45965.512662037036</v>
       </c>
@@ -12675,7 +12640,7 @@
       <c r="AM48" s="6"/>
       <c r="AN48" s="6"/>
     </row>
-    <row r="49" spans="1:40" ht="15.75" customHeight="1">
+    <row r="49" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
         <v>45965.874374999999</v>
       </c>
@@ -12713,7 +12678,7 @@
         <v>9842445404</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>2056</v>
+        <v>2049</v>
       </c>
       <c r="N49" s="9" t="s">
         <v>346</v>
@@ -12781,7 +12746,7 @@
       <c r="AM49" s="13"/>
       <c r="AN49" s="13"/>
     </row>
-    <row r="50" spans="1:40" ht="15.75" customHeight="1">
+    <row r="50" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>45966.385312500002</v>
       </c>
@@ -12822,7 +12787,7 @@
         <v>354</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>2057</v>
+        <v>2050</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>57</v>
@@ -12885,7 +12850,7 @@
       <c r="AM50" s="6"/>
       <c r="AN50" s="6"/>
     </row>
-    <row r="51" spans="1:40" ht="15.75" customHeight="1">
+    <row r="51" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
         <v>45966.389178240737</v>
       </c>
@@ -12989,7 +12954,7 @@
       <c r="AM51" s="13"/>
       <c r="AN51" s="13"/>
     </row>
-    <row r="52" spans="1:40" ht="15.75" customHeight="1">
+    <row r="52" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>45966.392407407409</v>
       </c>
@@ -13093,7 +13058,7 @@
       <c r="AM52" s="6"/>
       <c r="AN52" s="6"/>
     </row>
-    <row r="53" spans="1:40" ht="15.75" customHeight="1">
+    <row r="53" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
         <v>45966.418391203704</v>
       </c>
@@ -13197,7 +13162,7 @@
       <c r="AM53" s="13"/>
       <c r="AN53" s="13"/>
     </row>
-    <row r="54" spans="1:40" ht="15.75" customHeight="1">
+    <row r="54" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>45966.540497685186</v>
       </c>
@@ -13238,7 +13203,7 @@
         <v>376</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>2058</v>
+        <v>2051</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>57</v>
@@ -13301,7 +13266,7 @@
       <c r="AM54" s="6"/>
       <c r="AN54" s="6"/>
     </row>
-    <row r="55" spans="1:40" ht="15.75" customHeight="1">
+    <row r="55" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
         <v>45966.62300925926</v>
       </c>
@@ -13411,7 +13376,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="56" spans="1:40" ht="15.75" customHeight="1">
+    <row r="56" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>45966.626886574071</v>
       </c>
@@ -13515,7 +13480,7 @@
       <c r="AM56" s="6"/>
       <c r="AN56" s="6"/>
     </row>
-    <row r="57" spans="1:40" ht="15.75" customHeight="1">
+    <row r="57" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
         <v>45966.640393518515</v>
       </c>
@@ -13553,7 +13518,7 @@
         <v>9865841473</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>2059</v>
+        <v>2052</v>
       </c>
       <c r="N57" s="9" t="s">
         <v>400</v>
@@ -13618,12 +13583,12 @@
       <c r="AJ57" s="13"/>
       <c r="AK57" s="13"/>
       <c r="AL57" s="12" t="s">
-        <v>2060</v>
+        <v>2053</v>
       </c>
       <c r="AM57" s="13"/>
       <c r="AN57" s="13"/>
     </row>
-    <row r="58" spans="1:40" ht="24" customHeight="1">
+    <row r="58" spans="1:40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>45967.46361111111</v>
       </c>
@@ -13733,7 +13698,7 @@
       </c>
       <c r="AN58" s="6"/>
     </row>
-    <row r="59" spans="1:40" ht="15.75" customHeight="1">
+    <row r="59" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
         <v>45967.559479166666</v>
       </c>
@@ -13771,7 +13736,7 @@
         <v>9994020894</v>
       </c>
       <c r="M59" s="9" t="s">
-        <v>2061</v>
+        <v>2054</v>
       </c>
       <c r="N59" s="9" t="s">
         <v>560</v>
@@ -13839,7 +13804,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="60" spans="1:40" ht="15.75" customHeight="1">
+    <row r="60" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>45967.610891203702</v>
       </c>
@@ -13945,7 +13910,7 @@
       <c r="AM60" s="6"/>
       <c r="AN60" s="6"/>
     </row>
-    <row r="61" spans="1:40" ht="15.75" customHeight="1">
+    <row r="61" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
         <v>45967.617152777777</v>
       </c>
@@ -14049,7 +14014,7 @@
       <c r="AM61" s="13"/>
       <c r="AN61" s="13"/>
     </row>
-    <row r="62" spans="1:40" ht="15.75" customHeight="1">
+    <row r="62" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>45967.620428240742</v>
       </c>
@@ -14090,7 +14055,7 @@
         <v>586</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>2062</v>
+        <v>2055</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>57</v>
@@ -14153,7 +14118,7 @@
       <c r="AM62" s="6"/>
       <c r="AN62" s="6"/>
     </row>
-    <row r="63" spans="1:40" ht="15.75" customHeight="1">
+    <row r="63" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
         <v>45967.624560185184</v>
       </c>
@@ -14194,7 +14159,7 @@
         <v>594</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>2063</v>
+        <v>2056</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>57</v>
@@ -14259,7 +14224,7 @@
       <c r="AM63" s="13"/>
       <c r="AN63" s="13"/>
     </row>
-    <row r="64" spans="1:40" ht="15.75" customHeight="1">
+    <row r="64" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>45967.633842592593</v>
       </c>
@@ -14365,7 +14330,7 @@
       <c r="AM64" s="6"/>
       <c r="AN64" s="6"/>
     </row>
-    <row r="65" spans="1:40" ht="15.75" customHeight="1">
+    <row r="65" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
         <v>45967.635555555556</v>
       </c>
@@ -14471,7 +14436,7 @@
       <c r="AM65" s="13"/>
       <c r="AN65" s="13"/>
     </row>
-    <row r="66" spans="1:40" ht="15.75" customHeight="1">
+    <row r="66" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>45967.642025462963</v>
       </c>
@@ -14577,7 +14542,7 @@
       <c r="AM66" s="6"/>
       <c r="AN66" s="6"/>
     </row>
-    <row r="67" spans="1:40" ht="15.75" customHeight="1">
+    <row r="67" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
         <v>45967.643321759257</v>
       </c>
@@ -14681,7 +14646,7 @@
       <c r="AM67" s="13"/>
       <c r="AN67" s="13"/>
     </row>
-    <row r="68" spans="1:40" ht="15.75" customHeight="1">
+    <row r="68" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>45967.645590277774</v>
       </c>
@@ -14752,7 +14717,7 @@
         <v>45325</v>
       </c>
       <c r="X68" s="2" t="s">
-        <v>2064</v>
+        <v>2057</v>
       </c>
       <c r="Y68" s="2" t="s">
         <v>11</v>
@@ -14785,7 +14750,7 @@
       <c r="AM68" s="6"/>
       <c r="AN68" s="6"/>
     </row>
-    <row r="69" spans="1:40" ht="15.75" customHeight="1">
+    <row r="69" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
         <v>45967.695185185185</v>
       </c>
@@ -14823,10 +14788,10 @@
         <v>8870006474</v>
       </c>
       <c r="M69" s="9" t="s">
-        <v>2065</v>
+        <v>2058</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>2066</v>
+        <v>2059</v>
       </c>
       <c r="O69" s="9" t="s">
         <v>57</v>
@@ -14889,7 +14854,7 @@
       <c r="AM69" s="13"/>
       <c r="AN69" s="13"/>
     </row>
-    <row r="70" spans="1:40" ht="15.75" customHeight="1">
+    <row r="70" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>45968.390150462961</v>
       </c>
@@ -14960,7 +14925,7 @@
         <v>44681</v>
       </c>
       <c r="X70" s="2" t="s">
-        <v>2067</v>
+        <v>2060</v>
       </c>
       <c r="Y70" s="2" t="s">
         <v>11</v>
@@ -14993,7 +14958,7 @@
       <c r="AM70" s="6"/>
       <c r="AN70" s="6"/>
     </row>
-    <row r="71" spans="1:40" ht="15.75" customHeight="1">
+    <row r="71" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
         <v>45968.459675925929</v>
       </c>
@@ -15031,10 +14996,10 @@
         <v>8973764197</v>
       </c>
       <c r="M71" s="9" t="s">
-        <v>2068</v>
+        <v>2061</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>2069</v>
+        <v>2062</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>57</v>
@@ -15064,7 +15029,7 @@
         <v>45250</v>
       </c>
       <c r="X71" s="9" t="s">
-        <v>2070</v>
+        <v>2063</v>
       </c>
       <c r="Y71" s="9" t="s">
         <v>11</v>
@@ -15099,7 +15064,7 @@
       <c r="AM71" s="13"/>
       <c r="AN71" s="13"/>
     </row>
-    <row r="72" spans="1:40" ht="15.75" customHeight="1">
+    <row r="72" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>45968.466990740744</v>
       </c>
@@ -15140,7 +15105,7 @@
         <v>655</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>2071</v>
+        <v>2064</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>57</v>
@@ -15203,7 +15168,7 @@
       <c r="AM72" s="6"/>
       <c r="AN72" s="6"/>
     </row>
-    <row r="73" spans="1:40" ht="15.75" customHeight="1">
+    <row r="73" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
         <v>45968.480254629627</v>
       </c>
@@ -15244,7 +15209,7 @@
         <v>567</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>2072</v>
+        <v>2065</v>
       </c>
       <c r="O73" s="9" t="s">
         <v>57</v>
@@ -15309,7 +15274,7 @@
       <c r="AM73" s="13"/>
       <c r="AN73" s="13"/>
     </row>
-    <row r="74" spans="1:40" ht="15.75" customHeight="1">
+    <row r="74" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>45968.601412037038</v>
       </c>
@@ -15415,7 +15380,7 @@
       <c r="AM74" s="6"/>
       <c r="AN74" s="6"/>
     </row>
-    <row r="75" spans="1:40" ht="15.75" customHeight="1">
+    <row r="75" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
         <v>45968.787569444445</v>
       </c>
@@ -15519,7 +15484,7 @@
       <c r="AM75" s="13"/>
       <c r="AN75" s="13"/>
     </row>
-    <row r="76" spans="1:40" ht="15.75" customHeight="1">
+    <row r="76" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>45969.473912037036</v>
       </c>
@@ -15560,7 +15525,7 @@
         <v>681</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>2073</v>
+        <v>2066</v>
       </c>
       <c r="O76" s="2" t="s">
         <v>57</v>
@@ -15625,7 +15590,7 @@
       <c r="AM76" s="6"/>
       <c r="AN76" s="6"/>
     </row>
-    <row r="77" spans="1:40" ht="15.75" customHeight="1">
+    <row r="77" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
         <v>45971.35670138889</v>
       </c>
@@ -15663,10 +15628,10 @@
         <v>9789443655</v>
       </c>
       <c r="M77" s="9" t="s">
-        <v>2074</v>
+        <v>2067</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>2075</v>
+        <v>2068</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>57</v>
@@ -15729,7 +15694,7 @@
       <c r="AM77" s="13"/>
       <c r="AN77" s="13"/>
     </row>
-    <row r="78" spans="1:40" ht="15.75" customHeight="1">
+    <row r="78" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>45972.659039351849</v>
       </c>
@@ -15833,7 +15798,7 @@
       <c r="AM78" s="6"/>
       <c r="AN78" s="6"/>
     </row>
-    <row r="79" spans="1:40" ht="15.75" customHeight="1">
+    <row r="79" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
         <v>45973.38857638889</v>
       </c>
@@ -15874,7 +15839,7 @@
         <v>699</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>2076</v>
+        <v>2069</v>
       </c>
       <c r="O79" s="9" t="s">
         <v>57</v>
@@ -15937,7 +15902,7 @@
       <c r="AM79" s="13"/>
       <c r="AN79" s="13"/>
     </row>
-    <row r="80" spans="1:40" ht="15.75" customHeight="1">
+    <row r="80" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>45973.42355324074</v>
       </c>
@@ -15975,10 +15940,10 @@
         <v>9842103319</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>2077</v>
+        <v>2070</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>2078</v>
+        <v>2071</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>361</v>
@@ -16043,7 +16008,7 @@
       <c r="AM80" s="6"/>
       <c r="AN80" s="6"/>
     </row>
-    <row r="81" spans="1:40" ht="15.75" customHeight="1">
+    <row r="81" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
         <v>45973.453125</v>
       </c>
@@ -16084,7 +16049,7 @@
         <v>711</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>2079</v>
+        <v>2072</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>57</v>
@@ -16114,7 +16079,7 @@
         <v>45352</v>
       </c>
       <c r="X81" s="9" t="s">
-        <v>2080</v>
+        <v>2073</v>
       </c>
       <c r="Y81" s="9" t="s">
         <v>11</v>
@@ -16127,7 +16092,7 @@
       </c>
       <c r="AB81" s="13"/>
       <c r="AC81" s="9" t="s">
-        <v>2183</v>
+        <v>2172</v>
       </c>
       <c r="AD81" s="9" t="s">
         <v>229</v>
@@ -16149,7 +16114,7 @@
       <c r="AM81" s="13"/>
       <c r="AN81" s="13"/>
     </row>
-    <row r="82" spans="1:40" ht="15.75" customHeight="1">
+    <row r="82" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>45973.487337962964</v>
       </c>
@@ -16255,7 +16220,7 @@
       <c r="AM82" s="6"/>
       <c r="AN82" s="6"/>
     </row>
-    <row r="83" spans="1:40" ht="15.75" customHeight="1">
+    <row r="83" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="8">
         <v>45973.493680555555</v>
       </c>
@@ -16296,7 +16261,7 @@
         <v>725</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>2081</v>
+        <v>2074</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>78</v>
@@ -16359,7 +16324,7 @@
       <c r="AM83" s="13"/>
       <c r="AN83" s="13"/>
     </row>
-    <row r="84" spans="1:40" ht="15.75" customHeight="1">
+    <row r="84" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>45973.499756944446</v>
       </c>
@@ -16461,7 +16426,7 @@
       <c r="AM84" s="6"/>
       <c r="AN84" s="6"/>
     </row>
-    <row r="85" spans="1:40" ht="15.75" customHeight="1">
+    <row r="85" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="8">
         <v>45973.53</v>
       </c>
@@ -16532,7 +16497,7 @@
         <v>45954</v>
       </c>
       <c r="X85" s="9" t="s">
-        <v>2082</v>
+        <v>2075</v>
       </c>
       <c r="Y85" s="9" t="s">
         <v>11</v>
@@ -16545,7 +16510,7 @@
       </c>
       <c r="AB85" s="13"/>
       <c r="AC85" s="9" t="s">
-        <v>2083</v>
+        <v>2076</v>
       </c>
       <c r="AD85" s="13"/>
       <c r="AE85" s="9" t="s">
@@ -16565,7 +16530,7 @@
       <c r="AM85" s="13"/>
       <c r="AN85" s="13"/>
     </row>
-    <row r="86" spans="1:40" ht="15.75" customHeight="1">
+    <row r="86" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>45973.579444444447</v>
       </c>
@@ -16669,7 +16634,7 @@
       <c r="AM86" s="6"/>
       <c r="AN86" s="6"/>
     </row>
-    <row r="87" spans="1:40" ht="15.75" customHeight="1">
+    <row r="87" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="8">
         <v>45973.586597222224</v>
       </c>
@@ -16710,7 +16675,7 @@
         <v>225</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>2084</v>
+        <v>2077</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>57</v>
@@ -16775,7 +16740,7 @@
       <c r="AM87" s="13"/>
       <c r="AN87" s="13"/>
     </row>
-    <row r="88" spans="1:40" ht="15.75" customHeight="1">
+    <row r="88" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>45973.606805555559</v>
       </c>
@@ -16879,7 +16844,7 @@
       <c r="AM88" s="6"/>
       <c r="AN88" s="6"/>
     </row>
-    <row r="89" spans="1:40" ht="15.75" customHeight="1">
+    <row r="89" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="8">
         <v>45973.627118055556</v>
       </c>
@@ -16920,7 +16885,7 @@
         <v>759</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>2085</v>
+        <v>2078</v>
       </c>
       <c r="O89" s="9" t="s">
         <v>57</v>
@@ -16983,7 +16948,7 @@
       <c r="AM89" s="13"/>
       <c r="AN89" s="13"/>
     </row>
-    <row r="90" spans="1:40" ht="15.75" customHeight="1">
+    <row r="90" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>45973.630613425928</v>
       </c>
@@ -17087,7 +17052,7 @@
       <c r="AM90" s="6"/>
       <c r="AN90" s="6"/>
     </row>
-    <row r="91" spans="1:40" ht="15.75" customHeight="1">
+    <row r="91" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="8">
         <v>45973.637025462966</v>
       </c>
@@ -17191,7 +17156,7 @@
       <c r="AM91" s="13"/>
       <c r="AN91" s="13"/>
     </row>
-    <row r="92" spans="1:40" ht="15.75" customHeight="1">
+    <row r="92" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>45973.652430555558</v>
       </c>
@@ -17297,7 +17262,7 @@
       <c r="AM92" s="6"/>
       <c r="AN92" s="6"/>
     </row>
-    <row r="93" spans="1:40" ht="15.75" customHeight="1">
+    <row r="93" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="8">
         <v>45973.657650462963</v>
       </c>
@@ -17335,10 +17300,10 @@
         <v>9952541163</v>
       </c>
       <c r="M93" s="9" t="s">
-        <v>2086</v>
+        <v>2079</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>2087</v>
+        <v>2080</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>57</v>
@@ -17403,7 +17368,7 @@
       <c r="AM93" s="13"/>
       <c r="AN93" s="13"/>
     </row>
-    <row r="94" spans="1:40" ht="15.75" customHeight="1">
+    <row r="94" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>45973.66611111111</v>
       </c>
@@ -17511,7 +17476,7 @@
       </c>
       <c r="AN94" s="6"/>
     </row>
-    <row r="95" spans="1:40" ht="15.75" customHeight="1">
+    <row r="95" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="8">
         <v>45973.691122685188</v>
       </c>
@@ -17617,7 +17582,7 @@
       </c>
       <c r="AN95" s="13"/>
     </row>
-    <row r="96" spans="1:40" ht="15.75" customHeight="1">
+    <row r="96" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>45973.703530092593</v>
       </c>
@@ -17721,7 +17686,7 @@
       <c r="AM96" s="6"/>
       <c r="AN96" s="6"/>
     </row>
-    <row r="97" spans="1:40" ht="15.75" customHeight="1">
+    <row r="97" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="8">
         <v>45974.3046875</v>
       </c>
@@ -17825,7 +17790,7 @@
       <c r="AM97" s="13"/>
       <c r="AN97" s="13"/>
     </row>
-    <row r="98" spans="1:40" ht="15.75" customHeight="1">
+    <row r="98" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>45974.332615740743</v>
       </c>
@@ -17863,7 +17828,7 @@
         <v>9500799099</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>2088</v>
+        <v>2081</v>
       </c>
       <c r="N98" s="2" t="s">
         <v>826</v>
@@ -17929,7 +17894,7 @@
       <c r="AM98" s="6"/>
       <c r="AN98" s="6"/>
     </row>
-    <row r="99" spans="1:40" ht="15.75" customHeight="1">
+    <row r="99" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="8">
         <v>45974.383553240739</v>
       </c>
@@ -18035,7 +18000,7 @@
       <c r="AM99" s="13"/>
       <c r="AN99" s="13"/>
     </row>
-    <row r="100" spans="1:40" ht="15.75" customHeight="1">
+    <row r="100" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>45974.393182870372</v>
       </c>
@@ -18073,10 +18038,10 @@
         <v>8438103656</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>2089</v>
+        <v>2082</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>2090</v>
+        <v>2083</v>
       </c>
       <c r="O100" s="2" t="s">
         <v>57</v>
@@ -18141,7 +18106,7 @@
       <c r="AM100" s="6"/>
       <c r="AN100" s="6"/>
     </row>
-    <row r="101" spans="1:40" ht="15.75" customHeight="1">
+    <row r="101" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="8">
         <v>45974.406481481485</v>
       </c>
@@ -18182,7 +18147,7 @@
         <v>845</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>2091</v>
+        <v>2084</v>
       </c>
       <c r="O101" s="9" t="s">
         <v>57</v>
@@ -18245,7 +18210,7 @@
       <c r="AM101" s="13"/>
       <c r="AN101" s="13"/>
     </row>
-    <row r="102" spans="1:40" ht="15.75" customHeight="1">
+    <row r="102" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>45974.409050925926</v>
       </c>
@@ -18359,7 +18324,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="103" spans="1:40" ht="15.75" customHeight="1">
+    <row r="103" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8">
         <v>45974.417291666665</v>
       </c>
@@ -18463,7 +18428,7 @@
       <c r="AM103" s="13"/>
       <c r="AN103" s="13"/>
     </row>
-    <row r="104" spans="1:40" ht="15.75" customHeight="1">
+    <row r="104" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>45974.417326388888</v>
       </c>
@@ -18569,7 +18534,7 @@
       <c r="AM104" s="6"/>
       <c r="AN104" s="6"/>
     </row>
-    <row r="105" spans="1:40" ht="15.75" customHeight="1">
+    <row r="105" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="8">
         <v>45974.423506944448</v>
       </c>
@@ -18649,11 +18614,11 @@
         <v>739</v>
       </c>
       <c r="AA105" s="9" t="s">
-        <v>2184</v>
+        <v>2173</v>
       </c>
       <c r="AB105" s="13"/>
       <c r="AC105" s="9" t="s">
-        <v>2092</v>
+        <v>2085</v>
       </c>
       <c r="AD105" s="9" t="s">
         <v>881</v>
@@ -18677,7 +18642,7 @@
       </c>
       <c r="AN105" s="13"/>
     </row>
-    <row r="106" spans="1:40" ht="15.75" customHeight="1">
+    <row r="106" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>45974.42428240741</v>
       </c>
@@ -18781,7 +18746,7 @@
       <c r="AM106" s="6"/>
       <c r="AN106" s="6"/>
     </row>
-    <row r="107" spans="1:40" ht="15.75" customHeight="1">
+    <row r="107" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="8">
         <v>45974.435567129629</v>
       </c>
@@ -18822,7 +18787,7 @@
         <v>894</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>2093</v>
+        <v>2086</v>
       </c>
       <c r="O107" s="9" t="s">
         <v>57</v>
@@ -18885,7 +18850,7 @@
       <c r="AM107" s="13"/>
       <c r="AN107" s="13"/>
     </row>
-    <row r="108" spans="1:40" ht="15.75" customHeight="1">
+    <row r="108" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>45974.464259259257</v>
       </c>
@@ -18991,7 +18956,7 @@
       <c r="AM108" s="6"/>
       <c r="AN108" s="6"/>
     </row>
-    <row r="109" spans="1:40" ht="15.75" customHeight="1">
+    <row r="109" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="8">
         <v>45974.506307870368</v>
       </c>
@@ -19032,7 +18997,7 @@
         <v>907</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>2094</v>
+        <v>2087</v>
       </c>
       <c r="O109" s="9" t="s">
         <v>78</v>
@@ -19095,7 +19060,7 @@
       <c r="AM109" s="13"/>
       <c r="AN109" s="13"/>
     </row>
-    <row r="110" spans="1:40" ht="15.75" customHeight="1">
+    <row r="110" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>45974.516064814816</v>
       </c>
@@ -19179,7 +19144,7 @@
       </c>
       <c r="AB110" s="6"/>
       <c r="AC110" s="2" t="s">
-        <v>2095</v>
+        <v>2088</v>
       </c>
       <c r="AD110" s="6"/>
       <c r="AE110" s="2" t="s">
@@ -19199,7 +19164,7 @@
       <c r="AM110" s="6"/>
       <c r="AN110" s="6"/>
     </row>
-    <row r="111" spans="1:40" ht="15.75" customHeight="1">
+    <row r="111" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="8">
         <v>45974.594675925924</v>
       </c>
@@ -19305,7 +19270,7 @@
       </c>
       <c r="AN111" s="13"/>
     </row>
-    <row r="112" spans="1:40" ht="15.75" customHeight="1">
+    <row r="112" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>45974.605011574073</v>
       </c>
@@ -19411,7 +19376,7 @@
       <c r="AM112" s="6"/>
       <c r="AN112" s="6"/>
     </row>
-    <row r="113" spans="1:40" ht="15.75" customHeight="1">
+    <row r="113" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="8">
         <v>45974.619108796294</v>
       </c>
@@ -19515,7 +19480,7 @@
       <c r="AM113" s="13"/>
       <c r="AN113" s="13"/>
     </row>
-    <row r="114" spans="1:40" ht="15.75" customHeight="1">
+    <row r="114" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>45974.62736111111</v>
       </c>
@@ -19623,7 +19588,7 @@
       <c r="AM114" s="6"/>
       <c r="AN114" s="6"/>
     </row>
-    <row r="115" spans="1:40" ht="15.75" customHeight="1">
+    <row r="115" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="8">
         <v>45974.62972222222</v>
       </c>
@@ -19703,10 +19668,10 @@
         <v>739</v>
       </c>
       <c r="AA115" s="9" t="s">
-        <v>2185</v>
+        <v>2174</v>
       </c>
       <c r="AB115" s="9" t="s">
-        <v>2096</v>
+        <v>2089</v>
       </c>
       <c r="AC115" s="9" t="s">
         <v>209</v>
@@ -19731,7 +19696,7 @@
       <c r="AM115" s="13"/>
       <c r="AN115" s="13"/>
     </row>
-    <row r="116" spans="1:40" ht="15.75" customHeight="1">
+    <row r="116" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>45974.634756944448</v>
       </c>
@@ -19769,7 +19734,7 @@
         <v>9843841181</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>2097</v>
+        <v>2090</v>
       </c>
       <c r="N116" s="2" t="s">
         <v>956</v>
@@ -19837,7 +19802,7 @@
       <c r="AM116" s="6"/>
       <c r="AN116" s="6"/>
     </row>
-    <row r="117" spans="1:40" ht="15.75" customHeight="1">
+    <row r="117" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="8">
         <v>45974.639641203707</v>
       </c>
@@ -19875,7 +19840,7 @@
         <v>9443241424</v>
       </c>
       <c r="M117" s="9" t="s">
-        <v>2098</v>
+        <v>2091</v>
       </c>
       <c r="N117" s="9" t="s">
         <v>965</v>
@@ -19908,7 +19873,7 @@
         <v>43187</v>
       </c>
       <c r="X117" s="9" t="s">
-        <v>2099</v>
+        <v>2092</v>
       </c>
       <c r="Y117" s="9" t="s">
         <v>11</v>
@@ -19943,7 +19908,7 @@
       <c r="AM117" s="13"/>
       <c r="AN117" s="13"/>
     </row>
-    <row r="118" spans="1:40" ht="15.75" customHeight="1">
+    <row r="118" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>45975.367986111109</v>
       </c>
@@ -20049,7 +20014,7 @@
       <c r="AM118" s="6"/>
       <c r="AN118" s="6"/>
     </row>
-    <row r="119" spans="1:40" ht="15.75" customHeight="1">
+    <row r="119" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="8">
         <v>45975.375219907408</v>
       </c>
@@ -20155,7 +20120,7 @@
       <c r="AM119" s="13"/>
       <c r="AN119" s="13"/>
     </row>
-    <row r="120" spans="1:40" ht="15.75" customHeight="1">
+    <row r="120" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>45975.401122685187</v>
       </c>
@@ -20261,7 +20226,7 @@
       <c r="AM120" s="6"/>
       <c r="AN120" s="6"/>
     </row>
-    <row r="121" spans="1:40" ht="15.75" customHeight="1">
+    <row r="121" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="8">
         <v>45975.414409722223</v>
       </c>
@@ -20365,7 +20330,7 @@
       <c r="AM121" s="13"/>
       <c r="AN121" s="13"/>
     </row>
-    <row r="122" spans="1:40" ht="15.75" customHeight="1">
+    <row r="122" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>45975.419456018521</v>
       </c>
@@ -20403,7 +20368,7 @@
         <v>9884983543</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>2100</v>
+        <v>2093</v>
       </c>
       <c r="N122" s="2" t="s">
         <v>1003</v>
@@ -20469,7 +20434,7 @@
       <c r="AM122" s="6"/>
       <c r="AN122" s="6"/>
     </row>
-    <row r="123" spans="1:40" ht="15.75" customHeight="1">
+    <row r="123" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="8">
         <v>45975.426435185182</v>
       </c>
@@ -20507,7 +20472,7 @@
         <v>9585536854</v>
       </c>
       <c r="M123" s="9" t="s">
-        <v>2101</v>
+        <v>2094</v>
       </c>
       <c r="N123" s="9" t="s">
         <v>1009</v>
@@ -20573,7 +20538,7 @@
       <c r="AM123" s="13"/>
       <c r="AN123" s="13"/>
     </row>
-    <row r="124" spans="1:40" ht="15.75" customHeight="1">
+    <row r="124" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>45975.438136574077</v>
       </c>
@@ -20614,7 +20579,7 @@
         <v>1017</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>2102</v>
+        <v>2095</v>
       </c>
       <c r="O124" s="2" t="s">
         <v>57</v>
@@ -20677,7 +20642,7 @@
       <c r="AM124" s="6"/>
       <c r="AN124" s="6"/>
     </row>
-    <row r="125" spans="1:40" ht="15.75" customHeight="1">
+    <row r="125" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8">
         <v>45975.440763888888</v>
       </c>
@@ -20713,7 +20678,7 @@
         <v>9597484444</v>
       </c>
       <c r="M125" s="9" t="s">
-        <v>2103</v>
+        <v>2096</v>
       </c>
       <c r="N125" s="9" t="s">
         <v>1023</v>
@@ -20781,7 +20746,7 @@
       <c r="AM125" s="13"/>
       <c r="AN125" s="13"/>
     </row>
-    <row r="126" spans="1:40" ht="15.75" customHeight="1">
+    <row r="126" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>45975.442060185182</v>
       </c>
@@ -20885,7 +20850,7 @@
       <c r="AM126" s="6"/>
       <c r="AN126" s="6"/>
     </row>
-    <row r="127" spans="1:40" ht="15.75" customHeight="1">
+    <row r="127" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="8">
         <v>45975.49355324074</v>
       </c>
@@ -20923,7 +20888,7 @@
         <v>9943907528</v>
       </c>
       <c r="M127" s="9" t="s">
-        <v>2104</v>
+        <v>2097</v>
       </c>
       <c r="N127" s="9" t="s">
         <v>1038</v>
@@ -20999,7 +20964,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="128" spans="1:40" ht="15.75" customHeight="1">
+    <row r="128" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>45975.493923611109</v>
       </c>
@@ -21070,7 +21035,7 @@
         <v>45505</v>
       </c>
       <c r="X128" s="2" t="s">
-        <v>2105</v>
+        <v>2098</v>
       </c>
       <c r="Y128" s="2" t="s">
         <v>11</v>
@@ -21083,7 +21048,7 @@
       </c>
       <c r="AB128" s="6"/>
       <c r="AC128" s="2" t="s">
-        <v>2105</v>
+        <v>2098</v>
       </c>
       <c r="AD128" s="2" t="s">
         <v>1050</v>
@@ -21105,7 +21070,7 @@
       <c r="AM128" s="6"/>
       <c r="AN128" s="6"/>
     </row>
-    <row r="129" spans="1:40" ht="15.75" customHeight="1">
+    <row r="129" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="8">
         <v>45975.54855324074</v>
       </c>
@@ -21209,7 +21174,7 @@
       <c r="AM129" s="13"/>
       <c r="AN129" s="13"/>
     </row>
-    <row r="130" spans="1:40" ht="15.75" customHeight="1">
+    <row r="130" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>45975.615324074075</v>
       </c>
@@ -21250,7 +21215,7 @@
         <v>1060</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>2106</v>
+        <v>2099</v>
       </c>
       <c r="O130" s="2" t="s">
         <v>57</v>
@@ -21315,7 +21280,7 @@
       <c r="AM130" s="6"/>
       <c r="AN130" s="6"/>
     </row>
-    <row r="131" spans="1:40" ht="15.75" customHeight="1">
+    <row r="131" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="8">
         <v>45975.635601851849</v>
       </c>
@@ -21427,7 +21392,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="132" spans="1:40" ht="15.75" customHeight="1">
+    <row r="132" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>45975.643194444441</v>
       </c>
@@ -21468,7 +21433,7 @@
         <v>1078</v>
       </c>
       <c r="N132" s="2" t="s">
-        <v>2107</v>
+        <v>2100</v>
       </c>
       <c r="O132" s="2" t="s">
         <v>57</v>
@@ -21533,7 +21498,7 @@
       <c r="AM132" s="6"/>
       <c r="AN132" s="6"/>
     </row>
-    <row r="133" spans="1:40" ht="15.75" customHeight="1">
+    <row r="133" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="8">
         <v>45975.694756944446</v>
       </c>
@@ -21637,7 +21602,7 @@
       <c r="AM133" s="13"/>
       <c r="AN133" s="13"/>
     </row>
-    <row r="134" spans="1:40" ht="15.75" customHeight="1">
+    <row r="134" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>45975.972280092596</v>
       </c>
@@ -21675,10 +21640,10 @@
         <v>9994264019</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>2108</v>
+        <v>2101</v>
       </c>
       <c r="N134" s="2" t="s">
-        <v>2109</v>
+        <v>2102</v>
       </c>
       <c r="O134" s="2" t="s">
         <v>57</v>
@@ -21743,7 +21708,7 @@
       <c r="AM134" s="6"/>
       <c r="AN134" s="6"/>
     </row>
-    <row r="135" spans="1:40" ht="15.75" customHeight="1">
+    <row r="135" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="8">
         <v>45976.37872685185</v>
       </c>
@@ -21784,7 +21749,7 @@
         <v>1095</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>2110</v>
+        <v>2103</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>57</v>
@@ -21849,7 +21814,7 @@
       <c r="AM135" s="13"/>
       <c r="AN135" s="13"/>
     </row>
-    <row r="136" spans="1:40" ht="15.75" customHeight="1">
+    <row r="136" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>45976.633912037039</v>
       </c>
@@ -21890,7 +21855,7 @@
         <v>1102</v>
       </c>
       <c r="N136" s="2" t="s">
-        <v>2111</v>
+        <v>2104</v>
       </c>
       <c r="O136" s="2" t="s">
         <v>266</v>
@@ -21920,7 +21885,7 @@
         <v>44228</v>
       </c>
       <c r="X136" s="2" t="s">
-        <v>2112</v>
+        <v>2105</v>
       </c>
       <c r="Y136" s="2" t="s">
         <v>11</v>
@@ -21955,7 +21920,7 @@
       <c r="AM136" s="6"/>
       <c r="AN136" s="6"/>
     </row>
-    <row r="137" spans="1:40" ht="15.75" customHeight="1">
+    <row r="137" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8">
         <v>45978.611875000002</v>
       </c>
@@ -21996,7 +21961,7 @@
         <v>1222</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>2113</v>
+        <v>2106</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>57</v>
@@ -22061,7 +22026,7 @@
       <c r="AM137" s="13"/>
       <c r="AN137" s="13"/>
     </row>
-    <row r="138" spans="1:40" ht="15.75" customHeight="1">
+    <row r="138" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>45978.693738425929</v>
       </c>
@@ -22102,7 +22067,7 @@
         <v>1230</v>
       </c>
       <c r="N138" s="2" t="s">
-        <v>2114</v>
+        <v>2107</v>
       </c>
       <c r="O138" s="2" t="s">
         <v>1231</v>
@@ -22165,7 +22130,7 @@
       <c r="AM138" s="6"/>
       <c r="AN138" s="6"/>
     </row>
-    <row r="139" spans="1:40" ht="15.75" customHeight="1">
+    <row r="139" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="8">
         <v>45979.365844907406</v>
       </c>
@@ -22269,7 +22234,7 @@
       <c r="AM139" s="13"/>
       <c r="AN139" s="13"/>
     </row>
-    <row r="140" spans="1:40" ht="15.75" customHeight="1">
+    <row r="140" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>45979.369976851849</v>
       </c>
@@ -22373,7 +22338,7 @@
       <c r="AM140" s="6"/>
       <c r="AN140" s="6"/>
     </row>
-    <row r="141" spans="1:40" ht="15.75" customHeight="1">
+    <row r="141" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="8">
         <v>45979.371990740743</v>
       </c>
@@ -22411,7 +22376,7 @@
         <v>8189827034</v>
       </c>
       <c r="M141" s="9" t="s">
-        <v>2115</v>
+        <v>2108</v>
       </c>
       <c r="N141" s="9" t="s">
         <v>1252</v>
@@ -22479,7 +22444,7 @@
       <c r="AM141" s="13"/>
       <c r="AN141" s="13"/>
     </row>
-    <row r="142" spans="1:40" ht="15.75" customHeight="1">
+    <row r="142" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>45979.479664351849</v>
       </c>
@@ -22585,7 +22550,7 @@
       <c r="AM142" s="6"/>
       <c r="AN142" s="6"/>
     </row>
-    <row r="143" spans="1:40" ht="15.75" customHeight="1">
+    <row r="143" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="8">
         <v>45979.498854166668</v>
       </c>
@@ -22662,7 +22627,7 @@
         <v>11</v>
       </c>
       <c r="Z143" s="9" t="s">
-        <v>2182</v>
+        <v>2171</v>
       </c>
       <c r="AA143" s="9" t="s">
         <v>1675</v>
@@ -22691,7 +22656,7 @@
       <c r="AM143" s="13"/>
       <c r="AN143" s="13"/>
     </row>
-    <row r="144" spans="1:40" ht="15.75" customHeight="1">
+    <row r="144" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>45979.554236111115</v>
       </c>
@@ -22732,7 +22697,7 @@
         <v>1276</v>
       </c>
       <c r="N144" s="2" t="s">
-        <v>2116</v>
+        <v>2109</v>
       </c>
       <c r="O144" s="2" t="s">
         <v>57</v>
@@ -22795,7 +22760,7 @@
       <c r="AM144" s="6"/>
       <c r="AN144" s="6"/>
     </row>
-    <row r="145" spans="1:40" ht="15.75" customHeight="1">
+    <row r="145" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="8">
         <v>45980.316782407404</v>
       </c>
@@ -22875,7 +22840,7 @@
         <v>739</v>
       </c>
       <c r="AA145" s="9" t="s">
-        <v>2186</v>
+        <v>2175</v>
       </c>
       <c r="AB145" s="13"/>
       <c r="AC145" s="9" t="s">
@@ -22899,7 +22864,7 @@
       <c r="AM145" s="13"/>
       <c r="AN145" s="13"/>
     </row>
-    <row r="146" spans="1:40" ht="15.75" customHeight="1">
+    <row r="146" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>45980.370381944442</v>
       </c>
@@ -23001,7 +22966,7 @@
       <c r="AM146" s="6"/>
       <c r="AN146" s="6"/>
     </row>
-    <row r="147" spans="1:40" ht="15.75" customHeight="1">
+    <row r="147" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="8">
         <v>45980.380636574075</v>
       </c>
@@ -23039,7 +23004,7 @@
         <v>9894147545</v>
       </c>
       <c r="M147" s="9" t="s">
-        <v>2117</v>
+        <v>2110</v>
       </c>
       <c r="N147" s="9" t="s">
         <v>1300</v>
@@ -23105,7 +23070,7 @@
       <c r="AM147" s="13"/>
       <c r="AN147" s="13"/>
     </row>
-    <row r="148" spans="1:40" ht="15.75" customHeight="1">
+    <row r="148" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>45980.428622685184</v>
       </c>
@@ -23209,7 +23174,7 @@
       <c r="AM148" s="6"/>
       <c r="AN148" s="6"/>
     </row>
-    <row r="149" spans="1:40" ht="15.75" customHeight="1">
+    <row r="149" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="8">
         <v>45980.460347222222</v>
       </c>
@@ -23247,7 +23212,7 @@
         <v>9894593245</v>
       </c>
       <c r="M149" s="9" t="s">
-        <v>2118</v>
+        <v>2111</v>
       </c>
       <c r="N149" s="9" t="s">
         <v>1315</v>
@@ -23313,7 +23278,7 @@
       <c r="AM149" s="13"/>
       <c r="AN149" s="13"/>
     </row>
-    <row r="150" spans="1:40" ht="15.75" customHeight="1">
+    <row r="150" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>45980.519803240742</v>
       </c>
@@ -23384,7 +23349,7 @@
         <v>45980</v>
       </c>
       <c r="X150" s="2" t="s">
-        <v>2119</v>
+        <v>2112</v>
       </c>
       <c r="Y150" s="2" t="s">
         <v>11</v>
@@ -23419,7 +23384,7 @@
       <c r="AM150" s="6"/>
       <c r="AN150" s="6"/>
     </row>
-    <row r="151" spans="1:40" ht="15.75" customHeight="1">
+    <row r="151" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="8">
         <v>45980.595300925925</v>
       </c>
@@ -23460,7 +23425,7 @@
         <v>1329</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>2120</v>
+        <v>2113</v>
       </c>
       <c r="O151" s="9" t="s">
         <v>57</v>
@@ -23525,7 +23490,7 @@
       <c r="AM151" s="13"/>
       <c r="AN151" s="13"/>
     </row>
-    <row r="152" spans="1:40" ht="15.75" customHeight="1">
+    <row r="152" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>45981.411817129629</v>
       </c>
@@ -23629,7 +23594,7 @@
       <c r="AM152" s="6"/>
       <c r="AN152" s="6"/>
     </row>
-    <row r="153" spans="1:40" ht="15.75" customHeight="1">
+    <row r="153" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="8">
         <v>45981.414537037039</v>
       </c>
@@ -23670,7 +23635,7 @@
         <v>1343</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>2121</v>
+        <v>2114</v>
       </c>
       <c r="O153" s="9" t="s">
         <v>1344</v>
@@ -23691,7 +23656,7 @@
         <v>1345</v>
       </c>
       <c r="U153" s="9" t="s">
-        <v>2187</v>
+        <v>2176</v>
       </c>
       <c r="V153" s="9" t="s">
         <v>42</v>
@@ -23700,7 +23665,7 @@
         <v>43958</v>
       </c>
       <c r="X153" s="9" t="s">
-        <v>2188</v>
+        <v>2177</v>
       </c>
       <c r="Y153" s="9" t="s">
         <v>11</v>
@@ -23713,7 +23678,7 @@
       </c>
       <c r="AB153" s="13"/>
       <c r="AC153" s="9" t="s">
-        <v>2189</v>
+        <v>2178</v>
       </c>
       <c r="AD153" s="9" t="s">
         <v>1346</v>
@@ -23735,7 +23700,7 @@
       <c r="AM153" s="13"/>
       <c r="AN153" s="13"/>
     </row>
-    <row r="154" spans="1:40" ht="15.75" customHeight="1">
+    <row r="154" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>45981.63208333333</v>
       </c>
@@ -23843,7 +23808,7 @@
       <c r="AM154" s="6"/>
       <c r="AN154" s="6"/>
     </row>
-    <row r="155" spans="1:40" ht="15.75" customHeight="1">
+    <row r="155" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <v>45981.752314814818</v>
       </c>
@@ -23881,7 +23846,7 @@
         <v>8144380594</v>
       </c>
       <c r="M155" s="9" t="s">
-        <v>2122</v>
+        <v>2115</v>
       </c>
       <c r="N155" s="9" t="s">
         <v>1359</v>
@@ -23947,7 +23912,7 @@
       <c r="AM155" s="13"/>
       <c r="AN155" s="13"/>
     </row>
-    <row r="156" spans="1:40" ht="15.75" customHeight="1">
+    <row r="156" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>45981.991898148146</v>
       </c>
@@ -24051,7 +24016,7 @@
       <c r="AM156" s="6"/>
       <c r="AN156" s="6"/>
     </row>
-    <row r="157" spans="1:40" ht="15.75" customHeight="1">
+    <row r="157" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <v>45982.393425925926</v>
       </c>
@@ -24089,10 +24054,10 @@
         <v>9003056068</v>
       </c>
       <c r="M157" s="9" t="s">
-        <v>2123</v>
+        <v>2116</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>2124</v>
+        <v>2117</v>
       </c>
       <c r="O157" s="9" t="s">
         <v>57</v>
@@ -24155,7 +24120,7 @@
       <c r="AM157" s="13"/>
       <c r="AN157" s="13"/>
     </row>
-    <row r="158" spans="1:40" ht="15.75" customHeight="1">
+    <row r="158" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>45982.411249999997</v>
       </c>
@@ -24193,7 +24158,7 @@
         <v>9445972712</v>
       </c>
       <c r="M158" s="2" t="s">
-        <v>2125</v>
+        <v>2118</v>
       </c>
       <c r="N158" s="2" t="s">
         <v>1379</v>
@@ -24263,7 +24228,7 @@
       <c r="AM158" s="6"/>
       <c r="AN158" s="6"/>
     </row>
-    <row r="159" spans="1:40" ht="15.75" customHeight="1">
+    <row r="159" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <v>45982.422164351854</v>
       </c>
@@ -24371,7 +24336,7 @@
       </c>
       <c r="AN159" s="13"/>
     </row>
-    <row r="160" spans="1:40" ht="15.75" customHeight="1">
+    <row r="160" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>45982.430243055554</v>
       </c>
@@ -24442,7 +24407,7 @@
         <v>44203</v>
       </c>
       <c r="X160" s="2" t="s">
-        <v>2126</v>
+        <v>2119</v>
       </c>
       <c r="Y160" s="2" t="s">
         <v>11</v>
@@ -24477,7 +24442,7 @@
       <c r="AM160" s="6"/>
       <c r="AN160" s="6"/>
     </row>
-    <row r="161" spans="1:40" ht="15.75" customHeight="1">
+    <row r="161" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <v>45982.431990740741</v>
       </c>
@@ -24561,7 +24526,7 @@
       </c>
       <c r="AB161" s="13"/>
       <c r="AC161" s="9" t="s">
-        <v>2127</v>
+        <v>2120</v>
       </c>
       <c r="AD161" s="9" t="s">
         <v>1412</v>
@@ -24583,7 +24548,7 @@
       <c r="AM161" s="13"/>
       <c r="AN161" s="13"/>
     </row>
-    <row r="162" spans="1:40" ht="15.75" customHeight="1">
+    <row r="162" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>45982.458055555559</v>
       </c>
@@ -24654,7 +24619,7 @@
         <v>45607</v>
       </c>
       <c r="X162" s="2" t="s">
-        <v>2128</v>
+        <v>2121</v>
       </c>
       <c r="Y162" s="2" t="s">
         <v>11</v>
@@ -24689,7 +24654,7 @@
       <c r="AM162" s="6"/>
       <c r="AN162" s="6"/>
     </row>
-    <row r="163" spans="1:40" ht="15.75" customHeight="1">
+    <row r="163" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <v>45982.495347222219</v>
       </c>
@@ -24727,7 +24692,7 @@
         <v>9790628434</v>
       </c>
       <c r="M163" s="9" t="s">
-        <v>2129</v>
+        <v>2122</v>
       </c>
       <c r="N163" s="9" t="s">
         <v>1424</v>
@@ -24793,7 +24758,7 @@
       <c r="AM163" s="13"/>
       <c r="AN163" s="13"/>
     </row>
-    <row r="164" spans="1:40" ht="15.75" customHeight="1">
+    <row r="164" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>45982.528078703705</v>
       </c>
@@ -24831,19 +24796,19 @@
         <v>9899936858</v>
       </c>
       <c r="M164" s="2" t="s">
-        <v>2130</v>
+        <v>2123</v>
       </c>
       <c r="N164" s="2" t="s">
         <v>1431</v>
       </c>
       <c r="O164" s="2" t="s">
-        <v>2181</v>
+        <v>2170</v>
       </c>
       <c r="P164" s="3">
         <v>600014</v>
       </c>
       <c r="Q164" s="2" t="s">
-        <v>2181</v>
+        <v>2170</v>
       </c>
       <c r="R164" s="2" t="s">
         <v>39</v>
@@ -24897,7 +24862,7 @@
       <c r="AM164" s="6"/>
       <c r="AN164" s="6"/>
     </row>
-    <row r="165" spans="1:40" ht="15.75" customHeight="1">
+    <row r="165" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="8">
         <v>45982.531574074077</v>
       </c>
@@ -25001,7 +24966,7 @@
       <c r="AM165" s="13"/>
       <c r="AN165" s="13"/>
     </row>
-    <row r="166" spans="1:40" ht="15.75" customHeight="1">
+    <row r="166" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>45982.542037037034</v>
       </c>
@@ -25039,7 +25004,7 @@
         <v>9626913491</v>
       </c>
       <c r="M166" s="2" t="s">
-        <v>2131</v>
+        <v>2124</v>
       </c>
       <c r="N166" s="2" t="s">
         <v>1446</v>
@@ -25105,7 +25070,7 @@
       <c r="AM166" s="6"/>
       <c r="AN166" s="6"/>
     </row>
-    <row r="167" spans="1:40" ht="15.75" customHeight="1">
+    <row r="167" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="8">
         <v>45982.548090277778</v>
       </c>
@@ -25143,10 +25108,10 @@
         <v>8870946952</v>
       </c>
       <c r="M167" s="9" t="s">
-        <v>2132</v>
+        <v>2125</v>
       </c>
       <c r="N167" s="9" t="s">
-        <v>2133</v>
+        <v>2126</v>
       </c>
       <c r="O167" s="9" t="s">
         <v>57</v>
@@ -25211,7 +25176,7 @@
       <c r="AM167" s="13"/>
       <c r="AN167" s="13"/>
     </row>
-    <row r="168" spans="1:40" ht="15.75" customHeight="1">
+    <row r="168" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>45982.551319444443</v>
       </c>
@@ -25249,10 +25214,10 @@
         <v>9443357653</v>
       </c>
       <c r="M168" s="2" t="s">
-        <v>2134</v>
+        <v>2127</v>
       </c>
       <c r="N168" s="2" t="s">
-        <v>2135</v>
+        <v>2128</v>
       </c>
       <c r="O168" s="2" t="s">
         <v>57</v>
@@ -25282,7 +25247,7 @@
         <v>42109</v>
       </c>
       <c r="X168" s="2" t="s">
-        <v>2136</v>
+        <v>2129</v>
       </c>
       <c r="Y168" s="2" t="s">
         <v>11</v>
@@ -25295,7 +25260,7 @@
       </c>
       <c r="AB168" s="6"/>
       <c r="AC168" s="2" t="s">
-        <v>2137</v>
+        <v>2130</v>
       </c>
       <c r="AD168" s="2" t="s">
         <v>1462</v>
@@ -25319,7 +25284,7 @@
       <c r="AM168" s="6"/>
       <c r="AN168" s="6"/>
     </row>
-    <row r="169" spans="1:40" ht="15.75" customHeight="1">
+    <row r="169" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="8">
         <v>45982.616423611114</v>
       </c>
@@ -25360,7 +25325,7 @@
         <v>1466</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>2138</v>
+        <v>2131</v>
       </c>
       <c r="O169" s="9" t="s">
         <v>57</v>
@@ -25425,7 +25390,7 @@
       <c r="AM169" s="13"/>
       <c r="AN169" s="13"/>
     </row>
-    <row r="170" spans="1:40" ht="15.75" customHeight="1">
+    <row r="170" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>45982.621087962965</v>
       </c>
@@ -25529,7 +25494,7 @@
       <c r="AM170" s="6"/>
       <c r="AN170" s="6"/>
     </row>
-    <row r="171" spans="1:40" ht="15.75" customHeight="1">
+    <row r="171" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="8">
         <v>45982.628761574073</v>
       </c>
@@ -25567,7 +25532,7 @@
         <v>9786497001</v>
       </c>
       <c r="M171" s="9" t="s">
-        <v>2139</v>
+        <v>2132</v>
       </c>
       <c r="N171" s="9" t="s">
         <v>1485</v>
@@ -25637,7 +25602,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="172" spans="1:40" ht="15.75" customHeight="1">
+    <row r="172" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>45982.656342592592</v>
       </c>
@@ -25678,7 +25643,7 @@
         <v>1495</v>
       </c>
       <c r="N172" s="2" t="s">
-        <v>2140</v>
+        <v>2133</v>
       </c>
       <c r="O172" s="2" t="s">
         <v>78</v>
@@ -25708,7 +25673,7 @@
         <v>45681</v>
       </c>
       <c r="X172" s="2" t="s">
-        <v>2141</v>
+        <v>2134</v>
       </c>
       <c r="Y172" s="2" t="s">
         <v>11</v>
@@ -25721,7 +25686,7 @@
       </c>
       <c r="AB172" s="6"/>
       <c r="AC172" s="2" t="s">
-        <v>2142</v>
+        <v>2135</v>
       </c>
       <c r="AD172" s="2" t="s">
         <v>1497</v>
@@ -25743,7 +25708,7 @@
       <c r="AM172" s="6"/>
       <c r="AN172" s="6"/>
     </row>
-    <row r="173" spans="1:40" ht="15.75" customHeight="1">
+    <row r="173" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="8">
         <v>45983.417222222219</v>
       </c>
@@ -25849,7 +25814,7 @@
       <c r="AM173" s="13"/>
       <c r="AN173" s="13"/>
     </row>
-    <row r="174" spans="1:40" ht="15.75" customHeight="1">
+    <row r="174" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>45983.460949074077</v>
       </c>
@@ -25887,7 +25852,7 @@
         <v>9600733744</v>
       </c>
       <c r="M174" s="2" t="s">
-        <v>2143</v>
+        <v>2136</v>
       </c>
       <c r="N174" s="2" t="s">
         <v>1508</v>
@@ -25953,7 +25918,7 @@
       <c r="AM174" s="6"/>
       <c r="AN174" s="6"/>
     </row>
-    <row r="175" spans="1:40" ht="15.75" customHeight="1">
+    <row r="175" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="8">
         <v>45983.51185185185</v>
       </c>
@@ -26057,7 +26022,7 @@
       <c r="AM175" s="13"/>
       <c r="AN175" s="13"/>
     </row>
-    <row r="176" spans="1:40" ht="15.75" customHeight="1">
+    <row r="176" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>45983.530474537038</v>
       </c>
@@ -26169,7 +26134,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="177" spans="1:40" ht="15.75" customHeight="1">
+    <row r="177" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="8">
         <v>45983.538344907407</v>
       </c>
@@ -26210,7 +26175,7 @@
         <v>1532</v>
       </c>
       <c r="N177" s="9" t="s">
-        <v>2144</v>
+        <v>2137</v>
       </c>
       <c r="O177" s="9" t="s">
         <v>57</v>
@@ -26273,7 +26238,7 @@
       <c r="AM177" s="13"/>
       <c r="AN177" s="13"/>
     </row>
-    <row r="178" spans="1:40" ht="15.75" customHeight="1">
+    <row r="178" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>45983.560393518521</v>
       </c>
@@ -26377,7 +26342,7 @@
       <c r="AM178" s="6"/>
       <c r="AN178" s="6"/>
     </row>
-    <row r="179" spans="1:40" ht="15.75" customHeight="1">
+    <row r="179" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="8">
         <v>45983.568020833336</v>
       </c>
@@ -26415,7 +26380,7 @@
         <v>9486885993</v>
       </c>
       <c r="M179" s="9" t="s">
-        <v>2145</v>
+        <v>2138</v>
       </c>
       <c r="N179" s="9" t="s">
         <v>1547</v>
@@ -26481,7 +26446,7 @@
       <c r="AM179" s="13"/>
       <c r="AN179" s="13"/>
     </row>
-    <row r="180" spans="1:40" ht="15.75" customHeight="1">
+    <row r="180" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>45983.578020833331</v>
       </c>
@@ -26587,7 +26552,7 @@
       <c r="AM180" s="6"/>
       <c r="AN180" s="6"/>
     </row>
-    <row r="181" spans="1:40" ht="15.75" customHeight="1">
+    <row r="181" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="8">
         <v>45983.761250000003</v>
       </c>
@@ -26691,7 +26656,7 @@
       <c r="AM181" s="13"/>
       <c r="AN181" s="13"/>
     </row>
-    <row r="182" spans="1:40" ht="15.75" customHeight="1">
+    <row r="182" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>45984.822141203702</v>
       </c>
@@ -26732,7 +26697,7 @@
         <v>1571</v>
       </c>
       <c r="N182" s="2" t="s">
-        <v>2146</v>
+        <v>2139</v>
       </c>
       <c r="O182" s="2" t="s">
         <v>57</v>
@@ -26795,7 +26760,7 @@
       <c r="AM182" s="6"/>
       <c r="AN182" s="6"/>
     </row>
-    <row r="183" spans="1:40" ht="15.75" customHeight="1">
+    <row r="183" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="8">
         <v>45985.483148148145</v>
       </c>
@@ -26833,7 +26798,7 @@
         <v>9976551564</v>
       </c>
       <c r="M183" s="9" t="s">
-        <v>2147</v>
+        <v>2140</v>
       </c>
       <c r="N183" s="9" t="s">
         <v>1578</v>
@@ -26899,7 +26864,7 @@
       <c r="AM183" s="13"/>
       <c r="AN183" s="13"/>
     </row>
-    <row r="184" spans="1:40" ht="15.75" customHeight="1">
+    <row r="184" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>45985.525810185187</v>
       </c>
@@ -26940,7 +26905,7 @@
         <v>1583</v>
       </c>
       <c r="N184" s="2" t="s">
-        <v>2148</v>
+        <v>2141</v>
       </c>
       <c r="O184" s="2" t="s">
         <v>57</v>
@@ -27003,7 +26968,7 @@
       <c r="AM184" s="6"/>
       <c r="AN184" s="6"/>
     </row>
-    <row r="185" spans="1:40" ht="15.75" customHeight="1">
+    <row r="185" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="8">
         <v>45985.53052083333</v>
       </c>
@@ -27044,7 +27009,7 @@
         <v>1589</v>
       </c>
       <c r="N185" s="9" t="s">
-        <v>2149</v>
+        <v>2142</v>
       </c>
       <c r="O185" s="9" t="s">
         <v>57</v>
@@ -27107,7 +27072,7 @@
       <c r="AM185" s="13"/>
       <c r="AN185" s="13"/>
     </row>
-    <row r="186" spans="1:40" ht="15.75" customHeight="1">
+    <row r="186" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>45985.622858796298</v>
       </c>
@@ -27213,7 +27178,7 @@
       <c r="AM186" s="6"/>
       <c r="AN186" s="6"/>
     </row>
-    <row r="187" spans="1:40" ht="15.75" customHeight="1">
+    <row r="187" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="8">
         <v>45985.623449074075</v>
       </c>
@@ -27254,7 +27219,7 @@
         <v>1604</v>
       </c>
       <c r="N187" s="9" t="s">
-        <v>2150</v>
+        <v>2143</v>
       </c>
       <c r="O187" s="9" t="s">
         <v>57</v>
@@ -27275,7 +27240,7 @@
         <v>1605</v>
       </c>
       <c r="U187" s="9" t="s">
-        <v>2190</v>
+        <v>2179</v>
       </c>
       <c r="V187" s="9" t="s">
         <v>42</v>
@@ -27284,7 +27249,7 @@
         <v>45474</v>
       </c>
       <c r="X187" s="9" t="s">
-        <v>2191</v>
+        <v>2180</v>
       </c>
       <c r="Y187" s="9" t="s">
         <v>11</v>
@@ -27293,7 +27258,7 @@
         <v>739</v>
       </c>
       <c r="AA187" s="9" t="s">
-        <v>2192</v>
+        <v>2181</v>
       </c>
       <c r="AB187" s="13"/>
       <c r="AC187" s="9" t="s">
@@ -27317,7 +27282,7 @@
       <c r="AM187" s="13"/>
       <c r="AN187" s="13"/>
     </row>
-    <row r="188" spans="1:40" ht="15.75" customHeight="1">
+    <row r="188" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>45986.487766203703</v>
       </c>
@@ -27421,7 +27386,7 @@
       <c r="AM188" s="6"/>
       <c r="AN188" s="6"/>
     </row>
-    <row r="189" spans="1:40" ht="15.75" customHeight="1">
+    <row r="189" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="8">
         <v>45987.438449074078</v>
       </c>
@@ -27459,10 +27424,10 @@
         <v>9980839365</v>
       </c>
       <c r="M189" s="9" t="s">
-        <v>2151</v>
+        <v>2144</v>
       </c>
       <c r="N189" s="9" t="s">
-        <v>2152</v>
+        <v>2145</v>
       </c>
       <c r="O189" s="9" t="s">
         <v>57</v>
@@ -27527,7 +27492,7 @@
       <c r="AM189" s="13"/>
       <c r="AN189" s="13"/>
     </row>
-    <row r="190" spans="1:40" ht="15.75" customHeight="1">
+    <row r="190" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>45987.540578703702</v>
       </c>
@@ -27633,7 +27598,7 @@
       <c r="AM190" s="6"/>
       <c r="AN190" s="6"/>
     </row>
-    <row r="191" spans="1:40" ht="15.75" customHeight="1">
+    <row r="191" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="8">
         <v>45987.690243055556</v>
       </c>
@@ -27704,7 +27669,7 @@
         <v>45680</v>
       </c>
       <c r="X191" s="9" t="s">
-        <v>2153</v>
+        <v>2146</v>
       </c>
       <c r="Y191" s="9" t="s">
         <v>11</v>
@@ -27745,7 +27710,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="192" spans="1:40" ht="15.75" customHeight="1">
+    <row r="192" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>45987.704791666663</v>
       </c>
@@ -27786,7 +27751,7 @@
         <v>1735</v>
       </c>
       <c r="N192" s="2" t="s">
-        <v>2154</v>
+        <v>2147</v>
       </c>
       <c r="O192" s="2" t="s">
         <v>57</v>
@@ -27816,7 +27781,7 @@
         <v>39995</v>
       </c>
       <c r="X192" s="2" t="s">
-        <v>2155</v>
+        <v>2148</v>
       </c>
       <c r="Y192" s="2" t="s">
         <v>11</v>
@@ -27829,10 +27794,10 @@
       </c>
       <c r="AB192" s="6"/>
       <c r="AC192" s="2" t="s">
-        <v>2156</v>
+        <v>2149</v>
       </c>
       <c r="AD192" s="2" t="s">
-        <v>2157</v>
+        <v>2150</v>
       </c>
       <c r="AE192" s="2" t="s">
         <v>44</v>
@@ -27851,7 +27816,7 @@
       <c r="AM192" s="6"/>
       <c r="AN192" s="6"/>
     </row>
-    <row r="193" spans="1:40" ht="15.75" customHeight="1">
+    <row r="193" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="8">
         <v>45987.893125000002</v>
       </c>
@@ -27928,10 +27893,10 @@
         <v>11</v>
       </c>
       <c r="Z193" s="9" t="s">
-        <v>2182</v>
+        <v>2171</v>
       </c>
       <c r="AA193" s="9" t="s">
-        <v>2260</v>
+        <v>2249</v>
       </c>
       <c r="AB193" s="13"/>
       <c r="AC193" s="9" t="s">
@@ -27957,7 +27922,7 @@
       <c r="AM193" s="13"/>
       <c r="AN193" s="13"/>
     </row>
-    <row r="194" spans="1:40" ht="15.75" customHeight="1">
+    <row r="194" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>45988.458819444444</v>
       </c>
@@ -28028,7 +27993,7 @@
         <v>45432</v>
       </c>
       <c r="X194" s="2" t="s">
-        <v>2193</v>
+        <v>2182</v>
       </c>
       <c r="Y194" s="2" t="s">
         <v>11</v>
@@ -28041,7 +28006,7 @@
       </c>
       <c r="AB194" s="6"/>
       <c r="AC194" s="2" t="s">
-        <v>2194</v>
+        <v>2183</v>
       </c>
       <c r="AD194" s="6"/>
       <c r="AE194" s="2" t="s">
@@ -28061,7 +28026,7 @@
       <c r="AM194" s="6"/>
       <c r="AN194" s="6"/>
     </row>
-    <row r="195" spans="1:40" ht="15.75" customHeight="1">
+    <row r="195" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="8">
         <v>45988.494988425926</v>
       </c>
@@ -28102,7 +28067,7 @@
         <v>1753</v>
       </c>
       <c r="N195" s="9" t="s">
-        <v>2158</v>
+        <v>2151</v>
       </c>
       <c r="O195" s="2" t="s">
         <v>78</v>
@@ -28141,7 +28106,7 @@
         <v>739</v>
       </c>
       <c r="AA195" s="9" t="s">
-        <v>2195</v>
+        <v>2184</v>
       </c>
       <c r="AB195" s="13"/>
       <c r="AC195" s="9" t="s">
@@ -28165,7 +28130,7 @@
       <c r="AM195" s="13"/>
       <c r="AN195" s="13"/>
     </row>
-    <row r="196" spans="1:40" ht="15.75" customHeight="1">
+    <row r="196" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>45988.519699074073</v>
       </c>
@@ -28269,7 +28234,7 @@
       <c r="AM196" s="6"/>
       <c r="AN196" s="6"/>
     </row>
-    <row r="197" spans="1:40" ht="15.75" customHeight="1">
+    <row r="197" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="8">
         <v>45988.540254629632</v>
       </c>
@@ -28375,7 +28340,7 @@
       <c r="AM197" s="13"/>
       <c r="AN197" s="13"/>
     </row>
-    <row r="198" spans="1:40" ht="15.75" customHeight="1">
+    <row r="198" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>45988.613645833335</v>
       </c>
@@ -28416,7 +28381,7 @@
         <v>1776</v>
       </c>
       <c r="N198" s="2" t="s">
-        <v>2159</v>
+        <v>2152</v>
       </c>
       <c r="O198" s="2" t="s">
         <v>57</v>
@@ -28481,7 +28446,7 @@
       <c r="AM198" s="6"/>
       <c r="AN198" s="6"/>
     </row>
-    <row r="199" spans="1:40" ht="15.75" customHeight="1">
+    <row r="199" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="8">
         <v>45988.676562499997</v>
       </c>
@@ -28585,7 +28550,7 @@
       <c r="AM199" s="13"/>
       <c r="AN199" s="13"/>
     </row>
-    <row r="200" spans="1:40" ht="15.75" customHeight="1">
+    <row r="200" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>45989.404143518521</v>
       </c>
@@ -28623,7 +28588,7 @@
         <v>9791788778</v>
       </c>
       <c r="M200" s="2" t="s">
-        <v>2160</v>
+        <v>2153</v>
       </c>
       <c r="N200" s="2" t="s">
         <v>1795</v>
@@ -28669,7 +28634,7 @@
       </c>
       <c r="AB200" s="6"/>
       <c r="AC200" s="2" t="s">
-        <v>2161</v>
+        <v>2154</v>
       </c>
       <c r="AD200" s="6"/>
       <c r="AE200" s="2" t="s">
@@ -28691,7 +28656,7 @@
       <c r="AM200" s="6"/>
       <c r="AN200" s="6"/>
     </row>
-    <row r="201" spans="1:40" ht="15.75" customHeight="1">
+    <row r="201" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <v>45989.442962962959</v>
       </c>
@@ -28762,7 +28727,7 @@
         <v>45068</v>
       </c>
       <c r="X201" s="9" t="s">
-        <v>2162</v>
+        <v>2155</v>
       </c>
       <c r="Y201" s="9" t="s">
         <v>11</v>
@@ -28801,7 +28766,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="202" spans="1:40" ht="15.75" customHeight="1">
+    <row r="202" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>45989.531435185185</v>
       </c>
@@ -28872,7 +28837,7 @@
         <v>43633</v>
       </c>
       <c r="X202" s="2" t="s">
-        <v>2163</v>
+        <v>2156</v>
       </c>
       <c r="Y202" s="2" t="s">
         <v>11</v>
@@ -28887,7 +28852,7 @@
         <v>1810</v>
       </c>
       <c r="AC202" s="2" t="s">
-        <v>2163</v>
+        <v>2156</v>
       </c>
       <c r="AD202" s="2" t="s">
         <v>1813</v>
@@ -28909,7 +28874,7 @@
       <c r="AM202" s="6"/>
       <c r="AN202" s="6"/>
     </row>
-    <row r="203" spans="1:40" ht="15.75" customHeight="1">
+    <row r="203" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <v>45989.533159722225</v>
       </c>
@@ -29015,7 +28980,7 @@
       <c r="AM203" s="13"/>
       <c r="AN203" s="13"/>
     </row>
-    <row r="204" spans="1:40" ht="15.75" customHeight="1">
+    <row r="204" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>45989.555358796293</v>
       </c>
@@ -29053,10 +29018,10 @@
         <v>9489567930</v>
       </c>
       <c r="M204" s="2" t="s">
-        <v>2164</v>
+        <v>2157</v>
       </c>
       <c r="N204" s="2" t="s">
-        <v>2165</v>
+        <v>2158</v>
       </c>
       <c r="O204" s="2" t="s">
         <v>57</v>
@@ -29086,7 +29051,7 @@
         <v>45537</v>
       </c>
       <c r="X204" s="2" t="s">
-        <v>2166</v>
+        <v>2159</v>
       </c>
       <c r="Y204" s="2" t="s">
         <v>11</v>
@@ -29119,7 +29084,7 @@
       <c r="AM204" s="6"/>
       <c r="AN204" s="6"/>
     </row>
-    <row r="205" spans="1:40" ht="15.75" customHeight="1">
+    <row r="205" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="8">
         <v>45989.562418981484</v>
       </c>
@@ -29160,7 +29125,7 @@
         <v>1834</v>
       </c>
       <c r="N205" s="9" t="s">
-        <v>2167</v>
+        <v>2160</v>
       </c>
       <c r="O205" s="9" t="s">
         <v>997</v>
@@ -29225,2889 +29190,2783 @@
       <c r="AM205" s="13"/>
       <c r="AN205" s="13"/>
     </row>
-    <row r="206" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A206" s="1">
-        <v>45989.562986111108</v>
-      </c>
-      <c r="B206" s="2" t="s">
+    <row r="206" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A206" s="8">
+        <v>45989.598379629628</v>
+      </c>
+      <c r="B206" s="9" t="s">
         <v>1841</v>
       </c>
-      <c r="C206" s="2" t="s">
+      <c r="C206" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D206" s="10">
+        <v>63</v>
+      </c>
+      <c r="E206" s="11">
+        <v>22774</v>
+      </c>
+      <c r="F206" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="G206" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H206" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I206" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J206" s="12" t="s">
+        <v>1842</v>
+      </c>
+      <c r="K206" s="9" t="s">
+        <v>1843</v>
+      </c>
+      <c r="L206" s="10">
+        <v>9245171296</v>
+      </c>
+      <c r="M206" s="9" t="s">
+        <v>2161</v>
+      </c>
+      <c r="N206" s="9" t="s">
+        <v>1844</v>
+      </c>
+      <c r="O206" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="P206" s="10">
+        <v>613002</v>
+      </c>
+      <c r="Q206" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="R206" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="S206" s="10">
+        <v>20</v>
+      </c>
+      <c r="T206" s="9" t="s">
+        <v>980</v>
+      </c>
+      <c r="U206" s="9" t="s">
+        <v>1845</v>
+      </c>
+      <c r="V206" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="W206" s="11">
+        <v>44713</v>
+      </c>
+      <c r="X206" s="9" t="s">
+        <v>1846</v>
+      </c>
+      <c r="Y206" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z206" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="AA206" s="9" t="s">
+        <v>1659</v>
+      </c>
+      <c r="AB206" s="13"/>
+      <c r="AC206" s="9" t="s">
+        <v>1847</v>
+      </c>
+      <c r="AD206" s="9" t="s">
+        <v>1848</v>
+      </c>
+      <c r="AE206" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF206" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AG206" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AH206" s="13"/>
+      <c r="AI206" s="13"/>
+      <c r="AJ206" s="13"/>
+      <c r="AK206" s="13"/>
+      <c r="AL206" s="13"/>
+      <c r="AM206" s="13"/>
+      <c r="AN206" s="13"/>
+    </row>
+    <row r="207" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A207" s="1">
+        <v>45989.642604166664</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D207" s="3">
+        <v>29</v>
+      </c>
+      <c r="E207" s="4">
+        <v>35289</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H207" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I207" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J207" s="5" t="s">
+        <v>1850</v>
+      </c>
+      <c r="K207" s="2" t="s">
+        <v>1851</v>
+      </c>
+      <c r="L207" s="3">
+        <v>8220999766</v>
+      </c>
+      <c r="M207" s="2" t="s">
+        <v>1852</v>
+      </c>
+      <c r="N207" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="O207" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="P207" s="3">
+        <v>614803</v>
+      </c>
+      <c r="Q207" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="R207" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S207" s="3">
+        <v>1</v>
+      </c>
+      <c r="T207" s="3">
+        <v>8220999766</v>
+      </c>
+      <c r="U207" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="V207" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W207" s="4">
+        <v>45777</v>
+      </c>
+      <c r="X207" s="2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="Y207" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z207" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA207" s="2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="AB207" s="6"/>
+      <c r="AC207" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="AD207" s="6"/>
+      <c r="AE207" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF207" s="7">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AG207" s="7">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="AH207" s="6"/>
+      <c r="AI207" s="6"/>
+      <c r="AJ207" s="6"/>
+      <c r="AK207" s="6"/>
+      <c r="AL207" s="6"/>
+      <c r="AM207" s="5" t="s">
+        <v>1858</v>
+      </c>
+      <c r="AN207" s="6"/>
+    </row>
+    <row r="208" spans="1:40" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A208" s="8">
+        <v>45989.642881944441</v>
+      </c>
+      <c r="B208" s="9" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C208" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D206" s="3">
+      <c r="D208" s="10">
+        <v>34</v>
+      </c>
+      <c r="E208" s="11">
+        <v>33452</v>
+      </c>
+      <c r="F208" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="G208" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H208" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I208" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J208" s="12" t="s">
+        <v>1860</v>
+      </c>
+      <c r="K208" s="9" t="s">
+        <v>1861</v>
+      </c>
+      <c r="L208" s="10">
+        <v>9963556484</v>
+      </c>
+      <c r="M208" s="9" t="s">
+        <v>1862</v>
+      </c>
+      <c r="N208" s="9" t="s">
+        <v>1863</v>
+      </c>
+      <c r="O208" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="P208" s="10">
+        <v>620017</v>
+      </c>
+      <c r="Q208" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="R208" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="S208" s="10">
+        <v>6</v>
+      </c>
+      <c r="T208" s="9" t="s">
+        <v>1864</v>
+      </c>
+      <c r="U208" s="9" t="s">
+        <v>1865</v>
+      </c>
+      <c r="V208" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="W208" s="11">
+        <v>43711</v>
+      </c>
+      <c r="X208" s="9" t="s">
+        <v>1866</v>
+      </c>
+      <c r="Y208" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z208" s="9" t="s">
+        <v>1064</v>
+      </c>
+      <c r="AA208" s="9" t="s">
+        <v>1657</v>
+      </c>
+      <c r="AB208" s="13"/>
+      <c r="AC208" s="9" t="s">
+        <v>2162</v>
+      </c>
+      <c r="AD208" s="9" t="s">
+        <v>1867</v>
+      </c>
+      <c r="AE208" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E206" s="4">
-        <v>29741</v>
-      </c>
-      <c r="F206" s="2" t="s">
-        <v>1842</v>
-      </c>
-      <c r="G206" s="2" t="s">
+      <c r="AF208" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AG208" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AH208" s="13"/>
+      <c r="AI208" s="13"/>
+      <c r="AJ208" s="13"/>
+      <c r="AK208" s="13"/>
+      <c r="AL208" s="13"/>
+      <c r="AM208" s="13"/>
+      <c r="AN208" s="13"/>
+    </row>
+    <row r="209" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A209" s="1">
+        <v>45989.647222222222</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D209" s="3">
+        <v>32</v>
+      </c>
+      <c r="E209" s="4">
+        <v>34256</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="G209" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H206" s="2" t="s">
+      <c r="H209" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I206" s="2" t="s">
+      <c r="I209" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J206" s="5" t="s">
-        <v>1843</v>
-      </c>
-      <c r="K206" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L206" s="3">
-        <v>9444163130</v>
-      </c>
-      <c r="M206" s="2" t="s">
-        <v>1844</v>
-      </c>
-      <c r="N206" s="2" t="s">
-        <v>2168</v>
-      </c>
-      <c r="O206" s="2" t="s">
-        <v>2180</v>
-      </c>
-      <c r="P206" s="3">
-        <v>620001</v>
-      </c>
-      <c r="Q206" s="9" t="s">
+      <c r="J209" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K209" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="L209" s="3">
+        <v>9944311724</v>
+      </c>
+      <c r="M209" s="2" t="s">
+        <v>1872</v>
+      </c>
+      <c r="N209" s="2" t="s">
+        <v>1873</v>
+      </c>
+      <c r="O209" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="R206" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="S206" s="3">
-        <v>14</v>
-      </c>
-      <c r="T206" s="2" t="s">
-        <v>1845</v>
-      </c>
-      <c r="U206" s="2" t="s">
-        <v>1846</v>
-      </c>
-      <c r="V206" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="W206" s="4">
-        <v>44986</v>
-      </c>
-      <c r="X206" s="2" t="s">
-        <v>2169</v>
-      </c>
-      <c r="Y206" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z206" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="AA206" s="2" t="s">
-        <v>1719</v>
-      </c>
-      <c r="AB206" s="6"/>
-      <c r="AC206" s="2" t="s">
-        <v>1847</v>
-      </c>
-      <c r="AD206" s="2" t="s">
-        <v>2170</v>
-      </c>
-      <c r="AE206" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF206" s="7">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="AG206" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="AH206" s="6"/>
-      <c r="AI206" s="6"/>
-      <c r="AJ206" s="6"/>
-      <c r="AK206" s="6"/>
-      <c r="AL206" s="6"/>
-      <c r="AM206" s="6"/>
-      <c r="AN206" s="6"/>
-    </row>
-    <row r="207" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A207" s="8">
-        <v>45989.598379629628</v>
-      </c>
-      <c r="B207" s="9" t="s">
-        <v>1848</v>
-      </c>
-      <c r="C207" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D207" s="10">
-        <v>63</v>
-      </c>
-      <c r="E207" s="11">
-        <v>22774</v>
-      </c>
-      <c r="F207" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="G207" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H207" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I207" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J207" s="12" t="s">
-        <v>1849</v>
-      </c>
-      <c r="K207" s="9" t="s">
-        <v>1850</v>
-      </c>
-      <c r="L207" s="10">
-        <v>9245171296</v>
-      </c>
-      <c r="M207" s="9" t="s">
-        <v>2171</v>
-      </c>
-      <c r="N207" s="9" t="s">
-        <v>1851</v>
-      </c>
-      <c r="O207" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="P207" s="10">
-        <v>613002</v>
-      </c>
-      <c r="Q207" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="R207" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="S207" s="10">
-        <v>20</v>
-      </c>
-      <c r="T207" s="9" t="s">
-        <v>980</v>
-      </c>
-      <c r="U207" s="9" t="s">
-        <v>1852</v>
-      </c>
-      <c r="V207" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="W207" s="11">
-        <v>44713</v>
-      </c>
-      <c r="X207" s="9" t="s">
-        <v>1853</v>
-      </c>
-      <c r="Y207" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z207" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="AA207" s="9" t="s">
-        <v>1659</v>
-      </c>
-      <c r="AB207" s="13"/>
-      <c r="AC207" s="9" t="s">
-        <v>1854</v>
-      </c>
-      <c r="AD207" s="9" t="s">
-        <v>1855</v>
-      </c>
-      <c r="AE207" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF207" s="14">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="AG207" s="14">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="AH207" s="13"/>
-      <c r="AI207" s="13"/>
-      <c r="AJ207" s="13"/>
-      <c r="AK207" s="13"/>
-      <c r="AL207" s="13"/>
-      <c r="AM207" s="13"/>
-      <c r="AN207" s="13"/>
-    </row>
-    <row r="208" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A208" s="1">
-        <v>45989.642604166664</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>1856</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D208" s="3">
-        <v>29</v>
-      </c>
-      <c r="E208" s="4">
-        <v>35289</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="G208" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H208" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I208" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J208" s="5" t="s">
-        <v>1857</v>
-      </c>
-      <c r="K208" s="2" t="s">
-        <v>1858</v>
-      </c>
-      <c r="L208" s="3">
-        <v>8220999766</v>
-      </c>
-      <c r="M208" s="2" t="s">
-        <v>1859</v>
-      </c>
-      <c r="N208" s="2" t="s">
-        <v>1860</v>
-      </c>
-      <c r="O208" s="2" t="s">
-        <v>1417</v>
-      </c>
-      <c r="P208" s="3">
-        <v>614803</v>
-      </c>
-      <c r="Q208" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="R208" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="S208" s="3">
-        <v>1</v>
-      </c>
-      <c r="T208" s="3">
-        <v>8220999766</v>
-      </c>
-      <c r="U208" s="2" t="s">
-        <v>1861</v>
-      </c>
-      <c r="V208" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="W208" s="4">
-        <v>45777</v>
-      </c>
-      <c r="X208" s="2" t="s">
-        <v>1862</v>
-      </c>
-      <c r="Y208" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z208" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA208" s="2" t="s">
-        <v>1863</v>
-      </c>
-      <c r="AB208" s="6"/>
-      <c r="AC208" s="2" t="s">
-        <v>1864</v>
-      </c>
-      <c r="AD208" s="6"/>
-      <c r="AE208" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF208" s="7">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="AG208" s="7">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="AH208" s="6"/>
-      <c r="AI208" s="6"/>
-      <c r="AJ208" s="6"/>
-      <c r="AK208" s="6"/>
-      <c r="AL208" s="6"/>
-      <c r="AM208" s="5" t="s">
-        <v>1865</v>
-      </c>
-      <c r="AN208" s="6"/>
-    </row>
-    <row r="209" spans="1:40" ht="409.5">
-      <c r="A209" s="8">
-        <v>45989.642881944441</v>
-      </c>
-      <c r="B209" s="9" t="s">
-        <v>1866</v>
-      </c>
-      <c r="C209" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D209" s="10">
-        <v>34</v>
-      </c>
-      <c r="E209" s="11">
-        <v>33452</v>
-      </c>
-      <c r="F209" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="G209" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H209" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I209" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J209" s="12" t="s">
-        <v>1867</v>
-      </c>
-      <c r="K209" s="9" t="s">
-        <v>1868</v>
-      </c>
-      <c r="L209" s="10">
-        <v>9963556484</v>
-      </c>
-      <c r="M209" s="9" t="s">
-        <v>1869</v>
-      </c>
-      <c r="N209" s="9" t="s">
-        <v>1870</v>
-      </c>
-      <c r="O209" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P209" s="10">
-        <v>620017</v>
+      <c r="P209" s="3">
+        <v>620003</v>
       </c>
       <c r="Q209" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="R209" s="9" t="s">
+      <c r="R209" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="S209" s="10">
-        <v>6</v>
-      </c>
-      <c r="T209" s="9" t="s">
-        <v>1871</v>
-      </c>
-      <c r="U209" s="9" t="s">
-        <v>1872</v>
-      </c>
-      <c r="V209" s="9" t="s">
+      <c r="S209" s="3">
+        <v>5</v>
+      </c>
+      <c r="T209" s="2" t="s">
+        <v>1874</v>
+      </c>
+      <c r="U209" s="2" t="s">
+        <v>1875</v>
+      </c>
+      <c r="V209" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W209" s="11">
-        <v>43711</v>
-      </c>
-      <c r="X209" s="9" t="s">
-        <v>1873</v>
-      </c>
-      <c r="Y209" s="9" t="s">
+      <c r="W209" s="4">
+        <v>45689</v>
+      </c>
+      <c r="X209" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="Y209" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="Z209" s="9" t="s">
-        <v>1064</v>
-      </c>
-      <c r="AA209" s="9" t="s">
-        <v>1657</v>
-      </c>
-      <c r="AB209" s="13"/>
-      <c r="AC209" s="9" t="s">
-        <v>2172</v>
-      </c>
-      <c r="AD209" s="9" t="s">
-        <v>1874</v>
-      </c>
-      <c r="AE209" s="9" t="s">
+      <c r="Z209" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA209" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB209" s="6"/>
+      <c r="AC209" s="2" t="s">
+        <v>1877</v>
+      </c>
+      <c r="AD209" s="2" t="s">
+        <v>1878</v>
+      </c>
+      <c r="AE209" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF209" s="14">
+      <c r="AF209" s="7">
         <v>0.35416666666666669</v>
       </c>
-      <c r="AG209" s="14">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="AH209" s="13"/>
-      <c r="AI209" s="13"/>
-      <c r="AJ209" s="13"/>
-      <c r="AK209" s="13"/>
-      <c r="AL209" s="13"/>
-      <c r="AM209" s="13"/>
-      <c r="AN209" s="13"/>
+      <c r="AG209" s="7">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="AH209" s="6"/>
+      <c r="AI209" s="6"/>
+      <c r="AJ209" s="6"/>
+      <c r="AK209" s="6"/>
+      <c r="AL209" s="5" t="s">
+        <v>1879</v>
+      </c>
+      <c r="AM209" s="5" t="s">
+        <v>1879</v>
+      </c>
+      <c r="AN209" s="6"/>
     </row>
-    <row r="210" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A210" s="1">
-        <v>45989.647222222222</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>1875</v>
-      </c>
-      <c r="C210" s="2" t="s">
+    <row r="210" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A210" s="8">
+        <v>45990.525219907409</v>
+      </c>
+      <c r="B210" s="9" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C210" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D210" s="3">
-        <v>32</v>
-      </c>
-      <c r="E210" s="4">
-        <v>34256</v>
-      </c>
-      <c r="F210" s="2" t="s">
-        <v>1876</v>
-      </c>
-      <c r="G210" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H210" s="2" t="s">
+      <c r="D210" s="10">
+        <v>64</v>
+      </c>
+      <c r="E210" s="11">
+        <v>22597</v>
+      </c>
+      <c r="F210" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="G210" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H210" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="I210" s="2" t="s">
+      <c r="I210" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="J210" s="5" t="s">
-        <v>1877</v>
-      </c>
-      <c r="K210" s="2" t="s">
-        <v>1878</v>
-      </c>
-      <c r="L210" s="3">
-        <v>9944311724</v>
-      </c>
-      <c r="M210" s="2" t="s">
-        <v>1879</v>
-      </c>
-      <c r="N210" s="2" t="s">
-        <v>1880</v>
-      </c>
-      <c r="O210" s="2" t="s">
+      <c r="J210" s="12" t="s">
+        <v>1881</v>
+      </c>
+      <c r="K210" s="9" t="s">
+        <v>1882</v>
+      </c>
+      <c r="L210" s="10">
+        <v>9448072069</v>
+      </c>
+      <c r="M210" s="9" t="s">
+        <v>1883</v>
+      </c>
+      <c r="N210" s="9" t="s">
+        <v>2163</v>
+      </c>
+      <c r="O210" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="P210" s="3">
-        <v>620003</v>
+      <c r="P210" s="10">
+        <v>621105</v>
       </c>
       <c r="Q210" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="R210" s="2" t="s">
+      <c r="R210" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="S210" s="3">
+      <c r="S210" s="10">
+        <v>31</v>
+      </c>
+      <c r="T210" s="10">
+        <v>9448072069</v>
+      </c>
+      <c r="U210" s="9" t="s">
+        <v>1884</v>
+      </c>
+      <c r="V210" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="W210" s="11">
+        <v>44375</v>
+      </c>
+      <c r="X210" s="9" t="s">
+        <v>1885</v>
+      </c>
+      <c r="Y210" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z210" s="9" t="s">
+        <v>1064</v>
+      </c>
+      <c r="AA210" s="9" t="s">
+        <v>1719</v>
+      </c>
+      <c r="AB210" s="9" t="s">
+        <v>1883</v>
+      </c>
+      <c r="AC210" s="9" t="s">
+        <v>1886</v>
+      </c>
+      <c r="AD210" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE210" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF210" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AG210" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AH210" s="13"/>
+      <c r="AI210" s="13"/>
+      <c r="AJ210" s="13"/>
+      <c r="AK210" s="13"/>
+      <c r="AL210" s="13"/>
+      <c r="AM210" s="13"/>
+      <c r="AN210" s="13"/>
+    </row>
+    <row r="211" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="1">
+        <v>45991.461608796293</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D211" s="3">
+        <v>33</v>
+      </c>
+      <c r="E211" s="4">
+        <v>33736</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>1766</v>
+      </c>
+      <c r="G211" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H211" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I211" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J211" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K211" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L211" s="3">
+        <v>8056496100</v>
+      </c>
+      <c r="M211" s="2" t="s">
+        <v>2164</v>
+      </c>
+      <c r="N211" s="2" t="s">
+        <v>1889</v>
+      </c>
+      <c r="O211" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="P211" s="3">
+        <v>636109</v>
+      </c>
+      <c r="Q211" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="R211" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S211" s="3">
         <v>5</v>
       </c>
-      <c r="T210" s="2" t="s">
-        <v>1881</v>
-      </c>
-      <c r="U210" s="2" t="s">
-        <v>1882</v>
-      </c>
-      <c r="V210" s="2" t="s">
+      <c r="T211" s="2" t="s">
+        <v>1890</v>
+      </c>
+      <c r="U211" s="2" t="s">
+        <v>1891</v>
+      </c>
+      <c r="V211" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="W211" s="4">
+        <v>45495</v>
+      </c>
+      <c r="X211" s="2" t="s">
+        <v>1892</v>
+      </c>
+      <c r="Y211" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z211" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA211" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="AB211" s="6"/>
+      <c r="AC211" s="2" t="s">
+        <v>1894</v>
+      </c>
+      <c r="AD211" s="2" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AE211" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF211" s="7">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="AG211" s="7">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="AH211" s="6"/>
+      <c r="AI211" s="6"/>
+      <c r="AJ211" s="6"/>
+      <c r="AK211" s="6"/>
+      <c r="AL211" s="6"/>
+      <c r="AM211" s="6"/>
+      <c r="AN211" s="6"/>
+    </row>
+    <row r="212" spans="1:40" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="A212" s="8">
+        <v>45991.931631944448</v>
+      </c>
+      <c r="B212" s="9" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C212" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D212" s="10">
+        <v>30</v>
+      </c>
+      <c r="E212" s="11">
+        <v>34893</v>
+      </c>
+      <c r="F212" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="G212" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H212" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I212" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J212" s="12" t="s">
+        <v>1897</v>
+      </c>
+      <c r="K212" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="L212" s="10">
+        <v>8056856800</v>
+      </c>
+      <c r="M212" s="9" t="s">
+        <v>1898</v>
+      </c>
+      <c r="N212" s="9" t="s">
+        <v>1899</v>
+      </c>
+      <c r="O212" s="9" t="s">
+        <v>1486</v>
+      </c>
+      <c r="P212" s="10">
+        <v>622001</v>
+      </c>
+      <c r="Q212" s="9" t="s">
+        <v>1486</v>
+      </c>
+      <c r="R212" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="S212" s="10">
+        <v>3</v>
+      </c>
+      <c r="T212" s="9" t="s">
+        <v>1900</v>
+      </c>
+      <c r="U212" s="9" t="s">
+        <v>2250</v>
+      </c>
+      <c r="V212" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="W210" s="4">
-        <v>45689</v>
-      </c>
-      <c r="X210" s="2" t="s">
-        <v>1883</v>
-      </c>
-      <c r="Y210" s="2" t="s">
+      <c r="W212" s="11">
+        <v>45136</v>
+      </c>
+      <c r="X212" s="9" t="s">
+        <v>1901</v>
+      </c>
+      <c r="Y212" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="Z210" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA210" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB210" s="6"/>
-      <c r="AC210" s="2" t="s">
-        <v>1884</v>
-      </c>
-      <c r="AD210" s="2" t="s">
-        <v>1885</v>
-      </c>
-      <c r="AE210" s="2" t="s">
+      <c r="Z212" s="9" t="s">
+        <v>2171</v>
+      </c>
+      <c r="AA212" s="9" t="s">
+        <v>1902</v>
+      </c>
+      <c r="AB212" s="13"/>
+      <c r="AC212" s="9" t="s">
+        <v>1903</v>
+      </c>
+      <c r="AD212" s="9" t="s">
+        <v>1904</v>
+      </c>
+      <c r="AE212" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="AF210" s="7">
+      <c r="AF212" s="14">
         <v>0.35416666666666669</v>
       </c>
-      <c r="AG210" s="7">
+      <c r="AG212" s="14">
         <v>0.64583333333333337</v>
       </c>
-      <c r="AH210" s="6"/>
-      <c r="AI210" s="6"/>
-      <c r="AJ210" s="6"/>
-      <c r="AK210" s="6"/>
-      <c r="AL210" s="5" t="s">
-        <v>1886</v>
-      </c>
-      <c r="AM210" s="5" t="s">
-        <v>1886</v>
-      </c>
-      <c r="AN210" s="6"/>
+      <c r="AH212" s="13"/>
+      <c r="AI212" s="13"/>
+      <c r="AJ212" s="13"/>
+      <c r="AK212" s="13"/>
+      <c r="AL212" s="13"/>
+      <c r="AM212" s="13"/>
+      <c r="AN212" s="13"/>
     </row>
-    <row r="211" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A211" s="8">
-        <v>45990.525219907409</v>
-      </c>
-      <c r="B211" s="9" t="s">
-        <v>1887</v>
-      </c>
-      <c r="C211" s="9" t="s">
+    <row r="213" spans="1:40" ht="229.5" x14ac:dyDescent="0.2">
+      <c r="A213" s="1">
+        <v>45992.409791666665</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C213" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D211" s="10">
-        <v>64</v>
-      </c>
-      <c r="E211" s="11">
-        <v>22597</v>
-      </c>
-      <c r="F211" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="G211" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H211" s="9" t="s">
+      <c r="D213" s="3">
+        <v>72</v>
+      </c>
+      <c r="E213" s="4">
+        <v>19441</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>1906</v>
+      </c>
+      <c r="G213" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="H213" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I211" s="9" t="s">
+      <c r="I213" s="2" t="s">
+        <v>1907</v>
+      </c>
+      <c r="J213" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="K213" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L213" s="3">
+        <v>7708490384</v>
+      </c>
+      <c r="M213" s="2" t="s">
+        <v>2165</v>
+      </c>
+      <c r="N213" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="O213" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P213" s="3">
+        <v>620017</v>
+      </c>
+      <c r="Q213" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="R213" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S213" s="3">
+        <v>40</v>
+      </c>
+      <c r="T213" s="2" t="s">
+        <v>1910</v>
+      </c>
+      <c r="U213" s="2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="V213" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="W213" s="4">
+        <v>45768</v>
+      </c>
+      <c r="X213" s="2" t="s">
+        <v>1912</v>
+      </c>
+      <c r="Y213" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z213" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA213" s="2" t="s">
+        <v>1913</v>
+      </c>
+      <c r="AB213" s="5" t="s">
+        <v>1914</v>
+      </c>
+      <c r="AC213" s="2" t="s">
+        <v>1915</v>
+      </c>
+      <c r="AD213" s="2" t="s">
+        <v>1916</v>
+      </c>
+      <c r="AE213" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF213" s="7">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AG213" s="7">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="AH213" s="6"/>
+      <c r="AI213" s="6"/>
+      <c r="AJ213" s="6"/>
+      <c r="AK213" s="6"/>
+      <c r="AL213" s="5" t="s">
+        <v>1917</v>
+      </c>
+      <c r="AM213" s="6"/>
+      <c r="AN213" s="6"/>
+    </row>
+    <row r="214" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214" s="8">
+        <v>45992.539317129631</v>
+      </c>
+      <c r="B214" s="9" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C214" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D214" s="10">
+        <v>30</v>
+      </c>
+      <c r="E214" s="11">
+        <v>34914</v>
+      </c>
+      <c r="F214" s="9" t="s">
+        <v>1919</v>
+      </c>
+      <c r="G214" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H214" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I214" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="J211" s="12" t="s">
-        <v>1888</v>
-      </c>
-      <c r="K211" s="9" t="s">
-        <v>1889</v>
-      </c>
-      <c r="L211" s="10">
-        <v>9448072069</v>
-      </c>
-      <c r="M211" s="9" t="s">
-        <v>1890</v>
-      </c>
-      <c r="N211" s="9" t="s">
-        <v>2173</v>
-      </c>
-      <c r="O211" s="9" t="s">
+      <c r="J214" s="12" t="s">
+        <v>1920</v>
+      </c>
+      <c r="K214" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="L214" s="10">
+        <v>9159874787</v>
+      </c>
+      <c r="M214" s="9" t="s">
+        <v>1921</v>
+      </c>
+      <c r="N214" s="9" t="s">
+        <v>1922</v>
+      </c>
+      <c r="O214" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="P211" s="10">
-        <v>621105</v>
-      </c>
-      <c r="Q211" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="R211" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="S211" s="10">
-        <v>31</v>
-      </c>
-      <c r="T211" s="10">
-        <v>9448072069</v>
-      </c>
-      <c r="U211" s="9" t="s">
-        <v>1891</v>
-      </c>
-      <c r="V211" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="W211" s="11">
-        <v>44375</v>
-      </c>
-      <c r="X211" s="9" t="s">
-        <v>1892</v>
-      </c>
-      <c r="Y211" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z211" s="9" t="s">
-        <v>1064</v>
-      </c>
-      <c r="AA211" s="9" t="s">
-        <v>1719</v>
-      </c>
-      <c r="AB211" s="9" t="s">
-        <v>1890</v>
-      </c>
-      <c r="AC211" s="9" t="s">
-        <v>1893</v>
-      </c>
-      <c r="AD211" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="AE211" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF211" s="14">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="AG211" s="14">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="AH211" s="13"/>
-      <c r="AI211" s="13"/>
-      <c r="AJ211" s="13"/>
-      <c r="AK211" s="13"/>
-      <c r="AL211" s="13"/>
-      <c r="AM211" s="13"/>
-      <c r="AN211" s="13"/>
-    </row>
-    <row r="212" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A212" s="1">
-        <v>45991.461608796293</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>1894</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D212" s="3">
-        <v>33</v>
-      </c>
-      <c r="E212" s="4">
-        <v>33736</v>
-      </c>
-      <c r="F212" s="2" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G212" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H212" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I212" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J212" s="5" t="s">
-        <v>1895</v>
-      </c>
-      <c r="K212" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="L212" s="3">
-        <v>8056496100</v>
-      </c>
-      <c r="M212" s="2" t="s">
-        <v>2174</v>
-      </c>
-      <c r="N212" s="2" t="s">
-        <v>1896</v>
-      </c>
-      <c r="O212" s="2" t="s">
-        <v>834</v>
-      </c>
-      <c r="P212" s="3">
-        <v>636109</v>
-      </c>
-      <c r="Q212" s="2" t="s">
-        <v>834</v>
-      </c>
-      <c r="R212" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="S212" s="3">
-        <v>5</v>
-      </c>
-      <c r="T212" s="2" t="s">
-        <v>1897</v>
-      </c>
-      <c r="U212" s="2" t="s">
-        <v>1898</v>
-      </c>
-      <c r="V212" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="W212" s="4">
-        <v>45495</v>
-      </c>
-      <c r="X212" s="2" t="s">
-        <v>1899</v>
-      </c>
-      <c r="Y212" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z212" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA212" s="2" t="s">
-        <v>1900</v>
-      </c>
-      <c r="AB212" s="6"/>
-      <c r="AC212" s="2" t="s">
-        <v>1901</v>
-      </c>
-      <c r="AD212" s="2" t="s">
-        <v>1902</v>
-      </c>
-      <c r="AE212" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF212" s="7">
-        <v>0.3611111111111111</v>
-      </c>
-      <c r="AG212" s="7">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="AH212" s="6"/>
-      <c r="AI212" s="6"/>
-      <c r="AJ212" s="6"/>
-      <c r="AK212" s="6"/>
-      <c r="AL212" s="6"/>
-      <c r="AM212" s="6"/>
-      <c r="AN212" s="6"/>
-    </row>
-    <row r="213" spans="1:40" ht="127.5">
-      <c r="A213" s="8">
-        <v>45991.931631944448</v>
-      </c>
-      <c r="B213" s="9" t="s">
-        <v>1903</v>
-      </c>
-      <c r="C213" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D213" s="10">
-        <v>30</v>
-      </c>
-      <c r="E213" s="11">
-        <v>34893</v>
-      </c>
-      <c r="F213" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="G213" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H213" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I213" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J213" s="12" t="s">
-        <v>1904</v>
-      </c>
-      <c r="K213" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="L213" s="10">
-        <v>8056856800</v>
-      </c>
-      <c r="M213" s="9" t="s">
-        <v>1905</v>
-      </c>
-      <c r="N213" s="9" t="s">
-        <v>1906</v>
-      </c>
-      <c r="O213" s="9" t="s">
-        <v>1486</v>
-      </c>
-      <c r="P213" s="10">
-        <v>622001</v>
-      </c>
-      <c r="Q213" s="9" t="s">
-        <v>1486</v>
-      </c>
-      <c r="R213" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="S213" s="10">
-        <v>3</v>
-      </c>
-      <c r="T213" s="9" t="s">
-        <v>1907</v>
-      </c>
-      <c r="U213" s="9" t="s">
-        <v>2261</v>
-      </c>
-      <c r="V213" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="W213" s="11">
-        <v>45136</v>
-      </c>
-      <c r="X213" s="9" t="s">
-        <v>1908</v>
-      </c>
-      <c r="Y213" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z213" s="9" t="s">
-        <v>2182</v>
-      </c>
-      <c r="AA213" s="9" t="s">
-        <v>1909</v>
-      </c>
-      <c r="AB213" s="13"/>
-      <c r="AC213" s="9" t="s">
-        <v>1910</v>
-      </c>
-      <c r="AD213" s="9" t="s">
-        <v>1911</v>
-      </c>
-      <c r="AE213" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF213" s="14">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="AG213" s="14">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="AH213" s="13"/>
-      <c r="AI213" s="13"/>
-      <c r="AJ213" s="13"/>
-      <c r="AK213" s="13"/>
-      <c r="AL213" s="13"/>
-      <c r="AM213" s="13"/>
-      <c r="AN213" s="13"/>
-    </row>
-    <row r="214" spans="1:40" ht="229.5">
-      <c r="A214" s="1">
-        <v>45992.409791666665</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>1912</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D214" s="3">
-        <v>72</v>
-      </c>
-      <c r="E214" s="4">
-        <v>19441</v>
-      </c>
-      <c r="F214" s="2" t="s">
-        <v>1913</v>
-      </c>
-      <c r="G214" s="2" t="s">
-        <v>1815</v>
-      </c>
-      <c r="H214" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I214" s="2" t="s">
-        <v>1914</v>
-      </c>
-      <c r="J214" s="5" t="s">
-        <v>1915</v>
-      </c>
-      <c r="K214" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L214" s="3">
-        <v>7708490384</v>
-      </c>
-      <c r="M214" s="2" t="s">
-        <v>2175</v>
-      </c>
-      <c r="N214" s="2" t="s">
-        <v>1916</v>
-      </c>
-      <c r="O214" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="P214" s="3">
-        <v>620017</v>
+      <c r="P214" s="10">
+        <v>621306</v>
       </c>
       <c r="Q214" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="R214" s="2" t="s">
+      <c r="R214" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="S214" s="3">
-        <v>40</v>
-      </c>
-      <c r="T214" s="2" t="s">
-        <v>1917</v>
-      </c>
-      <c r="U214" s="2" t="s">
-        <v>1918</v>
-      </c>
-      <c r="V214" s="2" t="s">
+      <c r="S214" s="10">
+        <v>2</v>
+      </c>
+      <c r="T214" s="9" t="s">
+        <v>1923</v>
+      </c>
+      <c r="U214" s="9" t="s">
+        <v>1924</v>
+      </c>
+      <c r="V214" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="W214" s="11">
+        <v>45247</v>
+      </c>
+      <c r="X214" s="9" t="s">
+        <v>1925</v>
+      </c>
+      <c r="Y214" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z214" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="AA214" s="9" t="s">
+        <v>1926</v>
+      </c>
+      <c r="AB214" s="13"/>
+      <c r="AC214" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="AD214" s="13"/>
+      <c r="AE214" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF214" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AG214" s="14">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="AH214" s="13"/>
+      <c r="AI214" s="13"/>
+      <c r="AJ214" s="13"/>
+      <c r="AK214" s="13"/>
+      <c r="AL214" s="13"/>
+      <c r="AM214" s="13"/>
+      <c r="AN214" s="13"/>
+    </row>
+    <row r="215" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="1">
+        <v>45993.426747685182</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>1927</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D215" s="3">
+        <v>32</v>
+      </c>
+      <c r="E215" s="4">
+        <v>34192</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G215" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H215" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I215" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J215" s="5" t="s">
+        <v>1928</v>
+      </c>
+      <c r="K215" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L215" s="3">
+        <v>9047488954</v>
+      </c>
+      <c r="M215" s="2" t="s">
+        <v>1929</v>
+      </c>
+      <c r="N215" s="2" t="s">
+        <v>1930</v>
+      </c>
+      <c r="O215" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P215" s="3">
+        <v>620018</v>
+      </c>
+      <c r="Q215" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="R215" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S215" s="3">
+        <v>1</v>
+      </c>
+      <c r="T215" s="2" t="s">
+        <v>1931</v>
+      </c>
+      <c r="U215" s="2" t="s">
+        <v>1932</v>
+      </c>
+      <c r="V215" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W215" s="4">
+        <v>45748</v>
+      </c>
+      <c r="X215" s="2" t="s">
+        <v>1933</v>
+      </c>
+      <c r="Y215" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z215" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA215" s="2" t="s">
+        <v>1934</v>
+      </c>
+      <c r="AB215" s="6"/>
+      <c r="AC215" s="2" t="s">
+        <v>1935</v>
+      </c>
+      <c r="AD215" s="6"/>
+      <c r="AE215" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF215" s="7">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AG215" s="7">
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="AH215" s="6"/>
+      <c r="AI215" s="6"/>
+      <c r="AJ215" s="6"/>
+      <c r="AK215" s="6"/>
+      <c r="AL215" s="5" t="s">
+        <v>1936</v>
+      </c>
+      <c r="AM215" s="6"/>
+      <c r="AN215" s="6"/>
+    </row>
+    <row r="216" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="8">
+        <v>45993.819548611114</v>
+      </c>
+      <c r="B216" s="9" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C216" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D216" s="10">
+        <v>45</v>
+      </c>
+      <c r="E216" s="11">
+        <v>29639</v>
+      </c>
+      <c r="F216" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="G216" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H216" s="13"/>
+      <c r="I216" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J216" s="12" t="s">
+        <v>1938</v>
+      </c>
+      <c r="K216" s="9" t="s">
+        <v>1939</v>
+      </c>
+      <c r="L216" s="10">
+        <v>9842091151</v>
+      </c>
+      <c r="M216" s="9" t="s">
+        <v>2166</v>
+      </c>
+      <c r="N216" s="9" t="s">
+        <v>1940</v>
+      </c>
+      <c r="O216" s="9" t="s">
+        <v>942</v>
+      </c>
+      <c r="P216" s="10">
+        <v>638476</v>
+      </c>
+      <c r="Q216" s="9" t="s">
+        <v>942</v>
+      </c>
+      <c r="R216" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="S216" s="10">
+        <v>7</v>
+      </c>
+      <c r="T216" s="9" t="s">
+        <v>1941</v>
+      </c>
+      <c r="U216" s="9" t="s">
+        <v>2251</v>
+      </c>
+      <c r="V216" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="W216" s="11">
+        <v>43166</v>
+      </c>
+      <c r="X216" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y216" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z216" s="9" t="s">
+        <v>2171</v>
+      </c>
+      <c r="AA216" s="9" t="s">
+        <v>2171</v>
+      </c>
+      <c r="AB216" s="12" t="s">
+        <v>1942</v>
+      </c>
+      <c r="AC216" s="9" t="s">
+        <v>2252</v>
+      </c>
+      <c r="AD216" s="13"/>
+      <c r="AE216" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF216" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AG216" s="14">
+        <v>0.6875</v>
+      </c>
+      <c r="AH216" s="13"/>
+      <c r="AI216" s="13"/>
+      <c r="AJ216" s="13"/>
+      <c r="AK216" s="13"/>
+      <c r="AL216" s="12" t="s">
+        <v>1942</v>
+      </c>
+      <c r="AM216" s="13"/>
+      <c r="AN216" s="13"/>
+    </row>
+    <row r="217" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217" s="1">
+        <v>45994.393171296295</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D217" s="3">
+        <v>37</v>
+      </c>
+      <c r="E217" s="4">
+        <v>32289</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>1766</v>
+      </c>
+      <c r="G217" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H217" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I217" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J217" s="5" t="s">
+        <v>1944</v>
+      </c>
+      <c r="K217" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L217" s="3">
+        <v>9789882729</v>
+      </c>
+      <c r="M217" s="2" t="s">
+        <v>1945</v>
+      </c>
+      <c r="N217" s="2" t="s">
+        <v>1946</v>
+      </c>
+      <c r="O217" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P217" s="3">
+        <v>620018</v>
+      </c>
+      <c r="Q217" s="2" t="s">
+        <v>2167</v>
+      </c>
+      <c r="R217" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S217" s="3">
+        <v>5</v>
+      </c>
+      <c r="T217" s="2" t="s">
+        <v>1947</v>
+      </c>
+      <c r="U217" s="2" t="s">
+        <v>1948</v>
+      </c>
+      <c r="V217" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="W217" s="4">
+        <v>44004</v>
+      </c>
+      <c r="X217" s="2" t="s">
+        <v>1949</v>
+      </c>
+      <c r="Y217" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z217" s="2" t="s">
+        <v>2171</v>
+      </c>
+      <c r="AA217" s="2" t="s">
+        <v>2171</v>
+      </c>
+      <c r="AB217" s="5" t="s">
+        <v>1950</v>
+      </c>
+      <c r="AC217" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="AD217" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="AE217" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF217" s="7">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AG217" s="7">
+        <v>0.6875</v>
+      </c>
+      <c r="AH217" s="6"/>
+      <c r="AI217" s="6"/>
+      <c r="AJ217" s="6"/>
+      <c r="AK217" s="6"/>
+      <c r="AL217" s="5" t="s">
+        <v>1951</v>
+      </c>
+      <c r="AM217" s="5" t="s">
+        <v>1952</v>
+      </c>
+      <c r="AN217" s="5" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="218" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A218" s="8">
+        <v>45994.406215277777</v>
+      </c>
+      <c r="B218" s="9" t="s">
+        <v>1954</v>
+      </c>
+      <c r="C218" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D218" s="10">
+        <v>45</v>
+      </c>
+      <c r="E218" s="11">
+        <v>29232</v>
+      </c>
+      <c r="F218" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="G218" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H218" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I218" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J218" s="12" t="s">
+        <v>1955</v>
+      </c>
+      <c r="K218" s="9" t="s">
+        <v>1956</v>
+      </c>
+      <c r="L218" s="10">
+        <v>9442092653</v>
+      </c>
+      <c r="M218" s="9" t="s">
+        <v>1957</v>
+      </c>
+      <c r="N218" s="9" t="s">
+        <v>1958</v>
+      </c>
+      <c r="O218" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="P218" s="10">
+        <v>621112</v>
+      </c>
+      <c r="Q218" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="R218" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="S218" s="10">
+        <v>4</v>
+      </c>
+      <c r="T218" s="9" t="s">
+        <v>1959</v>
+      </c>
+      <c r="U218" s="9" t="s">
+        <v>1960</v>
+      </c>
+      <c r="V218" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="W214" s="4">
-        <v>45768</v>
-      </c>
-      <c r="X214" s="2" t="s">
-        <v>1919</v>
-      </c>
-      <c r="Y214" s="2" t="s">
+      <c r="W218" s="11">
+        <v>44721</v>
+      </c>
+      <c r="X218" s="9" t="s">
+        <v>2253</v>
+      </c>
+      <c r="Y218" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z218" s="9" t="s">
+        <v>2171</v>
+      </c>
+      <c r="AA218" s="9" t="s">
+        <v>1961</v>
+      </c>
+      <c r="AB218" s="12" t="s">
+        <v>1950</v>
+      </c>
+      <c r="AC218" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="AD218" s="9" t="s">
+        <v>1962</v>
+      </c>
+      <c r="AE218" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF218" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AG218" s="14">
+        <v>0.6875</v>
+      </c>
+      <c r="AH218" s="13"/>
+      <c r="AI218" s="13"/>
+      <c r="AJ218" s="13"/>
+      <c r="AK218" s="13"/>
+      <c r="AL218" s="12" t="s">
+        <v>1963</v>
+      </c>
+      <c r="AM218" s="12" t="s">
+        <v>1964</v>
+      </c>
+      <c r="AN218" s="12" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="219" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A219" s="1">
+        <v>45994.417268518519</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>1966</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D219" s="3">
+        <v>29</v>
+      </c>
+      <c r="E219" s="4">
+        <v>35199</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="G219" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H219" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I219" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J219" s="5" t="s">
+        <v>1967</v>
+      </c>
+      <c r="K219" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L219" s="3">
+        <v>9487590559</v>
+      </c>
+      <c r="M219" s="2" t="s">
+        <v>1968</v>
+      </c>
+      <c r="N219" s="2" t="s">
+        <v>1969</v>
+      </c>
+      <c r="O219" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="P219" s="3">
+        <v>637202</v>
+      </c>
+      <c r="Q219" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="R219" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S219" s="3">
+        <v>2</v>
+      </c>
+      <c r="T219" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="U219" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="V219" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="W219" s="4">
+        <v>45617</v>
+      </c>
+      <c r="X219" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y219" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z219" s="2" t="s">
+        <v>2171</v>
+      </c>
+      <c r="AA219" s="2" t="s">
+        <v>2171</v>
+      </c>
+      <c r="AB219" s="6"/>
+      <c r="AC219" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="AD219" s="6"/>
+      <c r="AE219" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF219" s="7">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AG219" s="7">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="AH219" s="6"/>
+      <c r="AI219" s="6"/>
+      <c r="AJ219" s="6"/>
+      <c r="AK219" s="6"/>
+      <c r="AL219" s="6"/>
+      <c r="AM219" s="6"/>
+      <c r="AN219" s="6"/>
+    </row>
+    <row r="220" spans="1:40" ht="165.75" x14ac:dyDescent="0.2">
+      <c r="A220" s="8">
+        <v>45994.485266203701</v>
+      </c>
+      <c r="B220" s="9" t="s">
+        <v>1971</v>
+      </c>
+      <c r="C220" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D220" s="10">
+        <v>59</v>
+      </c>
+      <c r="E220" s="11">
+        <v>24211</v>
+      </c>
+      <c r="F220" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="G220" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H220" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I220" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J220" s="12" t="s">
+        <v>1972</v>
+      </c>
+      <c r="K220" s="9" t="s">
+        <v>1973</v>
+      </c>
+      <c r="L220" s="10">
+        <v>9447345528</v>
+      </c>
+      <c r="M220" s="9" t="s">
+        <v>1974</v>
+      </c>
+      <c r="N220" s="9" t="s">
+        <v>1975</v>
+      </c>
+      <c r="O220" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="P220" s="10">
+        <v>621105</v>
+      </c>
+      <c r="Q220" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="R220" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="S220" s="10">
+        <v>32</v>
+      </c>
+      <c r="T220" s="9" t="s">
+        <v>1976</v>
+      </c>
+      <c r="U220" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="V220" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="W220" s="11">
+        <v>43801</v>
+      </c>
+      <c r="X220" s="9" t="s">
+        <v>1977</v>
+      </c>
+      <c r="Y220" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="Z214" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA214" s="2" t="s">
-        <v>1920</v>
-      </c>
-      <c r="AB214" s="5" t="s">
-        <v>1921</v>
-      </c>
-      <c r="AC214" s="2" t="s">
-        <v>1922</v>
-      </c>
-      <c r="AD214" s="2" t="s">
-        <v>1923</v>
-      </c>
-      <c r="AE214" s="2" t="s">
+      <c r="Z220" s="9" t="s">
+        <v>2171</v>
+      </c>
+      <c r="AA220" s="9" t="s">
+        <v>1978</v>
+      </c>
+      <c r="AB220" s="12" t="s">
+        <v>1979</v>
+      </c>
+      <c r="AC220" s="9" t="s">
+        <v>1980</v>
+      </c>
+      <c r="AD220" s="9" t="s">
+        <v>2185</v>
+      </c>
+      <c r="AE220" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="AF214" s="7">
+      <c r="AF220" s="14">
         <v>0.35416666666666669</v>
       </c>
-      <c r="AG214" s="7">
+      <c r="AG220" s="14">
         <v>0.64583333333333337</v>
       </c>
-      <c r="AH214" s="6"/>
-      <c r="AI214" s="6"/>
-      <c r="AJ214" s="6"/>
-      <c r="AK214" s="6"/>
-      <c r="AL214" s="5" t="s">
-        <v>1924</v>
-      </c>
-      <c r="AM214" s="6"/>
-      <c r="AN214" s="6"/>
+      <c r="AH220" s="13"/>
+      <c r="AI220" s="13"/>
+      <c r="AJ220" s="13"/>
+      <c r="AK220" s="13"/>
+      <c r="AL220" s="12" t="s">
+        <v>1981</v>
+      </c>
+      <c r="AM220" s="9" t="s">
+        <v>1982</v>
+      </c>
+      <c r="AN220" s="13"/>
     </row>
-    <row r="215" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A215" s="8">
-        <v>45992.539317129631</v>
-      </c>
-      <c r="B215" s="9" t="s">
-        <v>1925</v>
-      </c>
-      <c r="C215" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D215" s="10">
-        <v>30</v>
-      </c>
-      <c r="E215" s="11">
-        <v>34914</v>
-      </c>
-      <c r="F215" s="9" t="s">
-        <v>1926</v>
-      </c>
-      <c r="G215" s="9" t="s">
+    <row r="221" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A221" s="1">
+        <v>45994.618009259262</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>1983</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D221" s="3">
+        <v>65</v>
+      </c>
+      <c r="E221" s="4">
+        <v>22191</v>
+      </c>
+      <c r="F221" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G221" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H215" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I215" s="9" t="s">
+      <c r="H221" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I221" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J215" s="12" t="s">
-        <v>1927</v>
-      </c>
-      <c r="K215" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="L215" s="10">
-        <v>9159874787</v>
-      </c>
-      <c r="M215" s="9" t="s">
-        <v>1928</v>
-      </c>
-      <c r="N215" s="9" t="s">
-        <v>1929</v>
-      </c>
-      <c r="O215" s="9" t="s">
+      <c r="J221" s="5" t="s">
+        <v>1984</v>
+      </c>
+      <c r="K221" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L221" s="3">
+        <v>9787319750</v>
+      </c>
+      <c r="M221" s="2" t="s">
+        <v>1985</v>
+      </c>
+      <c r="N221" s="2" t="s">
+        <v>2168</v>
+      </c>
+      <c r="O221" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="P215" s="10">
-        <v>621306</v>
-      </c>
-      <c r="Q215" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="R215" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="S215" s="10">
-        <v>2</v>
-      </c>
-      <c r="T215" s="9" t="s">
-        <v>1930</v>
-      </c>
-      <c r="U215" s="9" t="s">
-        <v>1931</v>
-      </c>
-      <c r="V215" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="W215" s="11">
-        <v>45247</v>
-      </c>
-      <c r="X215" s="9" t="s">
-        <v>1932</v>
-      </c>
-      <c r="Y215" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z215" s="9" t="s">
-        <v>796</v>
-      </c>
-      <c r="AA215" s="9" t="s">
-        <v>1933</v>
-      </c>
-      <c r="AB215" s="13"/>
-      <c r="AC215" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="AD215" s="13"/>
-      <c r="AE215" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF215" s="14">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="AG215" s="14">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="AH215" s="13"/>
-      <c r="AI215" s="13"/>
-      <c r="AJ215" s="13"/>
-      <c r="AK215" s="13"/>
-      <c r="AL215" s="13"/>
-      <c r="AM215" s="13"/>
-      <c r="AN215" s="13"/>
-    </row>
-    <row r="216" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A216" s="1">
-        <v>45993.426747685182</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>1934</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D216" s="3">
-        <v>32</v>
-      </c>
-      <c r="E216" s="4">
-        <v>34192</v>
-      </c>
-      <c r="F216" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G216" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H216" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I216" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J216" s="5" t="s">
-        <v>1935</v>
-      </c>
-      <c r="K216" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L216" s="3">
-        <v>9047488954</v>
-      </c>
-      <c r="M216" s="2" t="s">
-        <v>1936</v>
-      </c>
-      <c r="N216" s="2" t="s">
-        <v>1937</v>
-      </c>
-      <c r="O216" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="P216" s="3">
-        <v>620018</v>
-      </c>
-      <c r="Q216" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="R216" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="S216" s="3">
-        <v>1</v>
-      </c>
-      <c r="T216" s="2" t="s">
-        <v>1938</v>
-      </c>
-      <c r="U216" s="2" t="s">
-        <v>1939</v>
-      </c>
-      <c r="V216" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="W216" s="4">
-        <v>45748</v>
-      </c>
-      <c r="X216" s="2" t="s">
-        <v>1940</v>
-      </c>
-      <c r="Y216" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z216" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA216" s="2" t="s">
-        <v>1941</v>
-      </c>
-      <c r="AB216" s="6"/>
-      <c r="AC216" s="2" t="s">
-        <v>1942</v>
-      </c>
-      <c r="AD216" s="6"/>
-      <c r="AE216" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF216" s="7">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="AG216" s="7">
-        <v>0.14583333333333334</v>
-      </c>
-      <c r="AH216" s="6"/>
-      <c r="AI216" s="6"/>
-      <c r="AJ216" s="6"/>
-      <c r="AK216" s="6"/>
-      <c r="AL216" s="5" t="s">
-        <v>1943</v>
-      </c>
-      <c r="AM216" s="6"/>
-      <c r="AN216" s="6"/>
-    </row>
-    <row r="217" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A217" s="8">
-        <v>45993.819548611114</v>
-      </c>
-      <c r="B217" s="9" t="s">
-        <v>1944</v>
-      </c>
-      <c r="C217" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D217" s="10">
-        <v>45</v>
-      </c>
-      <c r="E217" s="11">
-        <v>29639</v>
-      </c>
-      <c r="F217" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="G217" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H217" s="13"/>
-      <c r="I217" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J217" s="12" t="s">
-        <v>1945</v>
-      </c>
-      <c r="K217" s="9" t="s">
-        <v>1946</v>
-      </c>
-      <c r="L217" s="10">
-        <v>9842091151</v>
-      </c>
-      <c r="M217" s="9" t="s">
-        <v>2176</v>
-      </c>
-      <c r="N217" s="9" t="s">
-        <v>1947</v>
-      </c>
-      <c r="O217" s="9" t="s">
-        <v>942</v>
-      </c>
-      <c r="P217" s="10">
-        <v>638476</v>
-      </c>
-      <c r="Q217" s="9" t="s">
-        <v>942</v>
-      </c>
-      <c r="R217" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="S217" s="10">
-        <v>7</v>
-      </c>
-      <c r="T217" s="9" t="s">
-        <v>1948</v>
-      </c>
-      <c r="U217" s="9" t="s">
-        <v>2262</v>
-      </c>
-      <c r="V217" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="W217" s="11">
-        <v>43166</v>
-      </c>
-      <c r="X217" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y217" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z217" s="9" t="s">
-        <v>2182</v>
-      </c>
-      <c r="AA217" s="9" t="s">
-        <v>2182</v>
-      </c>
-      <c r="AB217" s="12" t="s">
-        <v>1949</v>
-      </c>
-      <c r="AC217" s="9" t="s">
-        <v>2263</v>
-      </c>
-      <c r="AD217" s="13"/>
-      <c r="AE217" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF217" s="14">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="AG217" s="14">
-        <v>0.6875</v>
-      </c>
-      <c r="AH217" s="13"/>
-      <c r="AI217" s="13"/>
-      <c r="AJ217" s="13"/>
-      <c r="AK217" s="13"/>
-      <c r="AL217" s="12" t="s">
-        <v>1949</v>
-      </c>
-      <c r="AM217" s="13"/>
-      <c r="AN217" s="13"/>
-    </row>
-    <row r="218" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A218" s="1">
-        <v>45994.393171296295</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>1950</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D218" s="3">
-        <v>37</v>
-      </c>
-      <c r="E218" s="4">
-        <v>32289</v>
-      </c>
-      <c r="F218" s="2" t="s">
-        <v>1766</v>
-      </c>
-      <c r="G218" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H218" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I218" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J218" s="5" t="s">
-        <v>1951</v>
-      </c>
-      <c r="K218" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L218" s="3">
-        <v>9789882729</v>
-      </c>
-      <c r="M218" s="2" t="s">
-        <v>1952</v>
-      </c>
-      <c r="N218" s="2" t="s">
-        <v>1953</v>
-      </c>
-      <c r="O218" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="P218" s="3">
-        <v>620018</v>
-      </c>
-      <c r="Q218" s="2" t="s">
-        <v>2177</v>
-      </c>
-      <c r="R218" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="S218" s="3">
-        <v>5</v>
-      </c>
-      <c r="T218" s="2" t="s">
-        <v>1954</v>
-      </c>
-      <c r="U218" s="2" t="s">
-        <v>1955</v>
-      </c>
-      <c r="V218" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="W218" s="4">
-        <v>44004</v>
-      </c>
-      <c r="X218" s="2" t="s">
-        <v>1956</v>
-      </c>
-      <c r="Y218" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z218" s="2" t="s">
-        <v>2182</v>
-      </c>
-      <c r="AA218" s="2" t="s">
-        <v>2182</v>
-      </c>
-      <c r="AB218" s="5" t="s">
-        <v>1957</v>
-      </c>
-      <c r="AC218" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="AD218" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="AE218" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF218" s="7">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="AG218" s="7">
-        <v>0.6875</v>
-      </c>
-      <c r="AH218" s="6"/>
-      <c r="AI218" s="6"/>
-      <c r="AJ218" s="6"/>
-      <c r="AK218" s="6"/>
-      <c r="AL218" s="5" t="s">
-        <v>1958</v>
-      </c>
-      <c r="AM218" s="5" t="s">
-        <v>1959</v>
-      </c>
-      <c r="AN218" s="5" t="s">
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="219" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A219" s="8">
-        <v>45994.406215277777</v>
-      </c>
-      <c r="B219" s="9" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C219" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D219" s="10">
-        <v>45</v>
-      </c>
-      <c r="E219" s="11">
-        <v>29232</v>
-      </c>
-      <c r="F219" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="G219" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H219" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I219" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J219" s="12" t="s">
-        <v>1962</v>
-      </c>
-      <c r="K219" s="9" t="s">
-        <v>1963</v>
-      </c>
-      <c r="L219" s="10">
-        <v>9442092653</v>
-      </c>
-      <c r="M219" s="9" t="s">
-        <v>1964</v>
-      </c>
-      <c r="N219" s="9" t="s">
-        <v>1965</v>
-      </c>
-      <c r="O219" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="P219" s="10">
-        <v>621112</v>
-      </c>
-      <c r="Q219" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="R219" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="S219" s="10">
-        <v>4</v>
-      </c>
-      <c r="T219" s="9" t="s">
-        <v>1966</v>
-      </c>
-      <c r="U219" s="9" t="s">
-        <v>1967</v>
-      </c>
-      <c r="V219" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="W219" s="11">
-        <v>44721</v>
-      </c>
-      <c r="X219" s="9" t="s">
-        <v>2264</v>
-      </c>
-      <c r="Y219" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z219" s="9" t="s">
-        <v>2182</v>
-      </c>
-      <c r="AA219" s="9" t="s">
-        <v>1968</v>
-      </c>
-      <c r="AB219" s="12" t="s">
-        <v>1957</v>
-      </c>
-      <c r="AC219" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="AD219" s="9" t="s">
-        <v>1969</v>
-      </c>
-      <c r="AE219" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF219" s="14">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="AG219" s="14">
-        <v>0.6875</v>
-      </c>
-      <c r="AH219" s="13"/>
-      <c r="AI219" s="13"/>
-      <c r="AJ219" s="13"/>
-      <c r="AK219" s="13"/>
-      <c r="AL219" s="12" t="s">
-        <v>1970</v>
-      </c>
-      <c r="AM219" s="12" t="s">
-        <v>1971</v>
-      </c>
-      <c r="AN219" s="12" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="220" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A220" s="1">
-        <v>45994.417268518519</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>1973</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D220" s="3">
-        <v>29</v>
-      </c>
-      <c r="E220" s="4">
-        <v>35199</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="G220" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H220" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I220" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J220" s="5" t="s">
-        <v>1974</v>
-      </c>
-      <c r="K220" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L220" s="3">
-        <v>9487590559</v>
-      </c>
-      <c r="M220" s="2" t="s">
-        <v>1975</v>
-      </c>
-      <c r="N220" s="2" t="s">
-        <v>1976</v>
-      </c>
-      <c r="O220" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="P220" s="3">
-        <v>637202</v>
-      </c>
-      <c r="Q220" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="R220" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="S220" s="3">
-        <v>2</v>
-      </c>
-      <c r="T220" s="2" t="s">
-        <v>1977</v>
-      </c>
-      <c r="U220" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="V220" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="W220" s="4">
-        <v>45617</v>
-      </c>
-      <c r="X220" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="Y220" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z220" s="2" t="s">
-        <v>2182</v>
-      </c>
-      <c r="AA220" s="2" t="s">
-        <v>2182</v>
-      </c>
-      <c r="AB220" s="6"/>
-      <c r="AC220" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="AD220" s="6"/>
-      <c r="AE220" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF220" s="7">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="AG220" s="7">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="AH220" s="6"/>
-      <c r="AI220" s="6"/>
-      <c r="AJ220" s="6"/>
-      <c r="AK220" s="6"/>
-      <c r="AL220" s="6"/>
-      <c r="AM220" s="6"/>
-      <c r="AN220" s="6"/>
-    </row>
-    <row r="221" spans="1:40" ht="165.75">
-      <c r="A221" s="8">
-        <v>45994.485266203701</v>
-      </c>
-      <c r="B221" s="9" t="s">
-        <v>1978</v>
-      </c>
-      <c r="C221" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D221" s="10">
-        <v>59</v>
-      </c>
-      <c r="E221" s="11">
-        <v>24211</v>
-      </c>
-      <c r="F221" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="G221" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H221" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I221" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J221" s="12" t="s">
-        <v>1979</v>
-      </c>
-      <c r="K221" s="9" t="s">
-        <v>1980</v>
-      </c>
-      <c r="L221" s="10">
-        <v>9447345528</v>
-      </c>
-      <c r="M221" s="9" t="s">
-        <v>1981</v>
-      </c>
-      <c r="N221" s="9" t="s">
-        <v>1982</v>
-      </c>
-      <c r="O221" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="P221" s="10">
-        <v>621105</v>
+      <c r="P221" s="3">
+        <v>620001</v>
       </c>
       <c r="Q221" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="R221" s="9" t="s">
+      <c r="R221" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="S221" s="10">
-        <v>32</v>
-      </c>
-      <c r="T221" s="9" t="s">
-        <v>1983</v>
-      </c>
-      <c r="U221" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="V221" s="9" t="s">
+      <c r="S221" s="3">
+        <v>20</v>
+      </c>
+      <c r="T221" s="2" t="s">
+        <v>1986</v>
+      </c>
+      <c r="U221" s="2" t="s">
+        <v>1987</v>
+      </c>
+      <c r="V221" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="W221" s="4">
+        <v>43985</v>
+      </c>
+      <c r="X221" s="2" t="s">
+        <v>1988</v>
+      </c>
+      <c r="Y221" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z221" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="AA221" s="2" t="s">
+        <v>1989</v>
+      </c>
+      <c r="AB221" s="6"/>
+      <c r="AC221" s="2" t="s">
+        <v>1990</v>
+      </c>
+      <c r="AD221" s="2" t="s">
+        <v>1991</v>
+      </c>
+      <c r="AE221" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF221" s="7">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AG221" s="7">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="AH221" s="6"/>
+      <c r="AI221" s="6"/>
+      <c r="AJ221" s="6"/>
+      <c r="AK221" s="6"/>
+      <c r="AL221" s="6"/>
+      <c r="AM221" s="6"/>
+      <c r="AN221" s="6"/>
+    </row>
+    <row r="222" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A222" s="8">
+        <v>45994.692442129628</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C222" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D222" s="10">
+        <v>28</v>
+      </c>
+      <c r="E222" s="11">
+        <v>35684</v>
+      </c>
+      <c r="F222" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="G222" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="H222" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I222" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J222" s="12" t="s">
+        <v>1993</v>
+      </c>
+      <c r="K222" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="L222" s="10">
+        <v>7708422167</v>
+      </c>
+      <c r="M222" s="9" t="s">
+        <v>1994</v>
+      </c>
+      <c r="N222" s="9" t="s">
+        <v>1995</v>
+      </c>
+      <c r="O222" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="P222" s="10">
+        <v>625018</v>
+      </c>
+      <c r="Q222" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="R222" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="S222" s="10">
+        <v>0</v>
+      </c>
+      <c r="T222" s="10">
+        <v>7708422167</v>
+      </c>
+      <c r="U222" s="9" t="s">
+        <v>1996</v>
+      </c>
+      <c r="V222" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="W221" s="11">
-        <v>43801</v>
-      </c>
-      <c r="X221" s="9" t="s">
-        <v>1984</v>
-      </c>
-      <c r="Y221" s="9" t="s">
+      <c r="W222" s="11">
+        <v>45982</v>
+      </c>
+      <c r="X222" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y222" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z222" s="9" t="s">
+        <v>2171</v>
+      </c>
+      <c r="AA222" s="9" t="s">
+        <v>2254</v>
+      </c>
+      <c r="AB222" s="13"/>
+      <c r="AC222" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD222" s="13"/>
+      <c r="AE222" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF222" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AG222" s="14">
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="AH222" s="13"/>
+      <c r="AI222" s="13"/>
+      <c r="AJ222" s="13"/>
+      <c r="AK222" s="13"/>
+      <c r="AL222" s="13"/>
+      <c r="AM222" s="13"/>
+      <c r="AN222" s="13"/>
+    </row>
+    <row r="223" spans="1:40" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A223" s="1">
+        <v>45995.725115740737</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>1997</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D223" s="3">
+        <v>42</v>
+      </c>
+      <c r="E223" s="4">
+        <v>30579</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G223" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H223" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I223" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J223" s="5" t="s">
+        <v>1998</v>
+      </c>
+      <c r="K223" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="L223" s="3">
+        <v>9943907528</v>
+      </c>
+      <c r="M223" s="2" t="s">
+        <v>2097</v>
+      </c>
+      <c r="N223" s="2" t="s">
+        <v>1999</v>
+      </c>
+      <c r="O223" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P223" s="3">
+        <v>620017</v>
+      </c>
+      <c r="Q223" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="R223" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S223" s="3">
+        <v>9</v>
+      </c>
+      <c r="T223" s="2" t="s">
+        <v>2000</v>
+      </c>
+      <c r="U223" s="2" t="s">
+        <v>2001</v>
+      </c>
+      <c r="V223" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="W223" s="4">
+        <v>42639</v>
+      </c>
+      <c r="X223" s="2" t="s">
+        <v>2002</v>
+      </c>
+      <c r="Y223" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z223" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="AA223" s="2" t="s">
+        <v>2003</v>
+      </c>
+      <c r="AB223" s="6"/>
+      <c r="AC223" s="2" t="s">
+        <v>2004</v>
+      </c>
+      <c r="AD223" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="AE223" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF223" s="7">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AG223" s="7">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="AH223" s="6"/>
+      <c r="AI223" s="6"/>
+      <c r="AJ223" s="6"/>
+      <c r="AK223" s="6"/>
+      <c r="AL223" s="5"/>
+      <c r="AM223" s="5"/>
+      <c r="AN223" s="5"/>
+    </row>
+    <row r="224" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224" s="8">
+        <v>45996.555462962962</v>
+      </c>
+      <c r="B224" s="9" t="s">
+        <v>2005</v>
+      </c>
+      <c r="C224" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D224" s="10">
+        <v>41</v>
+      </c>
+      <c r="E224" s="11">
+        <v>30674</v>
+      </c>
+      <c r="F224" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="G224" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H224" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I224" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J224" s="12" t="s">
+        <v>2006</v>
+      </c>
+      <c r="K224" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="L224" s="10">
+        <v>9159012345</v>
+      </c>
+      <c r="M224" s="9" t="s">
+        <v>2169</v>
+      </c>
+      <c r="N224" s="9" t="s">
+        <v>2007</v>
+      </c>
+      <c r="O224" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="P224" s="10">
+        <v>620001</v>
+      </c>
+      <c r="Q224" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="R224" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="S224" s="10">
+        <v>11</v>
+      </c>
+      <c r="T224" s="9" t="s">
+        <v>998</v>
+      </c>
+      <c r="U224" s="9" t="s">
+        <v>2008</v>
+      </c>
+      <c r="V224" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="W224" s="11">
+        <v>42632</v>
+      </c>
+      <c r="X224" s="9" t="s">
+        <v>1000</v>
+      </c>
+      <c r="Y224" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z224" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="AA224" s="9" t="s">
+        <v>2009</v>
+      </c>
+      <c r="AB224" s="13"/>
+      <c r="AC224" s="9" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AD224" s="13"/>
+      <c r="AE224" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF224" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AG224" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AH224" s="13"/>
+      <c r="AI224" s="13"/>
+      <c r="AJ224" s="13"/>
+      <c r="AK224" s="13"/>
+      <c r="AL224" s="13"/>
+      <c r="AM224" s="13"/>
+      <c r="AN224" s="13"/>
+    </row>
+    <row r="225" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A225" s="1">
+        <v>45999.364525462966</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>2186</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D225" s="3">
+        <v>47</v>
+      </c>
+      <c r="E225" s="4">
+        <v>28227</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G225" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H225" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I225" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J225" s="5" t="s">
+        <v>2187</v>
+      </c>
+      <c r="K225" s="2" t="s">
+        <v>2188</v>
+      </c>
+      <c r="L225" s="3">
+        <v>9779772227</v>
+      </c>
+      <c r="M225" s="2" t="s">
+        <v>2189</v>
+      </c>
+      <c r="N225" s="2" t="s">
+        <v>2190</v>
+      </c>
+      <c r="O225" s="2" t="s">
+        <v>2191</v>
+      </c>
+      <c r="P225" s="3">
+        <v>620017</v>
+      </c>
+      <c r="Q225" s="2" t="s">
+        <v>2191</v>
+      </c>
+      <c r="R225" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="S225" s="3">
+        <v>17</v>
+      </c>
+      <c r="T225" s="2" t="s">
+        <v>2192</v>
+      </c>
+      <c r="U225" s="2" t="s">
+        <v>2193</v>
+      </c>
+      <c r="V225" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W225" s="4">
+        <v>39636</v>
+      </c>
+      <c r="X225" s="2" t="s">
+        <v>2194</v>
+      </c>
+      <c r="Y225" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z225" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="AA225" s="2" t="s">
+        <v>2195</v>
+      </c>
+      <c r="AB225" s="6"/>
+      <c r="AC225" s="2" t="s">
+        <v>2196</v>
+      </c>
+      <c r="AD225" s="6"/>
+      <c r="AE225" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF225" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AG225" s="7">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AH225" s="6"/>
+      <c r="AI225" s="6"/>
+      <c r="AJ225" s="6"/>
+      <c r="AK225" s="6"/>
+      <c r="AL225" s="6"/>
+      <c r="AM225" s="6"/>
+      <c r="AN225" s="6"/>
+    </row>
+    <row r="226" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A226" s="8">
+        <v>46002.523680555554</v>
+      </c>
+      <c r="B226" s="9" t="s">
+        <v>2197</v>
+      </c>
+      <c r="C226" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D226" s="10">
+        <v>67</v>
+      </c>
+      <c r="E226" s="11">
+        <v>21407</v>
+      </c>
+      <c r="F226" s="9" t="s">
+        <v>2198</v>
+      </c>
+      <c r="G226" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H226" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I226" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J226" s="12" t="s">
+        <v>2199</v>
+      </c>
+      <c r="K226" s="9" t="s">
+        <v>2200</v>
+      </c>
+      <c r="L226" s="10">
+        <v>9842206348</v>
+      </c>
+      <c r="M226" s="9" t="s">
+        <v>2201</v>
+      </c>
+      <c r="N226" s="9" t="s">
+        <v>2202</v>
+      </c>
+      <c r="O226" s="9" t="s">
+        <v>1238</v>
+      </c>
+      <c r="P226" s="10">
+        <v>641030</v>
+      </c>
+      <c r="Q226" s="9" t="s">
+        <v>1238</v>
+      </c>
+      <c r="R226" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="S226" s="10">
+        <v>2</v>
+      </c>
+      <c r="T226" s="9" t="s">
+        <v>2203</v>
+      </c>
+      <c r="U226" s="9" t="s">
+        <v>2204</v>
+      </c>
+      <c r="V226" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="W226" s="11">
+        <v>45282</v>
+      </c>
+      <c r="X226" s="9" t="s">
+        <v>2205</v>
+      </c>
+      <c r="Y226" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="Z221" s="9" t="s">
-        <v>2182</v>
-      </c>
-      <c r="AA221" s="9" t="s">
-        <v>1985</v>
-      </c>
-      <c r="AB221" s="12" t="s">
-        <v>1986</v>
-      </c>
-      <c r="AC221" s="9" t="s">
-        <v>1987</v>
-      </c>
-      <c r="AD221" s="9" t="s">
-        <v>2196</v>
-      </c>
-      <c r="AE221" s="9" t="s">
+      <c r="Z226" s="9" t="s">
+        <v>2171</v>
+      </c>
+      <c r="AA226" s="9" t="s">
+        <v>2206</v>
+      </c>
+      <c r="AB226" s="13"/>
+      <c r="AC226" s="9" t="s">
+        <v>2207</v>
+      </c>
+      <c r="AD226" s="13"/>
+      <c r="AE226" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="AF221" s="14">
+      <c r="AF226" s="14">
         <v>0.35416666666666669</v>
       </c>
-      <c r="AG221" s="14">
+      <c r="AG226" s="14">
         <v>0.64583333333333337</v>
       </c>
-      <c r="AH221" s="13"/>
-      <c r="AI221" s="13"/>
-      <c r="AJ221" s="13"/>
-      <c r="AK221" s="13"/>
-      <c r="AL221" s="12" t="s">
-        <v>1988</v>
-      </c>
-      <c r="AM221" s="9" t="s">
-        <v>1989</v>
-      </c>
-      <c r="AN221" s="13"/>
+      <c r="AH226" s="13"/>
+      <c r="AI226" s="13"/>
+      <c r="AJ226" s="13"/>
+      <c r="AK226" s="13"/>
+      <c r="AL226" s="13"/>
+      <c r="AM226" s="13"/>
+      <c r="AN226" s="13"/>
     </row>
-    <row r="222" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A222" s="1">
-        <v>45994.618009259262</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>1990</v>
-      </c>
-      <c r="C222" s="2" t="s">
+    <row r="227" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227" s="1">
+        <v>46010.499398148146</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D227" s="3">
+        <v>36</v>
+      </c>
+      <c r="E227" s="4">
+        <v>32659</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H227" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I227" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J227" s="5" t="s">
+        <v>2209</v>
+      </c>
+      <c r="K227" s="2" t="s">
+        <v>2210</v>
+      </c>
+      <c r="L227" s="3">
+        <v>9486197358</v>
+      </c>
+      <c r="M227" s="2" t="s">
+        <v>2211</v>
+      </c>
+      <c r="N227" s="2" t="s">
+        <v>2212</v>
+      </c>
+      <c r="O227" s="2" t="s">
+        <v>2191</v>
+      </c>
+      <c r="P227" s="3">
+        <v>641048</v>
+      </c>
+      <c r="Q227" s="2" t="s">
+        <v>2191</v>
+      </c>
+      <c r="R227" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S227" s="3">
+        <v>7</v>
+      </c>
+      <c r="T227" s="2" t="s">
+        <v>2213</v>
+      </c>
+      <c r="U227" s="2" t="s">
+        <v>2214</v>
+      </c>
+      <c r="V227" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="W227" s="4">
+        <v>44760</v>
+      </c>
+      <c r="X227" s="2" t="s">
+        <v>2215</v>
+      </c>
+      <c r="Y227" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z227" s="2" t="s">
+        <v>2216</v>
+      </c>
+      <c r="AA227" s="2" t="s">
+        <v>2217</v>
+      </c>
+      <c r="AB227" s="6"/>
+      <c r="AC227" s="2" t="s">
+        <v>2218</v>
+      </c>
+      <c r="AD227" s="6"/>
+      <c r="AE227" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF227" s="7">
+        <v>0.375</v>
+      </c>
+      <c r="AG227" s="7">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="AH227" s="6"/>
+      <c r="AI227" s="6"/>
+      <c r="AJ227" s="6"/>
+      <c r="AK227" s="6"/>
+      <c r="AL227" s="6"/>
+      <c r="AM227" s="6"/>
+      <c r="AN227" s="6"/>
+    </row>
+    <row r="228" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A228" s="8">
+        <v>46015.435925925929</v>
+      </c>
+      <c r="B228" s="9" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C228" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D228" s="10">
+        <v>41</v>
+      </c>
+      <c r="E228" s="11">
+        <v>30438</v>
+      </c>
+      <c r="F228" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="G228" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="H228" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="I228" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J228" s="12" t="s">
+        <v>2220</v>
+      </c>
+      <c r="K228" s="9" t="s">
+        <v>1244</v>
+      </c>
+      <c r="L228" s="10">
+        <v>9003184325</v>
+      </c>
+      <c r="M228" s="9" t="s">
+        <v>2221</v>
+      </c>
+      <c r="N228" s="9" t="s">
+        <v>2222</v>
+      </c>
+      <c r="O228" s="9" t="s">
+        <v>2191</v>
+      </c>
+      <c r="P228" s="10">
+        <v>620006</v>
+      </c>
+      <c r="Q228" s="9" t="s">
+        <v>2191</v>
+      </c>
+      <c r="R228" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="S228" s="10">
+        <v>5</v>
+      </c>
+      <c r="T228" s="9" t="s">
+        <v>2223</v>
+      </c>
+      <c r="U228" s="9" t="s">
+        <v>2224</v>
+      </c>
+      <c r="V228" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="W228" s="11">
+        <v>45796</v>
+      </c>
+      <c r="X228" s="9" t="s">
+        <v>2225</v>
+      </c>
+      <c r="Y228" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z228" s="9" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AA228" s="9" t="s">
+        <v>2226</v>
+      </c>
+      <c r="AB228" s="12" t="s">
+        <v>2227</v>
+      </c>
+      <c r="AC228" s="9" t="s">
+        <v>2228</v>
+      </c>
+      <c r="AD228" s="9" t="s">
+        <v>2229</v>
+      </c>
+      <c r="AE228" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF228" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="AG228" s="14">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="AH228" s="13"/>
+      <c r="AI228" s="13"/>
+      <c r="AJ228" s="13"/>
+      <c r="AK228" s="13"/>
+      <c r="AL228" s="13"/>
+      <c r="AM228" s="13"/>
+      <c r="AN228" s="13"/>
+    </row>
+    <row r="229" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A229" s="1">
+        <v>46017.628229166665</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>2230</v>
+      </c>
+      <c r="C229" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D222" s="3">
-        <v>65</v>
-      </c>
-      <c r="E222" s="4">
-        <v>22191</v>
-      </c>
-      <c r="F222" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G222" s="2" t="s">
+      <c r="D229" s="3">
+        <v>48</v>
+      </c>
+      <c r="E229" s="4">
+        <v>28613</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>2231</v>
+      </c>
+      <c r="G229" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H229" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I229" s="2" t="s">
+        <v>1712</v>
+      </c>
+      <c r="J229" s="5" t="s">
+        <v>2232</v>
+      </c>
+      <c r="K229" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L229" s="3">
+        <v>7598539347</v>
+      </c>
+      <c r="M229" s="2" t="s">
+        <v>2233</v>
+      </c>
+      <c r="N229" s="2" t="s">
+        <v>2234</v>
+      </c>
+      <c r="O229" s="2" t="s">
+        <v>2191</v>
+      </c>
+      <c r="P229" s="3">
+        <v>620006</v>
+      </c>
+      <c r="Q229" s="9" t="s">
+        <v>2191</v>
+      </c>
+      <c r="R229" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="S229" s="3">
+        <v>21</v>
+      </c>
+      <c r="T229" s="2" t="s">
+        <v>2235</v>
+      </c>
+      <c r="U229" s="2" t="s">
+        <v>2236</v>
+      </c>
+      <c r="V229" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="W229" s="4">
+        <v>44303</v>
+      </c>
+      <c r="X229" s="2" t="s">
+        <v>2237</v>
+      </c>
+      <c r="Y229" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z229" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="AA229" s="2" t="s">
+        <v>2238</v>
+      </c>
+      <c r="AB229" s="6"/>
+      <c r="AC229" s="2" t="s">
+        <v>2239</v>
+      </c>
+      <c r="AD229" s="6"/>
+      <c r="AE229" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF229" s="7">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AG229" s="7">
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="AH229" s="6"/>
+      <c r="AI229" s="6"/>
+      <c r="AJ229" s="6"/>
+      <c r="AK229" s="6"/>
+      <c r="AL229" s="6"/>
+      <c r="AM229" s="6"/>
+      <c r="AN229" s="6"/>
+    </row>
+    <row r="230" spans="1:46" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A230" s="8">
+        <v>46028.591863425929</v>
+      </c>
+      <c r="B230" s="9" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C230" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D230" s="10">
+        <v>29</v>
+      </c>
+      <c r="E230" s="11">
+        <v>34892</v>
+      </c>
+      <c r="F230" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="G230" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="H222" s="2" t="s">
+      <c r="H230" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="I222" s="2" t="s">
+      <c r="I230" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="J222" s="5" t="s">
-        <v>1991</v>
-      </c>
-      <c r="K222" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L222" s="3">
-        <v>9787319750</v>
-      </c>
-      <c r="M222" s="2" t="s">
-        <v>1992</v>
-      </c>
-      <c r="N222" s="2" t="s">
-        <v>2178</v>
-      </c>
-      <c r="O222" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="P222" s="3">
-        <v>620001</v>
-      </c>
-      <c r="Q222" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="R222" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="S222" s="3">
-        <v>20</v>
-      </c>
-      <c r="T222" s="2" t="s">
-        <v>1993</v>
-      </c>
-      <c r="U222" s="2" t="s">
-        <v>1994</v>
-      </c>
-      <c r="V222" s="2" t="s">
+      <c r="J230" s="12" t="s">
+        <v>2241</v>
+      </c>
+      <c r="K230" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="L230" s="10">
+        <v>9976115391</v>
+      </c>
+      <c r="M230" s="9" t="s">
+        <v>2242</v>
+      </c>
+      <c r="N230" s="9" t="s">
+        <v>2243</v>
+      </c>
+      <c r="O230" s="9" t="s">
+        <v>1819</v>
+      </c>
+      <c r="P230" s="10">
+        <v>608001</v>
+      </c>
+      <c r="Q230" s="9" t="s">
+        <v>888</v>
+      </c>
+      <c r="R230" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="S230" s="10">
+        <v>1</v>
+      </c>
+      <c r="T230" s="9" t="s">
+        <v>2244</v>
+      </c>
+      <c r="U230" s="9" t="s">
+        <v>2245</v>
+      </c>
+      <c r="V230" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="W222" s="4">
-        <v>43985</v>
-      </c>
-      <c r="X222" s="2" t="s">
-        <v>1995</v>
-      </c>
-      <c r="Y222" s="2" t="s">
+      <c r="W230" s="11">
+        <v>45735</v>
+      </c>
+      <c r="X230" s="9" t="s">
+        <v>2246</v>
+      </c>
+      <c r="Y230" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="Z222" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="AA222" s="2" t="s">
-        <v>1996</v>
-      </c>
-      <c r="AB222" s="6"/>
-      <c r="AC222" s="2" t="s">
-        <v>1997</v>
-      </c>
-      <c r="AD222" s="2" t="s">
-        <v>1998</v>
-      </c>
-      <c r="AE222" s="2" t="s">
+      <c r="Z230" s="9" t="s">
+        <v>2171</v>
+      </c>
+      <c r="AA230" s="9" t="s">
+        <v>2247</v>
+      </c>
+      <c r="AB230" s="13"/>
+      <c r="AC230" s="9" t="s">
+        <v>2248</v>
+      </c>
+      <c r="AD230" s="13"/>
+      <c r="AE230" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="AF222" s="7">
+      <c r="AF230" s="14">
         <v>0.35416666666666669</v>
       </c>
-      <c r="AG222" s="7">
+      <c r="AG230" s="14">
         <v>0.64583333333333337</v>
       </c>
-      <c r="AH222" s="6"/>
-      <c r="AI222" s="6"/>
-      <c r="AJ222" s="6"/>
-      <c r="AK222" s="6"/>
-      <c r="AL222" s="6"/>
-      <c r="AM222" s="6"/>
-      <c r="AN222" s="6"/>
+      <c r="AH230" s="13"/>
+      <c r="AI230" s="13"/>
+      <c r="AJ230" s="13"/>
+      <c r="AK230" s="13"/>
+      <c r="AL230" s="13"/>
+      <c r="AM230" s="13"/>
+      <c r="AN230" s="13"/>
     </row>
-    <row r="223" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A223" s="8">
-        <v>45994.692442129628</v>
-      </c>
-      <c r="B223" s="9" t="s">
-        <v>1999</v>
-      </c>
-      <c r="C223" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D223" s="10">
+    <row r="231" spans="1:46" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="1">
+        <v>46032.41710648148</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>2261</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D231" s="3">
         <v>28</v>
       </c>
-      <c r="E223" s="11">
-        <v>35684</v>
-      </c>
-      <c r="F223" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="G223" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="H223" s="9" t="s">
+      <c r="E231" s="4">
+        <v>46099</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="G231" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H231" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I223" s="9" t="s">
+      <c r="I231" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J223" s="12" t="s">
-        <v>2000</v>
-      </c>
-      <c r="K223" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="L223" s="10">
-        <v>7708422167</v>
-      </c>
-      <c r="M223" s="9" t="s">
-        <v>2001</v>
-      </c>
-      <c r="N223" s="9" t="s">
-        <v>2002</v>
-      </c>
-      <c r="O223" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="P223" s="10">
-        <v>625018</v>
-      </c>
-      <c r="Q223" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="R223" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="S223" s="10">
-        <v>0</v>
-      </c>
-      <c r="T223" s="10">
-        <v>7708422167</v>
-      </c>
-      <c r="U223" s="9" t="s">
-        <v>2003</v>
-      </c>
-      <c r="V223" s="9" t="s">
+      <c r="J231" s="5" t="s">
+        <v>2255</v>
+      </c>
+      <c r="K231" s="2" t="s">
+        <v>2256</v>
+      </c>
+      <c r="L231" s="3">
+        <v>8098893437</v>
+      </c>
+      <c r="M231" s="2" t="s">
+        <v>2257</v>
+      </c>
+      <c r="N231" s="2" t="s">
+        <v>2258</v>
+      </c>
+      <c r="O231" s="2" t="s">
+        <v>2191</v>
+      </c>
+      <c r="P231" s="3">
+        <v>620019</v>
+      </c>
+      <c r="Q231" s="2" t="s">
+        <v>2191</v>
+      </c>
+      <c r="R231" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="S231" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T231" s="3">
+        <v>8098893437</v>
+      </c>
+      <c r="U231" s="2" t="s">
+        <v>2259</v>
+      </c>
+      <c r="V231" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W223" s="11">
-        <v>45982</v>
-      </c>
-      <c r="X223" s="9" t="s">
+      <c r="W231" s="4">
+        <v>45733</v>
+      </c>
+      <c r="X231" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Y223" s="9" t="s">
+      <c r="Y231" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="Z223" s="9" t="s">
-        <v>2182</v>
-      </c>
-      <c r="AA223" s="9" t="s">
-        <v>2265</v>
-      </c>
-      <c r="AB223" s="13"/>
-      <c r="AC223" s="9" t="s">
+      <c r="Z231" s="2" t="s">
+        <v>2171</v>
+      </c>
+      <c r="AA231" s="2" t="s">
+        <v>2260</v>
+      </c>
+      <c r="AB231" s="6"/>
+      <c r="AC231" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="AD223" s="13"/>
-      <c r="AE223" s="9" t="s">
+      <c r="AD231" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE231" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF223" s="14">
+      <c r="AF231" s="7">
         <v>0.35416666666666669</v>
       </c>
-      <c r="AG223" s="14">
-        <v>0.14583333333333334</v>
-      </c>
-      <c r="AH223" s="13"/>
-      <c r="AI223" s="13"/>
-      <c r="AJ223" s="13"/>
-      <c r="AK223" s="13"/>
-      <c r="AL223" s="13"/>
-      <c r="AM223" s="13"/>
-      <c r="AN223" s="13"/>
-    </row>
-    <row r="224" spans="1:40" ht="409.5">
-      <c r="A224" s="1">
-        <v>45995.725115740737</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>2004</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D224" s="3">
-        <v>42</v>
-      </c>
-      <c r="E224" s="4">
-        <v>30579</v>
-      </c>
-      <c r="F224" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G224" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H224" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I224" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J224" s="5" t="s">
-        <v>2005</v>
-      </c>
-      <c r="K224" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="L224" s="3">
-        <v>9943907528</v>
-      </c>
-      <c r="M224" s="2" t="s">
-        <v>2104</v>
-      </c>
-      <c r="N224" s="2" t="s">
-        <v>2006</v>
-      </c>
-      <c r="O224" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="P224" s="3">
-        <v>620017</v>
-      </c>
-      <c r="Q224" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="R224" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="S224" s="3">
-        <v>9</v>
-      </c>
-      <c r="T224" s="2" t="s">
-        <v>2007</v>
-      </c>
-      <c r="U224" s="2" t="s">
-        <v>2008</v>
-      </c>
-      <c r="V224" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="W224" s="4">
-        <v>42639</v>
-      </c>
-      <c r="X224" s="2" t="s">
-        <v>2009</v>
-      </c>
-      <c r="Y224" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z224" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="AA224" s="2" t="s">
-        <v>2010</v>
-      </c>
-      <c r="AB224" s="6"/>
-      <c r="AC224" s="2" t="s">
-        <v>2011</v>
-      </c>
-      <c r="AD224" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="AE224" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF224" s="7">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="AG224" s="7">
+      <c r="AG231" s="7">
         <v>0.64583333333333337</v>
       </c>
-      <c r="AH224" s="6"/>
-      <c r="AI224" s="6"/>
-      <c r="AJ224" s="6"/>
-      <c r="AK224" s="6"/>
-      <c r="AL224" s="5"/>
-      <c r="AM224" s="5"/>
-      <c r="AN224" s="5"/>
-    </row>
-    <row r="225" spans="1:46" ht="15.75" customHeight="1">
-      <c r="A225" s="8">
-        <v>45996.555462962962</v>
-      </c>
-      <c r="B225" s="9" t="s">
-        <v>2012</v>
-      </c>
-      <c r="C225" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D225" s="10">
-        <v>41</v>
-      </c>
-      <c r="E225" s="11">
-        <v>30674</v>
-      </c>
-      <c r="F225" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="G225" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H225" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I225" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J225" s="12" t="s">
-        <v>2013</v>
-      </c>
-      <c r="K225" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="L225" s="10">
-        <v>9159012345</v>
-      </c>
-      <c r="M225" s="9" t="s">
-        <v>2179</v>
-      </c>
-      <c r="N225" s="9" t="s">
-        <v>2014</v>
-      </c>
-      <c r="O225" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="P225" s="10">
-        <v>620001</v>
-      </c>
-      <c r="Q225" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="R225" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="S225" s="10">
-        <v>11</v>
-      </c>
-      <c r="T225" s="9" t="s">
-        <v>998</v>
-      </c>
-      <c r="U225" s="9" t="s">
-        <v>2015</v>
-      </c>
-      <c r="V225" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="W225" s="11">
-        <v>42632</v>
-      </c>
-      <c r="X225" s="9" t="s">
-        <v>1000</v>
-      </c>
-      <c r="Y225" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z225" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="AA225" s="9" t="s">
-        <v>2016</v>
-      </c>
-      <c r="AB225" s="13"/>
-      <c r="AC225" s="9" t="s">
-        <v>1001</v>
-      </c>
-      <c r="AD225" s="13"/>
-      <c r="AE225" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF225" s="14">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="AG225" s="14">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="AH225" s="13"/>
-      <c r="AI225" s="13"/>
-      <c r="AJ225" s="13"/>
-      <c r="AK225" s="13"/>
-      <c r="AL225" s="13"/>
-      <c r="AM225" s="13"/>
-      <c r="AN225" s="13"/>
-    </row>
-    <row r="226" spans="1:46" ht="15.75" customHeight="1">
-      <c r="A226" s="1">
-        <v>45999.364525462966</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>2197</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D226" s="3">
-        <v>47</v>
-      </c>
-      <c r="E226" s="4">
-        <v>28227</v>
-      </c>
-      <c r="F226" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G226" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H226" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I226" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J226" s="5" t="s">
-        <v>2198</v>
-      </c>
-      <c r="K226" s="2" t="s">
-        <v>2199</v>
-      </c>
-      <c r="L226" s="3">
-        <v>9779772227</v>
-      </c>
-      <c r="M226" s="2" t="s">
-        <v>2200</v>
-      </c>
-      <c r="N226" s="2" t="s">
-        <v>2201</v>
-      </c>
-      <c r="O226" s="2" t="s">
-        <v>2202</v>
-      </c>
-      <c r="P226" s="3">
-        <v>620017</v>
-      </c>
-      <c r="Q226" s="2" t="s">
-        <v>2202</v>
-      </c>
-      <c r="R226" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="S226" s="3">
-        <v>17</v>
-      </c>
-      <c r="T226" s="2" t="s">
-        <v>2203</v>
-      </c>
-      <c r="U226" s="2" t="s">
-        <v>2204</v>
-      </c>
-      <c r="V226" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="W226" s="4">
-        <v>39636</v>
-      </c>
-      <c r="X226" s="2" t="s">
-        <v>2205</v>
-      </c>
-      <c r="Y226" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z226" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="AA226" s="2" t="s">
-        <v>2206</v>
-      </c>
-      <c r="AB226" s="6"/>
-      <c r="AC226" s="2" t="s">
-        <v>2207</v>
-      </c>
-      <c r="AD226" s="6"/>
-      <c r="AE226" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF226" s="7">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="AG226" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="AH226" s="6"/>
-      <c r="AI226" s="6"/>
-      <c r="AJ226" s="6"/>
-      <c r="AK226" s="6"/>
-      <c r="AL226" s="6"/>
-      <c r="AM226" s="6"/>
-      <c r="AN226" s="6"/>
-    </row>
-    <row r="227" spans="1:46" ht="15.75" customHeight="1">
-      <c r="A227" s="8">
-        <v>46002.523680555554</v>
-      </c>
-      <c r="B227" s="9" t="s">
-        <v>2208</v>
-      </c>
-      <c r="C227" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D227" s="10">
-        <v>67</v>
-      </c>
-      <c r="E227" s="11">
-        <v>21407</v>
-      </c>
-      <c r="F227" s="9" t="s">
-        <v>2209</v>
-      </c>
-      <c r="G227" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H227" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I227" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J227" s="12" t="s">
-        <v>2210</v>
-      </c>
-      <c r="K227" s="9" t="s">
-        <v>2211</v>
-      </c>
-      <c r="L227" s="10">
-        <v>9842206348</v>
-      </c>
-      <c r="M227" s="9" t="s">
-        <v>2212</v>
-      </c>
-      <c r="N227" s="9" t="s">
-        <v>2213</v>
-      </c>
-      <c r="O227" s="9" t="s">
-        <v>1238</v>
-      </c>
-      <c r="P227" s="10">
-        <v>641030</v>
-      </c>
-      <c r="Q227" s="9" t="s">
-        <v>1238</v>
-      </c>
-      <c r="R227" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="S227" s="10">
-        <v>2</v>
-      </c>
-      <c r="T227" s="9" t="s">
-        <v>2214</v>
-      </c>
-      <c r="U227" s="9" t="s">
-        <v>2215</v>
-      </c>
-      <c r="V227" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="W227" s="11">
-        <v>45282</v>
-      </c>
-      <c r="X227" s="9" t="s">
-        <v>2216</v>
-      </c>
-      <c r="Y227" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z227" s="9" t="s">
-        <v>2182</v>
-      </c>
-      <c r="AA227" s="9" t="s">
-        <v>2217</v>
-      </c>
-      <c r="AB227" s="13"/>
-      <c r="AC227" s="9" t="s">
-        <v>2218</v>
-      </c>
-      <c r="AD227" s="13"/>
-      <c r="AE227" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF227" s="14">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="AG227" s="14">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="AH227" s="13"/>
-      <c r="AI227" s="13"/>
-      <c r="AJ227" s="13"/>
-      <c r="AK227" s="13"/>
-      <c r="AL227" s="13"/>
-      <c r="AM227" s="13"/>
-      <c r="AN227" s="13"/>
-    </row>
-    <row r="228" spans="1:46" ht="15.75" customHeight="1">
-      <c r="A228" s="1">
-        <v>46010.499398148146</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>2219</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D228" s="3">
-        <v>36</v>
-      </c>
-      <c r="E228" s="4">
-        <v>32659</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="G228" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H228" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I228" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J228" s="5" t="s">
-        <v>2220</v>
-      </c>
-      <c r="K228" s="2" t="s">
-        <v>2221</v>
-      </c>
-      <c r="L228" s="3">
-        <v>9486197358</v>
-      </c>
-      <c r="M228" s="2" t="s">
-        <v>2222</v>
-      </c>
-      <c r="N228" s="2" t="s">
-        <v>2223</v>
-      </c>
-      <c r="O228" s="2" t="s">
-        <v>2202</v>
-      </c>
-      <c r="P228" s="3">
-        <v>641048</v>
-      </c>
-      <c r="Q228" s="2" t="s">
-        <v>2202</v>
-      </c>
-      <c r="R228" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="S228" s="3">
-        <v>7</v>
-      </c>
-      <c r="T228" s="2" t="s">
-        <v>2224</v>
-      </c>
-      <c r="U228" s="2" t="s">
-        <v>2225</v>
-      </c>
-      <c r="V228" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="W228" s="4">
-        <v>44760</v>
-      </c>
-      <c r="X228" s="2" t="s">
-        <v>2226</v>
-      </c>
-      <c r="Y228" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z228" s="2" t="s">
-        <v>2227</v>
-      </c>
-      <c r="AA228" s="2" t="s">
-        <v>2228</v>
-      </c>
-      <c r="AB228" s="6"/>
-      <c r="AC228" s="2" t="s">
-        <v>2229</v>
-      </c>
-      <c r="AD228" s="6"/>
-      <c r="AE228" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF228" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="AG228" s="7">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="AH228" s="6"/>
-      <c r="AI228" s="6"/>
-      <c r="AJ228" s="6"/>
-      <c r="AK228" s="6"/>
-      <c r="AL228" s="6"/>
-      <c r="AM228" s="6"/>
-      <c r="AN228" s="6"/>
-    </row>
-    <row r="229" spans="1:46" ht="15.75" customHeight="1">
-      <c r="A229" s="8">
-        <v>46015.435925925929</v>
-      </c>
-      <c r="B229" s="9" t="s">
-        <v>2230</v>
-      </c>
-      <c r="C229" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D229" s="10">
-        <v>41</v>
-      </c>
-      <c r="E229" s="11">
-        <v>30438</v>
-      </c>
-      <c r="F229" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="G229" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="H229" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="I229" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J229" s="12" t="s">
-        <v>2231</v>
-      </c>
-      <c r="K229" s="9" t="s">
-        <v>1244</v>
-      </c>
-      <c r="L229" s="10">
-        <v>9003184325</v>
-      </c>
-      <c r="M229" s="9" t="s">
-        <v>2232</v>
-      </c>
-      <c r="N229" s="9" t="s">
-        <v>2233</v>
-      </c>
-      <c r="O229" s="9" t="s">
-        <v>2202</v>
-      </c>
-      <c r="P229" s="10">
-        <v>620006</v>
-      </c>
-      <c r="Q229" s="9" t="s">
-        <v>2202</v>
-      </c>
-      <c r="R229" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="S229" s="10">
-        <v>5</v>
-      </c>
-      <c r="T229" s="9" t="s">
-        <v>2234</v>
-      </c>
-      <c r="U229" s="9" t="s">
-        <v>2235</v>
-      </c>
-      <c r="V229" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="W229" s="11">
-        <v>45796</v>
-      </c>
-      <c r="X229" s="9" t="s">
-        <v>2236</v>
-      </c>
-      <c r="Y229" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z229" s="9" t="s">
-        <v>1036</v>
-      </c>
-      <c r="AA229" s="9" t="s">
-        <v>2237</v>
-      </c>
-      <c r="AB229" s="12" t="s">
-        <v>2238</v>
-      </c>
-      <c r="AC229" s="9" t="s">
-        <v>2239</v>
-      </c>
-      <c r="AD229" s="9" t="s">
-        <v>2240</v>
-      </c>
-      <c r="AE229" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF229" s="14">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="AG229" s="14">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="AH229" s="13"/>
-      <c r="AI229" s="13"/>
-      <c r="AJ229" s="13"/>
-      <c r="AK229" s="13"/>
-      <c r="AL229" s="13"/>
-      <c r="AM229" s="13"/>
-      <c r="AN229" s="13"/>
-    </row>
-    <row r="230" spans="1:46" ht="15.75" customHeight="1">
-      <c r="A230" s="1">
-        <v>46017.628229166665</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>2241</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D230" s="3">
-        <v>48</v>
-      </c>
-      <c r="E230" s="4">
-        <v>28613</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>2242</v>
-      </c>
-      <c r="G230" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H230" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I230" s="2" t="s">
-        <v>1712</v>
-      </c>
-      <c r="J230" s="5" t="s">
-        <v>2243</v>
-      </c>
-      <c r="K230" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L230" s="3">
-        <v>7598539347</v>
-      </c>
-      <c r="M230" s="2" t="s">
-        <v>2244</v>
-      </c>
-      <c r="N230" s="2" t="s">
-        <v>2245</v>
-      </c>
-      <c r="O230" s="2" t="s">
-        <v>2202</v>
-      </c>
-      <c r="P230" s="3">
-        <v>620006</v>
-      </c>
-      <c r="Q230" s="9" t="s">
-        <v>2202</v>
-      </c>
-      <c r="R230" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="S230" s="3">
-        <v>21</v>
-      </c>
-      <c r="T230" s="2" t="s">
-        <v>2246</v>
-      </c>
-      <c r="U230" s="2" t="s">
-        <v>2247</v>
-      </c>
-      <c r="V230" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="W230" s="4">
-        <v>44303</v>
-      </c>
-      <c r="X230" s="2" t="s">
-        <v>2248</v>
-      </c>
-      <c r="Y230" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z230" s="2" t="s">
-        <v>1374</v>
-      </c>
-      <c r="AA230" s="2" t="s">
-        <v>2249</v>
-      </c>
-      <c r="AB230" s="6"/>
-      <c r="AC230" s="2" t="s">
-        <v>2250</v>
-      </c>
-      <c r="AD230" s="6"/>
-      <c r="AE230" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF230" s="7">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="AG230" s="7">
-        <v>0.14583333333333334</v>
-      </c>
-      <c r="AH230" s="6"/>
-      <c r="AI230" s="6"/>
-      <c r="AJ230" s="6"/>
-      <c r="AK230" s="6"/>
-      <c r="AL230" s="6"/>
-      <c r="AM230" s="6"/>
-      <c r="AN230" s="6"/>
-    </row>
-    <row r="231" spans="1:46" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A231" s="8">
-        <v>46028.591863425929</v>
-      </c>
-      <c r="B231" s="9" t="s">
-        <v>2251</v>
-      </c>
-      <c r="C231" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D231" s="10">
-        <v>29</v>
-      </c>
-      <c r="E231" s="11">
-        <v>34892</v>
-      </c>
-      <c r="F231" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="G231" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H231" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="I231" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J231" s="12" t="s">
-        <v>2252</v>
-      </c>
-      <c r="K231" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="L231" s="10">
-        <v>9976115391</v>
-      </c>
-      <c r="M231" s="9" t="s">
-        <v>2253</v>
-      </c>
-      <c r="N231" s="9" t="s">
-        <v>2254</v>
-      </c>
-      <c r="O231" s="9" t="s">
-        <v>1819</v>
-      </c>
-      <c r="P231" s="10">
-        <v>608001</v>
-      </c>
-      <c r="Q231" s="9" t="s">
-        <v>888</v>
-      </c>
-      <c r="R231" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="S231" s="10">
-        <v>1</v>
-      </c>
-      <c r="T231" s="9" t="s">
-        <v>2255</v>
-      </c>
-      <c r="U231" s="9" t="s">
-        <v>2256</v>
-      </c>
-      <c r="V231" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="W231" s="11">
-        <v>45735</v>
-      </c>
-      <c r="X231" s="9" t="s">
-        <v>2257</v>
-      </c>
-      <c r="Y231" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z231" s="9" t="s">
-        <v>2182</v>
-      </c>
-      <c r="AA231" s="9" t="s">
-        <v>2258</v>
-      </c>
-      <c r="AB231" s="13"/>
-      <c r="AC231" s="9" t="s">
-        <v>2259</v>
-      </c>
-      <c r="AD231" s="13"/>
-      <c r="AE231" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF231" s="14">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="AG231" s="14">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="AH231" s="13"/>
-      <c r="AI231" s="13"/>
-      <c r="AJ231" s="13"/>
-      <c r="AK231" s="13"/>
-      <c r="AL231" s="13"/>
-      <c r="AM231" s="13"/>
-      <c r="AN231" s="13"/>
-    </row>
-    <row r="232" spans="1:46" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A232" s="1">
-        <v>46032.41710648148</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>2272</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D232" s="3">
-        <v>28</v>
-      </c>
-      <c r="E232" s="4">
-        <v>46099</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="G232" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H232" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I232" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J232" s="5" t="s">
-        <v>2266</v>
-      </c>
-      <c r="K232" s="2" t="s">
-        <v>2267</v>
-      </c>
-      <c r="L232" s="3">
-        <v>8098893437</v>
-      </c>
-      <c r="M232" s="2" t="s">
-        <v>2268</v>
-      </c>
-      <c r="N232" s="2" t="s">
-        <v>2269</v>
-      </c>
-      <c r="O232" s="2" t="s">
-        <v>2202</v>
-      </c>
-      <c r="P232" s="3">
-        <v>620019</v>
-      </c>
-      <c r="Q232" s="2" t="s">
-        <v>2202</v>
-      </c>
-      <c r="R232" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="S232" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T232" s="3">
-        <v>8098893437</v>
-      </c>
-      <c r="U232" s="2" t="s">
-        <v>2270</v>
-      </c>
-      <c r="V232" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="W232" s="4">
-        <v>45733</v>
-      </c>
-      <c r="X232" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y232" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z232" s="2" t="s">
-        <v>2182</v>
-      </c>
-      <c r="AA232" s="2" t="s">
-        <v>2271</v>
-      </c>
-      <c r="AB232" s="6"/>
-      <c r="AC232" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD232" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AE232" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF232" s="7">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="AG232" s="7">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="AH232" s="6"/>
-      <c r="AI232" s="6"/>
-      <c r="AJ232" s="6"/>
-      <c r="AK232" s="6"/>
-      <c r="AL232" s="6"/>
-      <c r="AM232" s="6"/>
-      <c r="AN232" s="6"/>
-      <c r="AO232" s="20"/>
-      <c r="AP232" s="19"/>
-      <c r="AQ232" s="19"/>
-      <c r="AR232" s="19"/>
-      <c r="AS232" s="19"/>
-      <c r="AT232" s="19"/>
+      <c r="AH231" s="6"/>
+      <c r="AI231" s="6"/>
+      <c r="AJ231" s="6"/>
+      <c r="AK231" s="6"/>
+      <c r="AL231" s="6"/>
+      <c r="AM231" s="6"/>
+      <c r="AN231" s="6"/>
+      <c r="AO231" s="20"/>
+      <c r="AP231" s="19"/>
+      <c r="AQ231" s="19"/>
+      <c r="AR231" s="19"/>
+      <c r="AS231" s="19"/>
+      <c r="AT231" s="19"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -32369,38 +32228,38 @@
     <hyperlink ref="J205" r:id="rId256"/>
     <hyperlink ref="J206" r:id="rId257"/>
     <hyperlink ref="J207" r:id="rId258"/>
-    <hyperlink ref="J208" r:id="rId259"/>
-    <hyperlink ref="AM208" r:id="rId260"/>
+    <hyperlink ref="AM207" r:id="rId259"/>
+    <hyperlink ref="J208" r:id="rId260"/>
     <hyperlink ref="J209" r:id="rId261"/>
-    <hyperlink ref="J210" r:id="rId262"/>
-    <hyperlink ref="AL210" r:id="rId263"/>
-    <hyperlink ref="AM210" r:id="rId264"/>
+    <hyperlink ref="AL209" r:id="rId262"/>
+    <hyperlink ref="AM209" r:id="rId263"/>
+    <hyperlink ref="J210" r:id="rId264"/>
     <hyperlink ref="J211" r:id="rId265"/>
     <hyperlink ref="J212" r:id="rId266"/>
     <hyperlink ref="J213" r:id="rId267"/>
-    <hyperlink ref="J214" r:id="rId268"/>
-    <hyperlink ref="AB214" r:id="rId269"/>
-    <hyperlink ref="AL214" r:id="rId270"/>
+    <hyperlink ref="AB213" r:id="rId268"/>
+    <hyperlink ref="AL213" r:id="rId269"/>
+    <hyperlink ref="J214" r:id="rId270"/>
     <hyperlink ref="J215" r:id="rId271"/>
-    <hyperlink ref="J216" r:id="rId272"/>
-    <hyperlink ref="AL216" r:id="rId273"/>
-    <hyperlink ref="J217" r:id="rId274"/>
-    <hyperlink ref="AB217" r:id="rId275" display="http://www.linkedin.com/in/drsaraswathi2k"/>
-    <hyperlink ref="AL217" r:id="rId276" display="http://www.linkedin.com/in/drsaraswathi2k"/>
-    <hyperlink ref="J218" r:id="rId277"/>
-    <hyperlink ref="AB218" r:id="rId278" display="http://www.google.com/"/>
-    <hyperlink ref="AL218" r:id="rId279" display="http://www.linkedln.com/"/>
-    <hyperlink ref="AM218" r:id="rId280" display="http://www.instagram.com/"/>
-    <hyperlink ref="AN218" r:id="rId281" display="http://www.youtube.com/"/>
-    <hyperlink ref="J219" r:id="rId282"/>
-    <hyperlink ref="AB219" r:id="rId283" display="http://www.google.com/"/>
-    <hyperlink ref="AL219" r:id="rId284" display="http://www.linkden.com/"/>
-    <hyperlink ref="AM219" r:id="rId285" display="http://insta.com/"/>
-    <hyperlink ref="AN219" r:id="rId286" display="http://utube.com/"/>
+    <hyperlink ref="AL215" r:id="rId272"/>
+    <hyperlink ref="J216" r:id="rId273"/>
+    <hyperlink ref="AB216" r:id="rId274" display="http://www.linkedin.com/in/drsaraswathi2k"/>
+    <hyperlink ref="AL216" r:id="rId275" display="http://www.linkedin.com/in/drsaraswathi2k"/>
+    <hyperlink ref="J217" r:id="rId276"/>
+    <hyperlink ref="AB217" r:id="rId277" display="http://www.google.com/"/>
+    <hyperlink ref="AL217" r:id="rId278" display="http://www.linkedln.com/"/>
+    <hyperlink ref="AM217" r:id="rId279" display="http://www.instagram.com/"/>
+    <hyperlink ref="AN217" r:id="rId280" display="http://www.youtube.com/"/>
+    <hyperlink ref="J218" r:id="rId281"/>
+    <hyperlink ref="AB218" r:id="rId282" display="http://www.google.com/"/>
+    <hyperlink ref="AL218" r:id="rId283" display="http://www.linkden.com/"/>
+    <hyperlink ref="AM218" r:id="rId284" display="http://insta.com/"/>
+    <hyperlink ref="AN218" r:id="rId285" display="http://utube.com/"/>
+    <hyperlink ref="J219" r:id="rId286"/>
     <hyperlink ref="J220" r:id="rId287"/>
-    <hyperlink ref="J221" r:id="rId288"/>
-    <hyperlink ref="AB221" r:id="rId289"/>
-    <hyperlink ref="AL221" r:id="rId290"/>
+    <hyperlink ref="AB220" r:id="rId288"/>
+    <hyperlink ref="AL220" r:id="rId289"/>
+    <hyperlink ref="J221" r:id="rId290"/>
     <hyperlink ref="J222" r:id="rId291"/>
     <hyperlink ref="J223" r:id="rId292"/>
     <hyperlink ref="J224" r:id="rId293"/>
@@ -32408,13 +32267,12 @@
     <hyperlink ref="J226" r:id="rId295"/>
     <hyperlink ref="J227" r:id="rId296"/>
     <hyperlink ref="J228" r:id="rId297"/>
-    <hyperlink ref="J229" r:id="rId298"/>
-    <hyperlink ref="AB229" r:id="rId299" display="http://www.tctmd.com/"/>
+    <hyperlink ref="AB228" r:id="rId298" display="http://www.tctmd.com/"/>
+    <hyperlink ref="J229" r:id="rId299"/>
     <hyperlink ref="J230" r:id="rId300"/>
-    <hyperlink ref="J231" r:id="rId301"/>
-    <hyperlink ref="J232" r:id="rId302" display="https://drive.google.com/open?id=1DdV0m0St0MUfekgVF6f_7SnKmkRAsjJZ"/>
+    <hyperlink ref="J231" r:id="rId301" display="https://drive.google.com/open?id=1DdV0m0St0MUfekgVF6f_7SnKmkRAsjJZ"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId303"/>
+  <pageSetup orientation="portrait" r:id="rId302"/>
 </worksheet>
 </file>
--- a/assets/excel/Staff_Doctor_Details(Responses).xlsx
+++ b/assets/excel/Staff_Doctor_Details(Responses).xlsx
@@ -7061,7 +7061,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -7097,6 +7097,11 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
+      <name val="Poppins"/>
     </font>
   </fonts>
   <fills count="5">
@@ -7181,7 +7186,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="22" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -7243,6 +7248,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -7511,7 +7517,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AT231"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
@@ -7548,7 +7554,7 @@
     <col min="40" max="40" width="58" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:40" ht="15.75" customHeight="1">
       <c r="A1" s="15">
         <v>45956.692314814813</v>
       </c>
@@ -7670,7 +7676,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="2" spans="1:40" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" ht="409.5">
       <c r="A2" s="1">
         <v>45957.692314814813</v>
       </c>
@@ -7776,7 +7782,7 @@
       <c r="AM2" s="6"/>
       <c r="AN2" s="6"/>
     </row>
-    <row r="3" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" ht="15.75" customHeight="1">
       <c r="A3" s="8">
         <v>45957.836099537039</v>
       </c>
@@ -7882,7 +7888,7 @@
       <c r="AM3" s="13"/>
       <c r="AN3" s="13"/>
     </row>
-    <row r="4" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" ht="15.75" customHeight="1">
       <c r="A4" s="1">
         <v>45957.892523148148</v>
       </c>
@@ -7992,7 +7998,7 @@
       </c>
       <c r="AN4" s="6"/>
     </row>
-    <row r="5" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" ht="15.75" customHeight="1">
       <c r="A5" s="8">
         <v>45959.447812500002</v>
       </c>
@@ -8068,8 +8074,8 @@
       <c r="Y5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="Z5" s="9" t="s">
-        <v>426</v>
+      <c r="Z5" s="21" t="s">
+        <v>1143</v>
       </c>
       <c r="AA5" s="9" t="s">
         <v>434</v>
@@ -8096,7 +8102,7 @@
       <c r="AM5" s="13"/>
       <c r="AN5" s="13"/>
     </row>
-    <row r="6" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" ht="15.75" customHeight="1">
       <c r="A6" s="1">
         <v>45959.619328703702</v>
       </c>
@@ -8202,7 +8208,7 @@
       <c r="AM6" s="6"/>
       <c r="AN6" s="6"/>
     </row>
-    <row r="7" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" ht="15.75" customHeight="1">
       <c r="A7" s="8">
         <v>45959.628240740742</v>
       </c>
@@ -8312,7 +8318,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" ht="15.75" customHeight="1">
       <c r="A8" s="1">
         <v>45962.704074074078</v>
       </c>
@@ -8418,7 +8424,7 @@
       <c r="AM8" s="6"/>
       <c r="AN8" s="6"/>
     </row>
-    <row r="9" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" ht="15.75" customHeight="1">
       <c r="A9" s="8">
         <v>45962.830706018518</v>
       </c>
@@ -8528,7 +8534,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" ht="15.75" customHeight="1">
       <c r="A10" s="1">
         <v>45962.861979166664</v>
       </c>
@@ -8634,7 +8640,7 @@
       <c r="AM10" s="6"/>
       <c r="AN10" s="6"/>
     </row>
-    <row r="11" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" ht="15.75" customHeight="1">
       <c r="A11" s="8">
         <v>45963.404826388891</v>
       </c>
@@ -8738,7 +8744,7 @@
       <c r="AM11" s="13"/>
       <c r="AN11" s="13"/>
     </row>
-    <row r="12" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" ht="15.75" customHeight="1">
       <c r="A12" s="1">
         <v>45963.419293981482</v>
       </c>
@@ -8844,7 +8850,7 @@
       <c r="AM12" s="6"/>
       <c r="AN12" s="6"/>
     </row>
-    <row r="13" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" ht="15.75" customHeight="1">
       <c r="A13" s="8">
         <v>45964.385462962964</v>
       </c>
@@ -8948,7 +8954,7 @@
       <c r="AM13" s="13"/>
       <c r="AN13" s="13"/>
     </row>
-    <row r="14" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" ht="15.75" customHeight="1">
       <c r="A14" s="1">
         <v>45964.427928240744</v>
       </c>
@@ -9052,7 +9058,7 @@
       <c r="AM14" s="6"/>
       <c r="AN14" s="6"/>
     </row>
-    <row r="15" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" ht="15.75" customHeight="1">
       <c r="A15" s="8">
         <v>45964.533125000002</v>
       </c>
@@ -9158,7 +9164,7 @@
       <c r="AM15" s="13"/>
       <c r="AN15" s="13"/>
     </row>
-    <row r="16" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" ht="15.75" customHeight="1">
       <c r="A16" s="1">
         <v>45964.573194444441</v>
       </c>
@@ -9262,7 +9268,7 @@
       <c r="AM16" s="6"/>
       <c r="AN16" s="6"/>
     </row>
-    <row r="17" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" ht="15.75" customHeight="1">
       <c r="A17" s="8">
         <v>45964.575567129628</v>
       </c>
@@ -9366,7 +9372,7 @@
       <c r="AM17" s="13"/>
       <c r="AN17" s="13"/>
     </row>
-    <row r="18" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" ht="15.75" customHeight="1">
       <c r="A18" s="1">
         <v>45964.577222222222</v>
       </c>
@@ -9472,7 +9478,7 @@
       <c r="AM18" s="6"/>
       <c r="AN18" s="6"/>
     </row>
-    <row r="19" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" ht="15.75" customHeight="1">
       <c r="A19" s="8">
         <v>45964.584108796298</v>
       </c>
@@ -9576,7 +9582,7 @@
       <c r="AM19" s="13"/>
       <c r="AN19" s="13"/>
     </row>
-    <row r="20" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" ht="15.75" customHeight="1">
       <c r="A20" s="1">
         <v>45964.591550925928</v>
       </c>
@@ -9680,7 +9686,7 @@
       <c r="AM20" s="6"/>
       <c r="AN20" s="6"/>
     </row>
-    <row r="21" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:40" ht="15.75" customHeight="1">
       <c r="A21" s="8">
         <v>45964.592106481483</v>
       </c>
@@ -9784,7 +9790,7 @@
       <c r="AM21" s="13"/>
       <c r="AN21" s="13"/>
     </row>
-    <row r="22" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:40" ht="15.75" customHeight="1">
       <c r="A22" s="1">
         <v>45964.598437499997</v>
       </c>
@@ -9890,7 +9896,7 @@
       <c r="AM22" s="6"/>
       <c r="AN22" s="6"/>
     </row>
-    <row r="23" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" ht="15.75" customHeight="1">
       <c r="A23" s="8">
         <v>45964.603194444448</v>
       </c>
@@ -9996,7 +10002,7 @@
       <c r="AM23" s="13"/>
       <c r="AN23" s="13"/>
     </row>
-    <row r="24" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:40" ht="15.75" customHeight="1">
       <c r="A24" s="1">
         <v>45964.606122685182</v>
       </c>
@@ -10102,7 +10108,7 @@
       <c r="AM24" s="6"/>
       <c r="AN24" s="6"/>
     </row>
-    <row r="25" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:40" ht="15.75" customHeight="1">
       <c r="A25" s="8">
         <v>45964.608634259261</v>
       </c>
@@ -10206,7 +10212,7 @@
       <c r="AM25" s="13"/>
       <c r="AN25" s="13"/>
     </row>
-    <row r="26" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:40" ht="15.75" customHeight="1">
       <c r="A26" s="1">
         <v>45964.610312500001</v>
       </c>
@@ -10312,7 +10318,7 @@
       <c r="AM26" s="6"/>
       <c r="AN26" s="6"/>
     </row>
-    <row r="27" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:40" ht="15.75" customHeight="1">
       <c r="A27" s="8">
         <v>45964.613171296296</v>
       </c>
@@ -10420,7 +10426,7 @@
       <c r="AM27" s="13"/>
       <c r="AN27" s="13"/>
     </row>
-    <row r="28" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:40" ht="15.75" customHeight="1">
       <c r="A28" s="1">
         <v>45964.617430555554</v>
       </c>
@@ -10524,7 +10530,7 @@
       <c r="AM28" s="6"/>
       <c r="AN28" s="6"/>
     </row>
-    <row r="29" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:40" ht="15.75" customHeight="1">
       <c r="A29" s="8">
         <v>45964.618437500001</v>
       </c>
@@ -10628,7 +10634,7 @@
       <c r="AM29" s="13"/>
       <c r="AN29" s="13"/>
     </row>
-    <row r="30" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:40" ht="15.75" customHeight="1">
       <c r="A30" s="1">
         <v>45964.621215277781</v>
       </c>
@@ -10738,7 +10744,7 @@
       <c r="AM30" s="6"/>
       <c r="AN30" s="6"/>
     </row>
-    <row r="31" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:40" ht="15.75" customHeight="1">
       <c r="A31" s="8">
         <v>45964.63071759259</v>
       </c>
@@ -10842,7 +10848,7 @@
       <c r="AM31" s="13"/>
       <c r="AN31" s="13"/>
     </row>
-    <row r="32" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:40" ht="15.75" customHeight="1">
       <c r="A32" s="1">
         <v>45964.632025462961</v>
       </c>
@@ -10946,7 +10952,7 @@
       <c r="AM32" s="6"/>
       <c r="AN32" s="6"/>
     </row>
-    <row r="33" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:40" ht="15.75" customHeight="1">
       <c r="A33" s="8">
         <v>45964.660057870373</v>
       </c>
@@ -11050,7 +11056,7 @@
       <c r="AM33" s="13"/>
       <c r="AN33" s="13"/>
     </row>
-    <row r="34" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:40" ht="15.75" customHeight="1">
       <c r="A34" s="1">
         <v>45964.683622685188</v>
       </c>
@@ -11154,7 +11160,7 @@
       <c r="AM34" s="6"/>
       <c r="AN34" s="6"/>
     </row>
-    <row r="35" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:40" ht="15.75" customHeight="1">
       <c r="A35" s="8">
         <v>45964.694976851853</v>
       </c>
@@ -11268,7 +11274,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="36" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:40" ht="15.75" customHeight="1">
       <c r="A36" s="1">
         <v>45964.718078703707</v>
       </c>
@@ -11372,7 +11378,7 @@
       <c r="AM36" s="6"/>
       <c r="AN36" s="6"/>
     </row>
-    <row r="37" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:40" ht="15.75" customHeight="1">
       <c r="A37" s="8">
         <v>45964.720648148148</v>
       </c>
@@ -11480,7 +11486,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="38" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:40" ht="15.75" customHeight="1">
       <c r="A38" s="1">
         <v>45964.749942129631</v>
       </c>
@@ -11584,7 +11590,7 @@
       <c r="AM38" s="6"/>
       <c r="AN38" s="6"/>
     </row>
-    <row r="39" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:40" ht="15.75" customHeight="1">
       <c r="A39" s="8">
         <v>45964.753599537034</v>
       </c>
@@ -11690,7 +11696,7 @@
       <c r="AM39" s="13"/>
       <c r="AN39" s="13"/>
     </row>
-    <row r="40" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:40" ht="15.75" customHeight="1">
       <c r="A40" s="1">
         <v>45964.756678240738</v>
       </c>
@@ -11794,7 +11800,7 @@
       <c r="AM40" s="6"/>
       <c r="AN40" s="6"/>
     </row>
-    <row r="41" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:40" ht="15.75" customHeight="1">
       <c r="A41" s="8">
         <v>45964.769467592596</v>
       </c>
@@ -11898,7 +11904,7 @@
       <c r="AM41" s="13"/>
       <c r="AN41" s="13"/>
     </row>
-    <row r="42" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:40" ht="15.75" customHeight="1">
       <c r="A42" s="1">
         <v>45964.770439814813</v>
       </c>
@@ -12004,7 +12010,7 @@
       <c r="AM42" s="6"/>
       <c r="AN42" s="6"/>
     </row>
-    <row r="43" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:40" ht="15.75" customHeight="1">
       <c r="A43" s="8">
         <v>45964.962500000001</v>
       </c>
@@ -12108,7 +12114,7 @@
       <c r="AM43" s="13"/>
       <c r="AN43" s="13"/>
     </row>
-    <row r="44" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:40" ht="15.75" customHeight="1">
       <c r="A44" s="1">
         <v>45965.415185185186</v>
       </c>
@@ -12214,7 +12220,7 @@
       <c r="AM44" s="6"/>
       <c r="AN44" s="6"/>
     </row>
-    <row r="45" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:40" ht="15.75" customHeight="1">
       <c r="A45" s="8">
         <v>45965.417916666665</v>
       </c>
@@ -12322,7 +12328,7 @@
       <c r="AM45" s="13"/>
       <c r="AN45" s="13"/>
     </row>
-    <row r="46" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:40" ht="15.75" customHeight="1">
       <c r="A46" s="1">
         <v>45965.447060185186</v>
       </c>
@@ -12428,7 +12434,7 @@
       <c r="AM46" s="6"/>
       <c r="AN46" s="6"/>
     </row>
-    <row r="47" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:40" ht="15.75" customHeight="1">
       <c r="A47" s="8">
         <v>45965.450416666667</v>
       </c>
@@ -12536,7 +12542,7 @@
       <c r="AM47" s="13"/>
       <c r="AN47" s="13"/>
     </row>
-    <row r="48" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:40" ht="15.75" customHeight="1">
       <c r="A48" s="1">
         <v>45965.512662037036</v>
       </c>
@@ -12640,7 +12646,7 @@
       <c r="AM48" s="6"/>
       <c r="AN48" s="6"/>
     </row>
-    <row r="49" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:40" ht="15.75" customHeight="1">
       <c r="A49" s="8">
         <v>45965.874374999999</v>
       </c>
@@ -12746,7 +12752,7 @@
       <c r="AM49" s="13"/>
       <c r="AN49" s="13"/>
     </row>
-    <row r="50" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:40" ht="15.75" customHeight="1">
       <c r="A50" s="1">
         <v>45966.385312500002</v>
       </c>
@@ -12850,7 +12856,7 @@
       <c r="AM50" s="6"/>
       <c r="AN50" s="6"/>
     </row>
-    <row r="51" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:40" ht="15.75" customHeight="1">
       <c r="A51" s="8">
         <v>45966.389178240737</v>
       </c>
@@ -12954,7 +12960,7 @@
       <c r="AM51" s="13"/>
       <c r="AN51" s="13"/>
     </row>
-    <row r="52" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:40" ht="15.75" customHeight="1">
       <c r="A52" s="1">
         <v>45966.392407407409</v>
       </c>
@@ -13058,7 +13064,7 @@
       <c r="AM52" s="6"/>
       <c r="AN52" s="6"/>
     </row>
-    <row r="53" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:40" ht="15.75" customHeight="1">
       <c r="A53" s="8">
         <v>45966.418391203704</v>
       </c>
@@ -13162,7 +13168,7 @@
       <c r="AM53" s="13"/>
       <c r="AN53" s="13"/>
     </row>
-    <row r="54" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:40" ht="15.75" customHeight="1">
       <c r="A54" s="1">
         <v>45966.540497685186</v>
       </c>
@@ -13266,7 +13272,7 @@
       <c r="AM54" s="6"/>
       <c r="AN54" s="6"/>
     </row>
-    <row r="55" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:40" ht="15.75" customHeight="1">
       <c r="A55" s="8">
         <v>45966.62300925926</v>
       </c>
@@ -13376,7 +13382,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="56" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:40" ht="15.75" customHeight="1">
       <c r="A56" s="1">
         <v>45966.626886574071</v>
       </c>
@@ -13480,7 +13486,7 @@
       <c r="AM56" s="6"/>
       <c r="AN56" s="6"/>
     </row>
-    <row r="57" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:40" ht="15.75" customHeight="1">
       <c r="A57" s="8">
         <v>45966.640393518515</v>
       </c>
@@ -13588,7 +13594,7 @@
       <c r="AM57" s="13"/>
       <c r="AN57" s="13"/>
     </row>
-    <row r="58" spans="1:40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:40" ht="24" customHeight="1">
       <c r="A58" s="1">
         <v>45967.46361111111</v>
       </c>
@@ -13698,7 +13704,7 @@
       </c>
       <c r="AN58" s="6"/>
     </row>
-    <row r="59" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:40" ht="15.75" customHeight="1">
       <c r="A59" s="8">
         <v>45967.559479166666</v>
       </c>
@@ -13804,7 +13810,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="60" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:40" ht="15.75" customHeight="1">
       <c r="A60" s="1">
         <v>45967.610891203702</v>
       </c>
@@ -13910,7 +13916,7 @@
       <c r="AM60" s="6"/>
       <c r="AN60" s="6"/>
     </row>
-    <row r="61" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:40" ht="15.75" customHeight="1">
       <c r="A61" s="8">
         <v>45967.617152777777</v>
       </c>
@@ -14014,7 +14020,7 @@
       <c r="AM61" s="13"/>
       <c r="AN61" s="13"/>
     </row>
-    <row r="62" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:40" ht="15.75" customHeight="1">
       <c r="A62" s="1">
         <v>45967.620428240742</v>
       </c>
@@ -14118,7 +14124,7 @@
       <c r="AM62" s="6"/>
       <c r="AN62" s="6"/>
     </row>
-    <row r="63" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:40" ht="15.75" customHeight="1">
       <c r="A63" s="8">
         <v>45967.624560185184</v>
       </c>
@@ -14224,7 +14230,7 @@
       <c r="AM63" s="13"/>
       <c r="AN63" s="13"/>
     </row>
-    <row r="64" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:40" ht="15.75" customHeight="1">
       <c r="A64" s="1">
         <v>45967.633842592593</v>
       </c>
@@ -14330,7 +14336,7 @@
       <c r="AM64" s="6"/>
       <c r="AN64" s="6"/>
     </row>
-    <row r="65" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:40" ht="15.75" customHeight="1">
       <c r="A65" s="8">
         <v>45967.635555555556</v>
       </c>
@@ -14436,7 +14442,7 @@
       <c r="AM65" s="13"/>
       <c r="AN65" s="13"/>
     </row>
-    <row r="66" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:40" ht="15.75" customHeight="1">
       <c r="A66" s="1">
         <v>45967.642025462963</v>
       </c>
@@ -14542,7 +14548,7 @@
       <c r="AM66" s="6"/>
       <c r="AN66" s="6"/>
     </row>
-    <row r="67" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:40" ht="15.75" customHeight="1">
       <c r="A67" s="8">
         <v>45967.643321759257</v>
       </c>
@@ -14646,7 +14652,7 @@
       <c r="AM67" s="13"/>
       <c r="AN67" s="13"/>
     </row>
-    <row r="68" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:40" ht="15.75" customHeight="1">
       <c r="A68" s="1">
         <v>45967.645590277774</v>
       </c>
@@ -14750,7 +14756,7 @@
       <c r="AM68" s="6"/>
       <c r="AN68" s="6"/>
     </row>
-    <row r="69" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:40" ht="15.75" customHeight="1">
       <c r="A69" s="8">
         <v>45967.695185185185</v>
       </c>
@@ -14854,7 +14860,7 @@
       <c r="AM69" s="13"/>
       <c r="AN69" s="13"/>
     </row>
-    <row r="70" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:40" ht="15.75" customHeight="1">
       <c r="A70" s="1">
         <v>45968.390150462961</v>
       </c>
@@ -14958,7 +14964,7 @@
       <c r="AM70" s="6"/>
       <c r="AN70" s="6"/>
     </row>
-    <row r="71" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:40" ht="15.75" customHeight="1">
       <c r="A71" s="8">
         <v>45968.459675925929</v>
       </c>
@@ -15064,7 +15070,7 @@
       <c r="AM71" s="13"/>
       <c r="AN71" s="13"/>
     </row>
-    <row r="72" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:40" ht="15.75" customHeight="1">
       <c r="A72" s="1">
         <v>45968.466990740744</v>
       </c>
@@ -15168,7 +15174,7 @@
       <c r="AM72" s="6"/>
       <c r="AN72" s="6"/>
     </row>
-    <row r="73" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:40" ht="15.75" customHeight="1">
       <c r="A73" s="8">
         <v>45968.480254629627</v>
       </c>
@@ -15274,7 +15280,7 @@
       <c r="AM73" s="13"/>
       <c r="AN73" s="13"/>
     </row>
-    <row r="74" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:40" ht="15.75" customHeight="1">
       <c r="A74" s="1">
         <v>45968.601412037038</v>
       </c>
@@ -15380,7 +15386,7 @@
       <c r="AM74" s="6"/>
       <c r="AN74" s="6"/>
     </row>
-    <row r="75" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:40" ht="15.75" customHeight="1">
       <c r="A75" s="8">
         <v>45968.787569444445</v>
       </c>
@@ -15484,7 +15490,7 @@
       <c r="AM75" s="13"/>
       <c r="AN75" s="13"/>
     </row>
-    <row r="76" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:40" ht="15.75" customHeight="1">
       <c r="A76" s="1">
         <v>45969.473912037036</v>
       </c>
@@ -15590,7 +15596,7 @@
       <c r="AM76" s="6"/>
       <c r="AN76" s="6"/>
     </row>
-    <row r="77" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:40" ht="15.75" customHeight="1">
       <c r="A77" s="8">
         <v>45971.35670138889</v>
       </c>
@@ -15694,7 +15700,7 @@
       <c r="AM77" s="13"/>
       <c r="AN77" s="13"/>
     </row>
-    <row r="78" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:40" ht="15.75" customHeight="1">
       <c r="A78" s="1">
         <v>45972.659039351849</v>
       </c>
@@ -15798,7 +15804,7 @@
       <c r="AM78" s="6"/>
       <c r="AN78" s="6"/>
     </row>
-    <row r="79" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:40" ht="15.75" customHeight="1">
       <c r="A79" s="8">
         <v>45973.38857638889</v>
       </c>
@@ -15902,7 +15908,7 @@
       <c r="AM79" s="13"/>
       <c r="AN79" s="13"/>
     </row>
-    <row r="80" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:40" ht="15.75" customHeight="1">
       <c r="A80" s="1">
         <v>45973.42355324074</v>
       </c>
@@ -16008,7 +16014,7 @@
       <c r="AM80" s="6"/>
       <c r="AN80" s="6"/>
     </row>
-    <row r="81" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:40" ht="15.75" customHeight="1">
       <c r="A81" s="8">
         <v>45973.453125</v>
       </c>
@@ -16114,7 +16120,7 @@
       <c r="AM81" s="13"/>
       <c r="AN81" s="13"/>
     </row>
-    <row r="82" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:40" ht="15.75" customHeight="1">
       <c r="A82" s="1">
         <v>45973.487337962964</v>
       </c>
@@ -16220,7 +16226,7 @@
       <c r="AM82" s="6"/>
       <c r="AN82" s="6"/>
     </row>
-    <row r="83" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:40" ht="15.75" customHeight="1">
       <c r="A83" s="8">
         <v>45973.493680555555</v>
       </c>
@@ -16324,7 +16330,7 @@
       <c r="AM83" s="13"/>
       <c r="AN83" s="13"/>
     </row>
-    <row r="84" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:40" ht="15.75" customHeight="1">
       <c r="A84" s="1">
         <v>45973.499756944446</v>
       </c>
@@ -16426,7 +16432,7 @@
       <c r="AM84" s="6"/>
       <c r="AN84" s="6"/>
     </row>
-    <row r="85" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:40" ht="15.75" customHeight="1">
       <c r="A85" s="8">
         <v>45973.53</v>
       </c>
@@ -16530,7 +16536,7 @@
       <c r="AM85" s="13"/>
       <c r="AN85" s="13"/>
     </row>
-    <row r="86" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:40" ht="15.75" customHeight="1">
       <c r="A86" s="1">
         <v>45973.579444444447</v>
       </c>
@@ -16634,7 +16640,7 @@
       <c r="AM86" s="6"/>
       <c r="AN86" s="6"/>
     </row>
-    <row r="87" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:40" ht="15.75" customHeight="1">
       <c r="A87" s="8">
         <v>45973.586597222224</v>
       </c>
@@ -16740,7 +16746,7 @@
       <c r="AM87" s="13"/>
       <c r="AN87" s="13"/>
     </row>
-    <row r="88" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:40" ht="15.75" customHeight="1">
       <c r="A88" s="1">
         <v>45973.606805555559</v>
       </c>
@@ -16844,7 +16850,7 @@
       <c r="AM88" s="6"/>
       <c r="AN88" s="6"/>
     </row>
-    <row r="89" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:40" ht="15.75" customHeight="1">
       <c r="A89" s="8">
         <v>45973.627118055556</v>
       </c>
@@ -16948,7 +16954,7 @@
       <c r="AM89" s="13"/>
       <c r="AN89" s="13"/>
     </row>
-    <row r="90" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:40" ht="15.75" customHeight="1">
       <c r="A90" s="1">
         <v>45973.630613425928</v>
       </c>
@@ -17052,7 +17058,7 @@
       <c r="AM90" s="6"/>
       <c r="AN90" s="6"/>
     </row>
-    <row r="91" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:40" ht="15.75" customHeight="1">
       <c r="A91" s="8">
         <v>45973.637025462966</v>
       </c>
@@ -17156,7 +17162,7 @@
       <c r="AM91" s="13"/>
       <c r="AN91" s="13"/>
     </row>
-    <row r="92" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:40" ht="15.75" customHeight="1">
       <c r="A92" s="1">
         <v>45973.652430555558</v>
       </c>
@@ -17262,7 +17268,7 @@
       <c r="AM92" s="6"/>
       <c r="AN92" s="6"/>
     </row>
-    <row r="93" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:40" ht="15.75" customHeight="1">
       <c r="A93" s="8">
         <v>45973.657650462963</v>
       </c>
@@ -17368,7 +17374,7 @@
       <c r="AM93" s="13"/>
       <c r="AN93" s="13"/>
     </row>
-    <row r="94" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:40" ht="15.75" customHeight="1">
       <c r="A94" s="1">
         <v>45973.66611111111</v>
       </c>
@@ -17476,7 +17482,7 @@
       </c>
       <c r="AN94" s="6"/>
     </row>
-    <row r="95" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:40" ht="15.75" customHeight="1">
       <c r="A95" s="8">
         <v>45973.691122685188</v>
       </c>
@@ -17582,7 +17588,7 @@
       </c>
       <c r="AN95" s="13"/>
     </row>
-    <row r="96" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:40" ht="15.75" customHeight="1">
       <c r="A96" s="1">
         <v>45973.703530092593</v>
       </c>
@@ -17686,7 +17692,7 @@
       <c r="AM96" s="6"/>
       <c r="AN96" s="6"/>
     </row>
-    <row r="97" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:40" ht="15.75" customHeight="1">
       <c r="A97" s="8">
         <v>45974.3046875</v>
       </c>
@@ -17790,7 +17796,7 @@
       <c r="AM97" s="13"/>
       <c r="AN97" s="13"/>
     </row>
-    <row r="98" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:40" ht="15.75" customHeight="1">
       <c r="A98" s="1">
         <v>45974.332615740743</v>
       </c>
@@ -17894,7 +17900,7 @@
       <c r="AM98" s="6"/>
       <c r="AN98" s="6"/>
     </row>
-    <row r="99" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:40" ht="15.75" customHeight="1">
       <c r="A99" s="8">
         <v>45974.383553240739</v>
       </c>
@@ -18000,7 +18006,7 @@
       <c r="AM99" s="13"/>
       <c r="AN99" s="13"/>
     </row>
-    <row r="100" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:40" ht="15.75" customHeight="1">
       <c r="A100" s="1">
         <v>45974.393182870372</v>
       </c>
@@ -18106,7 +18112,7 @@
       <c r="AM100" s="6"/>
       <c r="AN100" s="6"/>
     </row>
-    <row r="101" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:40" ht="15.75" customHeight="1">
       <c r="A101" s="8">
         <v>45974.406481481485</v>
       </c>
@@ -18210,7 +18216,7 @@
       <c r="AM101" s="13"/>
       <c r="AN101" s="13"/>
     </row>
-    <row r="102" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:40" ht="15.75" customHeight="1">
       <c r="A102" s="1">
         <v>45974.409050925926</v>
       </c>
@@ -18324,7 +18330,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="103" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:40" ht="15.75" customHeight="1">
       <c r="A103" s="8">
         <v>45974.417291666665</v>
       </c>
@@ -18428,7 +18434,7 @@
       <c r="AM103" s="13"/>
       <c r="AN103" s="13"/>
     </row>
-    <row r="104" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:40" ht="15.75" customHeight="1">
       <c r="A104" s="1">
         <v>45974.417326388888</v>
       </c>
@@ -18534,7 +18540,7 @@
       <c r="AM104" s="6"/>
       <c r="AN104" s="6"/>
     </row>
-    <row r="105" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:40" ht="15.75" customHeight="1">
       <c r="A105" s="8">
         <v>45974.423506944448</v>
       </c>
@@ -18642,7 +18648,7 @@
       </c>
       <c r="AN105" s="13"/>
     </row>
-    <row r="106" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:40" ht="15.75" customHeight="1">
       <c r="A106" s="1">
         <v>45974.42428240741</v>
       </c>
@@ -18746,7 +18752,7 @@
       <c r="AM106" s="6"/>
       <c r="AN106" s="6"/>
     </row>
-    <row r="107" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:40" ht="15.75" customHeight="1">
       <c r="A107" s="8">
         <v>45974.435567129629</v>
       </c>
@@ -18850,7 +18856,7 @@
       <c r="AM107" s="13"/>
       <c r="AN107" s="13"/>
     </row>
-    <row r="108" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:40" ht="15.75" customHeight="1">
       <c r="A108" s="1">
         <v>45974.464259259257</v>
       </c>
@@ -18956,7 +18962,7 @@
       <c r="AM108" s="6"/>
       <c r="AN108" s="6"/>
     </row>
-    <row r="109" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:40" ht="15.75" customHeight="1">
       <c r="A109" s="8">
         <v>45974.506307870368</v>
       </c>
@@ -19060,7 +19066,7 @@
       <c r="AM109" s="13"/>
       <c r="AN109" s="13"/>
     </row>
-    <row r="110" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:40" ht="15.75" customHeight="1">
       <c r="A110" s="1">
         <v>45974.516064814816</v>
       </c>
@@ -19164,7 +19170,7 @@
       <c r="AM110" s="6"/>
       <c r="AN110" s="6"/>
     </row>
-    <row r="111" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:40" ht="15.75" customHeight="1">
       <c r="A111" s="8">
         <v>45974.594675925924</v>
       </c>
@@ -19270,7 +19276,7 @@
       </c>
       <c r="AN111" s="13"/>
     </row>
-    <row r="112" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:40" ht="15.75" customHeight="1">
       <c r="A112" s="1">
         <v>45974.605011574073</v>
       </c>
@@ -19376,7 +19382,7 @@
       <c r="AM112" s="6"/>
       <c r="AN112" s="6"/>
     </row>
-    <row r="113" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:40" ht="15.75" customHeight="1">
       <c r="A113" s="8">
         <v>45974.619108796294</v>
       </c>
@@ -19480,7 +19486,7 @@
       <c r="AM113" s="13"/>
       <c r="AN113" s="13"/>
     </row>
-    <row r="114" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:40" ht="15.75" customHeight="1">
       <c r="A114" s="1">
         <v>45974.62736111111</v>
       </c>
@@ -19588,7 +19594,7 @@
       <c r="AM114" s="6"/>
       <c r="AN114" s="6"/>
     </row>
-    <row r="115" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:40" ht="15.75" customHeight="1">
       <c r="A115" s="8">
         <v>45974.62972222222</v>
       </c>
@@ -19696,7 +19702,7 @@
       <c r="AM115" s="13"/>
       <c r="AN115" s="13"/>
     </row>
-    <row r="116" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:40" ht="15.75" customHeight="1">
       <c r="A116" s="1">
         <v>45974.634756944448</v>
       </c>
@@ -19802,7 +19808,7 @@
       <c r="AM116" s="6"/>
       <c r="AN116" s="6"/>
     </row>
-    <row r="117" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:40" ht="15.75" customHeight="1">
       <c r="A117" s="8">
         <v>45974.639641203707</v>
       </c>
@@ -19908,7 +19914,7 @@
       <c r="AM117" s="13"/>
       <c r="AN117" s="13"/>
     </row>
-    <row r="118" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:40" ht="15.75" customHeight="1">
       <c r="A118" s="1">
         <v>45975.367986111109</v>
       </c>
@@ -20014,7 +20020,7 @@
       <c r="AM118" s="6"/>
       <c r="AN118" s="6"/>
     </row>
-    <row r="119" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:40" ht="15.75" customHeight="1">
       <c r="A119" s="8">
         <v>45975.375219907408</v>
       </c>
@@ -20120,7 +20126,7 @@
       <c r="AM119" s="13"/>
       <c r="AN119" s="13"/>
     </row>
-    <row r="120" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:40" ht="15.75" customHeight="1">
       <c r="A120" s="1">
         <v>45975.401122685187</v>
       </c>
@@ -20226,7 +20232,7 @@
       <c r="AM120" s="6"/>
       <c r="AN120" s="6"/>
     </row>
-    <row r="121" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:40" ht="15.75" customHeight="1">
       <c r="A121" s="8">
         <v>45975.414409722223</v>
       </c>
@@ -20330,7 +20336,7 @@
       <c r="AM121" s="13"/>
       <c r="AN121" s="13"/>
     </row>
-    <row r="122" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:40" ht="15.75" customHeight="1">
       <c r="A122" s="1">
         <v>45975.419456018521</v>
       </c>
@@ -20434,7 +20440,7 @@
       <c r="AM122" s="6"/>
       <c r="AN122" s="6"/>
     </row>
-    <row r="123" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:40" ht="15.75" customHeight="1">
       <c r="A123" s="8">
         <v>45975.426435185182</v>
       </c>
@@ -20538,7 +20544,7 @@
       <c r="AM123" s="13"/>
       <c r="AN123" s="13"/>
     </row>
-    <row r="124" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:40" ht="15.75" customHeight="1">
       <c r="A124" s="1">
         <v>45975.438136574077</v>
       </c>
@@ -20642,7 +20648,7 @@
       <c r="AM124" s="6"/>
       <c r="AN124" s="6"/>
     </row>
-    <row r="125" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:40" ht="15.75" customHeight="1">
       <c r="A125" s="8">
         <v>45975.440763888888</v>
       </c>
@@ -20746,7 +20752,7 @@
       <c r="AM125" s="13"/>
       <c r="AN125" s="13"/>
     </row>
-    <row r="126" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:40" ht="15.75" customHeight="1">
       <c r="A126" s="1">
         <v>45975.442060185182</v>
       </c>
@@ -20850,7 +20856,7 @@
       <c r="AM126" s="6"/>
       <c r="AN126" s="6"/>
     </row>
-    <row r="127" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:40" ht="15.75" customHeight="1">
       <c r="A127" s="8">
         <v>45975.49355324074</v>
       </c>
@@ -20964,7 +20970,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="128" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:40" ht="15.75" customHeight="1">
       <c r="A128" s="1">
         <v>45975.493923611109</v>
       </c>
@@ -21070,7 +21076,7 @@
       <c r="AM128" s="6"/>
       <c r="AN128" s="6"/>
     </row>
-    <row r="129" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:40" ht="15.75" customHeight="1">
       <c r="A129" s="8">
         <v>45975.54855324074</v>
       </c>
@@ -21174,7 +21180,7 @@
       <c r="AM129" s="13"/>
       <c r="AN129" s="13"/>
     </row>
-    <row r="130" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:40" ht="15.75" customHeight="1">
       <c r="A130" s="1">
         <v>45975.615324074075</v>
       </c>
@@ -21280,7 +21286,7 @@
       <c r="AM130" s="6"/>
       <c r="AN130" s="6"/>
     </row>
-    <row r="131" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:40" ht="15.75" customHeight="1">
       <c r="A131" s="8">
         <v>45975.635601851849</v>
       </c>
@@ -21392,7 +21398,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="132" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:40" ht="15.75" customHeight="1">
       <c r="A132" s="1">
         <v>45975.643194444441</v>
       </c>
@@ -21498,7 +21504,7 @@
       <c r="AM132" s="6"/>
       <c r="AN132" s="6"/>
     </row>
-    <row r="133" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:40" ht="15.75" customHeight="1">
       <c r="A133" s="8">
         <v>45975.694756944446</v>
       </c>
@@ -21602,7 +21608,7 @@
       <c r="AM133" s="13"/>
       <c r="AN133" s="13"/>
     </row>
-    <row r="134" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:40" ht="15.75" customHeight="1">
       <c r="A134" s="1">
         <v>45975.972280092596</v>
       </c>
@@ -21708,7 +21714,7 @@
       <c r="AM134" s="6"/>
       <c r="AN134" s="6"/>
     </row>
-    <row r="135" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:40" ht="15.75" customHeight="1">
       <c r="A135" s="8">
         <v>45976.37872685185</v>
       </c>
@@ -21814,7 +21820,7 @@
       <c r="AM135" s="13"/>
       <c r="AN135" s="13"/>
     </row>
-    <row r="136" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:40" ht="15.75" customHeight="1">
       <c r="A136" s="1">
         <v>45976.633912037039</v>
       </c>
@@ -21920,7 +21926,7 @@
       <c r="AM136" s="6"/>
       <c r="AN136" s="6"/>
     </row>
-    <row r="137" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:40" ht="15.75" customHeight="1">
       <c r="A137" s="8">
         <v>45978.611875000002</v>
       </c>
@@ -22026,7 +22032,7 @@
       <c r="AM137" s="13"/>
       <c r="AN137" s="13"/>
     </row>
-    <row r="138" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:40" ht="15.75" customHeight="1">
       <c r="A138" s="1">
         <v>45978.693738425929</v>
       </c>
@@ -22130,7 +22136,7 @@
       <c r="AM138" s="6"/>
       <c r="AN138" s="6"/>
     </row>
-    <row r="139" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:40" ht="15.75" customHeight="1">
       <c r="A139" s="8">
         <v>45979.365844907406</v>
       </c>
@@ -22234,7 +22240,7 @@
       <c r="AM139" s="13"/>
       <c r="AN139" s="13"/>
     </row>
-    <row r="140" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:40" ht="15.75" customHeight="1">
       <c r="A140" s="1">
         <v>45979.369976851849</v>
       </c>
@@ -22338,7 +22344,7 @@
       <c r="AM140" s="6"/>
       <c r="AN140" s="6"/>
     </row>
-    <row r="141" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:40" ht="15.75" customHeight="1">
       <c r="A141" s="8">
         <v>45979.371990740743</v>
       </c>
@@ -22444,7 +22450,7 @@
       <c r="AM141" s="13"/>
       <c r="AN141" s="13"/>
     </row>
-    <row r="142" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:40" ht="15.75" customHeight="1">
       <c r="A142" s="1">
         <v>45979.479664351849</v>
       </c>
@@ -22550,7 +22556,7 @@
       <c r="AM142" s="6"/>
       <c r="AN142" s="6"/>
     </row>
-    <row r="143" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:40" ht="15.75" customHeight="1">
       <c r="A143" s="8">
         <v>45979.498854166668</v>
       </c>
@@ -22656,7 +22662,7 @@
       <c r="AM143" s="13"/>
       <c r="AN143" s="13"/>
     </row>
-    <row r="144" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:40" ht="15.75" customHeight="1">
       <c r="A144" s="1">
         <v>45979.554236111115</v>
       </c>
@@ -22760,7 +22766,7 @@
       <c r="AM144" s="6"/>
       <c r="AN144" s="6"/>
     </row>
-    <row r="145" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:40" ht="15.75" customHeight="1">
       <c r="A145" s="8">
         <v>45980.316782407404</v>
       </c>
@@ -22864,7 +22870,7 @@
       <c r="AM145" s="13"/>
       <c r="AN145" s="13"/>
     </row>
-    <row r="146" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:40" ht="15.75" customHeight="1">
       <c r="A146" s="1">
         <v>45980.370381944442</v>
       </c>
@@ -22966,7 +22972,7 @@
       <c r="AM146" s="6"/>
       <c r="AN146" s="6"/>
     </row>
-    <row r="147" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:40" ht="15.75" customHeight="1">
       <c r="A147" s="8">
         <v>45980.380636574075</v>
       </c>
@@ -23070,7 +23076,7 @@
       <c r="AM147" s="13"/>
       <c r="AN147" s="13"/>
     </row>
-    <row r="148" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:40" ht="15.75" customHeight="1">
       <c r="A148" s="1">
         <v>45980.428622685184</v>
       </c>
@@ -23174,7 +23180,7 @@
       <c r="AM148" s="6"/>
       <c r="AN148" s="6"/>
     </row>
-    <row r="149" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:40" ht="15.75" customHeight="1">
       <c r="A149" s="8">
         <v>45980.460347222222</v>
       </c>
@@ -23278,7 +23284,7 @@
       <c r="AM149" s="13"/>
       <c r="AN149" s="13"/>
     </row>
-    <row r="150" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:40" ht="15.75" customHeight="1">
       <c r="A150" s="1">
         <v>45980.519803240742</v>
       </c>
@@ -23384,7 +23390,7 @@
       <c r="AM150" s="6"/>
       <c r="AN150" s="6"/>
     </row>
-    <row r="151" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:40" ht="15.75" customHeight="1">
       <c r="A151" s="8">
         <v>45980.595300925925</v>
       </c>
@@ -23490,7 +23496,7 @@
       <c r="AM151" s="13"/>
       <c r="AN151" s="13"/>
     </row>
-    <row r="152" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:40" ht="15.75" customHeight="1">
       <c r="A152" s="1">
         <v>45981.411817129629</v>
       </c>
@@ -23594,7 +23600,7 @@
       <c r="AM152" s="6"/>
       <c r="AN152" s="6"/>
     </row>
-    <row r="153" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:40" ht="15.75" customHeight="1">
       <c r="A153" s="8">
         <v>45981.414537037039</v>
       </c>
@@ -23700,7 +23706,7 @@
       <c r="AM153" s="13"/>
       <c r="AN153" s="13"/>
     </row>
-    <row r="154" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:40" ht="15.75" customHeight="1">
       <c r="A154" s="1">
         <v>45981.63208333333</v>
       </c>
@@ -23808,7 +23814,7 @@
       <c r="AM154" s="6"/>
       <c r="AN154" s="6"/>
     </row>
-    <row r="155" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:40" ht="15.75" customHeight="1">
       <c r="A155" s="8">
         <v>45981.752314814818</v>
       </c>
@@ -23912,7 +23918,7 @@
       <c r="AM155" s="13"/>
       <c r="AN155" s="13"/>
     </row>
-    <row r="156" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:40" ht="15.75" customHeight="1">
       <c r="A156" s="1">
         <v>45981.991898148146</v>
       </c>
@@ -24016,7 +24022,7 @@
       <c r="AM156" s="6"/>
       <c r="AN156" s="6"/>
     </row>
-    <row r="157" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:40" ht="15.75" customHeight="1">
       <c r="A157" s="8">
         <v>45982.393425925926</v>
       </c>
@@ -24120,7 +24126,7 @@
       <c r="AM157" s="13"/>
       <c r="AN157" s="13"/>
     </row>
-    <row r="158" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:40" ht="15.75" customHeight="1">
       <c r="A158" s="1">
         <v>45982.411249999997</v>
       </c>
@@ -24228,7 +24234,7 @@
       <c r="AM158" s="6"/>
       <c r="AN158" s="6"/>
     </row>
-    <row r="159" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:40" ht="15.75" customHeight="1">
       <c r="A159" s="8">
         <v>45982.422164351854</v>
       </c>
@@ -24336,7 +24342,7 @@
       </c>
       <c r="AN159" s="13"/>
     </row>
-    <row r="160" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:40" ht="15.75" customHeight="1">
       <c r="A160" s="1">
         <v>45982.430243055554</v>
       </c>
@@ -24442,7 +24448,7 @@
       <c r="AM160" s="6"/>
       <c r="AN160" s="6"/>
     </row>
-    <row r="161" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:40" ht="15.75" customHeight="1">
       <c r="A161" s="8">
         <v>45982.431990740741</v>
       </c>
@@ -24548,7 +24554,7 @@
       <c r="AM161" s="13"/>
       <c r="AN161" s="13"/>
     </row>
-    <row r="162" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:40" ht="15.75" customHeight="1">
       <c r="A162" s="1">
         <v>45982.458055555559</v>
       </c>
@@ -24654,7 +24660,7 @@
       <c r="AM162" s="6"/>
       <c r="AN162" s="6"/>
     </row>
-    <row r="163" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:40" ht="15.75" customHeight="1">
       <c r="A163" s="8">
         <v>45982.495347222219</v>
       </c>
@@ -24758,7 +24764,7 @@
       <c r="AM163" s="13"/>
       <c r="AN163" s="13"/>
     </row>
-    <row r="164" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:40" ht="15.75" customHeight="1">
       <c r="A164" s="1">
         <v>45982.528078703705</v>
       </c>
@@ -24862,7 +24868,7 @@
       <c r="AM164" s="6"/>
       <c r="AN164" s="6"/>
     </row>
-    <row r="165" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:40" ht="15.75" customHeight="1">
       <c r="A165" s="8">
         <v>45982.531574074077</v>
       </c>
@@ -24966,7 +24972,7 @@
       <c r="AM165" s="13"/>
       <c r="AN165" s="13"/>
     </row>
-    <row r="166" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:40" ht="15.75" customHeight="1">
       <c r="A166" s="1">
         <v>45982.542037037034</v>
       </c>
@@ -25070,7 +25076,7 @@
       <c r="AM166" s="6"/>
       <c r="AN166" s="6"/>
     </row>
-    <row r="167" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:40" ht="15.75" customHeight="1">
       <c r="A167" s="8">
         <v>45982.548090277778</v>
       </c>
@@ -25176,7 +25182,7 @@
       <c r="AM167" s="13"/>
       <c r="AN167" s="13"/>
     </row>
-    <row r="168" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:40" ht="15.75" customHeight="1">
       <c r="A168" s="1">
         <v>45982.551319444443</v>
       </c>
@@ -25284,7 +25290,7 @@
       <c r="AM168" s="6"/>
       <c r="AN168" s="6"/>
     </row>
-    <row r="169" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:40" ht="15.75" customHeight="1">
       <c r="A169" s="8">
         <v>45982.616423611114</v>
       </c>
@@ -25390,7 +25396,7 @@
       <c r="AM169" s="13"/>
       <c r="AN169" s="13"/>
     </row>
-    <row r="170" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:40" ht="15.75" customHeight="1">
       <c r="A170" s="1">
         <v>45982.621087962965</v>
       </c>
@@ -25494,7 +25500,7 @@
       <c r="AM170" s="6"/>
       <c r="AN170" s="6"/>
     </row>
-    <row r="171" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:40" ht="15.75" customHeight="1">
       <c r="A171" s="8">
         <v>45982.628761574073</v>
       </c>
@@ -25602,7 +25608,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="172" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:40" ht="15.75" customHeight="1">
       <c r="A172" s="1">
         <v>45982.656342592592</v>
       </c>
@@ -25708,7 +25714,7 @@
       <c r="AM172" s="6"/>
       <c r="AN172" s="6"/>
     </row>
-    <row r="173" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:40" ht="15.75" customHeight="1">
       <c r="A173" s="8">
         <v>45983.417222222219</v>
       </c>
@@ -25814,7 +25820,7 @@
       <c r="AM173" s="13"/>
       <c r="AN173" s="13"/>
     </row>
-    <row r="174" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:40" ht="15.75" customHeight="1">
       <c r="A174" s="1">
         <v>45983.460949074077</v>
       </c>
@@ -25918,7 +25924,7 @@
       <c r="AM174" s="6"/>
       <c r="AN174" s="6"/>
     </row>
-    <row r="175" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:40" ht="15.75" customHeight="1">
       <c r="A175" s="8">
         <v>45983.51185185185</v>
       </c>
@@ -26022,7 +26028,7 @@
       <c r="AM175" s="13"/>
       <c r="AN175" s="13"/>
     </row>
-    <row r="176" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:40" ht="15.75" customHeight="1">
       <c r="A176" s="1">
         <v>45983.530474537038</v>
       </c>
@@ -26134,7 +26140,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="177" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:40" ht="15.75" customHeight="1">
       <c r="A177" s="8">
         <v>45983.538344907407</v>
       </c>
@@ -26238,7 +26244,7 @@
       <c r="AM177" s="13"/>
       <c r="AN177" s="13"/>
     </row>
-    <row r="178" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:40" ht="15.75" customHeight="1">
       <c r="A178" s="1">
         <v>45983.560393518521</v>
       </c>
@@ -26342,7 +26348,7 @@
       <c r="AM178" s="6"/>
       <c r="AN178" s="6"/>
     </row>
-    <row r="179" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:40" ht="15.75" customHeight="1">
       <c r="A179" s="8">
         <v>45983.568020833336</v>
       </c>
@@ -26446,7 +26452,7 @@
       <c r="AM179" s="13"/>
       <c r="AN179" s="13"/>
     </row>
-    <row r="180" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:40" ht="15.75" customHeight="1">
       <c r="A180" s="1">
         <v>45983.578020833331</v>
       </c>
@@ -26552,7 +26558,7 @@
       <c r="AM180" s="6"/>
       <c r="AN180" s="6"/>
     </row>
-    <row r="181" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:40" ht="15.75" customHeight="1">
       <c r="A181" s="8">
         <v>45983.761250000003</v>
       </c>
@@ -26656,7 +26662,7 @@
       <c r="AM181" s="13"/>
       <c r="AN181" s="13"/>
     </row>
-    <row r="182" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:40" ht="15.75" customHeight="1">
       <c r="A182" s="1">
         <v>45984.822141203702</v>
       </c>
@@ -26760,7 +26766,7 @@
       <c r="AM182" s="6"/>
       <c r="AN182" s="6"/>
     </row>
-    <row r="183" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:40" ht="15.75" customHeight="1">
       <c r="A183" s="8">
         <v>45985.483148148145</v>
       </c>
@@ -26864,7 +26870,7 @@
       <c r="AM183" s="13"/>
       <c r="AN183" s="13"/>
     </row>
-    <row r="184" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:40" ht="15.75" customHeight="1">
       <c r="A184" s="1">
         <v>45985.525810185187</v>
       </c>
@@ -26968,7 +26974,7 @@
       <c r="AM184" s="6"/>
       <c r="AN184" s="6"/>
     </row>
-    <row r="185" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:40" ht="15.75" customHeight="1">
       <c r="A185" s="8">
         <v>45985.53052083333</v>
       </c>
@@ -27072,7 +27078,7 @@
       <c r="AM185" s="13"/>
       <c r="AN185" s="13"/>
     </row>
-    <row r="186" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:40" ht="15.75" customHeight="1">
       <c r="A186" s="1">
         <v>45985.622858796298</v>
       </c>
@@ -27178,7 +27184,7 @@
       <c r="AM186" s="6"/>
       <c r="AN186" s="6"/>
     </row>
-    <row r="187" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:40" ht="15.75" customHeight="1">
       <c r="A187" s="8">
         <v>45985.623449074075</v>
       </c>
@@ -27282,7 +27288,7 @@
       <c r="AM187" s="13"/>
       <c r="AN187" s="13"/>
     </row>
-    <row r="188" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:40" ht="15.75" customHeight="1">
       <c r="A188" s="1">
         <v>45986.487766203703</v>
       </c>
@@ -27386,7 +27392,7 @@
       <c r="AM188" s="6"/>
       <c r="AN188" s="6"/>
     </row>
-    <row r="189" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:40" ht="15.75" customHeight="1">
       <c r="A189" s="8">
         <v>45987.438449074078</v>
       </c>
@@ -27492,7 +27498,7 @@
       <c r="AM189" s="13"/>
       <c r="AN189" s="13"/>
     </row>
-    <row r="190" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:40" ht="15.75" customHeight="1">
       <c r="A190" s="1">
         <v>45987.540578703702</v>
       </c>
@@ -27598,7 +27604,7 @@
       <c r="AM190" s="6"/>
       <c r="AN190" s="6"/>
     </row>
-    <row r="191" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:40" ht="15.75" customHeight="1">
       <c r="A191" s="8">
         <v>45987.690243055556</v>
       </c>
@@ -27710,7 +27716,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="192" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:40" ht="15.75" customHeight="1">
       <c r="A192" s="1">
         <v>45987.704791666663</v>
       </c>
@@ -27816,7 +27822,7 @@
       <c r="AM192" s="6"/>
       <c r="AN192" s="6"/>
     </row>
-    <row r="193" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:40" ht="15.75" customHeight="1">
       <c r="A193" s="8">
         <v>45987.893125000002</v>
       </c>
@@ -27922,7 +27928,7 @@
       <c r="AM193" s="13"/>
       <c r="AN193" s="13"/>
     </row>
-    <row r="194" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:40" ht="15.75" customHeight="1">
       <c r="A194" s="1">
         <v>45988.458819444444</v>
       </c>
@@ -28026,7 +28032,7 @@
       <c r="AM194" s="6"/>
       <c r="AN194" s="6"/>
     </row>
-    <row r="195" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:40" ht="15.75" customHeight="1">
       <c r="A195" s="8">
         <v>45988.494988425926</v>
       </c>
@@ -28130,7 +28136,7 @@
       <c r="AM195" s="13"/>
       <c r="AN195" s="13"/>
     </row>
-    <row r="196" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:40" ht="15.75" customHeight="1">
       <c r="A196" s="1">
         <v>45988.519699074073</v>
       </c>
@@ -28234,7 +28240,7 @@
       <c r="AM196" s="6"/>
       <c r="AN196" s="6"/>
     </row>
-    <row r="197" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:40" ht="15.75" customHeight="1">
       <c r="A197" s="8">
         <v>45988.540254629632</v>
       </c>
@@ -28340,7 +28346,7 @@
       <c r="AM197" s="13"/>
       <c r="AN197" s="13"/>
     </row>
-    <row r="198" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:40" ht="15.75" customHeight="1">
       <c r="A198" s="1">
         <v>45988.613645833335</v>
       </c>
@@ -28446,7 +28452,7 @@
       <c r="AM198" s="6"/>
       <c r="AN198" s="6"/>
     </row>
-    <row r="199" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:40" ht="15.75" customHeight="1">
       <c r="A199" s="8">
         <v>45988.676562499997</v>
       </c>
@@ -28550,7 +28556,7 @@
       <c r="AM199" s="13"/>
       <c r="AN199" s="13"/>
     </row>
-    <row r="200" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:40" ht="15.75" customHeight="1">
       <c r="A200" s="1">
         <v>45989.404143518521</v>
       </c>
@@ -28656,7 +28662,7 @@
       <c r="AM200" s="6"/>
       <c r="AN200" s="6"/>
     </row>
-    <row r="201" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:40" ht="15.75" customHeight="1">
       <c r="A201" s="8">
         <v>45989.442962962959</v>
       </c>
@@ -28766,7 +28772,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="202" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:40" ht="15.75" customHeight="1">
       <c r="A202" s="1">
         <v>45989.531435185185</v>
       </c>
@@ -28874,7 +28880,7 @@
       <c r="AM202" s="6"/>
       <c r="AN202" s="6"/>
     </row>
-    <row r="203" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:40" ht="15.75" customHeight="1">
       <c r="A203" s="8">
         <v>45989.533159722225</v>
       </c>
@@ -28980,7 +28986,7 @@
       <c r="AM203" s="13"/>
       <c r="AN203" s="13"/>
     </row>
-    <row r="204" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:40" ht="15.75" customHeight="1">
       <c r="A204" s="1">
         <v>45989.555358796293</v>
       </c>
@@ -29084,7 +29090,7 @@
       <c r="AM204" s="6"/>
       <c r="AN204" s="6"/>
     </row>
-    <row r="205" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:40" ht="15.75" customHeight="1">
       <c r="A205" s="8">
         <v>45989.562418981484</v>
       </c>
@@ -29190,7 +29196,7 @@
       <c r="AM205" s="13"/>
       <c r="AN205" s="13"/>
     </row>
-    <row r="206" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:40" ht="15.75" customHeight="1">
       <c r="A206" s="8">
         <v>45989.598379629628</v>
       </c>
@@ -29296,7 +29302,7 @@
       <c r="AM206" s="13"/>
       <c r="AN206" s="13"/>
     </row>
-    <row r="207" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:40" ht="15.75" customHeight="1">
       <c r="A207" s="1">
         <v>45989.642604166664</v>
       </c>
@@ -29402,7 +29408,7 @@
       </c>
       <c r="AN207" s="6"/>
     </row>
-    <row r="208" spans="1:40" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:40" ht="409.5">
       <c r="A208" s="8">
         <v>45989.642881944441</v>
       </c>
@@ -29508,7 +29514,7 @@
       <c r="AM208" s="13"/>
       <c r="AN208" s="13"/>
     </row>
-    <row r="209" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:40" ht="15.75" customHeight="1">
       <c r="A209" s="1">
         <v>45989.647222222222</v>
       </c>
@@ -29618,7 +29624,7 @@
       </c>
       <c r="AN209" s="6"/>
     </row>
-    <row r="210" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:40" ht="15.75" customHeight="1">
       <c r="A210" s="8">
         <v>45990.525219907409</v>
       </c>
@@ -29726,7 +29732,7 @@
       <c r="AM210" s="13"/>
       <c r="AN210" s="13"/>
     </row>
-    <row r="211" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:40" ht="15.75" customHeight="1">
       <c r="A211" s="1">
         <v>45991.461608796293</v>
       </c>
@@ -29832,7 +29838,7 @@
       <c r="AM211" s="6"/>
       <c r="AN211" s="6"/>
     </row>
-    <row r="212" spans="1:40" ht="127.5" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:40" ht="127.5">
       <c r="A212" s="8">
         <v>45991.931631944448</v>
       </c>
@@ -29938,7 +29944,7 @@
       <c r="AM212" s="13"/>
       <c r="AN212" s="13"/>
     </row>
-    <row r="213" spans="1:40" ht="229.5" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:40" ht="255">
       <c r="A213" s="1">
         <v>45992.409791666665</v>
       </c>
@@ -30048,7 +30054,7 @@
       <c r="AM213" s="6"/>
       <c r="AN213" s="6"/>
     </row>
-    <row r="214" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:40" ht="15.75" customHeight="1">
       <c r="A214" s="8">
         <v>45992.539317129631</v>
       </c>
@@ -30152,7 +30158,7 @@
       <c r="AM214" s="13"/>
       <c r="AN214" s="13"/>
     </row>
-    <row r="215" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:40" ht="15.75" customHeight="1">
       <c r="A215" s="1">
         <v>45993.426747685182</v>
       </c>
@@ -30258,7 +30264,7 @@
       <c r="AM215" s="6"/>
       <c r="AN215" s="6"/>
     </row>
-    <row r="216" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:40" ht="15.75" customHeight="1">
       <c r="A216" s="8">
         <v>45993.819548611114</v>
       </c>
@@ -30364,7 +30370,7 @@
       <c r="AM216" s="13"/>
       <c r="AN216" s="13"/>
     </row>
-    <row r="217" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:40" ht="15.75" customHeight="1">
       <c r="A217" s="1">
         <v>45994.393171296295</v>
       </c>
@@ -30478,7 +30484,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="218" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:40" ht="15.75" customHeight="1">
       <c r="A218" s="8">
         <v>45994.406215277777</v>
       </c>
@@ -30592,7 +30598,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="219" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:40" ht="15.75" customHeight="1">
       <c r="A219" s="1">
         <v>45994.417268518519</v>
       </c>
@@ -30696,7 +30702,7 @@
       <c r="AM219" s="6"/>
       <c r="AN219" s="6"/>
     </row>
-    <row r="220" spans="1:40" ht="165.75" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:40" ht="178.5">
       <c r="A220" s="8">
         <v>45994.485266203701</v>
       </c>
@@ -30808,7 +30814,7 @@
       </c>
       <c r="AN220" s="13"/>
     </row>
-    <row r="221" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:40" ht="15.75" customHeight="1">
       <c r="A221" s="1">
         <v>45994.618009259262</v>
       </c>
@@ -30914,7 +30920,7 @@
       <c r="AM221" s="6"/>
       <c r="AN221" s="6"/>
     </row>
-    <row r="222" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:40" ht="15.75" customHeight="1">
       <c r="A222" s="8">
         <v>45994.692442129628</v>
       </c>
@@ -31018,7 +31024,7 @@
       <c r="AM222" s="13"/>
       <c r="AN222" s="13"/>
     </row>
-    <row r="223" spans="1:40" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:40" ht="409.5">
       <c r="A223" s="1">
         <v>45995.725115740737</v>
       </c>
@@ -31124,7 +31130,7 @@
       <c r="AM223" s="5"/>
       <c r="AN223" s="5"/>
     </row>
-    <row r="224" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:40" ht="15.75" customHeight="1">
       <c r="A224" s="8">
         <v>45996.555462962962</v>
       </c>
@@ -31228,7 +31234,7 @@
       <c r="AM224" s="13"/>
       <c r="AN224" s="13"/>
     </row>
-    <row r="225" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:46" ht="15.75" customHeight="1">
       <c r="A225" s="1">
         <v>45999.364525462966</v>
       </c>
@@ -31332,7 +31338,7 @@
       <c r="AM225" s="6"/>
       <c r="AN225" s="6"/>
     </row>
-    <row r="226" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:46" ht="15.75" customHeight="1">
       <c r="A226" s="8">
         <v>46002.523680555554</v>
       </c>
@@ -31436,7 +31442,7 @@
       <c r="AM226" s="13"/>
       <c r="AN226" s="13"/>
     </row>
-    <row r="227" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:46" ht="15.75" customHeight="1">
       <c r="A227" s="1">
         <v>46010.499398148146</v>
       </c>
@@ -31540,7 +31546,7 @@
       <c r="AM227" s="6"/>
       <c r="AN227" s="6"/>
     </row>
-    <row r="228" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:46" ht="15.75" customHeight="1">
       <c r="A228" s="8">
         <v>46015.435925925929</v>
       </c>
@@ -31648,7 +31654,7 @@
       <c r="AM228" s="13"/>
       <c r="AN228" s="13"/>
     </row>
-    <row r="229" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:46" ht="15.75" customHeight="1">
       <c r="A229" s="1">
         <v>46017.628229166665</v>
       </c>
@@ -31752,7 +31758,7 @@
       <c r="AM229" s="6"/>
       <c r="AN229" s="6"/>
     </row>
-    <row r="230" spans="1:46" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:46" ht="15.75" customHeight="1" thickBot="1">
       <c r="A230" s="8">
         <v>46028.591863425929</v>
       </c>
@@ -31856,7 +31862,7 @@
       <c r="AM230" s="13"/>
       <c r="AN230" s="13"/>
     </row>
-    <row r="231" spans="1:46" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:46" ht="15.75" customHeight="1" thickBot="1">
       <c r="A231" s="1">
         <v>46032.41710648148</v>
       </c>

--- a/assets/excel/Staff_Doctor_Details(Responses).xlsx
+++ b/assets/excel/Staff_Doctor_Details(Responses).xlsx
@@ -5837,9 +5837,6 @@
   </si>
   <si>
     <t>Prize paper presentation in 2023</t>
-  </si>
-  <si>
-    <t>Arun Dharmarajan</t>
   </si>
   <si>
     <t>Professor and Director of Biomedical Research</t>
@@ -7055,6 +7052,9 @@
   </si>
   <si>
     <t>Shridevi</t>
+  </si>
+  <si>
+    <t>Dr.Arun Dharmarajan</t>
   </si>
 </sst>
 </file>
@@ -7714,7 +7714,7 @@
         <v>9894489142</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>38</v>
@@ -7747,7 +7747,7 @@
         <v>44601</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="Y2" s="2" t="s">
         <v>11</v>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="AB2" s="6"/>
       <c r="AC2" s="2" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="AD2" s="6"/>
       <c r="AE2" s="2" t="s">
@@ -7926,7 +7926,7 @@
         <v>9486643131</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>56</v>
@@ -7959,7 +7959,7 @@
         <v>40050</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="Y4" s="2" t="s">
         <v>11</v>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="AB4" s="6"/>
       <c r="AC4" s="2" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="AD4" s="2" t="s">
         <v>63</v>
@@ -8246,7 +8246,7 @@
         <v>8122557996</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="N7" s="9" t="s">
         <v>84</v>
@@ -8279,7 +8279,7 @@
         <v>45691</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y7" s="9" t="s">
         <v>11</v>
@@ -8291,7 +8291,7 @@
         <v>88</v>
       </c>
       <c r="AB7" s="12" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="AC7" s="9" t="s">
         <v>89</v>
@@ -8356,7 +8356,7 @@
         <v>9840050180</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>92</v>
@@ -8462,10 +8462,10 @@
         <v>9629186681</v>
       </c>
       <c r="M9" s="9" t="s">
+        <v>2019</v>
+      </c>
+      <c r="N9" s="9" t="s">
         <v>2020</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>2021</v>
       </c>
       <c r="O9" s="9" t="s">
         <v>438</v>
@@ -8992,10 +8992,10 @@
         <v>9566518548</v>
       </c>
       <c r="M14" s="2" t="s">
+        <v>2021</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>2022</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>2023</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>57</v>
@@ -9099,7 +9099,7 @@
         <v>139</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>57</v>
@@ -9410,7 +9410,7 @@
         <v>9566593108</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>166</v>
@@ -9519,7 +9519,7 @@
         <v>174</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="O19" s="9" t="s">
         <v>78</v>
@@ -9934,7 +9934,7 @@
         <v>8248667938</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="N23" s="9" t="s">
         <v>203</v>
@@ -9967,7 +9967,7 @@
         <v>40369</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="Y23" s="9" t="s">
         <v>11</v>
@@ -10046,7 +10046,7 @@
         <v>207</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="P24" s="3">
         <v>620005</v>
@@ -10253,7 +10253,7 @@
         <v>220</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>78</v>
@@ -10464,7 +10464,7 @@
         <v>9790585720</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>488</v>
@@ -10675,7 +10675,7 @@
         <v>240</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>57</v>
@@ -10720,7 +10720,7 @@
         <v>241</v>
       </c>
       <c r="AC30" s="2" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="AD30" s="2" t="s">
         <v>242</v>
@@ -10785,7 +10785,7 @@
         <v>245</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>57</v>
@@ -10993,7 +10993,7 @@
         <v>254</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>57</v>
@@ -11094,7 +11094,7 @@
         <v>8248937326</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>260</v>
@@ -11201,7 +11201,7 @@
         <v>265</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>57</v>
@@ -11315,7 +11315,7 @@
         <v>277</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>57</v>
@@ -11449,7 +11449,7 @@
         <v>40372</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="Y37" s="9" t="s">
         <v>11</v>
@@ -11527,7 +11527,7 @@
         <v>287</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>57</v>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="AB39" s="13"/>
       <c r="AC39" s="9" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="AD39" s="13"/>
       <c r="AE39" s="9" t="s">
@@ -11734,10 +11734,10 @@
         <v>9980365664</v>
       </c>
       <c r="M40" s="2" t="s">
+        <v>2041</v>
+      </c>
+      <c r="N40" s="2" t="s">
         <v>2042</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>2043</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>57</v>
@@ -11945,7 +11945,7 @@
         <v>309</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>57</v>
@@ -12152,7 +12152,7 @@
         <v>9566945363</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>528</v>
@@ -12307,7 +12307,7 @@
         <v>532</v>
       </c>
       <c r="AD45" s="9" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="AE45" s="9" t="s">
         <v>44</v>
@@ -12472,10 +12472,10 @@
         <v>8098810385</v>
       </c>
       <c r="M47" s="9" t="s">
+        <v>2046</v>
+      </c>
+      <c r="N47" s="9" t="s">
         <v>2047</v>
-      </c>
-      <c r="N47" s="9" t="s">
-        <v>2048</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>57</v>
@@ -12684,7 +12684,7 @@
         <v>9842445404</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="N49" s="9" t="s">
         <v>346</v>
@@ -12793,7 +12793,7 @@
         <v>354</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>57</v>
@@ -13209,7 +13209,7 @@
         <v>376</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>57</v>
@@ -13524,7 +13524,7 @@
         <v>9865841473</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="N57" s="9" t="s">
         <v>400</v>
@@ -13589,7 +13589,7 @@
       <c r="AJ57" s="13"/>
       <c r="AK57" s="13"/>
       <c r="AL57" s="12" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="AM57" s="13"/>
       <c r="AN57" s="13"/>
@@ -13742,7 +13742,7 @@
         <v>9994020894</v>
       </c>
       <c r="M59" s="9" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="N59" s="9" t="s">
         <v>560</v>
@@ -14061,7 +14061,7 @@
         <v>586</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>57</v>
@@ -14165,7 +14165,7 @@
         <v>594</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>57</v>
@@ -14723,7 +14723,7 @@
         <v>45325</v>
       </c>
       <c r="X68" s="2" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="Y68" s="2" t="s">
         <v>11</v>
@@ -14794,10 +14794,10 @@
         <v>8870006474</v>
       </c>
       <c r="M69" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="N69" s="9" t="s">
         <v>2058</v>
-      </c>
-      <c r="N69" s="9" t="s">
-        <v>2059</v>
       </c>
       <c r="O69" s="9" t="s">
         <v>57</v>
@@ -14931,7 +14931,7 @@
         <v>44681</v>
       </c>
       <c r="X70" s="2" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="Y70" s="2" t="s">
         <v>11</v>
@@ -15002,10 +15002,10 @@
         <v>8973764197</v>
       </c>
       <c r="M71" s="9" t="s">
+        <v>2060</v>
+      </c>
+      <c r="N71" s="9" t="s">
         <v>2061</v>
-      </c>
-      <c r="N71" s="9" t="s">
-        <v>2062</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>57</v>
@@ -15035,7 +15035,7 @@
         <v>45250</v>
       </c>
       <c r="X71" s="9" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="Y71" s="9" t="s">
         <v>11</v>
@@ -15111,7 +15111,7 @@
         <v>655</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>57</v>
@@ -15215,7 +15215,7 @@
         <v>567</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="O73" s="9" t="s">
         <v>57</v>
@@ -15531,7 +15531,7 @@
         <v>681</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="O76" s="2" t="s">
         <v>57</v>
@@ -15634,10 +15634,10 @@
         <v>9789443655</v>
       </c>
       <c r="M77" s="9" t="s">
+        <v>2066</v>
+      </c>
+      <c r="N77" s="9" t="s">
         <v>2067</v>
-      </c>
-      <c r="N77" s="9" t="s">
-        <v>2068</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>57</v>
@@ -15845,7 +15845,7 @@
         <v>699</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="O79" s="9" t="s">
         <v>57</v>
@@ -15946,10 +15946,10 @@
         <v>9842103319</v>
       </c>
       <c r="M80" s="2" t="s">
+        <v>2069</v>
+      </c>
+      <c r="N80" s="2" t="s">
         <v>2070</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>2071</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>361</v>
@@ -16055,7 +16055,7 @@
         <v>711</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>57</v>
@@ -16085,7 +16085,7 @@
         <v>45352</v>
       </c>
       <c r="X81" s="9" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="Y81" s="9" t="s">
         <v>11</v>
@@ -16098,7 +16098,7 @@
       </c>
       <c r="AB81" s="13"/>
       <c r="AC81" s="9" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="AD81" s="9" t="s">
         <v>229</v>
@@ -16267,7 +16267,7 @@
         <v>725</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>78</v>
@@ -16503,7 +16503,7 @@
         <v>45954</v>
       </c>
       <c r="X85" s="9" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="Y85" s="9" t="s">
         <v>11</v>
@@ -16516,7 +16516,7 @@
       </c>
       <c r="AB85" s="13"/>
       <c r="AC85" s="9" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AD85" s="13"/>
       <c r="AE85" s="9" t="s">
@@ -16681,7 +16681,7 @@
         <v>225</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>57</v>
@@ -16891,7 +16891,7 @@
         <v>759</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="O89" s="9" t="s">
         <v>57</v>
@@ -17306,10 +17306,10 @@
         <v>9952541163</v>
       </c>
       <c r="M93" s="9" t="s">
+        <v>2078</v>
+      </c>
+      <c r="N93" s="9" t="s">
         <v>2079</v>
-      </c>
-      <c r="N93" s="9" t="s">
-        <v>2080</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>57</v>
@@ -17834,7 +17834,7 @@
         <v>9500799099</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="N98" s="2" t="s">
         <v>826</v>
@@ -18044,10 +18044,10 @@
         <v>8438103656</v>
       </c>
       <c r="M100" s="2" t="s">
+        <v>2081</v>
+      </c>
+      <c r="N100" s="2" t="s">
         <v>2082</v>
-      </c>
-      <c r="N100" s="2" t="s">
-        <v>2083</v>
       </c>
       <c r="O100" s="2" t="s">
         <v>57</v>
@@ -18153,7 +18153,7 @@
         <v>845</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="O101" s="9" t="s">
         <v>57</v>
@@ -18620,11 +18620,11 @@
         <v>739</v>
       </c>
       <c r="AA105" s="9" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="AB105" s="13"/>
       <c r="AC105" s="9" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="AD105" s="9" t="s">
         <v>881</v>
@@ -18793,7 +18793,7 @@
         <v>894</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="O107" s="9" t="s">
         <v>57</v>
@@ -19003,7 +19003,7 @@
         <v>907</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="O109" s="9" t="s">
         <v>78</v>
@@ -19150,7 +19150,7 @@
       </c>
       <c r="AB110" s="6"/>
       <c r="AC110" s="2" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="AD110" s="6"/>
       <c r="AE110" s="2" t="s">
@@ -19674,10 +19674,10 @@
         <v>739</v>
       </c>
       <c r="AA115" s="9" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="AB115" s="9" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="AC115" s="9" t="s">
         <v>209</v>
@@ -19740,7 +19740,7 @@
         <v>9843841181</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="N116" s="2" t="s">
         <v>956</v>
@@ -19846,7 +19846,7 @@
         <v>9443241424</v>
       </c>
       <c r="M117" s="9" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="N117" s="9" t="s">
         <v>965</v>
@@ -19879,7 +19879,7 @@
         <v>43187</v>
       </c>
       <c r="X117" s="9" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="Y117" s="9" t="s">
         <v>11</v>
@@ -20374,7 +20374,7 @@
         <v>9884983543</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="N122" s="2" t="s">
         <v>1003</v>
@@ -20478,7 +20478,7 @@
         <v>9585536854</v>
       </c>
       <c r="M123" s="9" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="N123" s="9" t="s">
         <v>1009</v>
@@ -20585,7 +20585,7 @@
         <v>1017</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="O124" s="2" t="s">
         <v>57</v>
@@ -20684,7 +20684,7 @@
         <v>9597484444</v>
       </c>
       <c r="M125" s="9" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="N125" s="9" t="s">
         <v>1023</v>
@@ -20894,7 +20894,7 @@
         <v>9943907528</v>
       </c>
       <c r="M127" s="9" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="N127" s="9" t="s">
         <v>1038</v>
@@ -21041,7 +21041,7 @@
         <v>45505</v>
       </c>
       <c r="X128" s="2" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="Y128" s="2" t="s">
         <v>11</v>
@@ -21054,7 +21054,7 @@
       </c>
       <c r="AB128" s="6"/>
       <c r="AC128" s="2" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="AD128" s="2" t="s">
         <v>1050</v>
@@ -21221,7 +21221,7 @@
         <v>1060</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="O130" s="2" t="s">
         <v>57</v>
@@ -21439,7 +21439,7 @@
         <v>1078</v>
       </c>
       <c r="N132" s="2" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="O132" s="2" t="s">
         <v>57</v>
@@ -21646,10 +21646,10 @@
         <v>9994264019</v>
       </c>
       <c r="M134" s="2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="N134" s="2" t="s">
         <v>2101</v>
-      </c>
-      <c r="N134" s="2" t="s">
-        <v>2102</v>
       </c>
       <c r="O134" s="2" t="s">
         <v>57</v>
@@ -21755,7 +21755,7 @@
         <v>1095</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>57</v>
@@ -21861,7 +21861,7 @@
         <v>1102</v>
       </c>
       <c r="N136" s="2" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="O136" s="2" t="s">
         <v>266</v>
@@ -21891,7 +21891,7 @@
         <v>44228</v>
       </c>
       <c r="X136" s="2" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="Y136" s="2" t="s">
         <v>11</v>
@@ -21967,7 +21967,7 @@
         <v>1222</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>57</v>
@@ -22073,7 +22073,7 @@
         <v>1230</v>
       </c>
       <c r="N138" s="2" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="O138" s="2" t="s">
         <v>1231</v>
@@ -22382,7 +22382,7 @@
         <v>8189827034</v>
       </c>
       <c r="M141" s="9" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="N141" s="9" t="s">
         <v>1252</v>
@@ -22633,7 +22633,7 @@
         <v>11</v>
       </c>
       <c r="Z143" s="9" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="AA143" s="9" t="s">
         <v>1675</v>
@@ -22703,7 +22703,7 @@
         <v>1276</v>
       </c>
       <c r="N144" s="2" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="O144" s="2" t="s">
         <v>57</v>
@@ -22846,7 +22846,7 @@
         <v>739</v>
       </c>
       <c r="AA145" s="9" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="AB145" s="13"/>
       <c r="AC145" s="9" t="s">
@@ -23010,7 +23010,7 @@
         <v>9894147545</v>
       </c>
       <c r="M147" s="9" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="N147" s="9" t="s">
         <v>1300</v>
@@ -23218,7 +23218,7 @@
         <v>9894593245</v>
       </c>
       <c r="M149" s="9" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="N149" s="9" t="s">
         <v>1315</v>
@@ -23355,7 +23355,7 @@
         <v>45980</v>
       </c>
       <c r="X150" s="2" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="Y150" s="2" t="s">
         <v>11</v>
@@ -23431,7 +23431,7 @@
         <v>1329</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="O151" s="9" t="s">
         <v>57</v>
@@ -23641,7 +23641,7 @@
         <v>1343</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="O153" s="9" t="s">
         <v>1344</v>
@@ -23662,7 +23662,7 @@
         <v>1345</v>
       </c>
       <c r="U153" s="9" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="V153" s="9" t="s">
         <v>42</v>
@@ -23671,7 +23671,7 @@
         <v>43958</v>
       </c>
       <c r="X153" s="9" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="Y153" s="9" t="s">
         <v>11</v>
@@ -23684,7 +23684,7 @@
       </c>
       <c r="AB153" s="13"/>
       <c r="AC153" s="9" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="AD153" s="9" t="s">
         <v>1346</v>
@@ -23852,7 +23852,7 @@
         <v>8144380594</v>
       </c>
       <c r="M155" s="9" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="N155" s="9" t="s">
         <v>1359</v>
@@ -24060,10 +24060,10 @@
         <v>9003056068</v>
       </c>
       <c r="M157" s="9" t="s">
+        <v>2115</v>
+      </c>
+      <c r="N157" s="9" t="s">
         <v>2116</v>
-      </c>
-      <c r="N157" s="9" t="s">
-        <v>2117</v>
       </c>
       <c r="O157" s="9" t="s">
         <v>57</v>
@@ -24164,7 +24164,7 @@
         <v>9445972712</v>
       </c>
       <c r="M158" s="2" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="N158" s="2" t="s">
         <v>1379</v>
@@ -24413,7 +24413,7 @@
         <v>44203</v>
       </c>
       <c r="X160" s="2" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="Y160" s="2" t="s">
         <v>11</v>
@@ -24532,7 +24532,7 @@
       </c>
       <c r="AB161" s="13"/>
       <c r="AC161" s="9" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="AD161" s="9" t="s">
         <v>1412</v>
@@ -24625,7 +24625,7 @@
         <v>45607</v>
       </c>
       <c r="X162" s="2" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="Y162" s="2" t="s">
         <v>11</v>
@@ -24698,7 +24698,7 @@
         <v>9790628434</v>
       </c>
       <c r="M163" s="9" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="N163" s="9" t="s">
         <v>1424</v>
@@ -24802,19 +24802,19 @@
         <v>9899936858</v>
       </c>
       <c r="M164" s="2" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="N164" s="2" t="s">
         <v>1431</v>
       </c>
       <c r="O164" s="2" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="P164" s="3">
         <v>600014</v>
       </c>
       <c r="Q164" s="2" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="R164" s="2" t="s">
         <v>39</v>
@@ -25010,7 +25010,7 @@
         <v>9626913491</v>
       </c>
       <c r="M166" s="2" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="N166" s="2" t="s">
         <v>1446</v>
@@ -25114,10 +25114,10 @@
         <v>8870946952</v>
       </c>
       <c r="M167" s="9" t="s">
+        <v>2124</v>
+      </c>
+      <c r="N167" s="9" t="s">
         <v>2125</v>
-      </c>
-      <c r="N167" s="9" t="s">
-        <v>2126</v>
       </c>
       <c r="O167" s="9" t="s">
         <v>57</v>
@@ -25220,10 +25220,10 @@
         <v>9443357653</v>
       </c>
       <c r="M168" s="2" t="s">
+        <v>2126</v>
+      </c>
+      <c r="N168" s="2" t="s">
         <v>2127</v>
-      </c>
-      <c r="N168" s="2" t="s">
-        <v>2128</v>
       </c>
       <c r="O168" s="2" t="s">
         <v>57</v>
@@ -25253,7 +25253,7 @@
         <v>42109</v>
       </c>
       <c r="X168" s="2" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="Y168" s="2" t="s">
         <v>11</v>
@@ -25266,7 +25266,7 @@
       </c>
       <c r="AB168" s="6"/>
       <c r="AC168" s="2" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="AD168" s="2" t="s">
         <v>1462</v>
@@ -25331,7 +25331,7 @@
         <v>1466</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="O169" s="9" t="s">
         <v>57</v>
@@ -25538,7 +25538,7 @@
         <v>9786497001</v>
       </c>
       <c r="M171" s="9" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="N171" s="9" t="s">
         <v>1485</v>
@@ -25649,7 +25649,7 @@
         <v>1495</v>
       </c>
       <c r="N172" s="2" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="O172" s="2" t="s">
         <v>78</v>
@@ -25679,7 +25679,7 @@
         <v>45681</v>
       </c>
       <c r="X172" s="2" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="Y172" s="2" t="s">
         <v>11</v>
@@ -25692,7 +25692,7 @@
       </c>
       <c r="AB172" s="6"/>
       <c r="AC172" s="2" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="AD172" s="2" t="s">
         <v>1497</v>
@@ -25858,7 +25858,7 @@
         <v>9600733744</v>
       </c>
       <c r="M174" s="2" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="N174" s="2" t="s">
         <v>1508</v>
@@ -26181,7 +26181,7 @@
         <v>1532</v>
       </c>
       <c r="N177" s="9" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="O177" s="9" t="s">
         <v>57</v>
@@ -26386,7 +26386,7 @@
         <v>9486885993</v>
       </c>
       <c r="M179" s="9" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="N179" s="9" t="s">
         <v>1547</v>
@@ -26703,7 +26703,7 @@
         <v>1571</v>
       </c>
       <c r="N182" s="2" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="O182" s="2" t="s">
         <v>57</v>
@@ -26804,7 +26804,7 @@
         <v>9976551564</v>
       </c>
       <c r="M183" s="9" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="N183" s="9" t="s">
         <v>1578</v>
@@ -26911,7 +26911,7 @@
         <v>1583</v>
       </c>
       <c r="N184" s="2" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="O184" s="2" t="s">
         <v>57</v>
@@ -27015,7 +27015,7 @@
         <v>1589</v>
       </c>
       <c r="N185" s="9" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="O185" s="9" t="s">
         <v>57</v>
@@ -27225,7 +27225,7 @@
         <v>1604</v>
       </c>
       <c r="N187" s="9" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="O187" s="9" t="s">
         <v>57</v>
@@ -27246,7 +27246,7 @@
         <v>1605</v>
       </c>
       <c r="U187" s="9" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="V187" s="9" t="s">
         <v>42</v>
@@ -27255,7 +27255,7 @@
         <v>45474</v>
       </c>
       <c r="X187" s="9" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="Y187" s="9" t="s">
         <v>11</v>
@@ -27264,7 +27264,7 @@
         <v>739</v>
       </c>
       <c r="AA187" s="9" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="AB187" s="13"/>
       <c r="AC187" s="9" t="s">
@@ -27430,10 +27430,10 @@
         <v>9980839365</v>
       </c>
       <c r="M189" s="9" t="s">
+        <v>2143</v>
+      </c>
+      <c r="N189" s="9" t="s">
         <v>2144</v>
-      </c>
-      <c r="N189" s="9" t="s">
-        <v>2145</v>
       </c>
       <c r="O189" s="9" t="s">
         <v>57</v>
@@ -27675,7 +27675,7 @@
         <v>45680</v>
       </c>
       <c r="X191" s="9" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="Y191" s="9" t="s">
         <v>11</v>
@@ -27757,7 +27757,7 @@
         <v>1735</v>
       </c>
       <c r="N192" s="2" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="O192" s="2" t="s">
         <v>57</v>
@@ -27787,7 +27787,7 @@
         <v>39995</v>
       </c>
       <c r="X192" s="2" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="Y192" s="2" t="s">
         <v>11</v>
@@ -27800,10 +27800,10 @@
       </c>
       <c r="AB192" s="6"/>
       <c r="AC192" s="2" t="s">
+        <v>2148</v>
+      </c>
+      <c r="AD192" s="2" t="s">
         <v>2149</v>
-      </c>
-      <c r="AD192" s="2" t="s">
-        <v>2150</v>
       </c>
       <c r="AE192" s="2" t="s">
         <v>44</v>
@@ -27899,10 +27899,10 @@
         <v>11</v>
       </c>
       <c r="Z193" s="9" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="AA193" s="9" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="AB193" s="13"/>
       <c r="AC193" s="9" t="s">
@@ -27999,7 +27999,7 @@
         <v>45432</v>
       </c>
       <c r="X194" s="2" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="Y194" s="2" t="s">
         <v>11</v>
@@ -28012,7 +28012,7 @@
       </c>
       <c r="AB194" s="6"/>
       <c r="AC194" s="2" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="AD194" s="6"/>
       <c r="AE194" s="2" t="s">
@@ -28073,7 +28073,7 @@
         <v>1753</v>
       </c>
       <c r="N195" s="9" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="O195" s="2" t="s">
         <v>78</v>
@@ -28112,7 +28112,7 @@
         <v>739</v>
       </c>
       <c r="AA195" s="9" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="AB195" s="13"/>
       <c r="AC195" s="9" t="s">
@@ -28387,7 +28387,7 @@
         <v>1776</v>
       </c>
       <c r="N198" s="2" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="O198" s="2" t="s">
         <v>57</v>
@@ -28594,7 +28594,7 @@
         <v>9791788778</v>
       </c>
       <c r="M200" s="2" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="N200" s="2" t="s">
         <v>1795</v>
@@ -28640,7 +28640,7 @@
       </c>
       <c r="AB200" s="6"/>
       <c r="AC200" s="2" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="AD200" s="6"/>
       <c r="AE200" s="2" t="s">
@@ -28733,7 +28733,7 @@
         <v>45068</v>
       </c>
       <c r="X201" s="9" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="Y201" s="9" t="s">
         <v>11</v>
@@ -28843,7 +28843,7 @@
         <v>43633</v>
       </c>
       <c r="X202" s="2" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="Y202" s="2" t="s">
         <v>11</v>
@@ -28858,7 +28858,7 @@
         <v>1810</v>
       </c>
       <c r="AC202" s="2" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="AD202" s="2" t="s">
         <v>1813</v>
@@ -29024,10 +29024,10 @@
         <v>9489567930</v>
       </c>
       <c r="M204" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="N204" s="2" t="s">
         <v>2157</v>
-      </c>
-      <c r="N204" s="2" t="s">
-        <v>2158</v>
       </c>
       <c r="O204" s="2" t="s">
         <v>57</v>
@@ -29057,7 +29057,7 @@
         <v>45537</v>
       </c>
       <c r="X204" s="2" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="Y204" s="2" t="s">
         <v>11</v>
@@ -29131,7 +29131,7 @@
         <v>1834</v>
       </c>
       <c r="N205" s="9" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="O205" s="9" t="s">
         <v>997</v>
@@ -29234,7 +29234,7 @@
         <v>9245171296</v>
       </c>
       <c r="M206" s="9" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="N206" s="9" t="s">
         <v>1844</v>
@@ -29492,7 +29492,7 @@
       </c>
       <c r="AB208" s="13"/>
       <c r="AC208" s="9" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="AD208" s="9" t="s">
         <v>1867</v>
@@ -29665,7 +29665,7 @@
         <v>1883</v>
       </c>
       <c r="N210" s="9" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="O210" s="9" t="s">
         <v>57</v>
@@ -29770,7 +29770,7 @@
         <v>8056496100</v>
       </c>
       <c r="M211" s="2" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="N211" s="2" t="s">
         <v>1889</v>
@@ -29900,7 +29900,7 @@
         <v>1900</v>
       </c>
       <c r="U212" s="9" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="V212" s="9" t="s">
         <v>42</v>
@@ -29915,7 +29915,7 @@
         <v>11</v>
       </c>
       <c r="Z212" s="9" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="AA212" s="9" t="s">
         <v>1902</v>
@@ -29944,12 +29944,12 @@
       <c r="AM212" s="13"/>
       <c r="AN212" s="13"/>
     </row>
-    <row r="213" spans="1:40" ht="255">
+    <row r="213" spans="1:40" ht="229.5">
       <c r="A213" s="1">
         <v>45992.409791666665</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>1905</v>
+        <v>2261</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>31</v>
@@ -29961,7 +29961,7 @@
         <v>19441</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>1815</v>
@@ -29970,10 +29970,10 @@
         <v>34</v>
       </c>
       <c r="I213" s="2" t="s">
+        <v>1906</v>
+      </c>
+      <c r="J213" s="5" t="s">
         <v>1907</v>
-      </c>
-      <c r="J213" s="5" t="s">
-        <v>1908</v>
       </c>
       <c r="K213" s="2" t="s">
         <v>55</v>
@@ -29982,10 +29982,10 @@
         <v>7708490384</v>
       </c>
       <c r="M213" s="2" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="N213" s="2" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="O213" s="2" t="s">
         <v>57</v>
@@ -30003,10 +30003,10 @@
         <v>40</v>
       </c>
       <c r="T213" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="U213" s="2" t="s">
         <v>1910</v>
-      </c>
-      <c r="U213" s="2" t="s">
-        <v>1911</v>
       </c>
       <c r="V213" s="2" t="s">
         <v>60</v>
@@ -30015,7 +30015,7 @@
         <v>45768</v>
       </c>
       <c r="X213" s="2" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="Y213" s="2" t="s">
         <v>199</v>
@@ -30024,16 +30024,16 @@
         <v>87</v>
       </c>
       <c r="AA213" s="2" t="s">
+        <v>1912</v>
+      </c>
+      <c r="AB213" s="5" t="s">
         <v>1913</v>
       </c>
-      <c r="AB213" s="5" t="s">
+      <c r="AC213" s="2" t="s">
         <v>1914</v>
       </c>
-      <c r="AC213" s="2" t="s">
+      <c r="AD213" s="2" t="s">
         <v>1915</v>
-      </c>
-      <c r="AD213" s="2" t="s">
-        <v>1916</v>
       </c>
       <c r="AE213" s="2" t="s">
         <v>44</v>
@@ -30049,7 +30049,7 @@
       <c r="AJ213" s="6"/>
       <c r="AK213" s="6"/>
       <c r="AL213" s="5" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="AM213" s="6"/>
       <c r="AN213" s="6"/>
@@ -30059,7 +30059,7 @@
         <v>45992.539317129631</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="C214" s="9" t="s">
         <v>52</v>
@@ -30071,7 +30071,7 @@
         <v>34914</v>
       </c>
       <c r="F214" s="9" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="G214" s="9" t="s">
         <v>46</v>
@@ -30083,7 +30083,7 @@
         <v>35</v>
       </c>
       <c r="J214" s="12" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="K214" s="9" t="s">
         <v>147</v>
@@ -30092,10 +30092,10 @@
         <v>9159874787</v>
       </c>
       <c r="M214" s="9" t="s">
+        <v>1920</v>
+      </c>
+      <c r="N214" s="9" t="s">
         <v>1921</v>
-      </c>
-      <c r="N214" s="9" t="s">
-        <v>1922</v>
       </c>
       <c r="O214" s="9" t="s">
         <v>57</v>
@@ -30113,10 +30113,10 @@
         <v>2</v>
       </c>
       <c r="T214" s="9" t="s">
+        <v>1922</v>
+      </c>
+      <c r="U214" s="9" t="s">
         <v>1923</v>
-      </c>
-      <c r="U214" s="9" t="s">
-        <v>1924</v>
       </c>
       <c r="V214" s="9" t="s">
         <v>98</v>
@@ -30125,7 +30125,7 @@
         <v>45247</v>
       </c>
       <c r="X214" s="9" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="Y214" s="9" t="s">
         <v>11</v>
@@ -30134,7 +30134,7 @@
         <v>796</v>
       </c>
       <c r="AA214" s="9" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="AB214" s="13"/>
       <c r="AC214" s="9" t="s">
@@ -30163,7 +30163,7 @@
         <v>45993.426747685182</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>31</v>
@@ -30187,7 +30187,7 @@
         <v>35</v>
       </c>
       <c r="J215" s="5" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="K215" s="2" t="s">
         <v>55</v>
@@ -30196,10 +30196,10 @@
         <v>9047488954</v>
       </c>
       <c r="M215" s="2" t="s">
+        <v>1928</v>
+      </c>
+      <c r="N215" s="2" t="s">
         <v>1929</v>
-      </c>
-      <c r="N215" s="2" t="s">
-        <v>1930</v>
       </c>
       <c r="O215" s="2" t="s">
         <v>57</v>
@@ -30217,10 +30217,10 @@
         <v>1</v>
       </c>
       <c r="T215" s="2" t="s">
+        <v>1930</v>
+      </c>
+      <c r="U215" s="2" t="s">
         <v>1931</v>
-      </c>
-      <c r="U215" s="2" t="s">
-        <v>1932</v>
       </c>
       <c r="V215" s="2" t="s">
         <v>42</v>
@@ -30229,7 +30229,7 @@
         <v>45748</v>
       </c>
       <c r="X215" s="2" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="Y215" s="2" t="s">
         <v>11</v>
@@ -30238,11 +30238,11 @@
         <v>82</v>
       </c>
       <c r="AA215" s="2" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="AB215" s="6"/>
       <c r="AC215" s="2" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="AD215" s="6"/>
       <c r="AE215" s="2" t="s">
@@ -30259,7 +30259,7 @@
       <c r="AJ215" s="6"/>
       <c r="AK215" s="6"/>
       <c r="AL215" s="5" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="AM215" s="6"/>
       <c r="AN215" s="6"/>
@@ -30269,7 +30269,7 @@
         <v>45993.819548611114</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="C216" s="9" t="s">
         <v>52</v>
@@ -30291,19 +30291,19 @@
         <v>35</v>
       </c>
       <c r="J216" s="12" t="s">
+        <v>1937</v>
+      </c>
+      <c r="K216" s="9" t="s">
         <v>1938</v>
-      </c>
-      <c r="K216" s="9" t="s">
-        <v>1939</v>
       </c>
       <c r="L216" s="10">
         <v>9842091151</v>
       </c>
       <c r="M216" s="9" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="N216" s="9" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="O216" s="9" t="s">
         <v>942</v>
@@ -30321,10 +30321,10 @@
         <v>7</v>
       </c>
       <c r="T216" s="9" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="U216" s="9" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="V216" s="9" t="s">
         <v>42</v>
@@ -30339,16 +30339,16 @@
         <v>11</v>
       </c>
       <c r="Z216" s="9" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="AA216" s="9" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="AB216" s="12" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="AC216" s="9" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="AD216" s="13"/>
       <c r="AE216" s="9" t="s">
@@ -30365,7 +30365,7 @@
       <c r="AJ216" s="13"/>
       <c r="AK216" s="13"/>
       <c r="AL216" s="12" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="AM216" s="13"/>
       <c r="AN216" s="13"/>
@@ -30375,7 +30375,7 @@
         <v>45994.393171296295</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>31</v>
@@ -30399,7 +30399,7 @@
         <v>35</v>
       </c>
       <c r="J217" s="5" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="K217" s="2" t="s">
         <v>55</v>
@@ -30408,10 +30408,10 @@
         <v>9789882729</v>
       </c>
       <c r="M217" s="2" t="s">
+        <v>1944</v>
+      </c>
+      <c r="N217" s="2" t="s">
         <v>1945</v>
-      </c>
-      <c r="N217" s="2" t="s">
-        <v>1946</v>
       </c>
       <c r="O217" s="2" t="s">
         <v>57</v>
@@ -30420,7 +30420,7 @@
         <v>620018</v>
       </c>
       <c r="Q217" s="2" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="R217" s="2" t="s">
         <v>39</v>
@@ -30429,10 +30429,10 @@
         <v>5</v>
       </c>
       <c r="T217" s="2" t="s">
+        <v>1946</v>
+      </c>
+      <c r="U217" s="2" t="s">
         <v>1947</v>
-      </c>
-      <c r="U217" s="2" t="s">
-        <v>1948</v>
       </c>
       <c r="V217" s="2" t="s">
         <v>98</v>
@@ -30441,19 +30441,19 @@
         <v>44004</v>
       </c>
       <c r="X217" s="2" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Y217" s="2" t="s">
         <v>11</v>
       </c>
       <c r="Z217" s="2" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="AA217" s="2" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="AB217" s="5" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="AC217" s="2" t="s">
         <v>229</v>
@@ -30475,13 +30475,13 @@
       <c r="AJ217" s="6"/>
       <c r="AK217" s="6"/>
       <c r="AL217" s="5" t="s">
+        <v>1950</v>
+      </c>
+      <c r="AM217" s="5" t="s">
         <v>1951</v>
       </c>
-      <c r="AM217" s="5" t="s">
+      <c r="AN217" s="5" t="s">
         <v>1952</v>
-      </c>
-      <c r="AN217" s="5" t="s">
-        <v>1953</v>
       </c>
     </row>
     <row r="218" spans="1:40" ht="15.75" customHeight="1">
@@ -30489,7 +30489,7 @@
         <v>45994.406215277777</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="C218" s="9" t="s">
         <v>31</v>
@@ -30513,19 +30513,19 @@
         <v>35</v>
       </c>
       <c r="J218" s="12" t="s">
+        <v>1954</v>
+      </c>
+      <c r="K218" s="9" t="s">
         <v>1955</v>
-      </c>
-      <c r="K218" s="9" t="s">
-        <v>1956</v>
       </c>
       <c r="L218" s="10">
         <v>9442092653</v>
       </c>
       <c r="M218" s="9" t="s">
+        <v>1956</v>
+      </c>
+      <c r="N218" s="9" t="s">
         <v>1957</v>
-      </c>
-      <c r="N218" s="9" t="s">
-        <v>1958</v>
       </c>
       <c r="O218" s="9" t="s">
         <v>438</v>
@@ -30543,10 +30543,10 @@
         <v>4</v>
       </c>
       <c r="T218" s="9" t="s">
+        <v>1958</v>
+      </c>
+      <c r="U218" s="9" t="s">
         <v>1959</v>
-      </c>
-      <c r="U218" s="9" t="s">
-        <v>1960</v>
       </c>
       <c r="V218" s="9" t="s">
         <v>60</v>
@@ -30555,25 +30555,25 @@
         <v>44721</v>
       </c>
       <c r="X218" s="9" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="Y218" s="9" t="s">
         <v>11</v>
       </c>
       <c r="Z218" s="9" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="AA218" s="9" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="AB218" s="12" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="AC218" s="9" t="s">
         <v>210</v>
       </c>
       <c r="AD218" s="9" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="AE218" s="9" t="s">
         <v>44</v>
@@ -30589,13 +30589,13 @@
       <c r="AJ218" s="13"/>
       <c r="AK218" s="13"/>
       <c r="AL218" s="12" t="s">
+        <v>1962</v>
+      </c>
+      <c r="AM218" s="12" t="s">
         <v>1963</v>
       </c>
-      <c r="AM218" s="12" t="s">
+      <c r="AN218" s="12" t="s">
         <v>1964</v>
-      </c>
-      <c r="AN218" s="12" t="s">
-        <v>1965</v>
       </c>
     </row>
     <row r="219" spans="1:40" ht="15.75" customHeight="1">
@@ -30603,7 +30603,7 @@
         <v>45994.417268518519</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>52</v>
@@ -30627,7 +30627,7 @@
         <v>35</v>
       </c>
       <c r="J219" s="5" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="K219" s="2" t="s">
         <v>55</v>
@@ -30636,10 +30636,10 @@
         <v>9487590559</v>
       </c>
       <c r="M219" s="2" t="s">
+        <v>1967</v>
+      </c>
+      <c r="N219" s="2" t="s">
         <v>1968</v>
-      </c>
-      <c r="N219" s="2" t="s">
-        <v>1969</v>
       </c>
       <c r="O219" s="2" t="s">
         <v>402</v>
@@ -30657,7 +30657,7 @@
         <v>2</v>
       </c>
       <c r="T219" s="2" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="U219" s="2" t="s">
         <v>574</v>
@@ -30675,10 +30675,10 @@
         <v>11</v>
       </c>
       <c r="Z219" s="2" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="AA219" s="2" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="AB219" s="6"/>
       <c r="AC219" s="2" t="s">
@@ -30702,12 +30702,12 @@
       <c r="AM219" s="6"/>
       <c r="AN219" s="6"/>
     </row>
-    <row r="220" spans="1:40" ht="178.5">
+    <row r="220" spans="1:40" ht="165.75">
       <c r="A220" s="8">
         <v>45994.485266203701</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="C220" s="9" t="s">
         <v>31</v>
@@ -30731,19 +30731,19 @@
         <v>35</v>
       </c>
       <c r="J220" s="12" t="s">
+        <v>1971</v>
+      </c>
+      <c r="K220" s="9" t="s">
         <v>1972</v>
-      </c>
-      <c r="K220" s="9" t="s">
-        <v>1973</v>
       </c>
       <c r="L220" s="10">
         <v>9447345528</v>
       </c>
       <c r="M220" s="9" t="s">
+        <v>1973</v>
+      </c>
+      <c r="N220" s="9" t="s">
         <v>1974</v>
-      </c>
-      <c r="N220" s="9" t="s">
-        <v>1975</v>
       </c>
       <c r="O220" s="9" t="s">
         <v>79</v>
@@ -30761,7 +30761,7 @@
         <v>32</v>
       </c>
       <c r="T220" s="9" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="U220" s="9" t="s">
         <v>130</v>
@@ -30773,25 +30773,25 @@
         <v>43801</v>
       </c>
       <c r="X220" s="9" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="Y220" s="9" t="s">
         <v>199</v>
       </c>
       <c r="Z220" s="9" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="AA220" s="9" t="s">
+        <v>1977</v>
+      </c>
+      <c r="AB220" s="12" t="s">
         <v>1978</v>
       </c>
-      <c r="AB220" s="12" t="s">
+      <c r="AC220" s="9" t="s">
         <v>1979</v>
       </c>
-      <c r="AC220" s="9" t="s">
-        <v>1980</v>
-      </c>
       <c r="AD220" s="9" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="AE220" s="9" t="s">
         <v>44</v>
@@ -30807,10 +30807,10 @@
       <c r="AJ220" s="13"/>
       <c r="AK220" s="13"/>
       <c r="AL220" s="12" t="s">
+        <v>1980</v>
+      </c>
+      <c r="AM220" s="9" t="s">
         <v>1981</v>
-      </c>
-      <c r="AM220" s="9" t="s">
-        <v>1982</v>
       </c>
       <c r="AN220" s="13"/>
     </row>
@@ -30819,7 +30819,7 @@
         <v>45994.618009259262</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>31</v>
@@ -30843,7 +30843,7 @@
         <v>35</v>
       </c>
       <c r="J221" s="5" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="K221" s="2" t="s">
         <v>55</v>
@@ -30852,10 +30852,10 @@
         <v>9787319750</v>
       </c>
       <c r="M221" s="2" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="N221" s="2" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="O221" s="2" t="s">
         <v>57</v>
@@ -30873,10 +30873,10 @@
         <v>20</v>
       </c>
       <c r="T221" s="2" t="s">
+        <v>1985</v>
+      </c>
+      <c r="U221" s="2" t="s">
         <v>1986</v>
-      </c>
-      <c r="U221" s="2" t="s">
-        <v>1987</v>
       </c>
       <c r="V221" s="2" t="s">
         <v>60</v>
@@ -30885,7 +30885,7 @@
         <v>43985</v>
       </c>
       <c r="X221" s="2" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="Y221" s="2" t="s">
         <v>11</v>
@@ -30894,14 +30894,14 @@
         <v>796</v>
       </c>
       <c r="AA221" s="2" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="AB221" s="6"/>
       <c r="AC221" s="2" t="s">
+        <v>1989</v>
+      </c>
+      <c r="AD221" s="2" t="s">
         <v>1990</v>
-      </c>
-      <c r="AD221" s="2" t="s">
-        <v>1991</v>
       </c>
       <c r="AE221" s="2" t="s">
         <v>44</v>
@@ -30925,7 +30925,7 @@
         <v>45994.692442129628</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="C222" s="9" t="s">
         <v>31</v>
@@ -30949,7 +30949,7 @@
         <v>35</v>
       </c>
       <c r="J222" s="12" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="K222" s="9" t="s">
         <v>55</v>
@@ -30958,10 +30958,10 @@
         <v>7708422167</v>
       </c>
       <c r="M222" s="9" t="s">
+        <v>1993</v>
+      </c>
+      <c r="N222" s="9" t="s">
         <v>1994</v>
-      </c>
-      <c r="N222" s="9" t="s">
-        <v>1995</v>
       </c>
       <c r="O222" s="9" t="s">
         <v>450</v>
@@ -30982,7 +30982,7 @@
         <v>7708422167</v>
       </c>
       <c r="U222" s="9" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="V222" s="9" t="s">
         <v>42</v>
@@ -30997,10 +30997,10 @@
         <v>11</v>
       </c>
       <c r="Z222" s="9" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="AA222" s="9" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="AB222" s="13"/>
       <c r="AC222" s="9" t="s">
@@ -31029,7 +31029,7 @@
         <v>45995.725115740737</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>52</v>
@@ -31053,7 +31053,7 @@
         <v>35</v>
       </c>
       <c r="J223" s="5" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="K223" s="2" t="s">
         <v>186</v>
@@ -31062,10 +31062,10 @@
         <v>9943907528</v>
       </c>
       <c r="M223" s="2" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="N223" s="2" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="O223" s="2" t="s">
         <v>57</v>
@@ -31083,10 +31083,10 @@
         <v>9</v>
       </c>
       <c r="T223" s="2" t="s">
+        <v>1999</v>
+      </c>
+      <c r="U223" s="2" t="s">
         <v>2000</v>
-      </c>
-      <c r="U223" s="2" t="s">
-        <v>2001</v>
       </c>
       <c r="V223" s="2" t="s">
         <v>98</v>
@@ -31095,7 +31095,7 @@
         <v>42639</v>
       </c>
       <c r="X223" s="2" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="Y223" s="2" t="s">
         <v>11</v>
@@ -31104,11 +31104,11 @@
         <v>426</v>
       </c>
       <c r="AA223" s="2" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="AB223" s="6"/>
       <c r="AC223" s="2" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="AD223" s="2" t="s">
         <v>209</v>
@@ -31135,7 +31135,7 @@
         <v>45996.555462962962</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="C224" s="9" t="s">
         <v>31</v>
@@ -31159,7 +31159,7 @@
         <v>35</v>
       </c>
       <c r="J224" s="12" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="K224" s="9" t="s">
         <v>55</v>
@@ -31168,10 +31168,10 @@
         <v>9159012345</v>
       </c>
       <c r="M224" s="9" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="N224" s="9" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="O224" s="9" t="s">
         <v>78</v>
@@ -31192,7 +31192,7 @@
         <v>998</v>
       </c>
       <c r="U224" s="9" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="V224" s="9" t="s">
         <v>98</v>
@@ -31210,7 +31210,7 @@
         <v>426</v>
       </c>
       <c r="AA224" s="9" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="AB224" s="13"/>
       <c r="AC224" s="9" t="s">
@@ -31239,7 +31239,7 @@
         <v>45999.364525462966</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>31</v>
@@ -31263,28 +31263,28 @@
         <v>35</v>
       </c>
       <c r="J225" s="5" t="s">
+        <v>2186</v>
+      </c>
+      <c r="K225" s="2" t="s">
         <v>2187</v>
-      </c>
-      <c r="K225" s="2" t="s">
-        <v>2188</v>
       </c>
       <c r="L225" s="3">
         <v>9779772227</v>
       </c>
       <c r="M225" s="2" t="s">
+        <v>2188</v>
+      </c>
+      <c r="N225" s="2" t="s">
         <v>2189</v>
       </c>
-      <c r="N225" s="2" t="s">
+      <c r="O225" s="2" t="s">
         <v>2190</v>
-      </c>
-      <c r="O225" s="2" t="s">
-        <v>2191</v>
       </c>
       <c r="P225" s="3">
         <v>620017</v>
       </c>
       <c r="Q225" s="2" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="R225" s="2" t="s">
         <v>79</v>
@@ -31293,10 +31293,10 @@
         <v>17</v>
       </c>
       <c r="T225" s="2" t="s">
+        <v>2191</v>
+      </c>
+      <c r="U225" s="2" t="s">
         <v>2192</v>
-      </c>
-      <c r="U225" s="2" t="s">
-        <v>2193</v>
       </c>
       <c r="V225" s="2" t="s">
         <v>42</v>
@@ -31305,7 +31305,7 @@
         <v>39636</v>
       </c>
       <c r="X225" s="2" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="Y225" s="2" t="s">
         <v>11</v>
@@ -31314,11 +31314,11 @@
         <v>796</v>
       </c>
       <c r="AA225" s="2" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="AB225" s="6"/>
       <c r="AC225" s="2" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="AD225" s="6"/>
       <c r="AE225" s="2" t="s">
@@ -31343,7 +31343,7 @@
         <v>46002.523680555554</v>
       </c>
       <c r="B226" s="9" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="C226" s="9" t="s">
         <v>31</v>
@@ -31355,7 +31355,7 @@
         <v>21407</v>
       </c>
       <c r="F226" s="9" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="G226" s="9" t="s">
         <v>95</v>
@@ -31367,19 +31367,19 @@
         <v>35</v>
       </c>
       <c r="J226" s="12" t="s">
+        <v>2198</v>
+      </c>
+      <c r="K226" s="9" t="s">
         <v>2199</v>
-      </c>
-      <c r="K226" s="9" t="s">
-        <v>2200</v>
       </c>
       <c r="L226" s="10">
         <v>9842206348</v>
       </c>
       <c r="M226" s="9" t="s">
+        <v>2200</v>
+      </c>
+      <c r="N226" s="9" t="s">
         <v>2201</v>
-      </c>
-      <c r="N226" s="9" t="s">
-        <v>2202</v>
       </c>
       <c r="O226" s="9" t="s">
         <v>1238</v>
@@ -31397,10 +31397,10 @@
         <v>2</v>
       </c>
       <c r="T226" s="9" t="s">
+        <v>2202</v>
+      </c>
+      <c r="U226" s="9" t="s">
         <v>2203</v>
-      </c>
-      <c r="U226" s="9" t="s">
-        <v>2204</v>
       </c>
       <c r="V226" s="9" t="s">
         <v>60</v>
@@ -31409,20 +31409,20 @@
         <v>45282</v>
       </c>
       <c r="X226" s="9" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="Y226" s="9" t="s">
         <v>199</v>
       </c>
       <c r="Z226" s="9" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="AA226" s="9" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="AB226" s="13"/>
       <c r="AC226" s="9" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="AD226" s="13"/>
       <c r="AE226" s="9" t="s">
@@ -31447,7 +31447,7 @@
         <v>46010.499398148146</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>52</v>
@@ -31471,28 +31471,28 @@
         <v>35</v>
       </c>
       <c r="J227" s="5" t="s">
+        <v>2208</v>
+      </c>
+      <c r="K227" s="2" t="s">
         <v>2209</v>
-      </c>
-      <c r="K227" s="2" t="s">
-        <v>2210</v>
       </c>
       <c r="L227" s="3">
         <v>9486197358</v>
       </c>
       <c r="M227" s="2" t="s">
+        <v>2210</v>
+      </c>
+      <c r="N227" s="2" t="s">
         <v>2211</v>
       </c>
-      <c r="N227" s="2" t="s">
-        <v>2212</v>
-      </c>
       <c r="O227" s="2" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="P227" s="3">
         <v>641048</v>
       </c>
       <c r="Q227" s="2" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="R227" s="2" t="s">
         <v>39</v>
@@ -31501,10 +31501,10 @@
         <v>7</v>
       </c>
       <c r="T227" s="2" t="s">
+        <v>2212</v>
+      </c>
+      <c r="U227" s="2" t="s">
         <v>2213</v>
-      </c>
-      <c r="U227" s="2" t="s">
-        <v>2214</v>
       </c>
       <c r="V227" s="2" t="s">
         <v>98</v>
@@ -31513,20 +31513,20 @@
         <v>44760</v>
       </c>
       <c r="X227" s="2" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="Y227" s="2" t="s">
         <v>11</v>
       </c>
       <c r="Z227" s="2" t="s">
+        <v>2215</v>
+      </c>
+      <c r="AA227" s="2" t="s">
         <v>2216</v>
-      </c>
-      <c r="AA227" s="2" t="s">
-        <v>2217</v>
       </c>
       <c r="AB227" s="6"/>
       <c r="AC227" s="2" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="AD227" s="6"/>
       <c r="AE227" s="2" t="s">
@@ -31551,7 +31551,7 @@
         <v>46015.435925925929</v>
       </c>
       <c r="B228" s="9" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="C228" s="9" t="s">
         <v>52</v>
@@ -31575,7 +31575,7 @@
         <v>35</v>
       </c>
       <c r="J228" s="12" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="K228" s="9" t="s">
         <v>1244</v>
@@ -31584,19 +31584,19 @@
         <v>9003184325</v>
       </c>
       <c r="M228" s="9" t="s">
+        <v>2220</v>
+      </c>
+      <c r="N228" s="9" t="s">
         <v>2221</v>
       </c>
-      <c r="N228" s="9" t="s">
-        <v>2222</v>
-      </c>
       <c r="O228" s="9" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="P228" s="10">
         <v>620006</v>
       </c>
       <c r="Q228" s="9" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="R228" s="9" t="s">
         <v>39</v>
@@ -31605,10 +31605,10 @@
         <v>5</v>
       </c>
       <c r="T228" s="9" t="s">
+        <v>2222</v>
+      </c>
+      <c r="U228" s="9" t="s">
         <v>2223</v>
-      </c>
-      <c r="U228" s="9" t="s">
-        <v>2224</v>
       </c>
       <c r="V228" s="9" t="s">
         <v>60</v>
@@ -31617,7 +31617,7 @@
         <v>45796</v>
       </c>
       <c r="X228" s="9" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="Y228" s="9" t="s">
         <v>11</v>
@@ -31626,16 +31626,16 @@
         <v>1036</v>
       </c>
       <c r="AA228" s="9" t="s">
+        <v>2225</v>
+      </c>
+      <c r="AB228" s="12" t="s">
         <v>2226</v>
       </c>
-      <c r="AB228" s="12" t="s">
+      <c r="AC228" s="9" t="s">
         <v>2227</v>
       </c>
-      <c r="AC228" s="9" t="s">
+      <c r="AD228" s="9" t="s">
         <v>2228</v>
-      </c>
-      <c r="AD228" s="9" t="s">
-        <v>2229</v>
       </c>
       <c r="AE228" s="9" t="s">
         <v>44</v>
@@ -31659,7 +31659,7 @@
         <v>46017.628229166665</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>31</v>
@@ -31671,7 +31671,7 @@
         <v>28613</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>33</v>
@@ -31683,7 +31683,7 @@
         <v>1712</v>
       </c>
       <c r="J229" s="5" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="K229" s="2" t="s">
         <v>55</v>
@@ -31692,19 +31692,19 @@
         <v>7598539347</v>
       </c>
       <c r="M229" s="2" t="s">
+        <v>2232</v>
+      </c>
+      <c r="N229" s="2" t="s">
         <v>2233</v>
       </c>
-      <c r="N229" s="2" t="s">
-        <v>2234</v>
-      </c>
       <c r="O229" s="2" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="P229" s="3">
         <v>620006</v>
       </c>
       <c r="Q229" s="9" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="R229" s="2" t="s">
         <v>79</v>
@@ -31713,10 +31713,10 @@
         <v>21</v>
       </c>
       <c r="T229" s="2" t="s">
+        <v>2234</v>
+      </c>
+      <c r="U229" s="2" t="s">
         <v>2235</v>
-      </c>
-      <c r="U229" s="2" t="s">
-        <v>2236</v>
       </c>
       <c r="V229" s="2" t="s">
         <v>60</v>
@@ -31725,7 +31725,7 @@
         <v>44303</v>
       </c>
       <c r="X229" s="2" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="Y229" s="2" t="s">
         <v>199</v>
@@ -31734,11 +31734,11 @@
         <v>1374</v>
       </c>
       <c r="AA229" s="2" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="AB229" s="6"/>
       <c r="AC229" s="2" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="AD229" s="6"/>
       <c r="AE229" s="2" t="s">
@@ -31763,7 +31763,7 @@
         <v>46028.591863425929</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="C230" s="9" t="s">
         <v>31</v>
@@ -31787,7 +31787,7 @@
         <v>35</v>
       </c>
       <c r="J230" s="12" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="K230" s="9" t="s">
         <v>147</v>
@@ -31796,10 +31796,10 @@
         <v>9976115391</v>
       </c>
       <c r="M230" s="9" t="s">
+        <v>2241</v>
+      </c>
+      <c r="N230" s="9" t="s">
         <v>2242</v>
-      </c>
-      <c r="N230" s="9" t="s">
-        <v>2243</v>
       </c>
       <c r="O230" s="9" t="s">
         <v>1819</v>
@@ -31817,10 +31817,10 @@
         <v>1</v>
       </c>
       <c r="T230" s="9" t="s">
+        <v>2243</v>
+      </c>
+      <c r="U230" s="9" t="s">
         <v>2244</v>
-      </c>
-      <c r="U230" s="9" t="s">
-        <v>2245</v>
       </c>
       <c r="V230" s="9" t="s">
         <v>60</v>
@@ -31829,20 +31829,20 @@
         <v>45735</v>
       </c>
       <c r="X230" s="9" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="Y230" s="9" t="s">
         <v>11</v>
       </c>
       <c r="Z230" s="9" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="AA230" s="9" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="AB230" s="13"/>
       <c r="AC230" s="9" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="AD230" s="13"/>
       <c r="AE230" s="9" t="s">
@@ -31867,7 +31867,7 @@
         <v>46032.41710648148</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>52</v>
@@ -31891,28 +31891,28 @@
         <v>35</v>
       </c>
       <c r="J231" s="5" t="s">
+        <v>2254</v>
+      </c>
+      <c r="K231" s="2" t="s">
         <v>2255</v>
-      </c>
-      <c r="K231" s="2" t="s">
-        <v>2256</v>
       </c>
       <c r="L231" s="3">
         <v>8098893437</v>
       </c>
       <c r="M231" s="2" t="s">
+        <v>2256</v>
+      </c>
+      <c r="N231" s="2" t="s">
         <v>2257</v>
       </c>
-      <c r="N231" s="2" t="s">
-        <v>2258</v>
-      </c>
       <c r="O231" s="2" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="P231" s="3">
         <v>620019</v>
       </c>
       <c r="Q231" s="2" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="R231" s="2" t="s">
         <v>79</v>
@@ -31924,7 +31924,7 @@
         <v>8098893437</v>
       </c>
       <c r="U231" s="2" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="V231" s="2" t="s">
         <v>42</v>
@@ -31939,10 +31939,10 @@
         <v>11</v>
       </c>
       <c r="Z231" s="2" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="AA231" s="2" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="AB231" s="6"/>
       <c r="AC231" s="2" t="s">

--- a/assets/excel/Staff_Doctor_Details(Responses).xlsx
+++ b/assets/excel/Staff_Doctor_Details(Responses).xlsx
@@ -32193,426 +32193,426 @@
       <c r="AT229" s="19"/>
     </row>
     <row r="230" spans="1:46" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A230" s="38" t="s">
-        <v>2244</v>
-      </c>
-      <c r="B230" s="39" t="s">
-        <v>2245</v>
-      </c>
-      <c r="C230" s="39" t="s">
+      <c r="A230" s="30" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B230" s="31" t="s">
+        <v>2279</v>
+      </c>
+      <c r="C230" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D230" s="40">
-        <v>27</v>
-      </c>
-      <c r="E230" s="40" t="s">
-        <v>2246</v>
-      </c>
-      <c r="F230" s="39" t="s">
-        <v>1852</v>
-      </c>
-      <c r="G230" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="H230" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="I230" s="39" t="s">
-        <v>1695</v>
-      </c>
-      <c r="J230" s="42" t="s">
-        <v>2247</v>
-      </c>
-      <c r="K230" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="L230" s="40">
-        <v>7598716794</v>
-      </c>
-      <c r="M230" s="39" t="s">
-        <v>2248</v>
-      </c>
-      <c r="N230" s="39" t="s">
-        <v>2249</v>
-      </c>
-      <c r="O230" s="39" t="s">
-        <v>2250</v>
-      </c>
-      <c r="P230" s="40">
-        <v>606001</v>
-      </c>
-      <c r="Q230" s="39" t="s">
-        <v>2251</v>
-      </c>
-      <c r="R230" s="39" t="s">
-        <v>2252</v>
-      </c>
-      <c r="S230" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="T230" s="39" t="s">
-        <v>2253</v>
-      </c>
-      <c r="U230" s="39" t="s">
+      <c r="D230" s="32">
+        <v>53</v>
+      </c>
+      <c r="E230" s="34">
+        <v>26760</v>
+      </c>
+      <c r="F230" s="31" t="s">
+        <v>2280</v>
+      </c>
+      <c r="G230" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="H230" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I230" s="31" t="s">
+        <v>2281</v>
+      </c>
+      <c r="J230" s="33" t="s">
+        <v>2282</v>
+      </c>
+      <c r="K230" s="31" t="s">
+        <v>1008</v>
+      </c>
+      <c r="L230" s="32">
+        <v>9940192229</v>
+      </c>
+      <c r="M230" s="31" t="s">
+        <v>2283</v>
+      </c>
+      <c r="N230" s="31" t="s">
+        <v>2284</v>
+      </c>
+      <c r="O230" s="31" t="s">
+        <v>2173</v>
+      </c>
+      <c r="P230" s="32">
+        <v>621105</v>
+      </c>
+      <c r="Q230" s="31" t="s">
+        <v>2173</v>
+      </c>
+      <c r="R230" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="S230" s="32">
+        <v>26</v>
+      </c>
+      <c r="T230" s="31" t="s">
+        <v>2285</v>
+      </c>
+      <c r="U230" s="31" t="s">
         <v>2254</v>
       </c>
-      <c r="V230" s="39" t="s">
+      <c r="V230" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="W230" s="41">
-        <v>46057</v>
-      </c>
-      <c r="X230" s="39" t="s">
-        <v>2255</v>
-      </c>
-      <c r="Y230" s="39" t="s">
+      <c r="W230" s="32" t="s">
+        <v>2286</v>
+      </c>
+      <c r="X230" s="31" t="s">
+        <v>2287</v>
+      </c>
+      <c r="Y230" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="Z230" s="39" t="s">
+      <c r="Z230" s="31" t="s">
         <v>2315</v>
       </c>
-      <c r="AA230" s="39" t="s">
-        <v>2256</v>
-      </c>
-      <c r="AB230" s="43"/>
-      <c r="AC230" s="39" t="s">
+      <c r="AA230" s="31" t="s">
+        <v>2288</v>
+      </c>
+      <c r="AB230" s="35"/>
+      <c r="AC230" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="AD230" s="43"/>
-      <c r="AE230" s="39" t="s">
+      <c r="AD230" s="35"/>
+      <c r="AE230" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="AF230" s="44">
+      <c r="AF230" s="36">
         <v>0.35416666666666669</v>
       </c>
-      <c r="AG230" s="44">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="AH230" s="43"/>
-      <c r="AI230" s="43"/>
-      <c r="AJ230" s="43"/>
-      <c r="AK230" s="43"/>
-      <c r="AL230" s="43"/>
-      <c r="AM230" s="43"/>
-      <c r="AN230" s="45"/>
+      <c r="AG230" s="36">
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="AH230" s="35"/>
+      <c r="AI230" s="35"/>
+      <c r="AJ230" s="35"/>
+      <c r="AK230" s="35"/>
+      <c r="AL230" s="35"/>
+      <c r="AM230" s="35"/>
+      <c r="AN230" s="37"/>
     </row>
     <row r="231" spans="1:46" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A231" s="30" t="s">
-        <v>2257</v>
-      </c>
-      <c r="B231" s="31" t="s">
-        <v>2258</v>
-      </c>
-      <c r="C231" s="31" t="s">
+      <c r="A231" s="38" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B231" s="39" t="s">
+        <v>2245</v>
+      </c>
+      <c r="C231" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="D231" s="32">
+      <c r="D231" s="40">
+        <v>27</v>
+      </c>
+      <c r="E231" s="40" t="s">
+        <v>2246</v>
+      </c>
+      <c r="F231" s="39" t="s">
+        <v>1852</v>
+      </c>
+      <c r="G231" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="E231" s="32" t="s">
-        <v>2259</v>
-      </c>
-      <c r="F231" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="G231" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="H231" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I231" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="J231" s="33" t="s">
-        <v>2260</v>
-      </c>
-      <c r="K231" s="31" t="s">
+      <c r="H231" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="I231" s="39" t="s">
+        <v>1695</v>
+      </c>
+      <c r="J231" s="42" t="s">
+        <v>2247</v>
+      </c>
+      <c r="K231" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="L231" s="32">
-        <v>9095091334</v>
-      </c>
-      <c r="M231" s="31" t="s">
-        <v>2261</v>
-      </c>
-      <c r="N231" s="31" t="s">
-        <v>2262</v>
-      </c>
-      <c r="O231" s="31" t="s">
-        <v>450</v>
-      </c>
-      <c r="P231" s="32">
-        <v>625016</v>
-      </c>
-      <c r="Q231" s="31" t="s">
-        <v>450</v>
-      </c>
-      <c r="R231" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="S231" s="32">
-        <v>6</v>
-      </c>
-      <c r="T231" s="31" t="s">
-        <v>2263</v>
-      </c>
-      <c r="U231" s="31" t="s">
-        <v>2264</v>
-      </c>
-      <c r="V231" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="W231" s="34">
-        <v>43596</v>
-      </c>
-      <c r="X231" s="31" t="s">
-        <v>2265</v>
-      </c>
-      <c r="Y231" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z231" s="31" t="s">
+      <c r="L231" s="40">
+        <v>7598716794</v>
+      </c>
+      <c r="M231" s="39" t="s">
+        <v>2248</v>
+      </c>
+      <c r="N231" s="39" t="s">
+        <v>2249</v>
+      </c>
+      <c r="O231" s="39" t="s">
+        <v>2250</v>
+      </c>
+      <c r="P231" s="40">
+        <v>606001</v>
+      </c>
+      <c r="Q231" s="39" t="s">
+        <v>2251</v>
+      </c>
+      <c r="R231" s="39" t="s">
+        <v>2252</v>
+      </c>
+      <c r="S231" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="T231" s="39" t="s">
+        <v>2253</v>
+      </c>
+      <c r="U231" s="39" t="s">
+        <v>2254</v>
+      </c>
+      <c r="V231" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="W231" s="41">
+        <v>46057</v>
+      </c>
+      <c r="X231" s="39" t="s">
+        <v>2255</v>
+      </c>
+      <c r="Y231" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z231" s="39" t="s">
         <v>2315</v>
       </c>
-      <c r="AA231" s="31" t="s">
-        <v>2266</v>
-      </c>
-      <c r="AB231" s="35"/>
-      <c r="AC231" s="31" t="s">
+      <c r="AA231" s="39" t="s">
+        <v>2256</v>
+      </c>
+      <c r="AB231" s="43"/>
+      <c r="AC231" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="AD231" s="31" t="s">
-        <v>271</v>
-      </c>
-      <c r="AE231" s="31" t="s">
+      <c r="AD231" s="43"/>
+      <c r="AE231" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="AF231" s="36">
+      <c r="AF231" s="44">
         <v>0.35416666666666669</v>
       </c>
-      <c r="AG231" s="36">
+      <c r="AG231" s="44">
         <v>0.64583333333333337</v>
       </c>
-      <c r="AH231" s="35"/>
-      <c r="AI231" s="35"/>
-      <c r="AJ231" s="35"/>
-      <c r="AK231" s="35"/>
-      <c r="AL231" s="33" t="s">
-        <v>2267</v>
-      </c>
-      <c r="AM231" s="33" t="s">
-        <v>2268</v>
-      </c>
-      <c r="AN231" s="37"/>
+      <c r="AH231" s="43"/>
+      <c r="AI231" s="43"/>
+      <c r="AJ231" s="43"/>
+      <c r="AK231" s="43"/>
+      <c r="AL231" s="43"/>
+      <c r="AM231" s="43"/>
+      <c r="AN231" s="45"/>
     </row>
     <row r="232" spans="1:46" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A232" s="38" t="s">
-        <v>2269</v>
-      </c>
-      <c r="B232" s="39" t="s">
-        <v>2270</v>
-      </c>
-      <c r="C232" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="D232" s="40">
-        <v>38</v>
-      </c>
-      <c r="E232" s="41">
-        <v>32113</v>
-      </c>
-      <c r="F232" s="39" t="s">
-        <v>522</v>
-      </c>
-      <c r="G232" s="39" t="s">
+      <c r="A232" s="30" t="s">
+        <v>2257</v>
+      </c>
+      <c r="B232" s="31" t="s">
+        <v>2258</v>
+      </c>
+      <c r="C232" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D232" s="32">
         <v>33</v>
       </c>
-      <c r="H232" s="39" t="s">
+      <c r="E232" s="32" t="s">
+        <v>2259</v>
+      </c>
+      <c r="F232" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="G232" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="H232" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I232" s="39" t="s">
+      <c r="I232" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="J232" s="42" t="s">
-        <v>2271</v>
-      </c>
-      <c r="K232" s="39" t="s">
-        <v>1689</v>
-      </c>
-      <c r="L232" s="40">
-        <v>8754385626</v>
-      </c>
-      <c r="M232" s="39" t="s">
-        <v>2272</v>
-      </c>
-      <c r="N232" s="39" t="s">
-        <v>2273</v>
-      </c>
-      <c r="O232" s="39" t="s">
-        <v>2173</v>
-      </c>
-      <c r="P232" s="40">
-        <v>621112</v>
-      </c>
-      <c r="Q232" s="39" t="s">
-        <v>2173</v>
-      </c>
-      <c r="R232" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="S232" s="40">
-        <v>9</v>
-      </c>
-      <c r="T232" s="39" t="s">
-        <v>2274</v>
-      </c>
-      <c r="U232" s="39" t="s">
-        <v>2275</v>
-      </c>
-      <c r="V232" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="W232" s="41">
-        <v>42767</v>
-      </c>
-      <c r="X232" s="39" t="s">
-        <v>2276</v>
-      </c>
-      <c r="Y232" s="39" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z232" s="39" t="s">
+      <c r="J232" s="33" t="s">
+        <v>2260</v>
+      </c>
+      <c r="K232" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="L232" s="32">
+        <v>9095091334</v>
+      </c>
+      <c r="M232" s="31" t="s">
+        <v>2261</v>
+      </c>
+      <c r="N232" s="31" t="s">
+        <v>2262</v>
+      </c>
+      <c r="O232" s="31" t="s">
+        <v>450</v>
+      </c>
+      <c r="P232" s="32">
+        <v>625016</v>
+      </c>
+      <c r="Q232" s="31" t="s">
+        <v>450</v>
+      </c>
+      <c r="R232" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="S232" s="32">
+        <v>6</v>
+      </c>
+      <c r="T232" s="31" t="s">
+        <v>2263</v>
+      </c>
+      <c r="U232" s="31" t="s">
+        <v>2264</v>
+      </c>
+      <c r="V232" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="W232" s="34">
+        <v>43596</v>
+      </c>
+      <c r="X232" s="31" t="s">
+        <v>2265</v>
+      </c>
+      <c r="Y232" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z232" s="31" t="s">
         <v>2315</v>
       </c>
-      <c r="AA232" s="39" t="s">
-        <v>2277</v>
-      </c>
-      <c r="AB232" s="43"/>
-      <c r="AC232" s="39" t="s">
+      <c r="AA232" s="31" t="s">
+        <v>2266</v>
+      </c>
+      <c r="AB232" s="35"/>
+      <c r="AC232" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="AD232" s="43"/>
-      <c r="AE232" s="39" t="s">
+      <c r="AD232" s="31" t="s">
+        <v>271</v>
+      </c>
+      <c r="AE232" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="AF232" s="44">
+      <c r="AF232" s="36">
         <v>0.35416666666666669</v>
       </c>
-      <c r="AG232" s="44">
+      <c r="AG232" s="36">
         <v>0.64583333333333337</v>
       </c>
-      <c r="AH232" s="43"/>
-      <c r="AI232" s="43"/>
-      <c r="AJ232" s="43"/>
-      <c r="AK232" s="43"/>
-      <c r="AL232" s="43"/>
-      <c r="AM232" s="43"/>
-      <c r="AN232" s="45"/>
+      <c r="AH232" s="35"/>
+      <c r="AI232" s="35"/>
+      <c r="AJ232" s="35"/>
+      <c r="AK232" s="35"/>
+      <c r="AL232" s="33" t="s">
+        <v>2267</v>
+      </c>
+      <c r="AM232" s="33" t="s">
+        <v>2268</v>
+      </c>
+      <c r="AN232" s="37"/>
     </row>
     <row r="233" spans="1:46" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A233" s="30" t="s">
-        <v>2278</v>
-      </c>
-      <c r="B233" s="31" t="s">
-        <v>2279</v>
-      </c>
-      <c r="C233" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D233" s="32">
-        <v>53</v>
-      </c>
-      <c r="E233" s="34">
-        <v>26760</v>
-      </c>
-      <c r="F233" s="31" t="s">
-        <v>2280</v>
-      </c>
-      <c r="G233" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="H233" s="31" t="s">
+      <c r="A233" s="38" t="s">
+        <v>2269</v>
+      </c>
+      <c r="B233" s="39" t="s">
+        <v>2270</v>
+      </c>
+      <c r="C233" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D233" s="40">
+        <v>38</v>
+      </c>
+      <c r="E233" s="41">
+        <v>32113</v>
+      </c>
+      <c r="F233" s="39" t="s">
+        <v>522</v>
+      </c>
+      <c r="G233" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="H233" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="I233" s="31" t="s">
-        <v>2281</v>
-      </c>
-      <c r="J233" s="33" t="s">
-        <v>2282</v>
-      </c>
-      <c r="K233" s="31" t="s">
-        <v>1008</v>
-      </c>
-      <c r="L233" s="32">
-        <v>9940192229</v>
-      </c>
-      <c r="M233" s="31" t="s">
-        <v>2283</v>
-      </c>
-      <c r="N233" s="31" t="s">
-        <v>2284</v>
-      </c>
-      <c r="O233" s="31" t="s">
+      <c r="I233" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="J233" s="42" t="s">
+        <v>2271</v>
+      </c>
+      <c r="K233" s="39" t="s">
+        <v>1689</v>
+      </c>
+      <c r="L233" s="40">
+        <v>8754385626</v>
+      </c>
+      <c r="M233" s="39" t="s">
+        <v>2272</v>
+      </c>
+      <c r="N233" s="39" t="s">
+        <v>2273</v>
+      </c>
+      <c r="O233" s="39" t="s">
         <v>2173</v>
       </c>
-      <c r="P233" s="32">
-        <v>621105</v>
-      </c>
-      <c r="Q233" s="31" t="s">
+      <c r="P233" s="40">
+        <v>621112</v>
+      </c>
+      <c r="Q233" s="39" t="s">
         <v>2173</v>
       </c>
-      <c r="R233" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="S233" s="32">
-        <v>26</v>
-      </c>
-      <c r="T233" s="31" t="s">
-        <v>2285</v>
-      </c>
-      <c r="U233" s="31" t="s">
-        <v>2254</v>
-      </c>
-      <c r="V233" s="31" t="s">
+      <c r="R233" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="S233" s="40">
+        <v>9</v>
+      </c>
+      <c r="T233" s="39" t="s">
+        <v>2274</v>
+      </c>
+      <c r="U233" s="39" t="s">
+        <v>2275</v>
+      </c>
+      <c r="V233" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="W233" s="32" t="s">
-        <v>2286</v>
-      </c>
-      <c r="X233" s="31" t="s">
-        <v>2287</v>
-      </c>
-      <c r="Y233" s="31" t="s">
+      <c r="W233" s="41">
+        <v>42767</v>
+      </c>
+      <c r="X233" s="39" t="s">
+        <v>2276</v>
+      </c>
+      <c r="Y233" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="Z233" s="31" t="s">
+      <c r="Z233" s="39" t="s">
         <v>2315</v>
       </c>
-      <c r="AA233" s="31" t="s">
-        <v>2288</v>
-      </c>
-      <c r="AB233" s="35"/>
-      <c r="AC233" s="31" t="s">
+      <c r="AA233" s="39" t="s">
+        <v>2277</v>
+      </c>
+      <c r="AB233" s="43"/>
+      <c r="AC233" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="AD233" s="35"/>
-      <c r="AE233" s="31" t="s">
+      <c r="AD233" s="43"/>
+      <c r="AE233" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="AF233" s="36">
+      <c r="AF233" s="44">
         <v>0.35416666666666669</v>
       </c>
-      <c r="AG233" s="36">
-        <v>0.14583333333333334</v>
-      </c>
-      <c r="AH233" s="35"/>
-      <c r="AI233" s="35"/>
-      <c r="AJ233" s="35"/>
-      <c r="AK233" s="35"/>
-      <c r="AL233" s="35"/>
-      <c r="AM233" s="35"/>
-      <c r="AN233" s="37"/>
+      <c r="AG233" s="44">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="AH233" s="43"/>
+      <c r="AI233" s="43"/>
+      <c r="AJ233" s="43"/>
+      <c r="AK233" s="43"/>
+      <c r="AL233" s="43"/>
+      <c r="AM233" s="43"/>
+      <c r="AN233" s="45"/>
     </row>
     <row r="234" spans="1:46" ht="15.75" customHeight="1" thickBot="1">
       <c r="A234" s="38" t="s">
@@ -33123,12 +33123,12 @@
     <hyperlink ref="J227" r:id="rId297"/>
     <hyperlink ref="J228" r:id="rId298"/>
     <hyperlink ref="J229" r:id="rId299" display="https://drive.google.com/open?id=1DdV0m0St0MUfekgVF6f_7SnKmkRAsjJZ"/>
-    <hyperlink ref="J230" r:id="rId300"/>
-    <hyperlink ref="J231" r:id="rId301"/>
-    <hyperlink ref="AL231" r:id="rId302"/>
-    <hyperlink ref="AM231" r:id="rId303"/>
-    <hyperlink ref="J232" r:id="rId304"/>
-    <hyperlink ref="J233" r:id="rId305"/>
+    <hyperlink ref="J231" r:id="rId300"/>
+    <hyperlink ref="J232" r:id="rId301"/>
+    <hyperlink ref="AL232" r:id="rId302"/>
+    <hyperlink ref="AM232" r:id="rId303"/>
+    <hyperlink ref="J233" r:id="rId304"/>
+    <hyperlink ref="J230" r:id="rId305"/>
     <hyperlink ref="J234" r:id="rId306"/>
     <hyperlink ref="J235" r:id="rId307"/>
   </hyperlinks>

--- a/assets/excel/Staff_Doctor_Details(Responses).xlsx
+++ b/assets/excel/Staff_Doctor_Details(Responses).xlsx
@@ -1,19 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\NewSRMTrichy\assets\excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24240" windowHeight="12315"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Form Responses 1'!$A$1:$AN$235</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -7215,7 +7213,7 @@
     <t>3/17/2025</t>
   </si>
   <si>
-    <t>Dental</t>
+    <t>Dentistry</t>
   </si>
 </sst>
 </file>
@@ -7291,7 +7289,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -7507,12 +7505,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="22" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -7676,6 +7689,9 @@
     </xf>
     <xf numFmtId="22" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -28957,7 +28973,7 @@
         <v>11</v>
       </c>
       <c r="Z199" s="9" t="s">
-        <v>553</v>
+        <v>270</v>
       </c>
       <c r="AA199" s="9" t="s">
         <v>553</v>
@@ -32157,7 +32173,7 @@
         <v>11</v>
       </c>
       <c r="Z229" s="31" t="s">
-        <v>1943</v>
+        <v>2153</v>
       </c>
       <c r="AA229" s="31" t="s">
         <v>2241</v>
@@ -32476,7 +32492,7 @@
       <c r="Y232" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="Z232" s="31" t="s">
+      <c r="Z232" s="39" t="s">
         <v>2315</v>
       </c>
       <c r="AA232" s="31" t="s">
@@ -32794,7 +32810,7 @@
       <c r="Y235" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="Z235" s="47" t="s">
+      <c r="Z235" s="56" t="s">
         <v>2315</v>
       </c>
       <c r="AA235" s="47" t="s">
